--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,57 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -497,37 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>108147.973618</v>
       </c>
       <c r="C2" t="n">
-        <v>88598.506287</v>
+        <v>90202.090773</v>
       </c>
       <c r="D2" t="n">
-        <v>96160.737524</v>
+        <v>115583.774439</v>
       </c>
       <c r="E2" t="n">
-        <v>87803.636727</v>
+        <v>88280.45979350001</v>
       </c>
       <c r="F2" t="n">
-        <v>91791.218293</v>
+        <v>85140.476152</v>
       </c>
       <c r="G2" t="n">
-        <v>93540.802563</v>
+        <v>97469.493455</v>
       </c>
       <c r="H2" t="n">
-        <v>89676.875619</v>
+        <v>93023.65412000001</v>
       </c>
       <c r="I2" t="n">
-        <v>86789.287417</v>
+        <v>80100.52979</v>
       </c>
       <c r="J2" t="n">
-        <v>90420.579443</v>
-      </c>
-      <c r="K2" t="n">
-        <v>71424.58839999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>76952.889931</v>
+        <v>79486.70570525</v>
       </c>
     </row>
     <row r="3">
@@ -537,37 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3659.618535</v>
       </c>
       <c r="C3" t="n">
-        <v>5713.955689</v>
+        <v>1717.408387</v>
       </c>
       <c r="D3" t="n">
-        <v>4656.08377</v>
+        <v>1442.069167</v>
       </c>
       <c r="E3" t="n">
-        <v>4301.116236</v>
+        <v>1293.691735</v>
       </c>
       <c r="F3" t="n">
-        <v>4329.776904</v>
+        <v>1051.289579</v>
       </c>
       <c r="G3" t="n">
-        <v>5008.035316</v>
+        <v>1205.972422</v>
       </c>
       <c r="H3" t="n">
-        <v>3148.623193</v>
+        <v>1376.309944</v>
       </c>
       <c r="I3" t="n">
-        <v>4627.187556</v>
+        <v>1788.730843</v>
       </c>
       <c r="J3" t="n">
-        <v>3173.885258</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2287.909476</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2581.532565</v>
+        <v>1316.913868</v>
       </c>
     </row>
     <row r="4">
@@ -577,37 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>271299.418654</v>
       </c>
       <c r="C4" t="n">
-        <v>167153.084229</v>
+        <v>179360.190207</v>
       </c>
       <c r="D4" t="n">
-        <v>145719.689205</v>
+        <v>226359.872253</v>
       </c>
       <c r="E4" t="n">
-        <v>121289.303509</v>
+        <v>166179.907213</v>
       </c>
       <c r="F4" t="n">
-        <v>146071.345826</v>
+        <v>138946.48812</v>
       </c>
       <c r="G4" t="n">
-        <v>119923.441082</v>
+        <v>189646.737822</v>
       </c>
       <c r="H4" t="n">
-        <v>139723.613292</v>
+        <v>182760.686487</v>
       </c>
       <c r="I4" t="n">
-        <v>134418.644472</v>
+        <v>128660.880246</v>
       </c>
       <c r="J4" t="n">
-        <v>175517.676324</v>
-      </c>
-      <c r="K4" t="n">
-        <v>153398.726725</v>
-      </c>
-      <c r="L4" t="n">
-        <v>150871.083156</v>
+        <v>123539.16242</v>
       </c>
     </row>
     <row r="5">
@@ -616,36 +588,32 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>2361.305817</v>
+      </c>
       <c r="C5" t="n">
-        <v>3534.353106</v>
+        <v>1237.090225</v>
       </c>
       <c r="D5" t="n">
-        <v>2691.850606</v>
+        <v>1321.863769</v>
       </c>
       <c r="E5" t="n">
-        <v>8672.564984000001</v>
+        <v>1185.034685</v>
       </c>
       <c r="F5" t="n">
-        <v>5717.619545</v>
+        <v>1327.895339</v>
       </c>
       <c r="G5" t="n">
-        <v>4304.92424</v>
+        <v>1707.386623</v>
       </c>
       <c r="H5" t="n">
-        <v>3595.847728</v>
+        <v>1902.962393</v>
       </c>
       <c r="I5" t="n">
-        <v>2850.305968</v>
+        <v>1122.586086</v>
       </c>
       <c r="J5" t="n">
-        <v>7360.55158</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4653.424562</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3242.049996</v>
+        <v>1601.886093</v>
       </c>
     </row>
     <row r="6">
@@ -655,37 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100386.32367</v>
       </c>
       <c r="C6" t="n">
-        <v>112837.95976</v>
+        <v>99702.839399</v>
       </c>
       <c r="D6" t="n">
-        <v>93253.142507</v>
+        <v>121821.817605</v>
       </c>
       <c r="E6" t="n">
-        <v>110993.112155</v>
+        <v>129515.847183</v>
       </c>
       <c r="F6" t="n">
-        <v>134578.204752</v>
+        <v>130648.847117</v>
       </c>
       <c r="G6" t="n">
-        <v>107409.997348</v>
+        <v>102906.419806</v>
       </c>
       <c r="H6" t="n">
-        <v>117363.888895</v>
+        <v>129641.407368</v>
       </c>
       <c r="I6" t="n">
-        <v>143530.43716225</v>
+        <v>140476.595393</v>
       </c>
       <c r="J6" t="n">
-        <v>129351.052534</v>
-      </c>
-      <c r="K6" t="n">
-        <v>131399.084318</v>
-      </c>
-      <c r="L6" t="n">
-        <v>92225.13568199999</v>
+        <v>153960.233459</v>
       </c>
     </row>
     <row r="7">
@@ -694,36 +656,32 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>26471.264276</v>
+      </c>
       <c r="C7" t="n">
-        <v>8900.008325000001</v>
+        <v>20781.455792</v>
       </c>
       <c r="D7" t="n">
-        <v>7358.545216</v>
+        <v>22175.429716</v>
       </c>
       <c r="E7" t="n">
-        <v>10760.57437</v>
+        <v>13770.435178</v>
       </c>
       <c r="F7" t="n">
-        <v>11950.474095</v>
+        <v>10540.732272</v>
       </c>
       <c r="G7" t="n">
-        <v>8659.241715</v>
+        <v>13889.568317</v>
       </c>
       <c r="H7" t="n">
-        <v>8400.88963</v>
+        <v>13855.977711</v>
       </c>
       <c r="I7" t="n">
-        <v>6345.51457</v>
+        <v>20448.539832</v>
       </c>
       <c r="J7" t="n">
-        <v>22379.935182</v>
-      </c>
-      <c r="K7" t="n">
-        <v>17232.300574</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14307.419796</v>
+        <v>15846.945404</v>
       </c>
     </row>
     <row r="8">
@@ -733,37 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>13120.648025</v>
       </c>
       <c r="C8" t="n">
-        <v>15922.178994</v>
+        <v>10613.63104</v>
       </c>
       <c r="D8" t="n">
-        <v>18840.647933</v>
+        <v>9213.183336</v>
       </c>
       <c r="E8" t="n">
-        <v>6876.611752</v>
+        <v>8165.319383</v>
       </c>
       <c r="F8" t="n">
-        <v>19265.111106</v>
+        <v>5236.54811</v>
       </c>
       <c r="G8" t="n">
-        <v>15355.682028</v>
+        <v>5028.359153</v>
       </c>
       <c r="H8" t="n">
-        <v>6343.573759</v>
+        <v>6200.80261</v>
       </c>
       <c r="I8" t="n">
-        <v>9021.463277999999</v>
+        <v>5956.565974</v>
       </c>
       <c r="J8" t="n">
-        <v>10247.501186</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9393.976239</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7257.75481</v>
+        <v>9323.950983999999</v>
       </c>
     </row>
     <row r="9">
@@ -773,37 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>22459.343933</v>
       </c>
       <c r="C9" t="n">
-        <v>15660.876868</v>
+        <v>14982.790173</v>
       </c>
       <c r="D9" t="n">
-        <v>14003.726592</v>
+        <v>23907.352232</v>
       </c>
       <c r="E9" t="n">
-        <v>14720.92602675</v>
+        <v>16164.352791</v>
       </c>
       <c r="F9" t="n">
-        <v>19088.418743</v>
+        <v>12877.494238</v>
       </c>
       <c r="G9" t="n">
-        <v>9090.927068000001</v>
+        <v>12170.44137225</v>
       </c>
       <c r="H9" t="n">
-        <v>10112.755971</v>
+        <v>28574.762822</v>
       </c>
       <c r="I9" t="n">
-        <v>12660.991225</v>
+        <v>20694.5899575</v>
       </c>
       <c r="J9" t="n">
-        <v>12099.349718</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7140.345704</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6871.022261</v>
+        <v>18024.656341</v>
       </c>
     </row>
     <row r="10">
@@ -812,36 +758,32 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>2345.002665</v>
+      </c>
       <c r="C10" t="n">
-        <v>2832.47245</v>
+        <v>1728.446305666667</v>
       </c>
       <c r="D10" t="n">
-        <v>2505.109356</v>
+        <v>2505.415513</v>
       </c>
       <c r="E10" t="n">
-        <v>2410.949609</v>
+        <v>2014.82200825</v>
       </c>
       <c r="F10" t="n">
-        <v>2221.36277</v>
+        <v>1437.9102595</v>
       </c>
       <c r="G10" t="n">
-        <v>1871.1402985</v>
+        <v>1691.566047</v>
       </c>
       <c r="H10" t="n">
-        <v>1982.82457375</v>
+        <v>1739.207265</v>
       </c>
       <c r="I10" t="n">
-        <v>2556.872433</v>
+        <v>2361.4214135</v>
       </c>
       <c r="J10" t="n">
-        <v>2355.001443</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2177.360336916667</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2544.463354666666</v>
+        <v>2507.015601083333</v>
       </c>
     </row>
     <row r="11">
@@ -851,37 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>9408.10016</v>
       </c>
       <c r="C11" t="n">
-        <v>19548.391107</v>
+        <v>5176.242822</v>
       </c>
       <c r="D11" t="n">
-        <v>11207.899835</v>
+        <v>4538.158264666667</v>
       </c>
       <c r="E11" t="n">
-        <v>9532.790773999999</v>
+        <v>6392.108486</v>
       </c>
       <c r="F11" t="n">
-        <v>7891.366311</v>
+        <v>5028.581066</v>
       </c>
       <c r="G11" t="n">
-        <v>6104.097356</v>
+        <v>4289.738981</v>
       </c>
       <c r="H11" t="n">
-        <v>4690.243995</v>
+        <v>5741.6945715</v>
       </c>
       <c r="I11" t="n">
-        <v>6549.857077333333</v>
+        <v>5932.783523</v>
       </c>
       <c r="J11" t="n">
-        <v>6041.349581</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3631.671693</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3698.222422333333</v>
+        <v>5711.568377</v>
       </c>
     </row>
     <row r="12">
@@ -891,37 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>15291.684178</v>
       </c>
       <c r="C12" t="n">
-        <v>17190.201804</v>
+        <v>8832.563737</v>
       </c>
       <c r="D12" t="n">
-        <v>11001.386477</v>
+        <v>14287.592061</v>
       </c>
       <c r="E12" t="n">
-        <v>15380.736382</v>
+        <v>12754.3151</v>
       </c>
       <c r="F12" t="n">
-        <v>15662.865266</v>
+        <v>13061.21415</v>
       </c>
       <c r="G12" t="n">
-        <v>12293.855919</v>
+        <v>11174.18828</v>
       </c>
       <c r="H12" t="n">
-        <v>16470.471548</v>
+        <v>13638.882629</v>
       </c>
       <c r="I12" t="n">
-        <v>16124.627644</v>
+        <v>13065.508176</v>
       </c>
       <c r="J12" t="n">
-        <v>17859.165002</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9791.566118999999</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12181.302603</v>
+        <v>13474.480942</v>
       </c>
     </row>
     <row r="13">
@@ -931,37 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3549.744938</v>
       </c>
       <c r="C13" t="n">
-        <v>4656.090804</v>
+        <v>2701.740215</v>
       </c>
       <c r="D13" t="n">
-        <v>7604.725804</v>
+        <v>5209.950112</v>
       </c>
       <c r="E13" t="n">
-        <v>11587.631853</v>
+        <v>5233.847716</v>
       </c>
       <c r="F13" t="n">
-        <v>4644.755284</v>
+        <v>3371.427526</v>
       </c>
       <c r="G13" t="n">
-        <v>2903.186173</v>
+        <v>2394.061638</v>
       </c>
       <c r="H13" t="n">
-        <v>2934.978518</v>
+        <v>4286.652275</v>
       </c>
       <c r="I13" t="n">
-        <v>2932.9583</v>
+        <v>2976.017692</v>
       </c>
       <c r="J13" t="n">
-        <v>3126.90325</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1862.640104</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1674.635073</v>
+        <v>3786.824192</v>
       </c>
     </row>
     <row r="14">
@@ -971,37 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>25348.453042</v>
       </c>
       <c r="C14" t="n">
-        <v>9885.721189</v>
+        <v>13746.938159</v>
       </c>
       <c r="D14" t="n">
-        <v>10479.841009</v>
+        <v>13071.459356</v>
       </c>
       <c r="E14" t="n">
-        <v>7276.332612</v>
+        <v>11120.031796</v>
       </c>
       <c r="F14" t="n">
-        <v>13551.0417275</v>
+        <v>14305.724936</v>
       </c>
       <c r="G14" t="n">
-        <v>9473.158165999999</v>
+        <v>8735.041053249999</v>
       </c>
       <c r="H14" t="n">
-        <v>9462.977505999999</v>
+        <v>9585.149552999999</v>
       </c>
       <c r="I14" t="n">
-        <v>10711.157962</v>
+        <v>6695.3773</v>
       </c>
       <c r="J14" t="n">
-        <v>7888.641668</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7122.727661</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7059.591216</v>
+        <v>6646.674439</v>
       </c>
     </row>
     <row r="15">
@@ -1011,37 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>37230.517994</v>
       </c>
       <c r="C15" t="n">
-        <v>19648.133959</v>
+        <v>25754.563201</v>
       </c>
       <c r="D15" t="n">
-        <v>28275.178925</v>
+        <v>30247.363515</v>
       </c>
       <c r="E15" t="n">
-        <v>32713.51962</v>
+        <v>29527.568526</v>
       </c>
       <c r="F15" t="n">
-        <v>31502.833173</v>
+        <v>35684.540649</v>
       </c>
       <c r="G15" t="n">
-        <v>21478.660413</v>
+        <v>33341.832677</v>
       </c>
       <c r="H15" t="n">
-        <v>15931.208238</v>
+        <v>24770.886724</v>
       </c>
       <c r="I15" t="n">
-        <v>17776.464524</v>
+        <v>21506.286768</v>
       </c>
       <c r="J15" t="n">
-        <v>23621.961726</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17418.678384</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14873.407576</v>
+        <v>33362.212799</v>
       </c>
     </row>
     <row r="16">
@@ -1051,37 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>20852.49387</v>
       </c>
       <c r="C16" t="n">
-        <v>24015.464412</v>
+        <v>24593.793714</v>
       </c>
       <c r="D16" t="n">
-        <v>25794.307829</v>
+        <v>23394.055888</v>
       </c>
       <c r="E16" t="n">
-        <v>17578.630824</v>
+        <v>28438.041727</v>
       </c>
       <c r="F16" t="n">
-        <v>25932.776924</v>
+        <v>18391.555121</v>
       </c>
       <c r="G16" t="n">
-        <v>25408.496716</v>
+        <v>18781.663985</v>
       </c>
       <c r="H16" t="n">
-        <v>17388.755584</v>
+        <v>24000.561306</v>
       </c>
       <c r="I16" t="n">
-        <v>18645.932911</v>
+        <v>16200.809153</v>
       </c>
       <c r="J16" t="n">
-        <v>22765.277285</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20777.976854</v>
-      </c>
-      <c r="L16" t="n">
-        <v>27650.041059</v>
+        <v>20930.807379</v>
       </c>
     </row>
     <row r="17">
@@ -1090,36 +996,32 @@
           <t>封裝測試</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>56819.751285</v>
+      </c>
       <c r="C17" t="n">
-        <v>52298.456461</v>
+        <v>53935.315237</v>
       </c>
       <c r="D17" t="n">
-        <v>59372.419079</v>
+        <v>70058.288533</v>
       </c>
       <c r="E17" t="n">
-        <v>80319.669951</v>
+        <v>44988.016253</v>
       </c>
       <c r="F17" t="n">
-        <v>71976.670912</v>
+        <v>30953.730487</v>
       </c>
       <c r="G17" t="n">
-        <v>44576.013202</v>
+        <v>28733.570505</v>
       </c>
       <c r="H17" t="n">
-        <v>48399.651564</v>
+        <v>38078.11666</v>
       </c>
       <c r="I17" t="n">
-        <v>50801.820834</v>
+        <v>24953.722837</v>
       </c>
       <c r="J17" t="n">
-        <v>45430.075217</v>
-      </c>
-      <c r="K17" t="n">
-        <v>43649.882212</v>
-      </c>
-      <c r="L17" t="n">
-        <v>57190.090936</v>
+        <v>41336.354249</v>
       </c>
     </row>
     <row r="18">
@@ -1128,36 +1030,32 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1453.397163</v>
+      </c>
       <c r="C18" t="n">
-        <v>1968.295902</v>
+        <v>843.593843</v>
       </c>
       <c r="D18" t="n">
-        <v>1359.881148</v>
+        <v>1189.748739</v>
       </c>
       <c r="E18" t="n">
-        <v>4951.018595</v>
+        <v>1567.479099</v>
       </c>
       <c r="F18" t="n">
-        <v>4399.016888</v>
+        <v>1374.791349</v>
       </c>
       <c r="G18" t="n">
-        <v>1903.263824</v>
+        <v>931.905278</v>
       </c>
       <c r="H18" t="n">
-        <v>1155.977184</v>
+        <v>1551.429113</v>
       </c>
       <c r="I18" t="n">
-        <v>2131.54531</v>
+        <v>916.4080719999999</v>
       </c>
       <c r="J18" t="n">
-        <v>2011.454996</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1415.953505</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1171.833509</v>
+        <v>1259.522176</v>
       </c>
     </row>
     <row r="19">
@@ -1167,37 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>451.440952</v>
       </c>
       <c r="C19" t="n">
-        <v>837.34279225</v>
+        <v>315.535051</v>
       </c>
       <c r="D19" t="n">
-        <v>377.587827</v>
+        <v>182.038654</v>
       </c>
       <c r="E19" t="n">
-        <v>295.416936</v>
+        <v>110.671611</v>
       </c>
       <c r="F19" t="n">
-        <v>331.236371</v>
+        <v>85.07476275</v>
       </c>
       <c r="G19" t="n">
-        <v>144.69071525</v>
+        <v>226.0066173333333</v>
       </c>
       <c r="H19" t="n">
-        <v>110.78874125</v>
+        <v>157.437316</v>
       </c>
       <c r="I19" t="n">
-        <v>396.19017125</v>
+        <v>90.02030033333332</v>
       </c>
       <c r="J19" t="n">
-        <v>276.7011906666666</v>
-      </c>
-      <c r="K19" t="n">
-        <v>217.98128675</v>
-      </c>
-      <c r="L19" t="n">
-        <v>238.387796</v>
+        <v>86.055667</v>
       </c>
     </row>
     <row r="20">
@@ -1206,36 +1098,32 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>22643.080858</v>
+      </c>
       <c r="C20" t="n">
-        <v>13739.125363</v>
+        <v>35044.727771</v>
       </c>
       <c r="D20" t="n">
-        <v>30584.646535</v>
+        <v>32619.344675</v>
       </c>
       <c r="E20" t="n">
-        <v>18891.58888</v>
+        <v>18556.167825</v>
       </c>
       <c r="F20" t="n">
-        <v>17886.724964</v>
+        <v>17169.781569</v>
       </c>
       <c r="G20" t="n">
-        <v>24583.40388</v>
+        <v>26765.247924</v>
       </c>
       <c r="H20" t="n">
-        <v>15818.732183</v>
+        <v>21132.136662</v>
       </c>
       <c r="I20" t="n">
-        <v>17941.019965</v>
+        <v>11587.069143</v>
       </c>
       <c r="J20" t="n">
-        <v>19919.902276</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16699.200282</v>
-      </c>
-      <c r="L20" t="n">
-        <v>16256.221967</v>
+        <v>11464.949012</v>
       </c>
     </row>
     <row r="21">
@@ -1244,36 +1132,32 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>5636.052303</v>
+      </c>
       <c r="C21" t="n">
-        <v>7035.525163</v>
+        <v>4241.862746</v>
       </c>
       <c r="D21" t="n">
-        <v>5365.015459</v>
+        <v>3718.826782</v>
       </c>
       <c r="E21" t="n">
-        <v>4522.711237</v>
+        <v>3337.890946</v>
       </c>
       <c r="F21" t="n">
-        <v>6140.522722</v>
+        <v>3450.698097</v>
       </c>
       <c r="G21" t="n">
-        <v>8479.949175</v>
+        <v>6353.527497</v>
       </c>
       <c r="H21" t="n">
-        <v>8133.546013</v>
+        <v>4324.242742</v>
       </c>
       <c r="I21" t="n">
-        <v>8366.282751999999</v>
+        <v>3288.161369</v>
       </c>
       <c r="J21" t="n">
-        <v>6243.374784</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3903.83947</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3848.612759</v>
+        <v>3740.481742</v>
       </c>
     </row>
     <row r="22">
@@ -1282,36 +1166,32 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>295.384989</v>
+      </c>
       <c r="C22" t="n">
-        <v>798.589026</v>
+        <v>162.87355125</v>
       </c>
       <c r="D22" t="n">
-        <v>596.141365</v>
+        <v>636.4326583333333</v>
       </c>
       <c r="E22" t="n">
-        <v>512.542686</v>
+        <v>332.069325</v>
       </c>
       <c r="F22" t="n">
-        <v>429.586223</v>
+        <v>284.626499</v>
       </c>
       <c r="G22" t="n">
-        <v>298.264043</v>
+        <v>234.591797</v>
       </c>
       <c r="H22" t="n">
-        <v>247.83608</v>
+        <v>213.95378</v>
       </c>
       <c r="I22" t="n">
-        <v>398.068332</v>
+        <v>146.3468013333333</v>
       </c>
       <c r="J22" t="n">
-        <v>410.449209</v>
-      </c>
-      <c r="K22" t="n">
-        <v>275.113776</v>
-      </c>
-      <c r="L22" t="n">
-        <v>231.358425</v>
+        <v>140.418245</v>
       </c>
     </row>
     <row r="23">
@@ -1321,37 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3.097406666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>1.864422</v>
+        <v>0.88782625</v>
       </c>
       <c r="D23" t="n">
-        <v>1.177961</v>
+        <v>0.911308</v>
       </c>
       <c r="E23" t="n">
-        <v>1.363398</v>
+        <v>0.6601315</v>
       </c>
       <c r="F23" t="n">
-        <v>1.964384</v>
+        <v>4.4233375</v>
       </c>
       <c r="G23" t="n">
-        <v>1.785037</v>
+        <v>2.78372875</v>
       </c>
       <c r="H23" t="n">
-        <v>0.972008</v>
+        <v>1.707734</v>
       </c>
       <c r="I23" t="n">
-        <v>1.270078333333333</v>
+        <v>4.863267</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5561325</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.43597325</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.99229</v>
+        <v>2.496508833333333</v>
       </c>
     </row>
     <row r="24">
@@ -1360,36 +1234,32 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1424.707369</v>
+      </c>
       <c r="C24" t="n">
-        <v>4424.701418</v>
+        <v>684.892696</v>
       </c>
       <c r="D24" t="n">
-        <v>3757.449953</v>
+        <v>873.041337</v>
       </c>
       <c r="E24" t="n">
-        <v>2813.437829</v>
+        <v>798.4179339999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1973.222453</v>
+        <v>579.415634</v>
       </c>
       <c r="G24" t="n">
-        <v>1196.93529</v>
+        <v>881.8031559999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1144.26408</v>
+        <v>740.897229</v>
       </c>
       <c r="I24" t="n">
-        <v>3668.857075</v>
+        <v>612.1953099999999</v>
       </c>
       <c r="J24" t="n">
-        <v>2203.184195</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1536.509673</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1678.455467</v>
+        <v>713.520144</v>
       </c>
     </row>
     <row r="25">
@@ -1398,36 +1268,32 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>611.61776</v>
+      </c>
       <c r="C25" t="n">
-        <v>1032.536116</v>
+        <v>420.723517</v>
       </c>
       <c r="D25" t="n">
-        <v>1826.056369</v>
+        <v>309.29352</v>
       </c>
       <c r="E25" t="n">
-        <v>1562.368136</v>
+        <v>527.454688</v>
       </c>
       <c r="F25" t="n">
-        <v>952.168662</v>
+        <v>285.874826</v>
       </c>
       <c r="G25" t="n">
-        <v>516.79069</v>
+        <v>324.489912</v>
       </c>
       <c r="H25" t="n">
-        <v>531.135145</v>
+        <v>368.164356</v>
       </c>
       <c r="I25" t="n">
-        <v>570.803195</v>
+        <v>271.009081</v>
       </c>
       <c r="J25" t="n">
-        <v>1171.607975</v>
-      </c>
-      <c r="K25" t="n">
-        <v>671.064316</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1403.470589</v>
+        <v>414.965774</v>
       </c>
     </row>
     <row r="26">
@@ -1436,36 +1302,32 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>945.357403</v>
+      </c>
       <c r="C26" t="n">
-        <v>1541.827726</v>
+        <v>495.909465</v>
       </c>
       <c r="D26" t="n">
-        <v>1377.766638</v>
+        <v>972.210448</v>
       </c>
       <c r="E26" t="n">
-        <v>840.157786</v>
+        <v>3770.951635</v>
       </c>
       <c r="F26" t="n">
-        <v>1270.286425</v>
+        <v>1284.573526</v>
       </c>
       <c r="G26" t="n">
-        <v>876.134365</v>
+        <v>1171.957497</v>
       </c>
       <c r="H26" t="n">
-        <v>1389.362274</v>
+        <v>2992.647381</v>
       </c>
       <c r="I26" t="n">
-        <v>1363.536415</v>
+        <v>1857.383228</v>
       </c>
       <c r="J26" t="n">
-        <v>1476.362156</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1627.78388</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1940.563596</v>
+        <v>833.4631900000001</v>
       </c>
     </row>
     <row r="27">
@@ -1474,36 +1336,32 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>2105.539015</v>
+      </c>
       <c r="C27" t="n">
-        <v>3283.934528</v>
+        <v>1502.922943</v>
       </c>
       <c r="D27" t="n">
-        <v>4013.995815</v>
+        <v>1448.419276</v>
       </c>
       <c r="E27" t="n">
-        <v>3952.226104</v>
+        <v>2137.2157825</v>
       </c>
       <c r="F27" t="n">
-        <v>4185.464957</v>
+        <v>1431.344338</v>
       </c>
       <c r="G27" t="n">
-        <v>2805.427179</v>
+        <v>2011.716407</v>
       </c>
       <c r="H27" t="n">
-        <v>2312.632165</v>
+        <v>3199.267601</v>
       </c>
       <c r="I27" t="n">
-        <v>2171.942578</v>
+        <v>1435.937866</v>
       </c>
       <c r="J27" t="n">
-        <v>2628.554959</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1886.664853</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1782.768154</v>
+        <v>2005.650755</v>
       </c>
     </row>
     <row r="28">
@@ -1512,36 +1370,32 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>2019.450246</v>
+      </c>
       <c r="C28" t="n">
-        <v>1378.836785</v>
+        <v>1355.427307</v>
       </c>
       <c r="D28" t="n">
-        <v>2521.775536</v>
+        <v>1444.859941</v>
       </c>
       <c r="E28" t="n">
-        <v>1141.917613</v>
+        <v>1127.132142</v>
       </c>
       <c r="F28" t="n">
-        <v>680.954303</v>
+        <v>953.2518679999999</v>
       </c>
       <c r="G28" t="n">
-        <v>799.4044825</v>
+        <v>3835.176519</v>
       </c>
       <c r="H28" t="n">
-        <v>739.270942</v>
+        <v>3658.626385</v>
       </c>
       <c r="I28" t="n">
-        <v>2131.834468</v>
+        <v>2593.799925</v>
       </c>
       <c r="J28" t="n">
-        <v>3321.131378</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4193.263171</v>
-      </c>
-      <c r="L28" t="n">
-        <v>7908.547337</v>
+        <v>3556.848112</v>
       </c>
     </row>
     <row r="29">
@@ -1551,37 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>3996.392377</v>
       </c>
       <c r="C29" t="n">
-        <v>1561.2769965</v>
+        <v>1900.92332</v>
       </c>
       <c r="D29" t="n">
-        <v>2086.840238</v>
+        <v>1874.387937</v>
       </c>
       <c r="E29" t="n">
-        <v>2152.21028</v>
+        <v>2796.918538</v>
       </c>
       <c r="F29" t="n">
-        <v>1801.717260666667</v>
+        <v>1159.083804</v>
       </c>
       <c r="G29" t="n">
-        <v>1481.4125085</v>
+        <v>1204.082537</v>
       </c>
       <c r="H29" t="n">
-        <v>1149.9222115</v>
+        <v>1371.787172</v>
       </c>
       <c r="I29" t="n">
-        <v>1922.980678</v>
+        <v>1143.675889666667</v>
       </c>
       <c r="J29" t="n">
-        <v>2247.294446</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1689.652544</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2060.897531</v>
+        <v>1170.92360425</v>
       </c>
     </row>
     <row r="30">
@@ -1590,36 +1438,32 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1960.267031</v>
+      </c>
       <c r="C30" t="n">
-        <v>2681.685764</v>
+        <v>1169.464009</v>
       </c>
       <c r="D30" t="n">
-        <v>2618.473442</v>
+        <v>1593.900291</v>
       </c>
       <c r="E30" t="n">
-        <v>2201.825597</v>
+        <v>931.223287</v>
       </c>
       <c r="F30" t="n">
-        <v>3637.452347</v>
+        <v>464.349189</v>
       </c>
       <c r="G30" t="n">
-        <v>2169.69448</v>
+        <v>460.082038</v>
       </c>
       <c r="H30" t="n">
-        <v>1839.806856</v>
+        <v>1411.506215</v>
       </c>
       <c r="I30" t="n">
-        <v>3497.731758</v>
+        <v>913.096038</v>
       </c>
       <c r="J30" t="n">
-        <v>2958.686563</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2290.735838</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1756.625796</v>
+        <v>716.628303</v>
       </c>
     </row>
     <row r="31">
@@ -1628,36 +1472,32 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>129.094295</v>
+      </c>
       <c r="C31" t="n">
-        <v>806.102949</v>
+        <v>97.96146</v>
       </c>
       <c r="D31" t="n">
-        <v>711.2830269999999</v>
+        <v>181.541844</v>
       </c>
       <c r="E31" t="n">
-        <v>788.365198</v>
+        <v>309.229901</v>
       </c>
       <c r="F31" t="n">
-        <v>732.770008</v>
+        <v>337.289111</v>
       </c>
       <c r="G31" t="n">
-        <v>954.158064</v>
+        <v>1395.007583</v>
       </c>
       <c r="H31" t="n">
-        <v>415.072136</v>
+        <v>981.782769</v>
       </c>
       <c r="I31" t="n">
-        <v>771.674121</v>
+        <v>300.275675</v>
       </c>
       <c r="J31" t="n">
-        <v>1575.860898</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2017.414174</v>
-      </c>
-      <c r="L31" t="n">
-        <v>970.115371</v>
+        <v>573.402185</v>
       </c>
     </row>
     <row r="32">
@@ -1666,36 +1506,32 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>15815.715517</v>
+      </c>
       <c r="C32" t="n">
-        <v>3888.174432</v>
+        <v>3706.578267</v>
       </c>
       <c r="D32" t="n">
-        <v>5694.213898</v>
+        <v>3919.093005</v>
       </c>
       <c r="E32" t="n">
-        <v>4209.891773</v>
+        <v>2995.886457</v>
       </c>
       <c r="F32" t="n">
-        <v>5752.685008</v>
+        <v>1914.022671</v>
       </c>
       <c r="G32" t="n">
-        <v>7426.032129</v>
+        <v>2767.071807</v>
       </c>
       <c r="H32" t="n">
-        <v>9176.665983999999</v>
+        <v>2175.603754</v>
       </c>
       <c r="I32" t="n">
-        <v>4525.95074</v>
+        <v>3293.053983</v>
       </c>
       <c r="J32" t="n">
-        <v>5217.603465</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3159.568737</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6451.34812</v>
+        <v>1634.098594</v>
       </c>
     </row>
     <row r="33">
@@ -1705,37 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>3729.761142</v>
       </c>
       <c r="C33" t="n">
-        <v>2101.889646</v>
+        <v>3265.066779</v>
       </c>
       <c r="D33" t="n">
-        <v>4731.279708</v>
+        <v>3576.81368125</v>
       </c>
       <c r="E33" t="n">
-        <v>3646.58812775</v>
+        <v>4231.049639</v>
       </c>
       <c r="F33" t="n">
-        <v>6828.137686</v>
+        <v>3152.723616083334</v>
       </c>
       <c r="G33" t="n">
-        <v>5754.878496</v>
+        <v>2054.422690333333</v>
       </c>
       <c r="H33" t="n">
-        <v>3600.862082</v>
+        <v>3157.254720666666</v>
       </c>
       <c r="I33" t="n">
-        <v>3335.18747175</v>
+        <v>4047.266548166667</v>
       </c>
       <c r="J33" t="n">
-        <v>3255.48374475</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3477.292396333333</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4419.1308515</v>
+        <v>2730.1196475</v>
       </c>
     </row>
     <row r="34">
@@ -1744,36 +1574,32 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>24942.40761725</v>
+      </c>
       <c r="C34" t="n">
-        <v>23104.700637</v>
+        <v>14640.291383</v>
       </c>
       <c r="D34" t="n">
-        <v>31734.558303</v>
+        <v>20499.14281033333</v>
       </c>
       <c r="E34" t="n">
-        <v>25008.893216</v>
+        <v>16008.9466375</v>
       </c>
       <c r="F34" t="n">
-        <v>15295.439048</v>
+        <v>18522.008159</v>
       </c>
       <c r="G34" t="n">
-        <v>30918.820524</v>
+        <v>24138.976642</v>
       </c>
       <c r="H34" t="n">
-        <v>31244.875852</v>
+        <v>38592.8304785</v>
       </c>
       <c r="I34" t="n">
-        <v>28310.92567</v>
+        <v>17726.891727</v>
       </c>
       <c r="J34" t="n">
-        <v>47447.265209</v>
-      </c>
-      <c r="K34" t="n">
-        <v>54480.084562</v>
-      </c>
-      <c r="L34" t="n">
-        <v>47474.01885525</v>
+        <v>18001.843649</v>
       </c>
     </row>
     <row r="35">
@@ -1782,36 +1608,32 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1496.018729333333</v>
+      </c>
       <c r="C35" t="n">
-        <v>3001.237544</v>
+        <v>891.2038680000001</v>
       </c>
       <c r="D35" t="n">
-        <v>5321.105164</v>
+        <v>1434.127968</v>
       </c>
       <c r="E35" t="n">
-        <v>7139.735404</v>
+        <v>864.776533</v>
       </c>
       <c r="F35" t="n">
-        <v>10185.076062</v>
+        <v>907.837418</v>
       </c>
       <c r="G35" t="n">
-        <v>5894.765257</v>
+        <v>883.170031</v>
       </c>
       <c r="H35" t="n">
-        <v>4111.108533</v>
+        <v>1354.065363</v>
       </c>
       <c r="I35" t="n">
-        <v>3653.085745</v>
+        <v>1121.706863</v>
       </c>
       <c r="J35" t="n">
-        <v>3327.911223</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2665.12637</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2276.828571</v>
+        <v>932.818224</v>
       </c>
     </row>
     <row r="36">
@@ -1820,36 +1642,32 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>6374.47776325</v>
+      </c>
       <c r="C36" t="n">
-        <v>2284.786336</v>
+        <v>2168.962247</v>
       </c>
       <c r="D36" t="n">
-        <v>4082.799946</v>
+        <v>1986.142069</v>
       </c>
       <c r="E36" t="n">
-        <v>3590.823931</v>
+        <v>1649.814433333333</v>
       </c>
       <c r="F36" t="n">
-        <v>3402.232283</v>
+        <v>1741.438457</v>
       </c>
       <c r="G36" t="n">
-        <v>5200.937717</v>
+        <v>1913.072300666667</v>
       </c>
       <c r="H36" t="n">
-        <v>4885.964885</v>
+        <v>2251.441003</v>
       </c>
       <c r="I36" t="n">
-        <v>4272.524023</v>
+        <v>1989.455276</v>
       </c>
       <c r="J36" t="n">
-        <v>4797.003426</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2972.311523</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3197.080644</v>
+        <v>2036.013433</v>
       </c>
     </row>
     <row r="37">
@@ -1858,36 +1676,32 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>12481.445979</v>
+      </c>
       <c r="C37" t="n">
-        <v>14442.149113</v>
+        <v>9107.543382</v>
       </c>
       <c r="D37" t="n">
-        <v>12080.552345</v>
+        <v>10602.834135</v>
       </c>
       <c r="E37" t="n">
-        <v>10158.08626</v>
+        <v>9503.746923999999</v>
       </c>
       <c r="F37" t="n">
-        <v>14705.573455</v>
+        <v>6766.767165</v>
       </c>
       <c r="G37" t="n">
-        <v>11738.374081</v>
+        <v>9354.171284</v>
       </c>
       <c r="H37" t="n">
-        <v>16109.552514</v>
+        <v>14735.204401</v>
       </c>
       <c r="I37" t="n">
-        <v>13956.282361</v>
+        <v>12505.335512</v>
       </c>
       <c r="J37" t="n">
-        <v>12610.076224</v>
-      </c>
-      <c r="K37" t="n">
-        <v>11756.75196</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7104.44914</v>
+        <v>12181.591653</v>
       </c>
     </row>
     <row r="38">
@@ -1896,36 +1710,32 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>1908.507394</v>
+      </c>
       <c r="C38" t="n">
-        <v>2675.286375</v>
+        <v>460.152903</v>
       </c>
       <c r="D38" t="n">
-        <v>2636.24437</v>
+        <v>1186.517079</v>
       </c>
       <c r="E38" t="n">
-        <v>2458.443435</v>
+        <v>2327.684013</v>
       </c>
       <c r="F38" t="n">
-        <v>4012.002755</v>
+        <v>1364.089271</v>
       </c>
       <c r="G38" t="n">
-        <v>5601.579287</v>
+        <v>755.371776</v>
       </c>
       <c r="H38" t="n">
-        <v>3904.213183</v>
+        <v>1522.638212</v>
       </c>
       <c r="I38" t="n">
-        <v>4671.800273</v>
+        <v>983.322091</v>
       </c>
       <c r="J38" t="n">
-        <v>4414.947263</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3189.448626</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1792.802037</v>
+        <v>514.825294</v>
       </c>
     </row>
     <row r="39">
@@ -1935,37 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>11181.0071735</v>
       </c>
       <c r="C39" t="n">
-        <v>6979.644655</v>
+        <v>6035.205858</v>
       </c>
       <c r="D39" t="n">
-        <v>14215.331356</v>
+        <v>4775.668836</v>
       </c>
       <c r="E39" t="n">
-        <v>12864.944536</v>
+        <v>5293.7077845</v>
       </c>
       <c r="F39" t="n">
-        <v>10991.670396</v>
+        <v>3869.600446</v>
       </c>
       <c r="G39" t="n">
-        <v>9388.082571999999</v>
+        <v>5798.788543</v>
       </c>
       <c r="H39" t="n">
-        <v>8936.101988</v>
+        <v>3937.918847</v>
       </c>
       <c r="I39" t="n">
-        <v>10391.033491</v>
+        <v>3621.251342</v>
       </c>
       <c r="J39" t="n">
-        <v>13680.33296</v>
-      </c>
-      <c r="K39" t="n">
-        <v>9820.331776499999</v>
-      </c>
-      <c r="L39" t="n">
-        <v>5729.974188</v>
+        <v>3802.02835</v>
       </c>
     </row>
     <row r="40">
@@ -1975,37 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>31220.348114</v>
       </c>
       <c r="C40" t="n">
-        <v>68932.892381</v>
+        <v>33189.891871</v>
       </c>
       <c r="D40" t="n">
-        <v>79084.248427</v>
+        <v>45038.124884</v>
       </c>
       <c r="E40" t="n">
-        <v>78158.25825499999</v>
+        <v>38221.90803</v>
       </c>
       <c r="F40" t="n">
-        <v>87528.221663</v>
+        <v>38620.912235</v>
       </c>
       <c r="G40" t="n">
-        <v>103226.359268</v>
+        <v>38788.057507</v>
       </c>
       <c r="H40" t="n">
-        <v>86927.33990399999</v>
+        <v>26515.97235</v>
       </c>
       <c r="I40" t="n">
-        <v>95037.149344</v>
+        <v>83369.64612400001</v>
       </c>
       <c r="J40" t="n">
-        <v>102675.023522</v>
-      </c>
-      <c r="K40" t="n">
-        <v>73283.451927</v>
-      </c>
-      <c r="L40" t="n">
-        <v>58667.223418</v>
+        <v>109528.711864</v>
       </c>
     </row>
     <row r="41">
@@ -2015,37 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>180.114267</v>
       </c>
       <c r="C41" t="n">
-        <v>314.338846</v>
+        <v>103.731344</v>
       </c>
       <c r="D41" t="n">
-        <v>482.88944</v>
+        <v>151.63697</v>
       </c>
       <c r="E41" t="n">
-        <v>424.064768</v>
+        <v>128.294805</v>
       </c>
       <c r="F41" t="n">
-        <v>406.796779</v>
+        <v>193.129646</v>
       </c>
       <c r="G41" t="n">
-        <v>349.60016</v>
+        <v>222.40962075</v>
       </c>
       <c r="H41" t="n">
-        <v>383.7701824166667</v>
+        <v>156.903562</v>
       </c>
       <c r="I41" t="n">
-        <v>366.134925</v>
+        <v>164.3006155</v>
       </c>
       <c r="J41" t="n">
-        <v>526.033987</v>
-      </c>
-      <c r="K41" t="n">
-        <v>426.159802</v>
-      </c>
-      <c r="L41" t="n">
-        <v>496.767816</v>
+        <v>143.66717925</v>
       </c>
     </row>
     <row r="42">
@@ -2054,36 +1846,32 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>82015.249931</v>
+      </c>
       <c r="C42" t="n">
-        <v>72248.127515</v>
+        <v>40610.057207</v>
       </c>
       <c r="D42" t="n">
-        <v>67261.764967</v>
+        <v>57852.103144</v>
       </c>
       <c r="E42" t="n">
-        <v>76227.290736</v>
+        <v>55538.57203</v>
       </c>
       <c r="F42" t="n">
-        <v>77696.395517</v>
+        <v>36425.530521</v>
       </c>
       <c r="G42" t="n">
-        <v>65417.258626</v>
+        <v>29728.764487</v>
       </c>
       <c r="H42" t="n">
-        <v>83973.279501</v>
+        <v>45172.5952</v>
       </c>
       <c r="I42" t="n">
-        <v>99502.408392</v>
+        <v>32010.529296</v>
       </c>
       <c r="J42" t="n">
-        <v>93333.881992</v>
-      </c>
-      <c r="K42" t="n">
-        <v>115093.335745</v>
-      </c>
-      <c r="L42" t="n">
-        <v>82753.160664</v>
+        <v>44356.231581</v>
       </c>
     </row>
     <row r="43">
@@ -2093,37 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>370.468524</v>
       </c>
       <c r="C43" t="n">
-        <v>241.572423</v>
+        <v>183.066952</v>
       </c>
       <c r="D43" t="n">
-        <v>350.569781</v>
+        <v>153.339739</v>
       </c>
       <c r="E43" t="n">
-        <v>238.30027025</v>
+        <v>214.148055</v>
       </c>
       <c r="F43" t="n">
-        <v>381.140633</v>
+        <v>137.208998</v>
       </c>
       <c r="G43" t="n">
-        <v>350.726938</v>
+        <v>140.3224923333333</v>
       </c>
       <c r="H43" t="n">
-        <v>768.466799</v>
+        <v>143.673452</v>
       </c>
       <c r="I43" t="n">
-        <v>526.5799510000001</v>
+        <v>126.829217</v>
       </c>
       <c r="J43" t="n">
-        <v>447.916782</v>
-      </c>
-      <c r="K43" t="n">
-        <v>635.692661</v>
-      </c>
-      <c r="L43" t="n">
-        <v>529.010567</v>
+        <v>153.965149</v>
       </c>
     </row>
     <row r="44">
@@ -2133,37 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>979.949574</v>
       </c>
       <c r="C44" t="n">
-        <v>341.000768</v>
+        <v>1650.056964</v>
       </c>
       <c r="D44" t="n">
-        <v>760.265355</v>
+        <v>550.6252469999999</v>
       </c>
       <c r="E44" t="n">
-        <v>564.406845</v>
+        <v>568.934852</v>
       </c>
       <c r="F44" t="n">
-        <v>488.885966</v>
+        <v>572.670523</v>
       </c>
       <c r="G44" t="n">
-        <v>269.7795465</v>
+        <v>273.551237</v>
       </c>
       <c r="H44" t="n">
-        <v>806.227009</v>
+        <v>406.0494</v>
       </c>
       <c r="I44" t="n">
-        <v>425.79034925</v>
+        <v>192.38958</v>
       </c>
       <c r="J44" t="n">
-        <v>361.377158</v>
-      </c>
-      <c r="K44" t="n">
-        <v>280.895837</v>
-      </c>
-      <c r="L44" t="n">
-        <v>195.61812075</v>
+        <v>159.333061</v>
       </c>
     </row>
     <row r="45">
@@ -2172,36 +1948,32 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>566.388916</v>
+      </c>
       <c r="C45" t="n">
-        <v>11468.717122</v>
+        <v>742.989564</v>
       </c>
       <c r="D45" t="n">
-        <v>4905.407286</v>
+        <v>629.646796</v>
       </c>
       <c r="E45" t="n">
-        <v>7372.408139</v>
+        <v>554.498075</v>
       </c>
       <c r="F45" t="n">
-        <v>3160.887187</v>
+        <v>431.843473</v>
       </c>
       <c r="G45" t="n">
-        <v>3245.000028</v>
+        <v>558.7608739999999</v>
       </c>
       <c r="H45" t="n">
-        <v>3302.637638</v>
+        <v>827.171639</v>
       </c>
       <c r="I45" t="n">
-        <v>5684.09593</v>
+        <v>608.8516980000001</v>
       </c>
       <c r="J45" t="n">
-        <v>11704.185083</v>
-      </c>
-      <c r="K45" t="n">
-        <v>6097.852704</v>
-      </c>
-      <c r="L45" t="n">
-        <v>4233.024229</v>
+        <v>1163.125599</v>
       </c>
     </row>
     <row r="46">
@@ -2210,36 +1982,32 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0.008626</v>
+      </c>
       <c r="C46" t="n">
-        <v>0.003966</v>
+        <v>0.036967</v>
       </c>
       <c r="D46" t="n">
-        <v>0.003958</v>
+        <v>0.012402</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004164</v>
+        <v>0.005706</v>
       </c>
       <c r="F46" t="n">
-        <v>0.005901</v>
+        <v>0.005351</v>
       </c>
       <c r="G46" t="n">
-        <v>0.006359</v>
+        <v>0.003217</v>
       </c>
       <c r="H46" t="n">
-        <v>0.003421</v>
+        <v>0.003287</v>
       </c>
       <c r="I46" t="n">
-        <v>0.008208</v>
+        <v>0.00215</v>
       </c>
       <c r="J46" t="n">
-        <v>0.00872</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.008957</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.005284</v>
+        <v>0.002401</v>
       </c>
     </row>
     <row r="47">
@@ -2249,37 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>5585.535666</v>
       </c>
       <c r="C47" t="n">
-        <v>2326.730837</v>
+        <v>1995.447133</v>
       </c>
       <c r="D47" t="n">
-        <v>2676.059374</v>
+        <v>3227.005332</v>
       </c>
       <c r="E47" t="n">
-        <v>1959.685577</v>
+        <v>2285.728811</v>
       </c>
       <c r="F47" t="n">
-        <v>2419.891652</v>
+        <v>2768.183649</v>
       </c>
       <c r="G47" t="n">
-        <v>2720.781831</v>
+        <v>2160.042912</v>
       </c>
       <c r="H47" t="n">
-        <v>5652.785715</v>
+        <v>2537.16588</v>
       </c>
       <c r="I47" t="n">
-        <v>2464.568477</v>
+        <v>1944.562274</v>
       </c>
       <c r="J47" t="n">
-        <v>2906.015548</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1028.73852225</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2182.115263</v>
+        <v>2607.919254</v>
       </c>
     </row>
     <row r="48">
@@ -2289,37 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>103.919057</v>
       </c>
       <c r="C48" t="n">
-        <v>292.876095</v>
+        <v>71.276222</v>
       </c>
       <c r="D48" t="n">
-        <v>452.726557</v>
+        <v>113.137448</v>
       </c>
       <c r="E48" t="n">
-        <v>580.721904</v>
+        <v>81.686544</v>
       </c>
       <c r="F48" t="n">
-        <v>354.815448</v>
+        <v>84.399334</v>
       </c>
       <c r="G48" t="n">
-        <v>333.690654</v>
+        <v>158.144148</v>
       </c>
       <c r="H48" t="n">
-        <v>417.293335</v>
+        <v>104.815151</v>
       </c>
       <c r="I48" t="n">
-        <v>257.30361</v>
+        <v>152.916565</v>
       </c>
       <c r="J48" t="n">
-        <v>215.258248</v>
-      </c>
-      <c r="K48" t="n">
-        <v>246.746099</v>
-      </c>
-      <c r="L48" t="n">
-        <v>173.015</v>
+        <v>102.306466</v>
       </c>
     </row>
     <row r="49">
@@ -2329,37 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>11927.853725</v>
       </c>
       <c r="C49" t="n">
-        <v>9165.324617</v>
+        <v>12782.254268</v>
       </c>
       <c r="D49" t="n">
-        <v>8168.176564</v>
+        <v>11076.491911</v>
       </c>
       <c r="E49" t="n">
-        <v>9385.644614999999</v>
+        <v>13492.845762</v>
       </c>
       <c r="F49" t="n">
-        <v>11529.361084</v>
+        <v>9220.807511999999</v>
       </c>
       <c r="G49" t="n">
-        <v>7236.325136</v>
+        <v>8228.998858999999</v>
       </c>
       <c r="H49" t="n">
-        <v>6844.984981</v>
+        <v>10620.880973</v>
       </c>
       <c r="I49" t="n">
-        <v>7197.916301</v>
+        <v>9718.66402</v>
       </c>
       <c r="J49" t="n">
-        <v>5734.647472</v>
-      </c>
-      <c r="K49" t="n">
-        <v>4747.239656</v>
-      </c>
-      <c r="L49" t="n">
-        <v>3893.342005</v>
+        <v>9504.345578</v>
       </c>
     </row>
     <row r="50">
@@ -2368,36 +2118,32 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>1639.139448</v>
+      </c>
       <c r="C50" t="n">
-        <v>2279.598036</v>
+        <v>759.747605</v>
       </c>
       <c r="D50" t="n">
-        <v>1769.322822</v>
+        <v>689.810168</v>
       </c>
       <c r="E50" t="n">
-        <v>1483.948348</v>
+        <v>796.660811</v>
       </c>
       <c r="F50" t="n">
-        <v>1255.311623</v>
+        <v>712.799925</v>
       </c>
       <c r="G50" t="n">
-        <v>953.238593</v>
+        <v>824.571243</v>
       </c>
       <c r="H50" t="n">
-        <v>1113.052389</v>
+        <v>787.650534</v>
       </c>
       <c r="I50" t="n">
-        <v>1454.87239</v>
+        <v>756.256289</v>
       </c>
       <c r="J50" t="n">
-        <v>1896.643305</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1376.650194</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3134.419538</v>
+        <v>741.500223</v>
       </c>
     </row>
     <row r="51">
@@ -2406,36 +2152,32 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0.029542</v>
+      </c>
       <c r="C51" t="n">
-        <v>0.017776</v>
+        <v>0.017833</v>
       </c>
       <c r="D51" t="n">
-        <v>0.058093</v>
+        <v>0.018883</v>
       </c>
       <c r="E51" t="n">
-        <v>0.043243</v>
+        <v>0.014946</v>
       </c>
       <c r="F51" t="n">
-        <v>0.033033</v>
+        <v>0.018067</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03803</v>
+        <v>0.017467</v>
       </c>
       <c r="H51" t="n">
-        <v>0.037978</v>
+        <v>0.015909</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03566</v>
+        <v>0.010093</v>
       </c>
       <c r="J51" t="n">
-        <v>0.035092</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.019424</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.032171</v>
+        <v>0.014062</v>
       </c>
     </row>
     <row r="52">
@@ -2445,37 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>20818.586488</v>
       </c>
       <c r="C52" t="n">
-        <v>21980.871084</v>
+        <v>9077.309005999999</v>
       </c>
       <c r="D52" t="n">
-        <v>12709.740397</v>
+        <v>8148.055404666667</v>
       </c>
       <c r="E52" t="n">
-        <v>11158.314321</v>
+        <v>9224.021632</v>
       </c>
       <c r="F52" t="n">
-        <v>13956.95503</v>
+        <v>5732.684626</v>
       </c>
       <c r="G52" t="n">
-        <v>12482.858632</v>
+        <v>10246.93227</v>
       </c>
       <c r="H52" t="n">
-        <v>10407.886265</v>
+        <v>8616.418030999999</v>
       </c>
       <c r="I52" t="n">
-        <v>11429.094372</v>
+        <v>10196.150336</v>
       </c>
       <c r="J52" t="n">
-        <v>13052.152444</v>
-      </c>
-      <c r="K52" t="n">
-        <v>10428.133967</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10264.161402</v>
+        <v>6597.266704</v>
       </c>
     </row>
     <row r="53">
@@ -2485,37 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>3298.6393515</v>
       </c>
       <c r="C53" t="n">
-        <v>2370.1633815</v>
+        <v>1901.163406</v>
       </c>
       <c r="D53" t="n">
-        <v>2903.25195</v>
+        <v>2784.567429</v>
       </c>
       <c r="E53" t="n">
-        <v>3008.693679</v>
+        <v>2840.801426</v>
       </c>
       <c r="F53" t="n">
-        <v>2909.4882165</v>
+        <v>2553.3653815</v>
       </c>
       <c r="G53" t="n">
-        <v>2054.805565666667</v>
+        <v>3519.341702</v>
       </c>
       <c r="H53" t="n">
-        <v>2104.006457</v>
+        <v>6191.425248333333</v>
       </c>
       <c r="I53" t="n">
-        <v>3082.661907</v>
+        <v>7155.879135</v>
       </c>
       <c r="J53" t="n">
-        <v>3011.654045166666</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3151.338611</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2043.768603</v>
+        <v>3091.901302</v>
       </c>
     </row>
     <row r="54">
@@ -2524,36 +2254,32 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>602.596304</v>
+      </c>
       <c r="C54" t="n">
-        <v>890.284184</v>
+        <v>251.282962</v>
       </c>
       <c r="D54" t="n">
-        <v>846.64126</v>
+        <v>206.789119</v>
       </c>
       <c r="E54" t="n">
-        <v>1038.466277</v>
+        <v>486.365714</v>
       </c>
       <c r="F54" t="n">
-        <v>831.610321</v>
+        <v>467.102515</v>
       </c>
       <c r="G54" t="n">
-        <v>571.511905</v>
+        <v>316.776227</v>
       </c>
       <c r="H54" t="n">
-        <v>712.5856</v>
+        <v>353.129823</v>
       </c>
       <c r="I54" t="n">
-        <v>565.690379</v>
+        <v>467.278976</v>
       </c>
       <c r="J54" t="n">
-        <v>652.515478</v>
-      </c>
-      <c r="K54" t="n">
-        <v>908.045359</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1248.31464</v>
+        <v>627.997406</v>
       </c>
     </row>
     <row r="55">
@@ -2562,36 +2288,32 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>4079.32611</v>
+      </c>
       <c r="C55" t="n">
-        <v>2332.055948</v>
+        <v>1300.476742</v>
       </c>
       <c r="D55" t="n">
-        <v>2492.356583</v>
+        <v>789.765672</v>
       </c>
       <c r="E55" t="n">
-        <v>1888.644065</v>
+        <v>1208.391141</v>
       </c>
       <c r="F55" t="n">
-        <v>2680.828124</v>
+        <v>918.019598</v>
       </c>
       <c r="G55" t="n">
-        <v>3556.651406</v>
+        <v>1676.725028</v>
       </c>
       <c r="H55" t="n">
-        <v>8013.003406</v>
+        <v>1524.028999</v>
       </c>
       <c r="I55" t="n">
-        <v>2680.976494</v>
+        <v>1248.190797</v>
       </c>
       <c r="J55" t="n">
-        <v>3771.271381</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1424.015382</v>
-      </c>
-      <c r="L55" t="n">
-        <v>2892.322324</v>
+        <v>1458.3181</v>
       </c>
     </row>
     <row r="56">
@@ -2600,36 +2322,32 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>14074.023657</v>
+      </c>
       <c r="C56" t="n">
-        <v>3345.104427</v>
+        <v>10237.123019</v>
       </c>
       <c r="D56" t="n">
-        <v>4732.491147</v>
+        <v>13781.334479</v>
       </c>
       <c r="E56" t="n">
-        <v>4269.993939</v>
+        <v>8485.200322000001</v>
       </c>
       <c r="F56" t="n">
-        <v>9809.202917000001</v>
+        <v>10685.838357</v>
       </c>
       <c r="G56" t="n">
-        <v>6922.324331</v>
+        <v>11086.499208</v>
       </c>
       <c r="H56" t="n">
-        <v>3726.891769</v>
+        <v>15936.008962</v>
       </c>
       <c r="I56" t="n">
-        <v>3560.216565</v>
+        <v>7870.13773</v>
       </c>
       <c r="J56" t="n">
-        <v>5235.960004</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6299.106521</v>
-      </c>
-      <c r="L56" t="n">
-        <v>5504.437376</v>
+        <v>7151.438405</v>
       </c>
     </row>
     <row r="57">
@@ -2638,36 +2356,32 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>288.648451</v>
+      </c>
       <c r="C57" t="n">
-        <v>452.626194</v>
+        <v>191.280322</v>
       </c>
       <c r="D57" t="n">
-        <v>879.320815</v>
+        <v>211.287875</v>
       </c>
       <c r="E57" t="n">
-        <v>1772.063561</v>
+        <v>134.946384</v>
       </c>
       <c r="F57" t="n">
-        <v>2469.073204</v>
+        <v>107.918206</v>
       </c>
       <c r="G57" t="n">
-        <v>968.953139</v>
+        <v>240.957821</v>
       </c>
       <c r="H57" t="n">
-        <v>525.838812</v>
+        <v>280.614387</v>
       </c>
       <c r="I57" t="n">
-        <v>617.980267</v>
+        <v>241.632148</v>
       </c>
       <c r="J57" t="n">
-        <v>585.400203</v>
-      </c>
-      <c r="K57" t="n">
-        <v>329.970395</v>
-      </c>
-      <c r="L57" t="n">
-        <v>282.641517</v>
+        <v>160.750781</v>
       </c>
     </row>
     <row r="58">
@@ -2676,36 +2390,32 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>1.501269</v>
+      </c>
       <c r="C58" t="n">
-        <v>3.387708</v>
+        <v>0.78407</v>
       </c>
       <c r="D58" t="n">
-        <v>2.726041</v>
+        <v>0.846683</v>
       </c>
       <c r="E58" t="n">
-        <v>2.656444</v>
+        <v>0.86441</v>
       </c>
       <c r="F58" t="n">
-        <v>1.823611</v>
+        <v>0.797876</v>
       </c>
       <c r="G58" t="n">
-        <v>1.03344</v>
+        <v>1.227215</v>
       </c>
       <c r="H58" t="n">
-        <v>1.14729</v>
+        <v>0.803998</v>
       </c>
       <c r="I58" t="n">
-        <v>0.881444</v>
+        <v>0.610103</v>
       </c>
       <c r="J58" t="n">
-        <v>1.499544</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1.471793</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.199521</v>
+        <v>0.848656</v>
       </c>
     </row>
     <row r="59">
@@ -2714,36 +2424,32 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>5377.855906</v>
+      </c>
       <c r="C59" t="n">
-        <v>6899.191375</v>
+        <v>3280.445867</v>
       </c>
       <c r="D59" t="n">
-        <v>7013.586511</v>
+        <v>3874.059874</v>
       </c>
       <c r="E59" t="n">
-        <v>5968.840244</v>
+        <v>3231.589884</v>
       </c>
       <c r="F59" t="n">
-        <v>7634.933173</v>
+        <v>3117.83436</v>
       </c>
       <c r="G59" t="n">
-        <v>6241.125868</v>
+        <v>3284.358638</v>
       </c>
       <c r="H59" t="n">
-        <v>4268.465629</v>
+        <v>3269.037075</v>
       </c>
       <c r="I59" t="n">
-        <v>8595.903146000001</v>
+        <v>4556.196035</v>
       </c>
       <c r="J59" t="n">
-        <v>8638.729899</v>
-      </c>
-      <c r="K59" t="n">
-        <v>9289.572972</v>
-      </c>
-      <c r="L59" t="n">
-        <v>7942.524325</v>
+        <v>3278.903084</v>
       </c>
     </row>
     <row r="60">
@@ -2753,37 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>12445.313083</v>
       </c>
       <c r="C60" t="n">
-        <v>28920.761135</v>
+        <v>11352.952924</v>
       </c>
       <c r="D60" t="n">
-        <v>41769.355689</v>
+        <v>10163.677225</v>
       </c>
       <c r="E60" t="n">
-        <v>27585.309019</v>
+        <v>14283.118326</v>
       </c>
       <c r="F60" t="n">
-        <v>27962.483956</v>
+        <v>15702.555225</v>
       </c>
       <c r="G60" t="n">
-        <v>21681.302242</v>
+        <v>16339.641228</v>
       </c>
       <c r="H60" t="n">
-        <v>15840.860489</v>
+        <v>13990.75545</v>
       </c>
       <c r="I60" t="n">
-        <v>12499.012054</v>
+        <v>17015.63981</v>
       </c>
       <c r="J60" t="n">
-        <v>10084.725157</v>
-      </c>
-      <c r="K60" t="n">
-        <v>11291.596383</v>
-      </c>
-      <c r="L60" t="n">
-        <v>16630.528475</v>
+        <v>22387.339779</v>
       </c>
     </row>
     <row r="61">
@@ -2793,37 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>3126.0001085</v>
       </c>
       <c r="C61" t="n">
-        <v>4120.435761</v>
+        <v>2465.182143</v>
       </c>
       <c r="D61" t="n">
-        <v>6529.92108</v>
+        <v>2654.157778</v>
       </c>
       <c r="E61" t="n">
-        <v>4715.459207</v>
+        <v>1915.343968333333</v>
       </c>
       <c r="F61" t="n">
-        <v>3317.038268</v>
+        <v>2833.24706325</v>
       </c>
       <c r="G61" t="n">
-        <v>2211.01862275</v>
+        <v>3220.483233</v>
       </c>
       <c r="H61" t="n">
-        <v>2216.09172175</v>
+        <v>3455.685055</v>
       </c>
       <c r="I61" t="n">
-        <v>2767.008758333333</v>
+        <v>2850.61244775</v>
       </c>
       <c r="J61" t="n">
-        <v>3690.2950805</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2758.031741</v>
-      </c>
-      <c r="L61" t="n">
-        <v>2164.388286</v>
+        <v>2993.695927</v>
       </c>
     </row>
     <row r="62">
@@ -2832,36 +2526,32 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>5528.695031</v>
+      </c>
       <c r="C62" t="n">
-        <v>3819.004259</v>
+        <v>3758.237494</v>
       </c>
       <c r="D62" t="n">
-        <v>3101.502802</v>
+        <v>2761.665087</v>
       </c>
       <c r="E62" t="n">
-        <v>5157.81446</v>
+        <v>2220.286172</v>
       </c>
       <c r="F62" t="n">
-        <v>4521.662025</v>
+        <v>3864.484353</v>
       </c>
       <c r="G62" t="n">
-        <v>2761.115567</v>
+        <v>3658.219779</v>
       </c>
       <c r="H62" t="n">
-        <v>2924.119381</v>
+        <v>3713.579148</v>
       </c>
       <c r="I62" t="n">
-        <v>3542.289416</v>
+        <v>5625.03953</v>
       </c>
       <c r="J62" t="n">
-        <v>3305.870399</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1777.83591</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1228.848841</v>
+        <v>5045.504785</v>
       </c>
     </row>
     <row r="63">
@@ -2870,36 +2560,32 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>16705.506837</v>
+      </c>
       <c r="C63" t="n">
-        <v>40327.554286</v>
+        <v>41270.985346</v>
       </c>
       <c r="D63" t="n">
-        <v>26917.934161</v>
+        <v>67962.25039299999</v>
       </c>
       <c r="E63" t="n">
-        <v>48632.589198</v>
+        <v>44299.675634</v>
       </c>
       <c r="F63" t="n">
-        <v>65621.112796</v>
+        <v>23766.421451</v>
       </c>
       <c r="G63" t="n">
-        <v>34660.886943</v>
+        <v>24131.35528</v>
       </c>
       <c r="H63" t="n">
-        <v>43477.771391</v>
+        <v>42390.318478</v>
       </c>
       <c r="I63" t="n">
-        <v>40824.802565</v>
+        <v>61009.00298</v>
       </c>
       <c r="J63" t="n">
-        <v>38911.887049</v>
-      </c>
-      <c r="K63" t="n">
-        <v>21265.766115</v>
-      </c>
-      <c r="L63" t="n">
-        <v>18242.226075</v>
+        <v>39186.48104</v>
       </c>
     </row>
     <row r="64">
@@ -2908,36 +2594,32 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>2059.662455</v>
+      </c>
       <c r="C64" t="n">
-        <v>1950.892856333333</v>
+        <v>639.320237</v>
       </c>
       <c r="D64" t="n">
-        <v>2286.9441</v>
+        <v>932.27086</v>
       </c>
       <c r="E64" t="n">
-        <v>2869.281352</v>
+        <v>894.284195</v>
       </c>
       <c r="F64" t="n">
-        <v>2375.942353</v>
+        <v>672.670647</v>
       </c>
       <c r="G64" t="n">
-        <v>2386.195759</v>
+        <v>822.513379</v>
       </c>
       <c r="H64" t="n">
-        <v>2100.562526</v>
+        <v>808.75627</v>
       </c>
       <c r="I64" t="n">
-        <v>2499.073621</v>
+        <v>729.3189609999999</v>
       </c>
       <c r="J64" t="n">
-        <v>2109.314043</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2338.540331</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2663.953698</v>
+        <v>1690.981625</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9408.10016</v>
+        <v>9404.327004000001</v>
       </c>
       <c r="C11" t="n">
-        <v>5176.242822</v>
+        <v>5174.835734</v>
       </c>
       <c r="D11" t="n">
-        <v>4538.158264666667</v>
+        <v>4536.195576666667</v>
       </c>
       <c r="E11" t="n">
-        <v>6392.108486</v>
+        <v>6391.552234</v>
       </c>
       <c r="F11" t="n">
-        <v>5028.581066</v>
+        <v>5027.901959</v>
       </c>
       <c r="G11" t="n">
-        <v>4289.738981</v>
+        <v>4287.608381</v>
       </c>
       <c r="H11" t="n">
-        <v>5741.6945715</v>
+        <v>5741.1415725</v>
       </c>
       <c r="I11" t="n">
-        <v>5932.783523</v>
+        <v>5931.790813</v>
       </c>
       <c r="J11" t="n">
-        <v>5711.568377</v>
+        <v>5709.634427</v>
       </c>
     </row>
     <row r="12">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20852.49387</v>
+        <v>20850.603828</v>
       </c>
       <c r="C16" t="n">
-        <v>24593.793714</v>
+        <v>24590.802669</v>
       </c>
       <c r="D16" t="n">
-        <v>23394.055888</v>
+        <v>23392.141195</v>
       </c>
       <c r="E16" t="n">
-        <v>28438.041727</v>
+        <v>28437.085444</v>
       </c>
       <c r="F16" t="n">
-        <v>18391.555121</v>
+        <v>18387.097511</v>
       </c>
       <c r="G16" t="n">
-        <v>18781.663985</v>
+        <v>18772.393694</v>
       </c>
       <c r="H16" t="n">
-        <v>24000.561306</v>
+        <v>23991.340089</v>
       </c>
       <c r="I16" t="n">
-        <v>16200.809153</v>
+        <v>16183.796468</v>
       </c>
       <c r="J16" t="n">
-        <v>20930.807379</v>
+        <v>20919.253641</v>
       </c>
     </row>
     <row r="17">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5636.052303</v>
+        <v>5245.902267</v>
       </c>
       <c r="C21" t="n">
-        <v>4241.862746</v>
+        <v>3741.81836</v>
       </c>
       <c r="D21" t="n">
-        <v>3718.826782</v>
+        <v>3504.671797</v>
       </c>
       <c r="E21" t="n">
-        <v>3337.890946</v>
+        <v>3139.560877</v>
       </c>
       <c r="F21" t="n">
-        <v>3450.698097</v>
+        <v>3318.479694</v>
       </c>
       <c r="G21" t="n">
-        <v>6353.527497</v>
+        <v>5802.953388</v>
       </c>
       <c r="H21" t="n">
-        <v>4324.242742</v>
+        <v>3962.280094</v>
       </c>
       <c r="I21" t="n">
-        <v>3288.161369</v>
+        <v>3170.634716</v>
       </c>
       <c r="J21" t="n">
-        <v>3740.481742</v>
+        <v>3466.111153</v>
       </c>
     </row>
     <row r="22">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31220.348114</v>
+        <v>31220.241828</v>
       </c>
       <c r="C40" t="n">
-        <v>33189.891871</v>
+        <v>33189.695159</v>
       </c>
       <c r="D40" t="n">
-        <v>45038.124884</v>
+        <v>45038.042564</v>
       </c>
       <c r="E40" t="n">
-        <v>38221.90803</v>
+        <v>38221.871131</v>
       </c>
       <c r="F40" t="n">
-        <v>38620.912235</v>
+        <v>38620.855354</v>
       </c>
       <c r="G40" t="n">
-        <v>38788.057507</v>
+        <v>38787.989586</v>
       </c>
       <c r="H40" t="n">
-        <v>26515.97235</v>
+        <v>26515.935769</v>
       </c>
       <c r="I40" t="n">
-        <v>83369.64612400001</v>
+        <v>83369.59020000001</v>
       </c>
       <c r="J40" t="n">
-        <v>109528.711864</v>
+        <v>109528.620721</v>
       </c>
     </row>
     <row r="41">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>11927.853725</v>
+        <v>11881.843667</v>
       </c>
       <c r="C49" t="n">
-        <v>12782.254268</v>
+        <v>12517.186223</v>
       </c>
       <c r="D49" t="n">
-        <v>11076.491911</v>
+        <v>10630.8634</v>
       </c>
       <c r="E49" t="n">
-        <v>13492.845762</v>
+        <v>12588.924363</v>
       </c>
       <c r="F49" t="n">
-        <v>9220.807511999999</v>
+        <v>6628.107666</v>
       </c>
       <c r="G49" t="n">
-        <v>8228.998858999999</v>
+        <v>7771.289255</v>
       </c>
       <c r="H49" t="n">
-        <v>10620.880973</v>
+        <v>10297.83788</v>
       </c>
       <c r="I49" t="n">
-        <v>9718.66402</v>
+        <v>9437.364121000001</v>
       </c>
       <c r="J49" t="n">
-        <v>9504.345578</v>
+        <v>8742.657853999999</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1639.139448</v>
+        <v>1558.220295</v>
       </c>
       <c r="C50" t="n">
-        <v>759.747605</v>
+        <v>647.096954</v>
       </c>
       <c r="D50" t="n">
-        <v>689.810168</v>
+        <v>604.192691</v>
       </c>
       <c r="E50" t="n">
-        <v>796.660811</v>
+        <v>740.053436</v>
       </c>
       <c r="F50" t="n">
-        <v>712.799925</v>
+        <v>612.497166</v>
       </c>
       <c r="G50" t="n">
-        <v>824.571243</v>
+        <v>752.428062</v>
       </c>
       <c r="H50" t="n">
-        <v>787.650534</v>
+        <v>692.888991</v>
       </c>
       <c r="I50" t="n">
-        <v>756.256289</v>
+        <v>646.441073</v>
       </c>
       <c r="J50" t="n">
-        <v>741.500223</v>
+        <v>664.655217</v>
       </c>
     </row>
     <row r="51">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12445.313083</v>
+        <v>12445.301188</v>
       </c>
       <c r="C60" t="n">
-        <v>11352.952924</v>
+        <v>11352.946507</v>
       </c>
       <c r="D60" t="n">
-        <v>10163.677225</v>
+        <v>10163.667076</v>
       </c>
       <c r="E60" t="n">
-        <v>14283.118326</v>
+        <v>14283.112728</v>
       </c>
       <c r="F60" t="n">
-        <v>15702.555225</v>
+        <v>15702.55116</v>
       </c>
       <c r="G60" t="n">
-        <v>16339.641228</v>
+        <v>16339.630617</v>
       </c>
       <c r="H60" t="n">
-        <v>13990.75545</v>
+        <v>13990.739466</v>
       </c>
       <c r="I60" t="n">
-        <v>17015.63981</v>
+        <v>17015.629412</v>
       </c>
       <c r="J60" t="n">
-        <v>22387.339779</v>
+        <v>22387.334106</v>
       </c>
     </row>
     <row r="61">

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -487,31 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108147.973618</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>90202.090773</v>
+        <v>90201.344881</v>
       </c>
       <c r="D2" t="n">
-        <v>115583.774439</v>
+        <v>115582.265165</v>
       </c>
       <c r="E2" t="n">
-        <v>88280.45979350001</v>
+        <v>88278.6996525</v>
       </c>
       <c r="F2" t="n">
-        <v>85140.476152</v>
+        <v>85139.044972</v>
       </c>
       <c r="G2" t="n">
-        <v>97469.493455</v>
+        <v>97468.551733</v>
       </c>
       <c r="H2" t="n">
-        <v>93023.65412000001</v>
+        <v>93022.766947</v>
       </c>
       <c r="I2" t="n">
-        <v>80100.52979</v>
+        <v>80098.647251</v>
       </c>
       <c r="J2" t="n">
-        <v>79486.70570525</v>
+        <v>79486.13153324999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>129847.636549</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +529,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3659.618535</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1717.408387</v>
+        <v>1717.374217</v>
       </c>
       <c r="D3" t="n">
-        <v>1442.069167</v>
+        <v>1442.051502</v>
       </c>
       <c r="E3" t="n">
-        <v>1293.691735</v>
+        <v>1293.682623</v>
       </c>
       <c r="F3" t="n">
-        <v>1051.289579</v>
+        <v>1051.276545</v>
       </c>
       <c r="G3" t="n">
-        <v>1205.972422</v>
+        <v>1205.963345</v>
       </c>
       <c r="H3" t="n">
-        <v>1376.309944</v>
+        <v>1376.303467</v>
       </c>
       <c r="I3" t="n">
-        <v>1788.730843</v>
+        <v>1788.712576</v>
       </c>
       <c r="J3" t="n">
-        <v>1316.913868</v>
+        <v>1316.899044</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1865.363933</v>
       </c>
     </row>
     <row r="4">
@@ -554,32 +565,33 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>271299.418654</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>179360.190207</v>
+        <v>178538.931366</v>
       </c>
       <c r="D4" t="n">
-        <v>226359.872253</v>
+        <v>223594.517634</v>
       </c>
       <c r="E4" t="n">
-        <v>166179.907213</v>
+        <v>165402.902434</v>
       </c>
       <c r="F4" t="n">
-        <v>138946.48812</v>
+        <v>138499.150042</v>
       </c>
       <c r="G4" t="n">
-        <v>189646.737822</v>
+        <v>189359.179427</v>
       </c>
       <c r="H4" t="n">
-        <v>182760.686487</v>
+        <v>182345.333393</v>
       </c>
       <c r="I4" t="n">
-        <v>128660.880246</v>
+        <v>128106.303883</v>
       </c>
       <c r="J4" t="n">
-        <v>123539.16242</v>
+        <v>122579.80249</v>
+      </c>
+      <c r="K4" t="n">
+        <v>204717.298488</v>
       </c>
     </row>
     <row r="5">
@@ -588,9 +600,7 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2361.305817</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>1237.090225</v>
       </c>
@@ -615,6 +625,9 @@
       <c r="J5" t="n">
         <v>1601.886093</v>
       </c>
+      <c r="K5" t="n">
+        <v>1716.223375</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -623,31 +636,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100386.32367</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>99702.839399</v>
+        <v>99702.83822600001</v>
       </c>
       <c r="D6" t="n">
-        <v>121821.817605</v>
+        <v>121821.815051</v>
       </c>
       <c r="E6" t="n">
-        <v>129515.847183</v>
+        <v>129515.845253</v>
       </c>
       <c r="F6" t="n">
-        <v>130648.847117</v>
+        <v>130648.846293</v>
       </c>
       <c r="G6" t="n">
-        <v>102906.419806</v>
+        <v>102906.416866</v>
       </c>
       <c r="H6" t="n">
-        <v>129641.407368</v>
+        <v>129641.404601</v>
       </c>
       <c r="I6" t="n">
-        <v>140476.595393</v>
+        <v>140476.592648</v>
       </c>
       <c r="J6" t="n">
-        <v>153960.233459</v>
+        <v>154082.837499</v>
+      </c>
+      <c r="K6" t="n">
+        <v>197491.588367</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +673,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26471.264276</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>20781.455792</v>
+        <v>20781.249811</v>
       </c>
       <c r="D7" t="n">
-        <v>22175.429716</v>
+        <v>22175.17617</v>
       </c>
       <c r="E7" t="n">
-        <v>13770.435178</v>
+        <v>13770.242891</v>
       </c>
       <c r="F7" t="n">
-        <v>10540.732272</v>
+        <v>10540.539311</v>
       </c>
       <c r="G7" t="n">
-        <v>13889.568317</v>
+        <v>13889.42986</v>
       </c>
       <c r="H7" t="n">
-        <v>13855.977711</v>
+        <v>13855.859454</v>
       </c>
       <c r="I7" t="n">
-        <v>20448.539832</v>
+        <v>20448.18439</v>
       </c>
       <c r="J7" t="n">
-        <v>15846.945404</v>
+        <v>15846.638001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24738.818616</v>
       </c>
     </row>
     <row r="8">
@@ -690,9 +709,7 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>13120.648025</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>10613.63104</v>
       </c>
@@ -715,7 +732,10 @@
         <v>5956.565974</v>
       </c>
       <c r="J8" t="n">
-        <v>9323.950983999999</v>
+        <v>18678.998933</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20069.059953</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +745,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22459.343933</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>14982.790173</v>
+        <v>14982.787477</v>
       </c>
       <c r="D9" t="n">
-        <v>23907.352232</v>
+        <v>23907.350078</v>
       </c>
       <c r="E9" t="n">
-        <v>16164.352791</v>
+        <v>16164.351487</v>
       </c>
       <c r="F9" t="n">
-        <v>12877.494238</v>
+        <v>12877.493172</v>
       </c>
       <c r="G9" t="n">
-        <v>12170.44137225</v>
+        <v>12170.439475</v>
       </c>
       <c r="H9" t="n">
-        <v>28574.762822</v>
+        <v>28574.761172</v>
       </c>
       <c r="I9" t="n">
-        <v>20694.5899575</v>
+        <v>20694.5882835</v>
       </c>
       <c r="J9" t="n">
-        <v>18024.656341</v>
+        <v>18024.651983</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20594.009557</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +782,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2345.002665</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1728.446305666667</v>
+        <v>1728.444248666666</v>
       </c>
       <c r="D10" t="n">
-        <v>2505.415513</v>
+        <v>2505.414117</v>
       </c>
       <c r="E10" t="n">
-        <v>2014.82200825</v>
+        <v>2014.81808325</v>
       </c>
       <c r="F10" t="n">
-        <v>1437.9102595</v>
+        <v>1437.9092845</v>
       </c>
       <c r="G10" t="n">
-        <v>1691.566047</v>
+        <v>1691.564228</v>
       </c>
       <c r="H10" t="n">
-        <v>1739.207265</v>
+        <v>1739.205435</v>
       </c>
       <c r="I10" t="n">
-        <v>2361.4214135</v>
+        <v>2361.4190265</v>
       </c>
       <c r="J10" t="n">
-        <v>2507.015601083333</v>
+        <v>2507.013628083334</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2915.59429875</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +819,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9404.327004000001</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5174.835734</v>
+        <v>5174.810084</v>
       </c>
       <c r="D11" t="n">
-        <v>4536.195576666667</v>
+        <v>4536.177807666667</v>
       </c>
       <c r="E11" t="n">
-        <v>6391.552234</v>
+        <v>6391.53562</v>
       </c>
       <c r="F11" t="n">
-        <v>5027.901959</v>
+        <v>5027.892198</v>
       </c>
       <c r="G11" t="n">
-        <v>4287.608381</v>
+        <v>4287.599429</v>
       </c>
       <c r="H11" t="n">
-        <v>5741.1415725</v>
+        <v>5741.1294755</v>
       </c>
       <c r="I11" t="n">
-        <v>5931.790813</v>
+        <v>5931.781489</v>
       </c>
       <c r="J11" t="n">
-        <v>5709.634427</v>
+        <v>5709.611439</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8910.424891000001</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +856,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15291.684178</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>8832.563737</v>
+        <v>8811.598866</v>
       </c>
       <c r="D12" t="n">
-        <v>14287.592061</v>
+        <v>14269.15132</v>
       </c>
       <c r="E12" t="n">
-        <v>12754.3151</v>
+        <v>12736.20801</v>
       </c>
       <c r="F12" t="n">
-        <v>13061.21415</v>
+        <v>13045.659288</v>
       </c>
       <c r="G12" t="n">
-        <v>11174.18828</v>
+        <v>11155.583009</v>
       </c>
       <c r="H12" t="n">
-        <v>13638.882629</v>
+        <v>13603.614018</v>
       </c>
       <c r="I12" t="n">
-        <v>13065.508176</v>
+        <v>13046.164949</v>
       </c>
       <c r="J12" t="n">
-        <v>13474.480942</v>
+        <v>13450.578291</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19989.466924</v>
       </c>
     </row>
     <row r="13">
@@ -860,32 +892,33 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>3549.744938</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>2701.740215</v>
+        <v>2700.539033</v>
       </c>
       <c r="D13" t="n">
-        <v>5209.950112</v>
+        <v>5207.91587</v>
       </c>
       <c r="E13" t="n">
-        <v>5233.847716</v>
+        <v>5232.44427</v>
       </c>
       <c r="F13" t="n">
-        <v>3371.427526</v>
+        <v>3371.054838</v>
       </c>
       <c r="G13" t="n">
-        <v>2394.061638</v>
+        <v>2392.600297</v>
       </c>
       <c r="H13" t="n">
-        <v>4286.652275</v>
+        <v>4281.926355</v>
       </c>
       <c r="I13" t="n">
-        <v>2976.017692</v>
+        <v>2975.120135</v>
       </c>
       <c r="J13" t="n">
-        <v>3786.824192</v>
+        <v>3785.307081</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4020.392913</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +928,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25348.453042</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13746.938159</v>
+        <v>13743.74672</v>
       </c>
       <c r="D14" t="n">
-        <v>13071.459356</v>
+        <v>13063.626124</v>
       </c>
       <c r="E14" t="n">
-        <v>11120.031796</v>
+        <v>11114.79322</v>
       </c>
       <c r="F14" t="n">
-        <v>14305.724936</v>
+        <v>14301.814538</v>
       </c>
       <c r="G14" t="n">
-        <v>8735.041053249999</v>
+        <v>8729.909638249999</v>
       </c>
       <c r="H14" t="n">
-        <v>9585.149552999999</v>
+        <v>9580.546229</v>
       </c>
       <c r="I14" t="n">
-        <v>6695.3773</v>
+        <v>6692.928605</v>
       </c>
       <c r="J14" t="n">
-        <v>6646.674439</v>
+        <v>6643.835136</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9484.962056</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +965,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37230.517994</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25754.563201</v>
+        <v>25753.415463</v>
       </c>
       <c r="D15" t="n">
-        <v>30247.363515</v>
+        <v>30246.267866</v>
       </c>
       <c r="E15" t="n">
-        <v>29527.568526</v>
+        <v>29526.550866</v>
       </c>
       <c r="F15" t="n">
-        <v>35684.540649</v>
+        <v>35682.909805</v>
       </c>
       <c r="G15" t="n">
-        <v>33341.832677</v>
+        <v>33334.868582</v>
       </c>
       <c r="H15" t="n">
-        <v>24770.886724</v>
+        <v>24766.553877</v>
       </c>
       <c r="I15" t="n">
-        <v>21506.286768</v>
+        <v>21497.169701</v>
       </c>
       <c r="J15" t="n">
-        <v>33362.212799</v>
+        <v>33351.716219</v>
+      </c>
+      <c r="K15" t="n">
+        <v>24129.937751</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +1002,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20850.603828</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24590.802669</v>
+        <v>24590.739754</v>
       </c>
       <c r="D16" t="n">
-        <v>23392.141195</v>
+        <v>23392.100511</v>
       </c>
       <c r="E16" t="n">
-        <v>28437.085444</v>
+        <v>28437.056461</v>
       </c>
       <c r="F16" t="n">
-        <v>18387.097511</v>
+        <v>18387.025013</v>
       </c>
       <c r="G16" t="n">
-        <v>18772.393694</v>
+        <v>18772.355641</v>
       </c>
       <c r="H16" t="n">
-        <v>23991.340089</v>
+        <v>23991.291969</v>
       </c>
       <c r="I16" t="n">
-        <v>16183.796468</v>
+        <v>16183.76353</v>
       </c>
       <c r="J16" t="n">
-        <v>20919.253641</v>
+        <v>20919.215662</v>
+      </c>
+      <c r="K16" t="n">
+        <v>21320.174174</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +1039,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56819.751285</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>53935.315237</v>
+        <v>53935.30093</v>
       </c>
       <c r="D17" t="n">
-        <v>70058.288533</v>
+        <v>70058.26046999999</v>
       </c>
       <c r="E17" t="n">
-        <v>44988.016253</v>
+        <v>44988.00722</v>
       </c>
       <c r="F17" t="n">
-        <v>30953.730487</v>
+        <v>30953.724456</v>
       </c>
       <c r="G17" t="n">
-        <v>28733.570505</v>
+        <v>28733.552849</v>
       </c>
       <c r="H17" t="n">
-        <v>38078.11666</v>
+        <v>38078.097503</v>
       </c>
       <c r="I17" t="n">
-        <v>24953.722837</v>
+        <v>24953.716725</v>
       </c>
       <c r="J17" t="n">
-        <v>41336.354249</v>
+        <v>41336.337735</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46582.468537</v>
       </c>
     </row>
     <row r="18">
@@ -1030,9 +1075,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1453.397163</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>843.593843</v>
       </c>
@@ -1057,6 +1100,9 @@
       <c r="J18" t="n">
         <v>1259.522176</v>
       </c>
+      <c r="K18" t="n">
+        <v>2058.870186</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1064,9 +1110,7 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>451.440952</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>315.535051</v>
       </c>
@@ -1091,6 +1135,9 @@
       <c r="J19" t="n">
         <v>86.055667</v>
       </c>
+      <c r="K19" t="n">
+        <v>94.680183</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1098,9 +1145,7 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>22643.080858</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>35044.727771</v>
       </c>
@@ -1125,6 +1170,9 @@
       <c r="J20" t="n">
         <v>11464.949012</v>
       </c>
+      <c r="K20" t="n">
+        <v>35323.290674</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1133,31 +1181,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5245.902267</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3741.81836</v>
+        <v>3741.800574</v>
       </c>
       <c r="D21" t="n">
-        <v>3504.671797</v>
+        <v>3504.655549</v>
       </c>
       <c r="E21" t="n">
-        <v>3139.560877</v>
+        <v>3139.555335</v>
       </c>
       <c r="F21" t="n">
-        <v>3318.479694</v>
+        <v>3318.472302</v>
       </c>
       <c r="G21" t="n">
-        <v>5802.953388</v>
+        <v>5802.946135</v>
       </c>
       <c r="H21" t="n">
-        <v>3962.280094</v>
+        <v>3962.276966</v>
       </c>
       <c r="I21" t="n">
-        <v>3170.634716</v>
+        <v>3170.626323</v>
       </c>
       <c r="J21" t="n">
-        <v>3466.111153</v>
+        <v>3466.105076</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3968.711627</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1218,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>295.384989</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>162.87355125</v>
+        <v>162.87271725</v>
       </c>
       <c r="D22" t="n">
-        <v>636.4326583333333</v>
+        <v>636.4310123333332</v>
       </c>
       <c r="E22" t="n">
-        <v>332.069325</v>
+        <v>332.06855</v>
       </c>
       <c r="F22" t="n">
-        <v>284.626499</v>
+        <v>284.626257</v>
       </c>
       <c r="G22" t="n">
-        <v>234.591797</v>
+        <v>234.59035</v>
       </c>
       <c r="H22" t="n">
-        <v>213.95378</v>
+        <v>213.95212</v>
       </c>
       <c r="I22" t="n">
-        <v>146.3468013333333</v>
+        <v>146.3349263333334</v>
       </c>
       <c r="J22" t="n">
-        <v>140.418245</v>
+        <v>140.41194</v>
+      </c>
+      <c r="K22" t="n">
+        <v>213.064699</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1255,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.097406666666667</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.88782625</v>
+        <v>0.88672425</v>
       </c>
       <c r="D23" t="n">
-        <v>0.911308</v>
+        <v>0.908826</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6601315</v>
+        <v>0.6576885</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4233375</v>
+        <v>4.4226345</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78372875</v>
+        <v>2.78197475</v>
       </c>
       <c r="H23" t="n">
-        <v>1.707734</v>
+        <v>1.703137</v>
       </c>
       <c r="I23" t="n">
-        <v>4.863267</v>
+        <v>4.861974</v>
       </c>
       <c r="J23" t="n">
-        <v>2.496508833333333</v>
+        <v>2.494071833333333</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.155741</v>
       </c>
     </row>
     <row r="24">
@@ -1234,9 +1291,7 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1424.707369</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>684.892696</v>
       </c>
@@ -1261,6 +1316,9 @@
       <c r="J24" t="n">
         <v>713.520144</v>
       </c>
+      <c r="K24" t="n">
+        <v>2092.159241</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1269,31 +1327,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>611.61776</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>420.723517</v>
+        <v>407.11546</v>
       </c>
       <c r="D25" t="n">
-        <v>309.29352</v>
+        <v>273.534399</v>
       </c>
       <c r="E25" t="n">
-        <v>527.454688</v>
+        <v>289.806209</v>
       </c>
       <c r="F25" t="n">
-        <v>285.874826</v>
+        <v>175.548515</v>
       </c>
       <c r="G25" t="n">
-        <v>324.489912</v>
+        <v>256.906976</v>
       </c>
       <c r="H25" t="n">
-        <v>368.164356</v>
+        <v>310.857097</v>
       </c>
       <c r="I25" t="n">
-        <v>271.009081</v>
+        <v>236.320722</v>
       </c>
       <c r="J25" t="n">
-        <v>414.965774</v>
+        <v>394.543233</v>
+      </c>
+      <c r="K25" t="n">
+        <v>490.41665</v>
       </c>
     </row>
     <row r="26">
@@ -1302,9 +1363,7 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>945.357403</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>495.909465</v>
       </c>
@@ -1329,6 +1388,9 @@
       <c r="J26" t="n">
         <v>833.4631900000001</v>
       </c>
+      <c r="K26" t="n">
+        <v>1101.311138</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1337,31 +1399,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2105.539015</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1502.922943</v>
+        <v>1269.439591</v>
       </c>
       <c r="D27" t="n">
-        <v>1448.419276</v>
+        <v>1216.979049</v>
       </c>
       <c r="E27" t="n">
-        <v>2137.2157825</v>
+        <v>1804.0845305</v>
       </c>
       <c r="F27" t="n">
-        <v>1431.344338</v>
+        <v>1129.581249</v>
       </c>
       <c r="G27" t="n">
-        <v>2011.716407</v>
+        <v>1616.985349</v>
       </c>
       <c r="H27" t="n">
-        <v>3199.267601</v>
+        <v>2955.059518</v>
       </c>
       <c r="I27" t="n">
-        <v>1435.937866</v>
+        <v>1213.347561</v>
       </c>
       <c r="J27" t="n">
-        <v>2005.650755</v>
+        <v>1704.726893</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2408.654783</v>
       </c>
     </row>
     <row r="28">
@@ -1370,9 +1435,7 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>2019.450246</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>1355.427307</v>
       </c>
@@ -1397,6 +1460,9 @@
       <c r="J28" t="n">
         <v>3556.848112</v>
       </c>
+      <c r="K28" t="n">
+        <v>2011.55405</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1405,31 +1471,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3996.392377</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1900.92332</v>
+        <v>1900.906818</v>
       </c>
       <c r="D29" t="n">
-        <v>1874.387937</v>
+        <v>1874.384192</v>
       </c>
       <c r="E29" t="n">
-        <v>2796.918538</v>
+        <v>2796.915373</v>
       </c>
       <c r="F29" t="n">
-        <v>1159.083804</v>
+        <v>1159.069364</v>
       </c>
       <c r="G29" t="n">
-        <v>1204.082537</v>
+        <v>1204.070588</v>
       </c>
       <c r="H29" t="n">
-        <v>1371.787172</v>
+        <v>1371.781209</v>
       </c>
       <c r="I29" t="n">
-        <v>1143.675889666667</v>
+        <v>1143.663769666667</v>
       </c>
       <c r="J29" t="n">
-        <v>1170.92360425</v>
+        <v>1175.57039225</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1745.208608</v>
       </c>
     </row>
     <row r="30">
@@ -1438,9 +1507,7 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1960.267031</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>1169.464009</v>
       </c>
@@ -1465,6 +1532,9 @@
       <c r="J30" t="n">
         <v>716.628303</v>
       </c>
+      <c r="K30" t="n">
+        <v>1391.651459</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1473,31 +1543,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>129.094295</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>97.96146</v>
+        <v>32.627476</v>
       </c>
       <c r="D31" t="n">
-        <v>181.541844</v>
+        <v>29.725872</v>
       </c>
       <c r="E31" t="n">
-        <v>309.229901</v>
+        <v>29.49059</v>
       </c>
       <c r="F31" t="n">
-        <v>337.289111</v>
+        <v>21.24001</v>
       </c>
       <c r="G31" t="n">
-        <v>1395.007583</v>
+        <v>27.393318</v>
       </c>
       <c r="H31" t="n">
-        <v>981.782769</v>
+        <v>65.72085</v>
       </c>
       <c r="I31" t="n">
-        <v>300.275675</v>
+        <v>35.226386</v>
       </c>
       <c r="J31" t="n">
-        <v>573.402185</v>
+        <v>29.874389</v>
+      </c>
+      <c r="K31" t="n">
+        <v>35.231929</v>
       </c>
     </row>
     <row r="32">
@@ -1506,9 +1579,7 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>15815.715517</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>3706.578267</v>
       </c>
@@ -1533,6 +1604,9 @@
       <c r="J32" t="n">
         <v>1634.098594</v>
       </c>
+      <c r="K32" t="n">
+        <v>2034.884553</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1541,31 +1615,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3729.761142</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>3265.066779</v>
+        <v>3256.66628</v>
       </c>
       <c r="D33" t="n">
-        <v>3576.81368125</v>
+        <v>3562.92841725</v>
       </c>
       <c r="E33" t="n">
-        <v>4231.049639</v>
+        <v>4224.962546</v>
       </c>
       <c r="F33" t="n">
-        <v>3152.723616083334</v>
+        <v>3147.187418083333</v>
       </c>
       <c r="G33" t="n">
-        <v>2054.422690333333</v>
+        <v>2041.066760333333</v>
       </c>
       <c r="H33" t="n">
-        <v>3157.254720666666</v>
+        <v>3145.790868666666</v>
       </c>
       <c r="I33" t="n">
-        <v>4047.266548166667</v>
+        <v>4039.925452166667</v>
       </c>
       <c r="J33" t="n">
-        <v>2730.1196475</v>
+        <v>2719.0837115</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2342.042780416667</v>
       </c>
     </row>
     <row r="34">
@@ -1574,9 +1651,7 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>24942.40761725</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>14640.291383</v>
       </c>
@@ -1601,6 +1676,9 @@
       <c r="J34" t="n">
         <v>18001.843649</v>
       </c>
+      <c r="K34" t="n">
+        <v>29683.7204415</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1608,9 +1686,7 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1496.018729333333</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>891.2038680000001</v>
       </c>
@@ -1635,6 +1711,9 @@
       <c r="J35" t="n">
         <v>932.818224</v>
       </c>
+      <c r="K35" t="n">
+        <v>1830.670428</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1642,9 +1721,7 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>6374.47776325</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>2168.962247</v>
       </c>
@@ -1669,6 +1746,9 @@
       <c r="J36" t="n">
         <v>2036.013433</v>
       </c>
+      <c r="K36" t="n">
+        <v>3601.325495</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1676,9 +1756,7 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>12481.445979</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>9107.543382</v>
       </c>
@@ -1703,6 +1781,9 @@
       <c r="J37" t="n">
         <v>12181.591653</v>
       </c>
+      <c r="K37" t="n">
+        <v>17010.454022</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1710,9 +1791,7 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1908.507394</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>460.152903</v>
       </c>
@@ -1737,6 +1816,9 @@
       <c r="J38" t="n">
         <v>514.825294</v>
       </c>
+      <c r="K38" t="n">
+        <v>678.614001</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1744,9 +1826,7 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>11181.0071735</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>6035.205858</v>
       </c>
@@ -1771,6 +1851,9 @@
       <c r="J39" t="n">
         <v>3802.02835</v>
       </c>
+      <c r="K39" t="n">
+        <v>5064.0600025</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1778,9 +1861,7 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>31220.241828</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>33189.695159</v>
       </c>
@@ -1805,6 +1886,9 @@
       <c r="J40" t="n">
         <v>109528.620721</v>
       </c>
+      <c r="K40" t="n">
+        <v>93985.398543</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1813,31 +1897,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>180.114267</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>103.731344</v>
+        <v>103.471182</v>
       </c>
       <c r="D41" t="n">
-        <v>151.63697</v>
+        <v>151.056149</v>
       </c>
       <c r="E41" t="n">
-        <v>128.294805</v>
+        <v>126.565595</v>
       </c>
       <c r="F41" t="n">
-        <v>193.129646</v>
+        <v>191.907869</v>
       </c>
       <c r="G41" t="n">
-        <v>222.40962075</v>
+        <v>222.13095675</v>
       </c>
       <c r="H41" t="n">
-        <v>156.903562</v>
+        <v>156.416678</v>
       </c>
       <c r="I41" t="n">
-        <v>164.3006155</v>
+        <v>163.7585305</v>
       </c>
       <c r="J41" t="n">
-        <v>143.66717925</v>
+        <v>143.28460225</v>
+      </c>
+      <c r="K41" t="n">
+        <v>154.808428</v>
       </c>
     </row>
     <row r="42">
@@ -1846,9 +1933,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>82015.249931</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>40610.057207</v>
       </c>
@@ -1873,6 +1958,9 @@
       <c r="J42" t="n">
         <v>44356.231581</v>
       </c>
+      <c r="K42" t="n">
+        <v>51876.083843</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1880,9 +1968,7 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>370.468524</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>183.066952</v>
       </c>
@@ -1907,6 +1993,9 @@
       <c r="J43" t="n">
         <v>153.965149</v>
       </c>
+      <c r="K43" t="n">
+        <v>216.040869</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1915,31 +2004,34 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>979.949574</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1650.056964</v>
+        <v>1650.007821</v>
       </c>
       <c r="D44" t="n">
-        <v>550.6252469999999</v>
+        <v>550.60604</v>
       </c>
       <c r="E44" t="n">
-        <v>568.934852</v>
+        <v>568.92696</v>
       </c>
       <c r="F44" t="n">
-        <v>572.670523</v>
+        <v>572.650055</v>
       </c>
       <c r="G44" t="n">
-        <v>273.551237</v>
+        <v>273.543601</v>
       </c>
       <c r="H44" t="n">
-        <v>406.0494</v>
+        <v>406.039514</v>
       </c>
       <c r="I44" t="n">
-        <v>192.38958</v>
+        <v>192.384708</v>
       </c>
       <c r="J44" t="n">
-        <v>159.333061</v>
+        <v>159.32824</v>
+      </c>
+      <c r="K44" t="n">
+        <v>305.274184</v>
       </c>
     </row>
     <row r="45">
@@ -1948,9 +2040,7 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>566.388916</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>742.989564</v>
       </c>
@@ -1975,6 +2065,9 @@
       <c r="J45" t="n">
         <v>1163.125599</v>
       </c>
+      <c r="K45" t="n">
+        <v>1017.672095</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1982,9 +2075,7 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0.008626</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>0.036967</v>
       </c>
@@ -2009,6 +2100,9 @@
       <c r="J46" t="n">
         <v>0.002401</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.008321</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2017,31 +2111,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5585.535666</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1995.447133</v>
+        <v>1995.445981</v>
       </c>
       <c r="D47" t="n">
-        <v>3227.005332</v>
+        <v>3227.004494</v>
       </c>
       <c r="E47" t="n">
-        <v>2285.728811</v>
+        <v>2285.727801</v>
       </c>
       <c r="F47" t="n">
-        <v>2768.183649</v>
+        <v>2768.183273</v>
       </c>
       <c r="G47" t="n">
-        <v>2160.042912</v>
+        <v>2160.041587</v>
       </c>
       <c r="H47" t="n">
-        <v>2537.16588</v>
+        <v>2537.164485</v>
       </c>
       <c r="I47" t="n">
-        <v>1944.562274</v>
+        <v>1944.561653</v>
       </c>
       <c r="J47" t="n">
-        <v>2607.919254</v>
+        <v>2607.917951</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3108.6326</v>
       </c>
     </row>
     <row r="48">
@@ -2050,9 +2147,7 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>103.919057</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>71.276222</v>
       </c>
@@ -2077,6 +2172,9 @@
       <c r="J48" t="n">
         <v>102.306466</v>
       </c>
+      <c r="K48" t="n">
+        <v>118.380095</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -2085,31 +2183,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>11881.843667</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>12517.186223</v>
+        <v>12511.16686</v>
       </c>
       <c r="D49" t="n">
-        <v>10630.8634</v>
+        <v>10623.52561</v>
       </c>
       <c r="E49" t="n">
-        <v>12588.924363</v>
+        <v>12579.584169</v>
       </c>
       <c r="F49" t="n">
-        <v>6628.107666</v>
+        <v>6620.155791</v>
       </c>
       <c r="G49" t="n">
-        <v>7771.289255</v>
+        <v>7766.043802</v>
       </c>
       <c r="H49" t="n">
-        <v>10297.83788</v>
+        <v>10288.97072</v>
       </c>
       <c r="I49" t="n">
-        <v>9437.364121000001</v>
+        <v>9431.7981</v>
       </c>
       <c r="J49" t="n">
-        <v>8742.657853999999</v>
+        <v>8734.995352</v>
+      </c>
+      <c r="K49" t="n">
+        <v>7855.820373</v>
       </c>
     </row>
     <row r="50">
@@ -2118,9 +2219,7 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1558.220295</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>647.096954</v>
       </c>
@@ -2145,6 +2244,9 @@
       <c r="J50" t="n">
         <v>664.655217</v>
       </c>
+      <c r="K50" t="n">
+        <v>1014.851735</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2152,9 +2254,7 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.029542</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0.017833</v>
       </c>
@@ -2179,6 +2279,9 @@
       <c r="J51" t="n">
         <v>0.014062</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.047371</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -2187,31 +2290,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>20818.586488</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>9077.309005999999</v>
+        <v>9074.235629000001</v>
       </c>
       <c r="D52" t="n">
-        <v>8148.055404666667</v>
+        <v>8146.462402666667</v>
       </c>
       <c r="E52" t="n">
-        <v>9224.021632</v>
+        <v>9221.820274</v>
       </c>
       <c r="F52" t="n">
-        <v>5732.684626</v>
+        <v>5729.825798</v>
       </c>
       <c r="G52" t="n">
-        <v>10246.93227</v>
+        <v>10244.585728</v>
       </c>
       <c r="H52" t="n">
-        <v>8616.418030999999</v>
+        <v>8613.641496</v>
       </c>
       <c r="I52" t="n">
-        <v>10196.150336</v>
+        <v>10195.288084</v>
       </c>
       <c r="J52" t="n">
-        <v>6597.266704</v>
+        <v>6593.543432</v>
+      </c>
+      <c r="K52" t="n">
+        <v>7936.555242</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2327,34 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3298.6393515</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1901.163406</v>
+        <v>1707.55237</v>
       </c>
       <c r="D53" t="n">
-        <v>2784.567429</v>
+        <v>2637.925009</v>
       </c>
       <c r="E53" t="n">
-        <v>2840.801426</v>
+        <v>2583.258658</v>
       </c>
       <c r="F53" t="n">
-        <v>2553.3653815</v>
+        <v>2360.7903395</v>
       </c>
       <c r="G53" t="n">
-        <v>3519.341702</v>
+        <v>3191.447185</v>
       </c>
       <c r="H53" t="n">
-        <v>6191.425248333333</v>
+        <v>5917.913341333333</v>
       </c>
       <c r="I53" t="n">
-        <v>7155.879135</v>
+        <v>6990.934332</v>
       </c>
       <c r="J53" t="n">
-        <v>3091.901302</v>
+        <v>2965.845225</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2978.61840275</v>
       </c>
     </row>
     <row r="54">
@@ -2254,9 +2363,7 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>602.596304</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>251.282962</v>
       </c>
@@ -2281,6 +2388,9 @@
       <c r="J54" t="n">
         <v>627.997406</v>
       </c>
+      <c r="K54" t="n">
+        <v>242.656285</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -2288,9 +2398,7 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>4079.32611</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>1300.476742</v>
       </c>
@@ -2315,6 +2423,9 @@
       <c r="J55" t="n">
         <v>1458.3181</v>
       </c>
+      <c r="K55" t="n">
+        <v>1239.700787</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2322,9 +2433,7 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>14074.023657</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>10237.123019</v>
       </c>
@@ -2349,6 +2458,9 @@
       <c r="J56" t="n">
         <v>7151.438405</v>
       </c>
+      <c r="K56" t="n">
+        <v>13323.285339</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2357,31 +2469,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>288.648451</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>191.280322</v>
+        <v>183.95473</v>
       </c>
       <c r="D57" t="n">
-        <v>211.287875</v>
+        <v>201.213138</v>
       </c>
       <c r="E57" t="n">
-        <v>134.946384</v>
+        <v>125.917386</v>
       </c>
       <c r="F57" t="n">
-        <v>107.918206</v>
+        <v>95.368484</v>
       </c>
       <c r="G57" t="n">
-        <v>240.957821</v>
+        <v>222.084387</v>
       </c>
       <c r="H57" t="n">
-        <v>280.614387</v>
+        <v>235.81675</v>
       </c>
       <c r="I57" t="n">
-        <v>241.632148</v>
+        <v>220.541561</v>
       </c>
       <c r="J57" t="n">
-        <v>160.750781</v>
+        <v>149.284232</v>
+      </c>
+      <c r="K57" t="n">
+        <v>185.684977</v>
       </c>
     </row>
     <row r="58">
@@ -2390,9 +2505,7 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1.501269</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0.78407</v>
       </c>
@@ -2417,6 +2530,9 @@
       <c r="J58" t="n">
         <v>0.848656</v>
       </c>
+      <c r="K58" t="n">
+        <v>1.13421</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2424,9 +2540,7 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>5377.855906</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>3280.445867</v>
       </c>
@@ -2451,6 +2565,9 @@
       <c r="J59" t="n">
         <v>3278.903084</v>
       </c>
+      <c r="K59" t="n">
+        <v>2987.686914</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2459,31 +2576,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12445.301188</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>11352.946507</v>
+        <v>11352.935399</v>
       </c>
       <c r="D60" t="n">
-        <v>10163.667076</v>
+        <v>10163.660786</v>
       </c>
       <c r="E60" t="n">
-        <v>14283.112728</v>
+        <v>14283.10676</v>
       </c>
       <c r="F60" t="n">
-        <v>15702.55116</v>
+        <v>15702.547219</v>
       </c>
       <c r="G60" t="n">
-        <v>16339.630617</v>
+        <v>16339.62805</v>
       </c>
       <c r="H60" t="n">
-        <v>13990.739466</v>
+        <v>13990.733693</v>
       </c>
       <c r="I60" t="n">
-        <v>17015.629412</v>
+        <v>17015.623284</v>
       </c>
       <c r="J60" t="n">
-        <v>22387.334106</v>
+        <v>22387.325547</v>
+      </c>
+      <c r="K60" t="n">
+        <v>21582.233912</v>
       </c>
     </row>
     <row r="61">
@@ -2493,31 +2613,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3126.0001085</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>2465.182143</v>
+        <v>2465.170009</v>
       </c>
       <c r="D61" t="n">
-        <v>2654.157778</v>
+        <v>2654.139277</v>
       </c>
       <c r="E61" t="n">
-        <v>1915.343968333333</v>
+        <v>1915.313872333333</v>
       </c>
       <c r="F61" t="n">
-        <v>2833.24706325</v>
+        <v>2833.23200825</v>
       </c>
       <c r="G61" t="n">
-        <v>3220.483233</v>
+        <v>3220.471648</v>
       </c>
       <c r="H61" t="n">
-        <v>3455.685055</v>
+        <v>3455.670585</v>
       </c>
       <c r="I61" t="n">
-        <v>2850.61244775</v>
+        <v>2850.60360375</v>
       </c>
       <c r="J61" t="n">
-        <v>2993.695927</v>
+        <v>2993.6702</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2674.08266375</v>
       </c>
     </row>
     <row r="62">
@@ -2526,9 +2649,7 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>5528.695031</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>3758.237494</v>
       </c>
@@ -2553,6 +2674,9 @@
       <c r="J62" t="n">
         <v>5045.504785</v>
       </c>
+      <c r="K62" t="n">
+        <v>4618.943971</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2560,9 +2684,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>16705.506837</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>41270.985346</v>
       </c>
@@ -2587,6 +2709,9 @@
       <c r="J63" t="n">
         <v>39186.48104</v>
       </c>
+      <c r="K63" t="n">
+        <v>58947.997898</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2595,31 +2720,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2059.662455</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>639.320237</v>
+        <v>639.318904</v>
       </c>
       <c r="D64" t="n">
-        <v>932.27086</v>
+        <v>932.26991</v>
       </c>
       <c r="E64" t="n">
-        <v>894.284195</v>
+        <v>894.282873</v>
       </c>
       <c r="F64" t="n">
-        <v>672.670647</v>
+        <v>672.665497</v>
       </c>
       <c r="G64" t="n">
-        <v>822.513379</v>
+        <v>822.511974</v>
       </c>
       <c r="H64" t="n">
-        <v>808.75627</v>
+        <v>808.754942</v>
       </c>
       <c r="I64" t="n">
-        <v>729.3189609999999</v>
+        <v>729.317989</v>
       </c>
       <c r="J64" t="n">
-        <v>1690.981625</v>
+        <v>1707.520135</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1123.523207</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>115583.774439</v>
       </c>
       <c r="C2" t="n">
-        <v>90201.344881</v>
+        <v>88280.45979350001</v>
       </c>
       <c r="D2" t="n">
-        <v>115582.265165</v>
+        <v>85140.476152</v>
       </c>
       <c r="E2" t="n">
-        <v>88278.6996525</v>
+        <v>97469.493455</v>
       </c>
       <c r="F2" t="n">
-        <v>85139.044972</v>
+        <v>93023.65412000001</v>
       </c>
       <c r="G2" t="n">
-        <v>97468.551733</v>
+        <v>80100.52979</v>
       </c>
       <c r="H2" t="n">
-        <v>93022.766947</v>
+        <v>79486.70570525</v>
       </c>
       <c r="I2" t="n">
-        <v>80098.647251</v>
+        <v>129848.67474</v>
       </c>
       <c r="J2" t="n">
-        <v>79486.13153324999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>129847.636549</v>
+        <v>116164.155528</v>
       </c>
     </row>
     <row r="3">
@@ -529,34 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1442.069167</v>
       </c>
       <c r="C3" t="n">
-        <v>1717.374217</v>
+        <v>1293.691735</v>
       </c>
       <c r="D3" t="n">
-        <v>1442.051502</v>
+        <v>1051.289579</v>
       </c>
       <c r="E3" t="n">
-        <v>1293.682623</v>
+        <v>1205.972422</v>
       </c>
       <c r="F3" t="n">
-        <v>1051.276545</v>
+        <v>1376.309944</v>
       </c>
       <c r="G3" t="n">
-        <v>1205.963345</v>
+        <v>1788.730843</v>
       </c>
       <c r="H3" t="n">
-        <v>1376.303467</v>
+        <v>1316.92416</v>
       </c>
       <c r="I3" t="n">
-        <v>1788.712576</v>
+        <v>1865.378455</v>
       </c>
       <c r="J3" t="n">
-        <v>1316.899044</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1865.363933</v>
+        <v>1171.961645</v>
       </c>
     </row>
     <row r="4">
@@ -565,33 +554,32 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>226359.872253</v>
+      </c>
       <c r="C4" t="n">
-        <v>178538.931366</v>
+        <v>166179.907213</v>
       </c>
       <c r="D4" t="n">
-        <v>223594.517634</v>
+        <v>138946.48812</v>
       </c>
       <c r="E4" t="n">
-        <v>165402.902434</v>
+        <v>189646.737822</v>
       </c>
       <c r="F4" t="n">
-        <v>138499.150042</v>
+        <v>182760.686487</v>
       </c>
       <c r="G4" t="n">
-        <v>189359.179427</v>
+        <v>128660.880246</v>
       </c>
       <c r="H4" t="n">
-        <v>182345.333393</v>
+        <v>123539.16242</v>
       </c>
       <c r="I4" t="n">
-        <v>128106.303883</v>
+        <v>205333.707724</v>
       </c>
       <c r="J4" t="n">
-        <v>122579.80249</v>
-      </c>
-      <c r="K4" t="n">
-        <v>204717.298488</v>
+        <v>205533.21934</v>
       </c>
     </row>
     <row r="5">
@@ -600,33 +588,32 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1321.863769</v>
+      </c>
       <c r="C5" t="n">
-        <v>1237.090225</v>
+        <v>1185.034685</v>
       </c>
       <c r="D5" t="n">
-        <v>1321.863769</v>
+        <v>1327.895339</v>
       </c>
       <c r="E5" t="n">
-        <v>1185.034685</v>
+        <v>1707.386623</v>
       </c>
       <c r="F5" t="n">
-        <v>1327.895339</v>
+        <v>1902.962393</v>
       </c>
       <c r="G5" t="n">
-        <v>1707.386623</v>
+        <v>1122.586086</v>
       </c>
       <c r="H5" t="n">
-        <v>1902.962393</v>
+        <v>1601.886093</v>
       </c>
       <c r="I5" t="n">
-        <v>1122.586086</v>
+        <v>1716.223375</v>
       </c>
       <c r="J5" t="n">
-        <v>1601.886093</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1716.223375</v>
+        <v>1784.390789</v>
       </c>
     </row>
     <row r="6">
@@ -636,34 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>121821.817605</v>
       </c>
       <c r="C6" t="n">
-        <v>99702.83822600001</v>
+        <v>129515.847183</v>
       </c>
       <c r="D6" t="n">
-        <v>121821.815051</v>
+        <v>130648.847117</v>
       </c>
       <c r="E6" t="n">
-        <v>129515.845253</v>
+        <v>102906.419806</v>
       </c>
       <c r="F6" t="n">
-        <v>130648.846293</v>
+        <v>129641.407368</v>
       </c>
       <c r="G6" t="n">
-        <v>102906.416866</v>
+        <v>140476.595393</v>
       </c>
       <c r="H6" t="n">
-        <v>129641.404601</v>
+        <v>154082.840107</v>
       </c>
       <c r="I6" t="n">
-        <v>140476.592648</v>
+        <v>197491.603846</v>
       </c>
       <c r="J6" t="n">
-        <v>154082.837499</v>
-      </c>
-      <c r="K6" t="n">
-        <v>197491.588367</v>
+        <v>165285.893329</v>
       </c>
     </row>
     <row r="7">
@@ -673,34 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>22175.429716</v>
       </c>
       <c r="C7" t="n">
-        <v>20781.249811</v>
+        <v>13770.435178</v>
       </c>
       <c r="D7" t="n">
-        <v>22175.17617</v>
+        <v>10540.732272</v>
       </c>
       <c r="E7" t="n">
-        <v>13770.242891</v>
+        <v>13889.568317</v>
       </c>
       <c r="F7" t="n">
-        <v>10540.539311</v>
+        <v>13855.977711</v>
       </c>
       <c r="G7" t="n">
-        <v>13889.42986</v>
+        <v>20448.539832</v>
       </c>
       <c r="H7" t="n">
-        <v>13855.859454</v>
+        <v>15846.945404</v>
       </c>
       <c r="I7" t="n">
-        <v>20448.18439</v>
+        <v>24740.317784</v>
       </c>
       <c r="J7" t="n">
-        <v>15846.638001</v>
-      </c>
-      <c r="K7" t="n">
-        <v>24738.818616</v>
+        <v>25336.378851</v>
       </c>
     </row>
     <row r="8">
@@ -709,33 +690,32 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>9213.183336</v>
+      </c>
       <c r="C8" t="n">
-        <v>10613.63104</v>
+        <v>8165.319383</v>
       </c>
       <c r="D8" t="n">
-        <v>9213.183336</v>
+        <v>5236.54811</v>
       </c>
       <c r="E8" t="n">
-        <v>8165.319383</v>
+        <v>5028.359153</v>
       </c>
       <c r="F8" t="n">
-        <v>5236.54811</v>
+        <v>6200.80261</v>
       </c>
       <c r="G8" t="n">
-        <v>5028.359153</v>
+        <v>5956.565974</v>
       </c>
       <c r="H8" t="n">
-        <v>6200.80261</v>
+        <v>18678.998933</v>
       </c>
       <c r="I8" t="n">
-        <v>5956.565974</v>
+        <v>20069.059953</v>
       </c>
       <c r="J8" t="n">
-        <v>18678.998933</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20069.059953</v>
+        <v>13943.679809</v>
       </c>
     </row>
     <row r="9">
@@ -745,34 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>23907.352232</v>
       </c>
       <c r="C9" t="n">
-        <v>14982.787477</v>
+        <v>16164.352791</v>
       </c>
       <c r="D9" t="n">
-        <v>23907.350078</v>
+        <v>12877.494238</v>
       </c>
       <c r="E9" t="n">
-        <v>16164.351487</v>
+        <v>12170.44137225</v>
       </c>
       <c r="F9" t="n">
-        <v>12877.493172</v>
+        <v>28574.762822</v>
       </c>
       <c r="G9" t="n">
-        <v>12170.439475</v>
+        <v>20694.5899575</v>
       </c>
       <c r="H9" t="n">
-        <v>28574.761172</v>
+        <v>18024.656341</v>
       </c>
       <c r="I9" t="n">
-        <v>20694.5882835</v>
+        <v>20594.013322</v>
       </c>
       <c r="J9" t="n">
-        <v>18024.651983</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20594.009557</v>
+        <v>19539.969903</v>
       </c>
     </row>
     <row r="10">
@@ -782,34 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2505.415513</v>
       </c>
       <c r="C10" t="n">
-        <v>1728.444248666666</v>
+        <v>2014.82200825</v>
       </c>
       <c r="D10" t="n">
-        <v>2505.414117</v>
+        <v>1437.9102595</v>
       </c>
       <c r="E10" t="n">
-        <v>2014.81808325</v>
+        <v>1691.566047</v>
       </c>
       <c r="F10" t="n">
-        <v>1437.9092845</v>
+        <v>1739.207265</v>
       </c>
       <c r="G10" t="n">
-        <v>1691.564228</v>
+        <v>2361.4214135</v>
       </c>
       <c r="H10" t="n">
-        <v>1739.205435</v>
+        <v>2507.015691083333</v>
       </c>
       <c r="I10" t="n">
-        <v>2361.4190265</v>
+        <v>2915.59794075</v>
       </c>
       <c r="J10" t="n">
-        <v>2507.013628083334</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2915.59429875</v>
+        <v>2010.5327855</v>
       </c>
     </row>
     <row r="11">
@@ -819,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4536.195576666667</v>
       </c>
       <c r="C11" t="n">
-        <v>5174.810084</v>
+        <v>6391.552234</v>
       </c>
       <c r="D11" t="n">
-        <v>4536.177807666667</v>
+        <v>5027.901959</v>
       </c>
       <c r="E11" t="n">
-        <v>6391.53562</v>
+        <v>4287.608381</v>
       </c>
       <c r="F11" t="n">
-        <v>5027.892198</v>
+        <v>5741.1415725</v>
       </c>
       <c r="G11" t="n">
-        <v>4287.599429</v>
+        <v>5931.790813</v>
       </c>
       <c r="H11" t="n">
-        <v>5741.1294755</v>
+        <v>5709.634427</v>
       </c>
       <c r="I11" t="n">
-        <v>5931.781489</v>
+        <v>8910.522211</v>
       </c>
       <c r="J11" t="n">
-        <v>5709.611439</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8910.424891000001</v>
+        <v>5980.956098</v>
       </c>
     </row>
     <row r="12">
@@ -856,34 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>14287.592061</v>
       </c>
       <c r="C12" t="n">
-        <v>8811.598866</v>
+        <v>12754.3151</v>
       </c>
       <c r="D12" t="n">
-        <v>14269.15132</v>
+        <v>13061.21415</v>
       </c>
       <c r="E12" t="n">
-        <v>12736.20801</v>
+        <v>11174.18828</v>
       </c>
       <c r="F12" t="n">
-        <v>13045.659288</v>
+        <v>13638.882629</v>
       </c>
       <c r="G12" t="n">
-        <v>11155.583009</v>
+        <v>13065.508176</v>
       </c>
       <c r="H12" t="n">
-        <v>13603.614018</v>
+        <v>13474.480942</v>
       </c>
       <c r="I12" t="n">
-        <v>13046.164949</v>
+        <v>20011.949809</v>
       </c>
       <c r="J12" t="n">
-        <v>13450.578291</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19989.466924</v>
+        <v>14586.43468</v>
       </c>
     </row>
     <row r="13">
@@ -892,33 +860,32 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>5209.950112</v>
+      </c>
       <c r="C13" t="n">
-        <v>2700.539033</v>
+        <v>5233.847716</v>
       </c>
       <c r="D13" t="n">
-        <v>5207.91587</v>
+        <v>3371.427526</v>
       </c>
       <c r="E13" t="n">
-        <v>5232.44427</v>
+        <v>2394.061638</v>
       </c>
       <c r="F13" t="n">
-        <v>3371.054838</v>
+        <v>4286.652275</v>
       </c>
       <c r="G13" t="n">
-        <v>2392.600297</v>
+        <v>2976.017692</v>
       </c>
       <c r="H13" t="n">
-        <v>4281.926355</v>
+        <v>3786.824192</v>
       </c>
       <c r="I13" t="n">
-        <v>2975.120135</v>
+        <v>4021.459276</v>
       </c>
       <c r="J13" t="n">
-        <v>3785.307081</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4020.392913</v>
+        <v>7703.003085</v>
       </c>
     </row>
     <row r="14">
@@ -928,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>13071.459356</v>
       </c>
       <c r="C14" t="n">
-        <v>13743.74672</v>
+        <v>11120.031796</v>
       </c>
       <c r="D14" t="n">
-        <v>13063.626124</v>
+        <v>14305.724936</v>
       </c>
       <c r="E14" t="n">
-        <v>11114.79322</v>
+        <v>8735.041053249999</v>
       </c>
       <c r="F14" t="n">
-        <v>14301.814538</v>
+        <v>9585.149552999999</v>
       </c>
       <c r="G14" t="n">
-        <v>8729.909638249999</v>
+        <v>6695.3773</v>
       </c>
       <c r="H14" t="n">
-        <v>9580.546229</v>
+        <v>6646.674439</v>
       </c>
       <c r="I14" t="n">
-        <v>6692.928605</v>
+        <v>9487.406014</v>
       </c>
       <c r="J14" t="n">
-        <v>6643.835136</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9484.962056</v>
+        <v>9178.032263999999</v>
       </c>
     </row>
     <row r="15">
@@ -965,34 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>30247.363515</v>
       </c>
       <c r="C15" t="n">
-        <v>25753.415463</v>
+        <v>29527.568526</v>
       </c>
       <c r="D15" t="n">
-        <v>30246.267866</v>
+        <v>35684.540649</v>
       </c>
       <c r="E15" t="n">
-        <v>29526.550866</v>
+        <v>33341.832677</v>
       </c>
       <c r="F15" t="n">
-        <v>35682.909805</v>
+        <v>24770.886724</v>
       </c>
       <c r="G15" t="n">
-        <v>33334.868582</v>
+        <v>21506.286768</v>
       </c>
       <c r="H15" t="n">
-        <v>24766.553877</v>
+        <v>33362.212799</v>
       </c>
       <c r="I15" t="n">
-        <v>21497.169701</v>
+        <v>24153.683866</v>
       </c>
       <c r="J15" t="n">
-        <v>33351.716219</v>
-      </c>
-      <c r="K15" t="n">
-        <v>24129.937751</v>
+        <v>43959.585443</v>
       </c>
     </row>
     <row r="16">
@@ -1002,34 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>23392.141195</v>
       </c>
       <c r="C16" t="n">
-        <v>24590.739754</v>
+        <v>28437.085444</v>
       </c>
       <c r="D16" t="n">
-        <v>23392.100511</v>
+        <v>18387.097511</v>
       </c>
       <c r="E16" t="n">
-        <v>28437.056461</v>
+        <v>18772.393694</v>
       </c>
       <c r="F16" t="n">
-        <v>18387.025013</v>
+        <v>23991.340089</v>
       </c>
       <c r="G16" t="n">
-        <v>18772.355641</v>
+        <v>16183.796468</v>
       </c>
       <c r="H16" t="n">
-        <v>23991.291969</v>
+        <v>20919.253641</v>
       </c>
       <c r="I16" t="n">
-        <v>16183.76353</v>
+        <v>21320.266226</v>
       </c>
       <c r="J16" t="n">
-        <v>20919.215662</v>
-      </c>
-      <c r="K16" t="n">
-        <v>21320.174174</v>
+        <v>17242.611229</v>
       </c>
     </row>
     <row r="17">
@@ -1039,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>70058.288533</v>
       </c>
       <c r="C17" t="n">
-        <v>53935.30093</v>
+        <v>44988.016253</v>
       </c>
       <c r="D17" t="n">
-        <v>70058.26046999999</v>
+        <v>30953.730487</v>
       </c>
       <c r="E17" t="n">
-        <v>44988.00722</v>
+        <v>28733.570505</v>
       </c>
       <c r="F17" t="n">
-        <v>30953.724456</v>
+        <v>38078.11666</v>
       </c>
       <c r="G17" t="n">
-        <v>28733.552849</v>
+        <v>24953.722837</v>
       </c>
       <c r="H17" t="n">
-        <v>38078.097503</v>
+        <v>41336.354249</v>
       </c>
       <c r="I17" t="n">
-        <v>24953.716725</v>
+        <v>46582.502105</v>
       </c>
       <c r="J17" t="n">
-        <v>41336.337735</v>
-      </c>
-      <c r="K17" t="n">
-        <v>46582.468537</v>
+        <v>44569.088771</v>
       </c>
     </row>
     <row r="18">
@@ -1075,33 +1030,32 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1189.748739</v>
+      </c>
       <c r="C18" t="n">
-        <v>843.593843</v>
+        <v>1567.479099</v>
       </c>
       <c r="D18" t="n">
-        <v>1189.748739</v>
+        <v>1374.791349</v>
       </c>
       <c r="E18" t="n">
-        <v>1567.479099</v>
+        <v>931.905278</v>
       </c>
       <c r="F18" t="n">
-        <v>1374.791349</v>
+        <v>1551.429113</v>
       </c>
       <c r="G18" t="n">
-        <v>931.905278</v>
+        <v>916.4080719999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1551.429113</v>
+        <v>1259.522176</v>
       </c>
       <c r="I18" t="n">
-        <v>916.4080719999999</v>
+        <v>2058.870186</v>
       </c>
       <c r="J18" t="n">
-        <v>1259.522176</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2058.870186</v>
+        <v>1142.857343</v>
       </c>
     </row>
     <row r="19">
@@ -1110,33 +1064,32 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>182.038654</v>
+      </c>
       <c r="C19" t="n">
-        <v>315.535051</v>
+        <v>110.671611</v>
       </c>
       <c r="D19" t="n">
-        <v>182.038654</v>
+        <v>85.07476275</v>
       </c>
       <c r="E19" t="n">
-        <v>110.671611</v>
+        <v>226.0066173333333</v>
       </c>
       <c r="F19" t="n">
-        <v>85.07476275</v>
+        <v>157.437316</v>
       </c>
       <c r="G19" t="n">
-        <v>226.0066173333333</v>
+        <v>90.02030033333332</v>
       </c>
       <c r="H19" t="n">
-        <v>157.437316</v>
+        <v>86.055667</v>
       </c>
       <c r="I19" t="n">
-        <v>90.02030033333332</v>
+        <v>94.680183</v>
       </c>
       <c r="J19" t="n">
-        <v>86.055667</v>
-      </c>
-      <c r="K19" t="n">
-        <v>94.680183</v>
+        <v>102.442166</v>
       </c>
     </row>
     <row r="20">
@@ -1145,33 +1098,32 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>32619.344675</v>
+      </c>
       <c r="C20" t="n">
-        <v>35044.727771</v>
+        <v>18556.167825</v>
       </c>
       <c r="D20" t="n">
-        <v>32619.344675</v>
+        <v>17169.781569</v>
       </c>
       <c r="E20" t="n">
-        <v>18556.167825</v>
+        <v>26765.247924</v>
       </c>
       <c r="F20" t="n">
-        <v>17169.781569</v>
+        <v>21132.136662</v>
       </c>
       <c r="G20" t="n">
-        <v>26765.247924</v>
+        <v>11587.069143</v>
       </c>
       <c r="H20" t="n">
-        <v>21132.136662</v>
+        <v>11464.949012</v>
       </c>
       <c r="I20" t="n">
-        <v>11587.069143</v>
+        <v>35323.290674</v>
       </c>
       <c r="J20" t="n">
-        <v>11464.949012</v>
-      </c>
-      <c r="K20" t="n">
-        <v>35323.290674</v>
+        <v>30712.336311</v>
       </c>
     </row>
     <row r="21">
@@ -1181,34 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3504.671797</v>
       </c>
       <c r="C21" t="n">
-        <v>3741.800574</v>
+        <v>3139.560877</v>
       </c>
       <c r="D21" t="n">
-        <v>3504.655549</v>
+        <v>3318.479694</v>
       </c>
       <c r="E21" t="n">
-        <v>3139.555335</v>
+        <v>5802.953388</v>
       </c>
       <c r="F21" t="n">
-        <v>3318.472302</v>
+        <v>3962.280094</v>
       </c>
       <c r="G21" t="n">
-        <v>5802.946135</v>
+        <v>3170.634716</v>
       </c>
       <c r="H21" t="n">
-        <v>3962.276966</v>
+        <v>3466.111153</v>
       </c>
       <c r="I21" t="n">
-        <v>3170.626323</v>
+        <v>3968.727804</v>
       </c>
       <c r="J21" t="n">
-        <v>3466.105076</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3968.711627</v>
+        <v>4713.418488</v>
       </c>
     </row>
     <row r="22">
@@ -1218,34 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>636.4326583333333</v>
       </c>
       <c r="C22" t="n">
-        <v>162.87271725</v>
+        <v>332.069325</v>
       </c>
       <c r="D22" t="n">
-        <v>636.4310123333332</v>
+        <v>284.626499</v>
       </c>
       <c r="E22" t="n">
-        <v>332.06855</v>
+        <v>234.591797</v>
       </c>
       <c r="F22" t="n">
-        <v>284.626257</v>
+        <v>213.95378</v>
       </c>
       <c r="G22" t="n">
-        <v>234.59035</v>
+        <v>146.3468013333333</v>
       </c>
       <c r="H22" t="n">
-        <v>213.95212</v>
+        <v>140.418245</v>
       </c>
       <c r="I22" t="n">
-        <v>146.3349263333334</v>
+        <v>213.065646</v>
       </c>
       <c r="J22" t="n">
-        <v>140.41194</v>
-      </c>
-      <c r="K22" t="n">
-        <v>213.064699</v>
+        <v>136.491058</v>
       </c>
     </row>
     <row r="23">
@@ -1255,34 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.911308</v>
       </c>
       <c r="C23" t="n">
-        <v>0.88672425</v>
+        <v>0.6601315</v>
       </c>
       <c r="D23" t="n">
-        <v>0.908826</v>
+        <v>4.4233375</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6576885</v>
+        <v>2.78372875</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4226345</v>
+        <v>1.707734</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78197475</v>
+        <v>4.863267</v>
       </c>
       <c r="H23" t="n">
-        <v>1.703137</v>
+        <v>2.496508833333333</v>
       </c>
       <c r="I23" t="n">
-        <v>4.861974</v>
+        <v>1.159543</v>
       </c>
       <c r="J23" t="n">
-        <v>2.494071833333333</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.155741</v>
+        <v>1.22882325</v>
       </c>
     </row>
     <row r="24">
@@ -1291,33 +1234,32 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>873.041337</v>
+      </c>
       <c r="C24" t="n">
-        <v>684.892696</v>
+        <v>798.4179339999999</v>
       </c>
       <c r="D24" t="n">
-        <v>873.041337</v>
+        <v>579.415634</v>
       </c>
       <c r="E24" t="n">
-        <v>798.4179339999999</v>
+        <v>881.8031559999999</v>
       </c>
       <c r="F24" t="n">
-        <v>579.415634</v>
+        <v>740.897229</v>
       </c>
       <c r="G24" t="n">
-        <v>881.8031559999999</v>
+        <v>612.1953099999999</v>
       </c>
       <c r="H24" t="n">
-        <v>740.897229</v>
+        <v>713.520144</v>
       </c>
       <c r="I24" t="n">
-        <v>612.1953099999999</v>
+        <v>2092.159241</v>
       </c>
       <c r="J24" t="n">
-        <v>713.520144</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2092.159241</v>
+        <v>1392.909789</v>
       </c>
     </row>
     <row r="25">
@@ -1327,34 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>309.29352</v>
       </c>
       <c r="C25" t="n">
-        <v>407.11546</v>
+        <v>527.454688</v>
       </c>
       <c r="D25" t="n">
-        <v>273.534399</v>
+        <v>285.874826</v>
       </c>
       <c r="E25" t="n">
-        <v>289.806209</v>
+        <v>324.489912</v>
       </c>
       <c r="F25" t="n">
-        <v>175.548515</v>
+        <v>368.164356</v>
       </c>
       <c r="G25" t="n">
-        <v>256.906976</v>
+        <v>271.009081</v>
       </c>
       <c r="H25" t="n">
-        <v>310.857097</v>
+        <v>414.965774</v>
       </c>
       <c r="I25" t="n">
-        <v>236.320722</v>
+        <v>545.1641</v>
       </c>
       <c r="J25" t="n">
-        <v>394.543233</v>
-      </c>
-      <c r="K25" t="n">
-        <v>490.41665</v>
+        <v>283.950176</v>
       </c>
     </row>
     <row r="26">
@@ -1363,33 +1302,32 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>972.210448</v>
+      </c>
       <c r="C26" t="n">
-        <v>495.909465</v>
+        <v>3770.951635</v>
       </c>
       <c r="D26" t="n">
-        <v>972.210448</v>
+        <v>1284.573526</v>
       </c>
       <c r="E26" t="n">
-        <v>3770.951635</v>
+        <v>1171.957497</v>
       </c>
       <c r="F26" t="n">
-        <v>1284.573526</v>
+        <v>2992.647381</v>
       </c>
       <c r="G26" t="n">
-        <v>1171.957497</v>
+        <v>1857.383228</v>
       </c>
       <c r="H26" t="n">
-        <v>2992.647381</v>
+        <v>833.4631900000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1857.383228</v>
+        <v>1101.311138</v>
       </c>
       <c r="J26" t="n">
-        <v>833.4631900000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1101.311138</v>
+        <v>940.165023</v>
       </c>
     </row>
     <row r="27">
@@ -1399,34 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1448.419276</v>
       </c>
       <c r="C27" t="n">
-        <v>1269.439591</v>
+        <v>2137.2157825</v>
       </c>
       <c r="D27" t="n">
-        <v>1216.979049</v>
+        <v>1431.344338</v>
       </c>
       <c r="E27" t="n">
-        <v>1804.0845305</v>
+        <v>2011.716407</v>
       </c>
       <c r="F27" t="n">
-        <v>1129.581249</v>
+        <v>3199.267601</v>
       </c>
       <c r="G27" t="n">
-        <v>1616.985349</v>
+        <v>1435.937866</v>
       </c>
       <c r="H27" t="n">
-        <v>2955.059518</v>
+        <v>2005.650755</v>
       </c>
       <c r="I27" t="n">
-        <v>1213.347561</v>
+        <v>2768.716692</v>
       </c>
       <c r="J27" t="n">
-        <v>1704.726893</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2408.654783</v>
+        <v>3171.539994</v>
       </c>
     </row>
     <row r="28">
@@ -1435,33 +1370,32 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1444.859941</v>
+      </c>
       <c r="C28" t="n">
-        <v>1355.427307</v>
+        <v>1127.132142</v>
       </c>
       <c r="D28" t="n">
-        <v>1444.859941</v>
+        <v>953.2518679999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1127.132142</v>
+        <v>3835.176519</v>
       </c>
       <c r="F28" t="n">
-        <v>953.2518679999999</v>
+        <v>3658.626385</v>
       </c>
       <c r="G28" t="n">
-        <v>3835.176519</v>
+        <v>2593.799925</v>
       </c>
       <c r="H28" t="n">
-        <v>3658.626385</v>
+        <v>3556.848112</v>
       </c>
       <c r="I28" t="n">
-        <v>2593.799925</v>
+        <v>2011.55405</v>
       </c>
       <c r="J28" t="n">
-        <v>3556.848112</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2011.55405</v>
+        <v>2430.059817</v>
       </c>
     </row>
     <row r="29">
@@ -1471,34 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1874.387937</v>
       </c>
       <c r="C29" t="n">
-        <v>1900.906818</v>
+        <v>2796.918538</v>
       </c>
       <c r="D29" t="n">
-        <v>1874.384192</v>
+        <v>1159.083804</v>
       </c>
       <c r="E29" t="n">
-        <v>2796.915373</v>
+        <v>1204.082537</v>
       </c>
       <c r="F29" t="n">
-        <v>1159.069364</v>
+        <v>1371.787172</v>
       </c>
       <c r="G29" t="n">
-        <v>1204.070588</v>
+        <v>1143.675889666667</v>
       </c>
       <c r="H29" t="n">
-        <v>1371.781209</v>
+        <v>1175.57370525</v>
       </c>
       <c r="I29" t="n">
-        <v>1143.663769666667</v>
+        <v>1745.240304</v>
       </c>
       <c r="J29" t="n">
-        <v>1175.57039225</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1745.208608</v>
+        <v>1111.336422</v>
       </c>
     </row>
     <row r="30">
@@ -1507,33 +1438,32 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1593.900291</v>
+      </c>
       <c r="C30" t="n">
-        <v>1169.464009</v>
+        <v>931.223287</v>
       </c>
       <c r="D30" t="n">
-        <v>1593.900291</v>
+        <v>464.349189</v>
       </c>
       <c r="E30" t="n">
-        <v>931.223287</v>
+        <v>460.082038</v>
       </c>
       <c r="F30" t="n">
-        <v>464.349189</v>
+        <v>1411.506215</v>
       </c>
       <c r="G30" t="n">
-        <v>460.082038</v>
+        <v>913.096038</v>
       </c>
       <c r="H30" t="n">
-        <v>1411.506215</v>
+        <v>716.628303</v>
       </c>
       <c r="I30" t="n">
-        <v>913.096038</v>
+        <v>1391.651459</v>
       </c>
       <c r="J30" t="n">
-        <v>716.628303</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1391.651459</v>
+        <v>1434.343204</v>
       </c>
     </row>
     <row r="31">
@@ -1543,34 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>181.541844</v>
       </c>
       <c r="C31" t="n">
-        <v>32.627476</v>
+        <v>309.229901</v>
       </c>
       <c r="D31" t="n">
-        <v>29.725872</v>
+        <v>337.289111</v>
       </c>
       <c r="E31" t="n">
-        <v>29.49059</v>
+        <v>1395.007583</v>
       </c>
       <c r="F31" t="n">
-        <v>21.24001</v>
+        <v>981.782769</v>
       </c>
       <c r="G31" t="n">
-        <v>27.393318</v>
+        <v>300.275675</v>
       </c>
       <c r="H31" t="n">
-        <v>65.72085</v>
+        <v>573.402185</v>
       </c>
       <c r="I31" t="n">
-        <v>35.226386</v>
+        <v>257.059214</v>
       </c>
       <c r="J31" t="n">
-        <v>29.874389</v>
-      </c>
-      <c r="K31" t="n">
-        <v>35.231929</v>
+        <v>150.92435</v>
       </c>
     </row>
     <row r="32">
@@ -1579,33 +1506,32 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>3919.093005</v>
+      </c>
       <c r="C32" t="n">
-        <v>3706.578267</v>
+        <v>2995.886457</v>
       </c>
       <c r="D32" t="n">
-        <v>3919.093005</v>
+        <v>1914.022671</v>
       </c>
       <c r="E32" t="n">
-        <v>2995.886457</v>
+        <v>2767.071807</v>
       </c>
       <c r="F32" t="n">
-        <v>1914.022671</v>
+        <v>2175.603754</v>
       </c>
       <c r="G32" t="n">
-        <v>2767.071807</v>
+        <v>3293.053983</v>
       </c>
       <c r="H32" t="n">
-        <v>2175.603754</v>
+        <v>1634.098594</v>
       </c>
       <c r="I32" t="n">
-        <v>3293.053983</v>
+        <v>2034.884553</v>
       </c>
       <c r="J32" t="n">
-        <v>1634.098594</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2034.884553</v>
+        <v>2066.430581</v>
       </c>
     </row>
     <row r="33">
@@ -1615,34 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>3576.81368125</v>
       </c>
       <c r="C33" t="n">
-        <v>3256.66628</v>
+        <v>4231.049639</v>
       </c>
       <c r="D33" t="n">
-        <v>3562.92841725</v>
+        <v>3152.723616083334</v>
       </c>
       <c r="E33" t="n">
-        <v>4224.962546</v>
+        <v>2054.422690333333</v>
       </c>
       <c r="F33" t="n">
-        <v>3147.187418083333</v>
+        <v>3157.254720666666</v>
       </c>
       <c r="G33" t="n">
-        <v>2041.066760333333</v>
+        <v>4047.266548166667</v>
       </c>
       <c r="H33" t="n">
-        <v>3145.790868666666</v>
+        <v>2730.1196475</v>
       </c>
       <c r="I33" t="n">
-        <v>4039.925452166667</v>
+        <v>2356.587739416666</v>
       </c>
       <c r="J33" t="n">
-        <v>2719.0837115</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2342.042780416667</v>
+        <v>1786.66304375</v>
       </c>
     </row>
     <row r="34">
@@ -1651,33 +1574,32 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>20499.14281033333</v>
+      </c>
       <c r="C34" t="n">
-        <v>14640.291383</v>
+        <v>16008.9466375</v>
       </c>
       <c r="D34" t="n">
-        <v>20499.14281033333</v>
+        <v>18522.008159</v>
       </c>
       <c r="E34" t="n">
-        <v>16008.9466375</v>
+        <v>24138.976642</v>
       </c>
       <c r="F34" t="n">
-        <v>18522.008159</v>
+        <v>38592.8304785</v>
       </c>
       <c r="G34" t="n">
-        <v>24138.976642</v>
+        <v>17726.891727</v>
       </c>
       <c r="H34" t="n">
-        <v>38592.8304785</v>
+        <v>18001.843649</v>
       </c>
       <c r="I34" t="n">
-        <v>17726.891727</v>
+        <v>29683.7204415</v>
       </c>
       <c r="J34" t="n">
-        <v>18001.843649</v>
-      </c>
-      <c r="K34" t="n">
-        <v>29683.7204415</v>
+        <v>37426.999642</v>
       </c>
     </row>
     <row r="35">
@@ -1686,33 +1608,32 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1434.127968</v>
+      </c>
       <c r="C35" t="n">
-        <v>891.2038680000001</v>
+        <v>864.776533</v>
       </c>
       <c r="D35" t="n">
-        <v>1434.127968</v>
+        <v>907.837418</v>
       </c>
       <c r="E35" t="n">
-        <v>864.776533</v>
+        <v>883.170031</v>
       </c>
       <c r="F35" t="n">
-        <v>907.837418</v>
+        <v>1354.065363</v>
       </c>
       <c r="G35" t="n">
-        <v>883.170031</v>
+        <v>1121.706863</v>
       </c>
       <c r="H35" t="n">
-        <v>1354.065363</v>
+        <v>932.818224</v>
       </c>
       <c r="I35" t="n">
-        <v>1121.706863</v>
+        <v>1830.670428</v>
       </c>
       <c r="J35" t="n">
-        <v>932.818224</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1830.670428</v>
+        <v>1885.095466</v>
       </c>
     </row>
     <row r="36">
@@ -1721,33 +1642,32 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>1986.142069</v>
+      </c>
       <c r="C36" t="n">
-        <v>2168.962247</v>
+        <v>1649.814433333333</v>
       </c>
       <c r="D36" t="n">
-        <v>1986.142069</v>
+        <v>1741.438457</v>
       </c>
       <c r="E36" t="n">
-        <v>1649.814433333333</v>
+        <v>1913.072300666667</v>
       </c>
       <c r="F36" t="n">
-        <v>1741.438457</v>
+        <v>2251.441003</v>
       </c>
       <c r="G36" t="n">
-        <v>1913.072300666667</v>
+        <v>1989.455276</v>
       </c>
       <c r="H36" t="n">
-        <v>2251.441003</v>
+        <v>2036.013433</v>
       </c>
       <c r="I36" t="n">
-        <v>1989.455276</v>
+        <v>3601.325495</v>
       </c>
       <c r="J36" t="n">
-        <v>2036.013433</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3601.325495</v>
+        <v>1921.06941</v>
       </c>
     </row>
     <row r="37">
@@ -1756,33 +1676,32 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>10602.834135</v>
+      </c>
       <c r="C37" t="n">
-        <v>9107.543382</v>
+        <v>9503.746923999999</v>
       </c>
       <c r="D37" t="n">
-        <v>10602.834135</v>
+        <v>6766.767165</v>
       </c>
       <c r="E37" t="n">
-        <v>9503.746923999999</v>
+        <v>9354.171284</v>
       </c>
       <c r="F37" t="n">
-        <v>6766.767165</v>
+        <v>14735.204401</v>
       </c>
       <c r="G37" t="n">
-        <v>9354.171284</v>
+        <v>12505.335512</v>
       </c>
       <c r="H37" t="n">
-        <v>14735.204401</v>
+        <v>12181.591653</v>
       </c>
       <c r="I37" t="n">
-        <v>12505.335512</v>
+        <v>17010.454022</v>
       </c>
       <c r="J37" t="n">
-        <v>12181.591653</v>
-      </c>
-      <c r="K37" t="n">
-        <v>17010.454022</v>
+        <v>14425.671246</v>
       </c>
     </row>
     <row r="38">
@@ -1791,33 +1710,32 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>1186.517079</v>
+      </c>
       <c r="C38" t="n">
-        <v>460.152903</v>
+        <v>2327.684013</v>
       </c>
       <c r="D38" t="n">
-        <v>1186.517079</v>
+        <v>1364.089271</v>
       </c>
       <c r="E38" t="n">
-        <v>2327.684013</v>
+        <v>755.371776</v>
       </c>
       <c r="F38" t="n">
-        <v>1364.089271</v>
+        <v>1522.638212</v>
       </c>
       <c r="G38" t="n">
-        <v>755.371776</v>
+        <v>983.322091</v>
       </c>
       <c r="H38" t="n">
-        <v>1522.638212</v>
+        <v>514.825294</v>
       </c>
       <c r="I38" t="n">
-        <v>983.322091</v>
+        <v>678.614001</v>
       </c>
       <c r="J38" t="n">
-        <v>514.825294</v>
-      </c>
-      <c r="K38" t="n">
-        <v>678.614001</v>
+        <v>812.177107</v>
       </c>
     </row>
     <row r="39">
@@ -1826,33 +1744,32 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>4775.668836</v>
+      </c>
       <c r="C39" t="n">
-        <v>6035.205858</v>
+        <v>5293.7077845</v>
       </c>
       <c r="D39" t="n">
-        <v>4775.668836</v>
+        <v>3869.600446</v>
       </c>
       <c r="E39" t="n">
-        <v>5293.7077845</v>
+        <v>5798.788543</v>
       </c>
       <c r="F39" t="n">
-        <v>3869.600446</v>
+        <v>3937.918847</v>
       </c>
       <c r="G39" t="n">
-        <v>5798.788543</v>
+        <v>3621.251342</v>
       </c>
       <c r="H39" t="n">
-        <v>3937.918847</v>
+        <v>3802.02835</v>
       </c>
       <c r="I39" t="n">
-        <v>3621.251342</v>
+        <v>5064.0600025</v>
       </c>
       <c r="J39" t="n">
-        <v>3802.02835</v>
-      </c>
-      <c r="K39" t="n">
-        <v>5064.0600025</v>
+        <v>4283.101274</v>
       </c>
     </row>
     <row r="40">
@@ -1861,33 +1778,32 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>45038.042564</v>
+      </c>
       <c r="C40" t="n">
-        <v>33189.695159</v>
+        <v>38221.871131</v>
       </c>
       <c r="D40" t="n">
-        <v>45038.042564</v>
+        <v>38620.855354</v>
       </c>
       <c r="E40" t="n">
-        <v>38221.871131</v>
+        <v>38787.989586</v>
       </c>
       <c r="F40" t="n">
-        <v>38620.855354</v>
+        <v>26515.935769</v>
       </c>
       <c r="G40" t="n">
-        <v>38787.989586</v>
+        <v>83369.59020000001</v>
       </c>
       <c r="H40" t="n">
-        <v>26515.935769</v>
+        <v>109528.620721</v>
       </c>
       <c r="I40" t="n">
-        <v>83369.59020000001</v>
+        <v>93985.398543</v>
       </c>
       <c r="J40" t="n">
-        <v>109528.620721</v>
-      </c>
-      <c r="K40" t="n">
-        <v>93985.398543</v>
+        <v>48833.372017</v>
       </c>
     </row>
     <row r="41">
@@ -1897,34 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>151.63697</v>
       </c>
       <c r="C41" t="n">
-        <v>103.471182</v>
+        <v>128.294805</v>
       </c>
       <c r="D41" t="n">
-        <v>151.056149</v>
+        <v>193.129646</v>
       </c>
       <c r="E41" t="n">
-        <v>126.565595</v>
+        <v>222.40962075</v>
       </c>
       <c r="F41" t="n">
-        <v>191.907869</v>
+        <v>156.903562</v>
       </c>
       <c r="G41" t="n">
-        <v>222.13095675</v>
+        <v>164.3006155</v>
       </c>
       <c r="H41" t="n">
-        <v>156.416678</v>
+        <v>143.66717925</v>
       </c>
       <c r="I41" t="n">
-        <v>163.7585305</v>
+        <v>155.329028</v>
       </c>
       <c r="J41" t="n">
-        <v>143.28460225</v>
-      </c>
-      <c r="K41" t="n">
-        <v>154.808428</v>
+        <v>110.388879</v>
       </c>
     </row>
     <row r="42">
@@ -1933,33 +1846,32 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>57852.103144</v>
+      </c>
       <c r="C42" t="n">
-        <v>40610.057207</v>
+        <v>55538.57203</v>
       </c>
       <c r="D42" t="n">
-        <v>57852.103144</v>
+        <v>36425.530521</v>
       </c>
       <c r="E42" t="n">
-        <v>55538.57203</v>
+        <v>29728.764487</v>
       </c>
       <c r="F42" t="n">
-        <v>36425.530521</v>
+        <v>45172.5952</v>
       </c>
       <c r="G42" t="n">
-        <v>29728.764487</v>
+        <v>32010.529296</v>
       </c>
       <c r="H42" t="n">
-        <v>45172.5952</v>
+        <v>44356.231581</v>
       </c>
       <c r="I42" t="n">
-        <v>32010.529296</v>
+        <v>51876.083843</v>
       </c>
       <c r="J42" t="n">
-        <v>44356.231581</v>
-      </c>
-      <c r="K42" t="n">
-        <v>51876.083843</v>
+        <v>37022.409219</v>
       </c>
     </row>
     <row r="43">
@@ -1968,33 +1880,32 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>153.339739</v>
+      </c>
       <c r="C43" t="n">
-        <v>183.066952</v>
+        <v>214.148055</v>
       </c>
       <c r="D43" t="n">
-        <v>153.339739</v>
+        <v>137.208998</v>
       </c>
       <c r="E43" t="n">
-        <v>214.148055</v>
+        <v>140.3224923333333</v>
       </c>
       <c r="F43" t="n">
-        <v>137.208998</v>
+        <v>143.673452</v>
       </c>
       <c r="G43" t="n">
-        <v>140.3224923333333</v>
+        <v>126.829217</v>
       </c>
       <c r="H43" t="n">
-        <v>143.673452</v>
+        <v>153.965149</v>
       </c>
       <c r="I43" t="n">
-        <v>126.829217</v>
+        <v>216.040869</v>
       </c>
       <c r="J43" t="n">
-        <v>153.965149</v>
-      </c>
-      <c r="K43" t="n">
-        <v>216.040869</v>
+        <v>144.108749</v>
       </c>
     </row>
     <row r="44">
@@ -2004,34 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>550.6252469999999</v>
       </c>
       <c r="C44" t="n">
-        <v>1650.007821</v>
+        <v>568.934852</v>
       </c>
       <c r="D44" t="n">
-        <v>550.60604</v>
+        <v>572.670523</v>
       </c>
       <c r="E44" t="n">
-        <v>568.92696</v>
+        <v>273.551237</v>
       </c>
       <c r="F44" t="n">
-        <v>572.650055</v>
+        <v>406.0494</v>
       </c>
       <c r="G44" t="n">
-        <v>273.543601</v>
+        <v>192.38958</v>
       </c>
       <c r="H44" t="n">
-        <v>406.039514</v>
+        <v>159.333061</v>
       </c>
       <c r="I44" t="n">
-        <v>192.384708</v>
+        <v>305.280954</v>
       </c>
       <c r="J44" t="n">
-        <v>159.32824</v>
-      </c>
-      <c r="K44" t="n">
-        <v>305.274184</v>
+        <v>466.65060525</v>
       </c>
     </row>
     <row r="45">
@@ -2040,33 +1948,32 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>629.646796</v>
+      </c>
       <c r="C45" t="n">
-        <v>742.989564</v>
+        <v>554.498075</v>
       </c>
       <c r="D45" t="n">
-        <v>629.646796</v>
+        <v>431.843473</v>
       </c>
       <c r="E45" t="n">
-        <v>554.498075</v>
+        <v>558.7608739999999</v>
       </c>
       <c r="F45" t="n">
-        <v>431.843473</v>
+        <v>827.171639</v>
       </c>
       <c r="G45" t="n">
-        <v>558.7608739999999</v>
+        <v>608.8516980000001</v>
       </c>
       <c r="H45" t="n">
-        <v>827.171639</v>
+        <v>1163.125599</v>
       </c>
       <c r="I45" t="n">
-        <v>608.8516980000001</v>
+        <v>1017.672095</v>
       </c>
       <c r="J45" t="n">
-        <v>1163.125599</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1017.672095</v>
+        <v>612.678449</v>
       </c>
     </row>
     <row r="46">
@@ -2075,33 +1982,32 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0.012402</v>
+      </c>
       <c r="C46" t="n">
-        <v>0.036967</v>
+        <v>0.005706</v>
       </c>
       <c r="D46" t="n">
-        <v>0.012402</v>
+        <v>0.005351</v>
       </c>
       <c r="E46" t="n">
-        <v>0.005706</v>
+        <v>0.003217</v>
       </c>
       <c r="F46" t="n">
-        <v>0.005351</v>
+        <v>0.003287</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003217</v>
+        <v>0.00215</v>
       </c>
       <c r="H46" t="n">
-        <v>0.003287</v>
+        <v>0.002401</v>
       </c>
       <c r="I46" t="n">
-        <v>0.00215</v>
+        <v>0.008321</v>
       </c>
       <c r="J46" t="n">
-        <v>0.002401</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.008321</v>
+        <v>0.004504</v>
       </c>
     </row>
     <row r="47">
@@ -2111,34 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>3227.005332</v>
       </c>
       <c r="C47" t="n">
-        <v>1995.445981</v>
+        <v>2285.728811</v>
       </c>
       <c r="D47" t="n">
-        <v>3227.004494</v>
+        <v>2768.183649</v>
       </c>
       <c r="E47" t="n">
-        <v>2285.727801</v>
+        <v>2160.042912</v>
       </c>
       <c r="F47" t="n">
-        <v>2768.183273</v>
+        <v>2537.16588</v>
       </c>
       <c r="G47" t="n">
-        <v>2160.041587</v>
+        <v>1944.562274</v>
       </c>
       <c r="H47" t="n">
-        <v>2537.164485</v>
+        <v>2607.919254</v>
       </c>
       <c r="I47" t="n">
-        <v>1944.561653</v>
+        <v>3108.633171</v>
       </c>
       <c r="J47" t="n">
-        <v>2607.917951</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3108.6326</v>
+        <v>1946.205721</v>
       </c>
     </row>
     <row r="48">
@@ -2147,33 +2050,32 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>113.137448</v>
+      </c>
       <c r="C48" t="n">
-        <v>71.276222</v>
+        <v>81.686544</v>
       </c>
       <c r="D48" t="n">
-        <v>113.137448</v>
+        <v>84.399334</v>
       </c>
       <c r="E48" t="n">
-        <v>81.686544</v>
+        <v>158.144148</v>
       </c>
       <c r="F48" t="n">
-        <v>84.399334</v>
+        <v>104.815151</v>
       </c>
       <c r="G48" t="n">
-        <v>158.144148</v>
+        <v>152.916565</v>
       </c>
       <c r="H48" t="n">
-        <v>104.815151</v>
+        <v>102.306466</v>
       </c>
       <c r="I48" t="n">
-        <v>152.916565</v>
+        <v>118.380095</v>
       </c>
       <c r="J48" t="n">
-        <v>102.306466</v>
-      </c>
-      <c r="K48" t="n">
-        <v>118.380095</v>
+        <v>103.558187</v>
       </c>
     </row>
     <row r="49">
@@ -2183,34 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>10630.8634</v>
       </c>
       <c r="C49" t="n">
-        <v>12511.16686</v>
+        <v>12588.924363</v>
       </c>
       <c r="D49" t="n">
-        <v>10623.52561</v>
+        <v>6628.107666</v>
       </c>
       <c r="E49" t="n">
-        <v>12579.584169</v>
+        <v>7771.289255</v>
       </c>
       <c r="F49" t="n">
-        <v>6620.155791</v>
+        <v>10297.83788</v>
       </c>
       <c r="G49" t="n">
-        <v>7766.043802</v>
+        <v>9437.364121000001</v>
       </c>
       <c r="H49" t="n">
-        <v>10288.97072</v>
+        <v>8742.657853999999</v>
       </c>
       <c r="I49" t="n">
-        <v>9431.7981</v>
+        <v>7863.080042</v>
       </c>
       <c r="J49" t="n">
-        <v>8734.995352</v>
-      </c>
-      <c r="K49" t="n">
-        <v>7855.820373</v>
+        <v>9302.300510999999</v>
       </c>
     </row>
     <row r="50">
@@ -2219,33 +2118,32 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>604.192691</v>
+      </c>
       <c r="C50" t="n">
-        <v>647.096954</v>
+        <v>740.053436</v>
       </c>
       <c r="D50" t="n">
-        <v>604.192691</v>
+        <v>612.497166</v>
       </c>
       <c r="E50" t="n">
-        <v>740.053436</v>
+        <v>752.428062</v>
       </c>
       <c r="F50" t="n">
-        <v>612.497166</v>
+        <v>692.888991</v>
       </c>
       <c r="G50" t="n">
-        <v>752.428062</v>
+        <v>646.441073</v>
       </c>
       <c r="H50" t="n">
-        <v>692.888991</v>
+        <v>664.655217</v>
       </c>
       <c r="I50" t="n">
-        <v>646.441073</v>
+        <v>1014.851735</v>
       </c>
       <c r="J50" t="n">
-        <v>664.655217</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1014.851735</v>
+        <v>622.302297</v>
       </c>
     </row>
     <row r="51">
@@ -2254,33 +2152,32 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0.018883</v>
+      </c>
       <c r="C51" t="n">
-        <v>0.017833</v>
+        <v>0.014946</v>
       </c>
       <c r="D51" t="n">
-        <v>0.018883</v>
+        <v>0.018067</v>
       </c>
       <c r="E51" t="n">
-        <v>0.014946</v>
+        <v>0.017467</v>
       </c>
       <c r="F51" t="n">
-        <v>0.018067</v>
+        <v>0.015909</v>
       </c>
       <c r="G51" t="n">
-        <v>0.017467</v>
+        <v>0.010093</v>
       </c>
       <c r="H51" t="n">
-        <v>0.015909</v>
+        <v>0.014062</v>
       </c>
       <c r="I51" t="n">
-        <v>0.010093</v>
+        <v>0.047371</v>
       </c>
       <c r="J51" t="n">
-        <v>0.014062</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.047371</v>
+        <v>0.021222</v>
       </c>
     </row>
     <row r="52">
@@ -2290,34 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>8148.055404666667</v>
       </c>
       <c r="C52" t="n">
-        <v>9074.235629000001</v>
+        <v>9224.021632</v>
       </c>
       <c r="D52" t="n">
-        <v>8146.462402666667</v>
+        <v>5732.684626</v>
       </c>
       <c r="E52" t="n">
-        <v>9221.820274</v>
+        <v>10246.93227</v>
       </c>
       <c r="F52" t="n">
-        <v>5729.825798</v>
+        <v>8616.418030999999</v>
       </c>
       <c r="G52" t="n">
-        <v>10244.585728</v>
+        <v>10196.150336</v>
       </c>
       <c r="H52" t="n">
-        <v>8613.641496</v>
+        <v>6597.266704</v>
       </c>
       <c r="I52" t="n">
-        <v>10195.288084</v>
+        <v>7939.043424</v>
       </c>
       <c r="J52" t="n">
-        <v>6593.543432</v>
-      </c>
-      <c r="K52" t="n">
-        <v>7936.555242</v>
+        <v>7452.984238</v>
       </c>
     </row>
     <row r="53">
@@ -2327,34 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>2784.567429</v>
       </c>
       <c r="C53" t="n">
-        <v>1707.55237</v>
+        <v>2840.801426</v>
       </c>
       <c r="D53" t="n">
-        <v>2637.925009</v>
+        <v>2553.3653815</v>
       </c>
       <c r="E53" t="n">
-        <v>2583.258658</v>
+        <v>3519.341702</v>
       </c>
       <c r="F53" t="n">
-        <v>2360.7903395</v>
+        <v>6191.425248333333</v>
       </c>
       <c r="G53" t="n">
-        <v>3191.447185</v>
+        <v>7155.879135</v>
       </c>
       <c r="H53" t="n">
-        <v>5917.913341333333</v>
+        <v>3091.901302</v>
       </c>
       <c r="I53" t="n">
-        <v>6990.934332</v>
+        <v>3451.97244275</v>
       </c>
       <c r="J53" t="n">
-        <v>2965.845225</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2978.61840275</v>
+        <v>1879.15980825</v>
       </c>
     </row>
     <row r="54">
@@ -2363,33 +2254,32 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>206.789119</v>
+      </c>
       <c r="C54" t="n">
-        <v>251.282962</v>
+        <v>486.365714</v>
       </c>
       <c r="D54" t="n">
-        <v>206.789119</v>
+        <v>467.102515</v>
       </c>
       <c r="E54" t="n">
-        <v>486.365714</v>
+        <v>316.776227</v>
       </c>
       <c r="F54" t="n">
-        <v>467.102515</v>
+        <v>353.129823</v>
       </c>
       <c r="G54" t="n">
-        <v>316.776227</v>
+        <v>467.278976</v>
       </c>
       <c r="H54" t="n">
-        <v>353.129823</v>
+        <v>627.997406</v>
       </c>
       <c r="I54" t="n">
-        <v>467.278976</v>
+        <v>242.656285</v>
       </c>
       <c r="J54" t="n">
-        <v>627.997406</v>
-      </c>
-      <c r="K54" t="n">
-        <v>242.656285</v>
+        <v>329.846967</v>
       </c>
     </row>
     <row r="55">
@@ -2398,33 +2288,32 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>789.765672</v>
+      </c>
       <c r="C55" t="n">
-        <v>1300.476742</v>
+        <v>1208.391141</v>
       </c>
       <c r="D55" t="n">
-        <v>789.765672</v>
+        <v>918.019598</v>
       </c>
       <c r="E55" t="n">
-        <v>1208.391141</v>
+        <v>1676.725028</v>
       </c>
       <c r="F55" t="n">
-        <v>918.019598</v>
+        <v>1524.028999</v>
       </c>
       <c r="G55" t="n">
-        <v>1676.725028</v>
+        <v>1248.190797</v>
       </c>
       <c r="H55" t="n">
-        <v>1524.028999</v>
+        <v>1458.3181</v>
       </c>
       <c r="I55" t="n">
-        <v>1248.190797</v>
+        <v>1239.700787</v>
       </c>
       <c r="J55" t="n">
-        <v>1458.3181</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1239.700787</v>
+        <v>1019.972816</v>
       </c>
     </row>
     <row r="56">
@@ -2433,33 +2322,32 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>13781.334479</v>
+      </c>
       <c r="C56" t="n">
-        <v>10237.123019</v>
+        <v>8485.200322000001</v>
       </c>
       <c r="D56" t="n">
-        <v>13781.334479</v>
+        <v>10685.838357</v>
       </c>
       <c r="E56" t="n">
-        <v>8485.200322000001</v>
+        <v>11086.499208</v>
       </c>
       <c r="F56" t="n">
-        <v>10685.838357</v>
+        <v>15936.008962</v>
       </c>
       <c r="G56" t="n">
-        <v>11086.499208</v>
+        <v>7870.13773</v>
       </c>
       <c r="H56" t="n">
-        <v>15936.008962</v>
+        <v>7151.438405</v>
       </c>
       <c r="I56" t="n">
-        <v>7870.13773</v>
+        <v>13323.285339</v>
       </c>
       <c r="J56" t="n">
-        <v>7151.438405</v>
-      </c>
-      <c r="K56" t="n">
-        <v>13323.285339</v>
+        <v>13127.663375</v>
       </c>
     </row>
     <row r="57">
@@ -2469,34 +2357,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>211.287875</v>
       </c>
       <c r="C57" t="n">
-        <v>183.95473</v>
+        <v>134.946384</v>
       </c>
       <c r="D57" t="n">
-        <v>201.213138</v>
+        <v>107.918206</v>
       </c>
       <c r="E57" t="n">
-        <v>125.917386</v>
+        <v>240.957821</v>
       </c>
       <c r="F57" t="n">
-        <v>95.368484</v>
+        <v>280.614387</v>
       </c>
       <c r="G57" t="n">
-        <v>222.084387</v>
+        <v>241.632148</v>
       </c>
       <c r="H57" t="n">
-        <v>235.81675</v>
+        <v>160.750781</v>
       </c>
       <c r="I57" t="n">
-        <v>220.541561</v>
+        <v>199.358638</v>
       </c>
       <c r="J57" t="n">
-        <v>149.284232</v>
-      </c>
-      <c r="K57" t="n">
-        <v>185.684977</v>
+        <v>156.92636</v>
       </c>
     </row>
     <row r="58">
@@ -2505,33 +2390,32 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0.846683</v>
+      </c>
       <c r="C58" t="n">
-        <v>0.78407</v>
+        <v>0.86441</v>
       </c>
       <c r="D58" t="n">
-        <v>0.846683</v>
+        <v>0.797876</v>
       </c>
       <c r="E58" t="n">
-        <v>0.86441</v>
+        <v>1.227215</v>
       </c>
       <c r="F58" t="n">
-        <v>0.797876</v>
+        <v>0.803998</v>
       </c>
       <c r="G58" t="n">
-        <v>1.227215</v>
+        <v>0.610103</v>
       </c>
       <c r="H58" t="n">
-        <v>0.803998</v>
+        <v>0.848656</v>
       </c>
       <c r="I58" t="n">
-        <v>0.610103</v>
+        <v>1.13421</v>
       </c>
       <c r="J58" t="n">
-        <v>0.848656</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1.13421</v>
+        <v>1.650141</v>
       </c>
     </row>
     <row r="59">
@@ -2540,33 +2424,32 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>3874.059874</v>
+      </c>
       <c r="C59" t="n">
-        <v>3280.445867</v>
+        <v>3231.589884</v>
       </c>
       <c r="D59" t="n">
-        <v>3874.059874</v>
+        <v>3117.83436</v>
       </c>
       <c r="E59" t="n">
-        <v>3231.589884</v>
+        <v>3284.358638</v>
       </c>
       <c r="F59" t="n">
-        <v>3117.83436</v>
+        <v>3269.037075</v>
       </c>
       <c r="G59" t="n">
-        <v>3284.358638</v>
+        <v>4556.196035</v>
       </c>
       <c r="H59" t="n">
-        <v>3269.037075</v>
+        <v>3278.903084</v>
       </c>
       <c r="I59" t="n">
-        <v>4556.196035</v>
+        <v>2987.686914</v>
       </c>
       <c r="J59" t="n">
-        <v>3278.903084</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2987.686914</v>
+        <v>2359.443202</v>
       </c>
     </row>
     <row r="60">
@@ -2576,34 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>10163.667076</v>
       </c>
       <c r="C60" t="n">
-        <v>11352.935399</v>
+        <v>14283.112728</v>
       </c>
       <c r="D60" t="n">
-        <v>10163.660786</v>
+        <v>15702.55116</v>
       </c>
       <c r="E60" t="n">
-        <v>14283.10676</v>
+        <v>16339.630617</v>
       </c>
       <c r="F60" t="n">
-        <v>15702.547219</v>
+        <v>13990.739466</v>
       </c>
       <c r="G60" t="n">
-        <v>16339.62805</v>
+        <v>17015.629412</v>
       </c>
       <c r="H60" t="n">
-        <v>13990.733693</v>
+        <v>22387.334106</v>
       </c>
       <c r="I60" t="n">
-        <v>17015.623284</v>
+        <v>21582.243303</v>
       </c>
       <c r="J60" t="n">
-        <v>22387.325547</v>
-      </c>
-      <c r="K60" t="n">
-        <v>21582.233912</v>
+        <v>19432.335148</v>
       </c>
     </row>
     <row r="61">
@@ -2613,34 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>2654.157778</v>
       </c>
       <c r="C61" t="n">
-        <v>2465.170009</v>
+        <v>1915.343968333333</v>
       </c>
       <c r="D61" t="n">
-        <v>2654.139277</v>
+        <v>2833.24706325</v>
       </c>
       <c r="E61" t="n">
-        <v>1915.313872333333</v>
+        <v>3220.483233</v>
       </c>
       <c r="F61" t="n">
-        <v>2833.23200825</v>
+        <v>3455.685055</v>
       </c>
       <c r="G61" t="n">
-        <v>3220.471648</v>
+        <v>2850.61244775</v>
       </c>
       <c r="H61" t="n">
-        <v>3455.670585</v>
+        <v>2993.695927</v>
       </c>
       <c r="I61" t="n">
-        <v>2850.60360375</v>
+        <v>2674.10022075</v>
       </c>
       <c r="J61" t="n">
-        <v>2993.6702</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2674.08266375</v>
+        <v>2069.6081</v>
       </c>
     </row>
     <row r="62">
@@ -2649,33 +2526,32 @@
           <t>電腦週邊</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>2761.665087</v>
+      </c>
       <c r="C62" t="n">
-        <v>3758.237494</v>
+        <v>2220.286172</v>
       </c>
       <c r="D62" t="n">
-        <v>2761.665087</v>
+        <v>3864.484353</v>
       </c>
       <c r="E62" t="n">
-        <v>2220.286172</v>
+        <v>3658.219779</v>
       </c>
       <c r="F62" t="n">
-        <v>3864.484353</v>
+        <v>3713.579148</v>
       </c>
       <c r="G62" t="n">
-        <v>3658.219779</v>
+        <v>5625.03953</v>
       </c>
       <c r="H62" t="n">
-        <v>3713.579148</v>
+        <v>5045.504785</v>
       </c>
       <c r="I62" t="n">
-        <v>5625.03953</v>
+        <v>4618.943971</v>
       </c>
       <c r="J62" t="n">
-        <v>5045.504785</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4618.943971</v>
+        <v>4452.85462</v>
       </c>
     </row>
     <row r="63">
@@ -2684,33 +2560,32 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>67962.25039299999</v>
+      </c>
       <c r="C63" t="n">
-        <v>41270.985346</v>
+        <v>44299.675634</v>
       </c>
       <c r="D63" t="n">
-        <v>67962.25039299999</v>
+        <v>23766.421451</v>
       </c>
       <c r="E63" t="n">
-        <v>44299.675634</v>
+        <v>24131.35528</v>
       </c>
       <c r="F63" t="n">
-        <v>23766.421451</v>
+        <v>42390.318478</v>
       </c>
       <c r="G63" t="n">
-        <v>24131.35528</v>
+        <v>61009.00298</v>
       </c>
       <c r="H63" t="n">
-        <v>42390.318478</v>
+        <v>39186.48104</v>
       </c>
       <c r="I63" t="n">
-        <v>61009.00298</v>
+        <v>58947.997898</v>
       </c>
       <c r="J63" t="n">
-        <v>39186.48104</v>
-      </c>
-      <c r="K63" t="n">
-        <v>58947.997898</v>
+        <v>25340.859125</v>
       </c>
     </row>
     <row r="64">
@@ -2720,34 +2595,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>932.27086</v>
       </c>
       <c r="C64" t="n">
-        <v>639.318904</v>
+        <v>894.284195</v>
       </c>
       <c r="D64" t="n">
-        <v>932.26991</v>
+        <v>672.670647</v>
       </c>
       <c r="E64" t="n">
-        <v>894.282873</v>
+        <v>822.513379</v>
       </c>
       <c r="F64" t="n">
-        <v>672.665497</v>
+        <v>808.75627</v>
       </c>
       <c r="G64" t="n">
-        <v>822.511974</v>
+        <v>729.3189609999999</v>
       </c>
       <c r="H64" t="n">
-        <v>808.754942</v>
+        <v>1707.523625</v>
       </c>
       <c r="I64" t="n">
-        <v>729.317989</v>
+        <v>1123.525856</v>
       </c>
       <c r="J64" t="n">
-        <v>1707.520135</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1123.523207</v>
+        <v>1288.255756</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -486,9 +491,7 @@
           <t>AI伺服器</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>115583.774439</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>88280.45979350001</v>
       </c>
@@ -513,6 +516,9 @@
       <c r="J2" t="n">
         <v>116164.155528</v>
       </c>
+      <c r="K2" t="n">
+        <v>89863.707416</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -520,9 +526,7 @@
           <t>AI應用服務</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1442.069167</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>1293.691735</v>
       </c>
@@ -547,6 +551,9 @@
       <c r="J3" t="n">
         <v>1171.961645</v>
       </c>
+      <c r="K3" t="n">
+        <v>1231.619958</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -554,9 +561,7 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>226359.872253</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>166179.907213</v>
       </c>
@@ -581,6 +586,9 @@
       <c r="J4" t="n">
         <v>205533.21934</v>
       </c>
+      <c r="K4" t="n">
+        <v>162010.552511</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -588,9 +596,7 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1321.863769</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>1185.034685</v>
       </c>
@@ -615,6 +621,9 @@
       <c r="J5" t="n">
         <v>1784.390789</v>
       </c>
+      <c r="K5" t="n">
+        <v>4443.690148</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -622,9 +631,7 @@
           <t>PCB載板</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>121821.817605</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>129515.847183</v>
       </c>
@@ -649,6 +656,9 @@
       <c r="J6" t="n">
         <v>165285.893329</v>
       </c>
+      <c r="K6" t="n">
+        <v>127508.207651</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -656,9 +666,7 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>22175.429716</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>13770.435178</v>
       </c>
@@ -683,6 +691,9 @@
       <c r="J7" t="n">
         <v>25336.378851</v>
       </c>
+      <c r="K7" t="n">
+        <v>22997.890573</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -690,9 +701,7 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>9213.183336</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>8165.319383</v>
       </c>
@@ -717,6 +726,9 @@
       <c r="J8" t="n">
         <v>13943.679809</v>
       </c>
+      <c r="K8" t="n">
+        <v>18547.719671</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -724,32 +736,33 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>23907.352232</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>16164.352791</v>
+        <v>16161.284088</v>
       </c>
       <c r="D9" t="n">
-        <v>12877.494238</v>
+        <v>12873.954103</v>
       </c>
       <c r="E9" t="n">
-        <v>12170.44137225</v>
+        <v>12165.33258825</v>
       </c>
       <c r="F9" t="n">
-        <v>28574.762822</v>
+        <v>28559.179172</v>
       </c>
       <c r="G9" t="n">
-        <v>20694.5899575</v>
+        <v>20689.1994985</v>
       </c>
       <c r="H9" t="n">
-        <v>18024.656341</v>
+        <v>18018.642021</v>
       </c>
       <c r="I9" t="n">
-        <v>20594.013322</v>
+        <v>20582.60128</v>
       </c>
       <c r="J9" t="n">
-        <v>19539.969903</v>
+        <v>19531.356429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22692.661642</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +772,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2505.415513</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2014.82200825</v>
+        <v>2014.80352225</v>
       </c>
       <c r="D10" t="n">
-        <v>1437.9102595</v>
+        <v>1437.8998815</v>
       </c>
       <c r="E10" t="n">
-        <v>1691.566047</v>
+        <v>1691.553326</v>
       </c>
       <c r="F10" t="n">
-        <v>1739.207265</v>
+        <v>1739.186102</v>
       </c>
       <c r="G10" t="n">
-        <v>2361.4214135</v>
+        <v>2361.4151405</v>
       </c>
       <c r="H10" t="n">
-        <v>2507.015691083333</v>
+        <v>2507.005788083333</v>
       </c>
       <c r="I10" t="n">
-        <v>2915.59794075</v>
+        <v>2915.58263275</v>
       </c>
       <c r="J10" t="n">
-        <v>2010.5327855</v>
+        <v>2010.5189185</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1639.8905345</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +809,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4536.195576666667</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6391.552234</v>
+        <v>6391.497263</v>
       </c>
       <c r="D11" t="n">
-        <v>5027.901959</v>
+        <v>5027.754084</v>
       </c>
       <c r="E11" t="n">
-        <v>4287.608381</v>
+        <v>4287.580833</v>
       </c>
       <c r="F11" t="n">
-        <v>5741.1415725</v>
+        <v>5741.1237475</v>
       </c>
       <c r="G11" t="n">
-        <v>5931.790813</v>
+        <v>5931.776942</v>
       </c>
       <c r="H11" t="n">
-        <v>5709.634427</v>
+        <v>5709.595615</v>
       </c>
       <c r="I11" t="n">
-        <v>8910.522211</v>
+        <v>8910.500819000001</v>
       </c>
       <c r="J11" t="n">
-        <v>5980.956098</v>
+        <v>5980.947734</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5153.694491</v>
       </c>
     </row>
     <row r="12">
@@ -826,32 +845,33 @@
           <t>功率元件</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>14287.592061</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>12754.3151</v>
+        <v>12750.393472</v>
       </c>
       <c r="D12" t="n">
-        <v>13061.21415</v>
+        <v>13057.708287</v>
       </c>
       <c r="E12" t="n">
-        <v>11174.18828</v>
+        <v>11166.867111</v>
       </c>
       <c r="F12" t="n">
-        <v>13638.882629</v>
+        <v>13632.901286</v>
       </c>
       <c r="G12" t="n">
-        <v>13065.508176</v>
+        <v>13057.294924</v>
       </c>
       <c r="H12" t="n">
-        <v>13474.480942</v>
+        <v>13467.645699</v>
       </c>
       <c r="I12" t="n">
-        <v>20011.949809</v>
+        <v>19993.997021</v>
       </c>
       <c r="J12" t="n">
-        <v>14586.43468</v>
+        <v>14579.659067</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12407.582239</v>
       </c>
     </row>
     <row r="13">
@@ -860,9 +880,7 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5209.950112</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>5233.847716</v>
       </c>
@@ -887,6 +905,9 @@
       <c r="J13" t="n">
         <v>7703.003085</v>
       </c>
+      <c r="K13" t="n">
+        <v>5986.185579</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -895,31 +916,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13071.459356</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11120.031796</v>
+        <v>11120.027229</v>
       </c>
       <c r="D14" t="n">
-        <v>14305.724936</v>
+        <v>14305.720707</v>
       </c>
       <c r="E14" t="n">
-        <v>8735.041053249999</v>
+        <v>8735.03156025</v>
       </c>
       <c r="F14" t="n">
-        <v>9585.149552999999</v>
+        <v>9585.138666999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6695.3773</v>
+        <v>6692.970496</v>
       </c>
       <c r="H14" t="n">
-        <v>6646.674439</v>
+        <v>6643.860699</v>
       </c>
       <c r="I14" t="n">
-        <v>9487.406014</v>
+        <v>9485.026313</v>
       </c>
       <c r="J14" t="n">
-        <v>9178.032263999999</v>
+        <v>9174.399729999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6649.385096</v>
       </c>
     </row>
     <row r="15">
@@ -928,9 +952,7 @@
           <t>半導體材料</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>30247.363515</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>29527.568526</v>
       </c>
@@ -953,7 +975,10 @@
         <v>24153.683866</v>
       </c>
       <c r="J15" t="n">
-        <v>43959.585443</v>
+        <v>44202.585443</v>
+      </c>
+      <c r="K15" t="n">
+        <v>31307.142058</v>
       </c>
     </row>
     <row r="16">
@@ -962,9 +987,7 @@
           <t>半導體設備</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>23392.141195</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>28437.085444</v>
       </c>
@@ -989,6 +1012,9 @@
       <c r="J16" t="n">
         <v>17242.611229</v>
       </c>
+      <c r="K16" t="n">
+        <v>31532.197277</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -997,31 +1023,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70058.288533</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>44988.016253</v>
+        <v>44987.968157</v>
       </c>
       <c r="D17" t="n">
-        <v>30953.730487</v>
+        <v>30953.651489</v>
       </c>
       <c r="E17" t="n">
-        <v>28733.570505</v>
+        <v>28733.507478</v>
       </c>
       <c r="F17" t="n">
-        <v>38078.11666</v>
+        <v>38078.083922</v>
       </c>
       <c r="G17" t="n">
-        <v>24953.722837</v>
+        <v>24953.469361</v>
       </c>
       <c r="H17" t="n">
-        <v>41336.354249</v>
+        <v>41336.094343</v>
       </c>
       <c r="I17" t="n">
-        <v>46582.502105</v>
+        <v>46582.338652</v>
       </c>
       <c r="J17" t="n">
-        <v>44569.088771</v>
+        <v>44567.919497</v>
+      </c>
+      <c r="K17" t="n">
+        <v>38389.504465</v>
       </c>
     </row>
     <row r="18">
@@ -1030,9 +1059,7 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1189.748739</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>1567.479099</v>
       </c>
@@ -1057,6 +1084,9 @@
       <c r="J18" t="n">
         <v>1142.857343</v>
       </c>
+      <c r="K18" t="n">
+        <v>2181.757307</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1064,9 +1094,7 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>182.038654</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>110.671611</v>
       </c>
@@ -1091,6 +1119,9 @@
       <c r="J19" t="n">
         <v>102.442166</v>
       </c>
+      <c r="K19" t="n">
+        <v>136.288246</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1098,9 +1129,7 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>32619.344675</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>18556.167825</v>
       </c>
@@ -1125,6 +1154,9 @@
       <c r="J20" t="n">
         <v>30712.336311</v>
       </c>
+      <c r="K20" t="n">
+        <v>21687.438595</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1132,9 +1164,7 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>3504.671797</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>3139.560877</v>
       </c>
@@ -1159,6 +1189,9 @@
       <c r="J21" t="n">
         <v>4713.418488</v>
       </c>
+      <c r="K21" t="n">
+        <v>4481.736606</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1166,9 +1199,7 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>636.4326583333333</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>332.069325</v>
       </c>
@@ -1193,6 +1224,9 @@
       <c r="J22" t="n">
         <v>136.491058</v>
       </c>
+      <c r="K22" t="n">
+        <v>198.7382336666667</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1201,31 +1235,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.911308</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6601315</v>
+        <v>0.6521165</v>
       </c>
       <c r="D23" t="n">
-        <v>4.4233375</v>
+        <v>4.4170895</v>
       </c>
       <c r="E23" t="n">
-        <v>2.78372875</v>
+        <v>2.78047475</v>
       </c>
       <c r="F23" t="n">
-        <v>1.707734</v>
+        <v>1.703674</v>
       </c>
       <c r="G23" t="n">
-        <v>4.863267</v>
+        <v>4.859908</v>
       </c>
       <c r="H23" t="n">
-        <v>2.496508833333333</v>
+        <v>2.490104833333334</v>
       </c>
       <c r="I23" t="n">
-        <v>1.159543</v>
+        <v>1.150598</v>
       </c>
       <c r="J23" t="n">
-        <v>1.22882325</v>
+        <v>1.22426025</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5626060000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1234,9 +1271,7 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>873.041337</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>798.4179339999999</v>
       </c>
@@ -1261,6 +1296,9 @@
       <c r="J24" t="n">
         <v>1392.909789</v>
       </c>
+      <c r="K24" t="n">
+        <v>1417.841848</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1268,9 +1306,7 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>309.29352</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>527.454688</v>
       </c>
@@ -1295,6 +1331,9 @@
       <c r="J25" t="n">
         <v>283.950176</v>
       </c>
+      <c r="K25" t="n">
+        <v>473.685355</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1302,9 +1341,7 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>972.210448</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>3770.951635</v>
       </c>
@@ -1329,6 +1366,9 @@
       <c r="J26" t="n">
         <v>940.165023</v>
       </c>
+      <c r="K26" t="n">
+        <v>856.65935</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1336,9 +1376,7 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1448.419276</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>2137.2157825</v>
       </c>
@@ -1363,6 +1401,9 @@
       <c r="J27" t="n">
         <v>3171.539994</v>
       </c>
+      <c r="K27" t="n">
+        <v>3402.919164</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1370,9 +1411,7 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1444.859941</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>1127.132142</v>
       </c>
@@ -1397,6 +1436,9 @@
       <c r="J28" t="n">
         <v>2430.059817</v>
       </c>
+      <c r="K28" t="n">
+        <v>3580.875052</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1405,31 +1447,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1874.387937</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2796.918538</v>
+        <v>2796.171064</v>
       </c>
       <c r="D29" t="n">
-        <v>1159.083804</v>
+        <v>1158.398251</v>
       </c>
       <c r="E29" t="n">
-        <v>1204.082537</v>
+        <v>1202.147611</v>
       </c>
       <c r="F29" t="n">
-        <v>1371.787172</v>
+        <v>1370.488331</v>
       </c>
       <c r="G29" t="n">
-        <v>1143.675889666667</v>
+        <v>1143.403515666667</v>
       </c>
       <c r="H29" t="n">
-        <v>1175.57370525</v>
+        <v>1174.58162225</v>
       </c>
       <c r="I29" t="n">
-        <v>1745.240304</v>
+        <v>1744.842309</v>
       </c>
       <c r="J29" t="n">
-        <v>1111.336422</v>
+        <v>1110.721052</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1187.202675666667</v>
       </c>
     </row>
     <row r="30">
@@ -1438,9 +1483,7 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1593.900291</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>931.223287</v>
       </c>
@@ -1465,6 +1508,9 @@
       <c r="J30" t="n">
         <v>1434.343204</v>
       </c>
+      <c r="K30" t="n">
+        <v>6893.350654</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1472,9 +1518,7 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>181.541844</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>309.229901</v>
       </c>
@@ -1499,6 +1543,9 @@
       <c r="J31" t="n">
         <v>150.92435</v>
       </c>
+      <c r="K31" t="n">
+        <v>244.369154</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1506,9 +1553,7 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>3919.093005</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>2995.886457</v>
       </c>
@@ -1533,6 +1578,9 @@
       <c r="J32" t="n">
         <v>2066.430581</v>
       </c>
+      <c r="K32" t="n">
+        <v>2022.323227</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1541,31 +1589,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3576.81368125</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>4231.049639</v>
+        <v>4224.64068</v>
       </c>
       <c r="D33" t="n">
-        <v>3152.723616083334</v>
+        <v>3145.755844083334</v>
       </c>
       <c r="E33" t="n">
-        <v>2054.422690333333</v>
+        <v>2045.924671333333</v>
       </c>
       <c r="F33" t="n">
-        <v>3157.254720666666</v>
+        <v>3142.089271666667</v>
       </c>
       <c r="G33" t="n">
-        <v>4047.266548166667</v>
+        <v>4037.758222166667</v>
       </c>
       <c r="H33" t="n">
-        <v>2730.1196475</v>
+        <v>2720.3130545</v>
       </c>
       <c r="I33" t="n">
-        <v>2356.587739416666</v>
+        <v>2335.765235416667</v>
       </c>
       <c r="J33" t="n">
-        <v>1786.66304375</v>
+        <v>1768.65947375</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2005.192064</v>
       </c>
     </row>
     <row r="34">
@@ -1574,9 +1625,7 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>20499.14281033333</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>16008.9466375</v>
       </c>
@@ -1601,6 +1650,9 @@
       <c r="J34" t="n">
         <v>37426.999642</v>
       </c>
+      <c r="K34" t="n">
+        <v>51575.626586</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1608,9 +1660,7 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1434.127968</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>864.776533</v>
       </c>
@@ -1633,7 +1683,10 @@
         <v>1830.670428</v>
       </c>
       <c r="J35" t="n">
-        <v>1885.095466</v>
+        <v>1965.363705</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3018.006728</v>
       </c>
     </row>
     <row r="36">
@@ -1642,9 +1695,7 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1986.142069</v>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>1649.814433333333</v>
       </c>
@@ -1669,6 +1720,9 @@
       <c r="J36" t="n">
         <v>1921.06941</v>
       </c>
+      <c r="K36" t="n">
+        <v>4151.709985</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1676,9 +1730,7 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>10602.834135</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>9503.746923999999</v>
       </c>
@@ -1703,6 +1755,9 @@
       <c r="J37" t="n">
         <v>14425.671246</v>
       </c>
+      <c r="K37" t="n">
+        <v>15693.638504</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1710,9 +1765,7 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1186.517079</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>2327.684013</v>
       </c>
@@ -1737,6 +1790,9 @@
       <c r="J38" t="n">
         <v>812.177107</v>
       </c>
+      <c r="K38" t="n">
+        <v>487.561978</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1744,9 +1800,7 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>4775.668836</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>5293.7077845</v>
       </c>
@@ -1771,6 +1825,9 @@
       <c r="J39" t="n">
         <v>4283.101274</v>
       </c>
+      <c r="K39" t="n">
+        <v>4286.426380333333</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1778,9 +1835,7 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>45038.042564</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>38221.871131</v>
       </c>
@@ -1805,6 +1860,9 @@
       <c r="J40" t="n">
         <v>48833.372017</v>
       </c>
+      <c r="K40" t="n">
+        <v>111204.781678</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1812,9 +1870,7 @@
           <t>觀光</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>151.63697</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>128.294805</v>
       </c>
@@ -1828,16 +1884,19 @@
         <v>156.903562</v>
       </c>
       <c r="G41" t="n">
-        <v>164.3006155</v>
+        <v>164.2989565</v>
       </c>
       <c r="H41" t="n">
-        <v>143.66717925</v>
+        <v>143.66557425</v>
       </c>
       <c r="I41" t="n">
-        <v>155.329028</v>
+        <v>155.325723</v>
       </c>
       <c r="J41" t="n">
-        <v>110.388879</v>
+        <v>110.384575</v>
+      </c>
+      <c r="K41" t="n">
+        <v>140.993987</v>
       </c>
     </row>
     <row r="42">
@@ -1846,9 +1905,7 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>57852.103144</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>55538.57203</v>
       </c>
@@ -1873,6 +1930,9 @@
       <c r="J42" t="n">
         <v>37022.409219</v>
       </c>
+      <c r="K42" t="n">
+        <v>40027.06992</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1880,9 +1940,7 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>153.339739</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>214.148055</v>
       </c>
@@ -1907,6 +1965,9 @@
       <c r="J43" t="n">
         <v>144.108749</v>
       </c>
+      <c r="K43" t="n">
+        <v>151.587706</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1914,9 +1975,7 @@
           <t>資訊服務</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>550.6252469999999</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>568.934852</v>
       </c>
@@ -1941,6 +2000,9 @@
       <c r="J44" t="n">
         <v>466.65060525</v>
       </c>
+      <c r="K44" t="n">
+        <v>249.136108</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1948,9 +2010,7 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>629.646796</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>554.498075</v>
       </c>
@@ -1975,6 +2035,9 @@
       <c r="J45" t="n">
         <v>612.678449</v>
       </c>
+      <c r="K45" t="n">
+        <v>779.085259</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1982,9 +2045,7 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0.012402</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>0.005706</v>
       </c>
@@ -2009,6 +2070,9 @@
       <c r="J46" t="n">
         <v>0.004504</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.023117</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2016,9 +2080,7 @@
           <t>通信網路</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>3227.005332</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>2285.728811</v>
       </c>
@@ -2043,6 +2105,9 @@
       <c r="J47" t="n">
         <v>1946.205721</v>
       </c>
+      <c r="K47" t="n">
+        <v>2257.682552</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2050,9 +2115,7 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>113.137448</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>81.686544</v>
       </c>
@@ -2077,6 +2140,9 @@
       <c r="J48" t="n">
         <v>103.558187</v>
       </c>
+      <c r="K48" t="n">
+        <v>646.385315</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -2084,9 +2150,7 @@
           <t>連接器</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>10630.8634</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>12588.924363</v>
       </c>
@@ -2111,6 +2175,9 @@
       <c r="J49" t="n">
         <v>9302.300510999999</v>
       </c>
+      <c r="K49" t="n">
+        <v>10160.952478</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -2118,9 +2185,7 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>604.192691</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>740.053436</v>
       </c>
@@ -2145,6 +2210,9 @@
       <c r="J50" t="n">
         <v>622.302297</v>
       </c>
+      <c r="K50" t="n">
+        <v>977.906638</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2152,9 +2220,7 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.018883</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0.014946</v>
       </c>
@@ -2179,6 +2245,9 @@
       <c r="J51" t="n">
         <v>0.021222</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.026907</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -2186,9 +2255,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>8148.055404666667</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>9224.021632</v>
       </c>
@@ -2213,6 +2280,9 @@
       <c r="J52" t="n">
         <v>7452.984238</v>
       </c>
+      <c r="K52" t="n">
+        <v>7304.302374</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2220,9 +2290,7 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>2784.567429</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>2840.801426</v>
       </c>
@@ -2247,6 +2315,9 @@
       <c r="J53" t="n">
         <v>1879.15980825</v>
       </c>
+      <c r="K53" t="n">
+        <v>3532.391397</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -2254,9 +2325,7 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>206.789119</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>486.365714</v>
       </c>
@@ -2281,6 +2350,9 @@
       <c r="J54" t="n">
         <v>329.846967</v>
       </c>
+      <c r="K54" t="n">
+        <v>407.87994</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -2288,9 +2360,7 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>789.765672</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>1208.391141</v>
       </c>
@@ -2315,6 +2385,9 @@
       <c r="J55" t="n">
         <v>1019.972816</v>
       </c>
+      <c r="K55" t="n">
+        <v>1027.931012</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2322,9 +2395,7 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>13781.334479</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>8485.200322000001</v>
       </c>
@@ -2349,6 +2420,9 @@
       <c r="J56" t="n">
         <v>13127.663375</v>
       </c>
+      <c r="K56" t="n">
+        <v>8039.549699</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2356,9 +2430,7 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>211.287875</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>134.946384</v>
       </c>
@@ -2383,6 +2455,9 @@
       <c r="J57" t="n">
         <v>156.92636</v>
       </c>
+      <c r="K57" t="n">
+        <v>294.384024</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2390,9 +2465,7 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0.846683</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0.86441</v>
       </c>
@@ -2417,6 +2490,9 @@
       <c r="J58" t="n">
         <v>1.650141</v>
       </c>
+      <c r="K58" t="n">
+        <v>0.983734</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2424,9 +2500,7 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>3874.059874</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>3231.589884</v>
       </c>
@@ -2451,6 +2525,9 @@
       <c r="J59" t="n">
         <v>2359.443202</v>
       </c>
+      <c r="K59" t="n">
+        <v>2828.691759</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2458,9 +2535,7 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>10163.667076</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>14283.112728</v>
       </c>
@@ -2485,6 +2560,9 @@
       <c r="J60" t="n">
         <v>19432.335148</v>
       </c>
+      <c r="K60" t="n">
+        <v>12667.172518</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2493,31 +2571,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2654.157778</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>1915.343968333333</v>
+        <v>1915.343102333333</v>
       </c>
       <c r="D61" t="n">
-        <v>2833.24706325</v>
+        <v>2833.24616725</v>
       </c>
       <c r="E61" t="n">
-        <v>3220.483233</v>
+        <v>3220.478314</v>
       </c>
       <c r="F61" t="n">
-        <v>3455.685055</v>
+        <v>3455.682265</v>
       </c>
       <c r="G61" t="n">
-        <v>2850.61244775</v>
+        <v>2850.60731175</v>
       </c>
       <c r="H61" t="n">
-        <v>2993.695927</v>
+        <v>2993.69383</v>
       </c>
       <c r="I61" t="n">
-        <v>2674.10022075</v>
+        <v>2674.09713375</v>
       </c>
       <c r="J61" t="n">
-        <v>2069.6081</v>
+        <v>2069.605911</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1959.642758</v>
       </c>
     </row>
     <row r="62">
@@ -2527,31 +2608,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2761.665087</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>2220.286172</v>
+        <v>2208.565915</v>
       </c>
       <c r="D62" t="n">
-        <v>3864.484353</v>
+        <v>3855.509947</v>
       </c>
       <c r="E62" t="n">
-        <v>3658.219779</v>
+        <v>3600.229293</v>
       </c>
       <c r="F62" t="n">
-        <v>3713.579148</v>
+        <v>3649.210777</v>
       </c>
       <c r="G62" t="n">
-        <v>5625.03953</v>
+        <v>5574.354356</v>
       </c>
       <c r="H62" t="n">
-        <v>5045.504785</v>
+        <v>5000.174158</v>
       </c>
       <c r="I62" t="n">
-        <v>4618.943971</v>
+        <v>4563.137917</v>
       </c>
       <c r="J62" t="n">
-        <v>4452.85462</v>
+        <v>4398.736399</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3519.123271</v>
       </c>
     </row>
     <row r="63">
@@ -2560,9 +2644,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>67962.25039299999</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>44299.675634</v>
       </c>
@@ -2587,6 +2669,9 @@
       <c r="J63" t="n">
         <v>25340.859125</v>
       </c>
+      <c r="K63" t="n">
+        <v>18413.67049</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2594,9 +2679,7 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>932.27086</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>894.284195</v>
       </c>
@@ -2620,6 +2703,9 @@
       </c>
       <c r="J64" t="n">
         <v>1288.255756</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1442.587978</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -491,33 +486,32 @@
           <t>AI伺服器</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>85140.476152</v>
+      </c>
       <c r="C2" t="n">
-        <v>88280.45979350001</v>
+        <v>97469.493455</v>
       </c>
       <c r="D2" t="n">
-        <v>85140.476152</v>
+        <v>93023.65412000001</v>
       </c>
       <c r="E2" t="n">
-        <v>97469.493455</v>
+        <v>80100.52979</v>
       </c>
       <c r="F2" t="n">
-        <v>93023.65412000001</v>
+        <v>79486.70570525</v>
       </c>
       <c r="G2" t="n">
-        <v>80100.52979</v>
+        <v>129848.67474</v>
       </c>
       <c r="H2" t="n">
-        <v>79486.70570525</v>
+        <v>116164.155528</v>
       </c>
       <c r="I2" t="n">
-        <v>129848.67474</v>
+        <v>89863.707416</v>
       </c>
       <c r="J2" t="n">
-        <v>116164.155528</v>
-      </c>
-      <c r="K2" t="n">
-        <v>89863.707416</v>
+        <v>82060.97606299999</v>
       </c>
     </row>
     <row r="3">
@@ -526,33 +520,32 @@
           <t>AI應用服務</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>1051.289579</v>
+      </c>
       <c r="C3" t="n">
-        <v>1293.691735</v>
+        <v>1205.972422</v>
       </c>
       <c r="D3" t="n">
-        <v>1051.289579</v>
+        <v>1376.309944</v>
       </c>
       <c r="E3" t="n">
-        <v>1205.972422</v>
+        <v>1788.730843</v>
       </c>
       <c r="F3" t="n">
-        <v>1376.309944</v>
+        <v>1316.92416</v>
       </c>
       <c r="G3" t="n">
-        <v>1788.730843</v>
+        <v>1865.378455</v>
       </c>
       <c r="H3" t="n">
-        <v>1316.92416</v>
+        <v>1171.961645</v>
       </c>
       <c r="I3" t="n">
-        <v>1865.378455</v>
+        <v>1231.619958</v>
       </c>
       <c r="J3" t="n">
-        <v>1171.961645</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1231.619958</v>
+        <v>1351.696174</v>
       </c>
     </row>
     <row r="4">
@@ -561,33 +554,32 @@
           <t>AI晶片</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>138946.48812</v>
+      </c>
       <c r="C4" t="n">
-        <v>166179.907213</v>
+        <v>189646.737822</v>
       </c>
       <c r="D4" t="n">
-        <v>138946.48812</v>
+        <v>182760.686487</v>
       </c>
       <c r="E4" t="n">
-        <v>189646.737822</v>
+        <v>128660.880246</v>
       </c>
       <c r="F4" t="n">
-        <v>182760.686487</v>
+        <v>123539.16242</v>
       </c>
       <c r="G4" t="n">
-        <v>128660.880246</v>
+        <v>205333.707724</v>
       </c>
       <c r="H4" t="n">
-        <v>123539.16242</v>
+        <v>205533.21934</v>
       </c>
       <c r="I4" t="n">
-        <v>205333.707724</v>
+        <v>162010.552511</v>
       </c>
       <c r="J4" t="n">
-        <v>205533.21934</v>
-      </c>
-      <c r="K4" t="n">
-        <v>162010.552511</v>
+        <v>170431.167476</v>
       </c>
     </row>
     <row r="5">
@@ -596,33 +588,32 @@
           <t>AI電力基建</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1327.895339</v>
+      </c>
       <c r="C5" t="n">
-        <v>1185.034685</v>
+        <v>1707.386623</v>
       </c>
       <c r="D5" t="n">
-        <v>1327.895339</v>
+        <v>1902.962393</v>
       </c>
       <c r="E5" t="n">
-        <v>1707.386623</v>
+        <v>1122.586086</v>
       </c>
       <c r="F5" t="n">
-        <v>1902.962393</v>
+        <v>1601.886093</v>
       </c>
       <c r="G5" t="n">
-        <v>1122.586086</v>
+        <v>1716.223375</v>
       </c>
       <c r="H5" t="n">
-        <v>1601.886093</v>
+        <v>1784.390789</v>
       </c>
       <c r="I5" t="n">
-        <v>1716.223375</v>
+        <v>4443.690148</v>
       </c>
       <c r="J5" t="n">
-        <v>1784.390789</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4443.690148</v>
+        <v>1992.966278</v>
       </c>
     </row>
     <row r="6">
@@ -631,33 +622,32 @@
           <t>PCB載板</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>130648.847117</v>
+      </c>
       <c r="C6" t="n">
-        <v>129515.847183</v>
+        <v>102906.419806</v>
       </c>
       <c r="D6" t="n">
-        <v>130648.847117</v>
+        <v>129641.407368</v>
       </c>
       <c r="E6" t="n">
-        <v>102906.419806</v>
+        <v>140476.595393</v>
       </c>
       <c r="F6" t="n">
-        <v>129641.407368</v>
+        <v>154082.840107</v>
       </c>
       <c r="G6" t="n">
-        <v>140476.595393</v>
+        <v>197491.603846</v>
       </c>
       <c r="H6" t="n">
-        <v>154082.840107</v>
+        <v>165285.893329</v>
       </c>
       <c r="I6" t="n">
-        <v>197491.603846</v>
+        <v>127508.207651</v>
       </c>
       <c r="J6" t="n">
-        <v>165285.893329</v>
-      </c>
-      <c r="K6" t="n">
-        <v>127508.207651</v>
+        <v>101210.657554</v>
       </c>
     </row>
     <row r="7">
@@ -666,33 +656,32 @@
           <t>光學</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>10540.732272</v>
+      </c>
       <c r="C7" t="n">
-        <v>13770.435178</v>
+        <v>13889.568317</v>
       </c>
       <c r="D7" t="n">
-        <v>10540.732272</v>
+        <v>13855.977711</v>
       </c>
       <c r="E7" t="n">
-        <v>13889.568317</v>
+        <v>20448.539832</v>
       </c>
       <c r="F7" t="n">
-        <v>13855.977711</v>
+        <v>15846.945404</v>
       </c>
       <c r="G7" t="n">
-        <v>20448.539832</v>
+        <v>24740.317784</v>
       </c>
       <c r="H7" t="n">
-        <v>15846.945404</v>
+        <v>25336.378851</v>
       </c>
       <c r="I7" t="n">
-        <v>24740.317784</v>
+        <v>22997.890573</v>
       </c>
       <c r="J7" t="n">
-        <v>25336.378851</v>
-      </c>
-      <c r="K7" t="n">
-        <v>22997.890573</v>
+        <v>17549.479583</v>
       </c>
     </row>
     <row r="8">
@@ -701,33 +690,32 @@
           <t>光通訊</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>5236.54811</v>
+      </c>
       <c r="C8" t="n">
-        <v>8165.319383</v>
+        <v>5028.359153</v>
       </c>
       <c r="D8" t="n">
-        <v>5236.54811</v>
+        <v>6200.80261</v>
       </c>
       <c r="E8" t="n">
-        <v>5028.359153</v>
+        <v>5956.565974</v>
       </c>
       <c r="F8" t="n">
-        <v>6200.80261</v>
+        <v>18678.998933</v>
       </c>
       <c r="G8" t="n">
-        <v>5956.565974</v>
+        <v>20069.059953</v>
       </c>
       <c r="H8" t="n">
-        <v>18678.998933</v>
+        <v>13943.679809</v>
       </c>
       <c r="I8" t="n">
-        <v>20069.059953</v>
+        <v>18547.719671</v>
       </c>
       <c r="J8" t="n">
-        <v>13943.679809</v>
-      </c>
-      <c r="K8" t="n">
-        <v>18547.719671</v>
+        <v>11700.144202</v>
       </c>
     </row>
     <row r="9">
@@ -736,33 +724,32 @@
           <t>光電</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>12877.494238</v>
+      </c>
       <c r="C9" t="n">
-        <v>16161.284088</v>
+        <v>12170.44137225</v>
       </c>
       <c r="D9" t="n">
-        <v>12873.954103</v>
+        <v>28574.762822</v>
       </c>
       <c r="E9" t="n">
-        <v>12165.33258825</v>
+        <v>20694.5899575</v>
       </c>
       <c r="F9" t="n">
-        <v>28559.179172</v>
+        <v>18024.656341</v>
       </c>
       <c r="G9" t="n">
-        <v>20689.1994985</v>
+        <v>20594.013322</v>
       </c>
       <c r="H9" t="n">
-        <v>18018.642021</v>
+        <v>19539.969903</v>
       </c>
       <c r="I9" t="n">
-        <v>20582.60128</v>
+        <v>22697.275345</v>
       </c>
       <c r="J9" t="n">
-        <v>19531.356429</v>
-      </c>
-      <c r="K9" t="n">
-        <v>22692.661642</v>
+        <v>15356.4371</v>
       </c>
     </row>
     <row r="10">
@@ -772,34 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1437.9102595</v>
       </c>
       <c r="C10" t="n">
-        <v>2014.80352225</v>
+        <v>1691.566047</v>
       </c>
       <c r="D10" t="n">
-        <v>1437.8998815</v>
+        <v>1739.207265</v>
       </c>
       <c r="E10" t="n">
-        <v>1691.553326</v>
+        <v>2361.4214135</v>
       </c>
       <c r="F10" t="n">
-        <v>1739.186102</v>
+        <v>2507.015691083333</v>
       </c>
       <c r="G10" t="n">
-        <v>2361.4151405</v>
+        <v>2915.59794075</v>
       </c>
       <c r="H10" t="n">
-        <v>2507.005788083333</v>
+        <v>2010.5327855</v>
       </c>
       <c r="I10" t="n">
-        <v>2915.58263275</v>
+        <v>1639.9031125</v>
       </c>
       <c r="J10" t="n">
-        <v>2010.5189185</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1639.8905345</v>
+        <v>1570.4074355</v>
       </c>
     </row>
     <row r="11">
@@ -809,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>5027.901959</v>
       </c>
       <c r="C11" t="n">
-        <v>6391.497263</v>
+        <v>4287.608381</v>
       </c>
       <c r="D11" t="n">
-        <v>5027.754084</v>
+        <v>5741.1415725</v>
       </c>
       <c r="E11" t="n">
-        <v>4287.580833</v>
+        <v>5931.790813</v>
       </c>
       <c r="F11" t="n">
-        <v>5741.1237475</v>
+        <v>5709.634427</v>
       </c>
       <c r="G11" t="n">
-        <v>5931.776942</v>
+        <v>8910.522211</v>
       </c>
       <c r="H11" t="n">
-        <v>5709.595615</v>
+        <v>5980.956098</v>
       </c>
       <c r="I11" t="n">
-        <v>8910.500819000001</v>
+        <v>5153.703854</v>
       </c>
       <c r="J11" t="n">
-        <v>5980.947734</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5153.694491</v>
+        <v>3413.142047</v>
       </c>
     </row>
     <row r="12">
@@ -845,33 +826,32 @@
           <t>功率元件</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>13061.21415</v>
+      </c>
       <c r="C12" t="n">
-        <v>12750.393472</v>
+        <v>11174.18828</v>
       </c>
       <c r="D12" t="n">
-        <v>13057.708287</v>
+        <v>13638.882629</v>
       </c>
       <c r="E12" t="n">
-        <v>11166.867111</v>
+        <v>13065.508176</v>
       </c>
       <c r="F12" t="n">
-        <v>13632.901286</v>
+        <v>13474.480942</v>
       </c>
       <c r="G12" t="n">
-        <v>13057.294924</v>
+        <v>20011.949809</v>
       </c>
       <c r="H12" t="n">
-        <v>13467.645699</v>
+        <v>14586.43468</v>
       </c>
       <c r="I12" t="n">
-        <v>19993.997021</v>
+        <v>12412.488155</v>
       </c>
       <c r="J12" t="n">
-        <v>14579.659067</v>
-      </c>
-      <c r="K12" t="n">
-        <v>12407.582239</v>
+        <v>12900.263706</v>
       </c>
     </row>
     <row r="13">
@@ -880,33 +860,32 @@
           <t>化學</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>3371.427526</v>
+      </c>
       <c r="C13" t="n">
-        <v>5233.847716</v>
+        <v>2394.061638</v>
       </c>
       <c r="D13" t="n">
-        <v>3371.427526</v>
+        <v>4286.652275</v>
       </c>
       <c r="E13" t="n">
-        <v>2394.061638</v>
+        <v>2976.017692</v>
       </c>
       <c r="F13" t="n">
-        <v>4286.652275</v>
+        <v>3786.824192</v>
       </c>
       <c r="G13" t="n">
-        <v>2976.017692</v>
+        <v>4021.459276</v>
       </c>
       <c r="H13" t="n">
-        <v>3786.824192</v>
+        <v>7703.003085</v>
       </c>
       <c r="I13" t="n">
-        <v>4021.459276</v>
+        <v>5986.185579</v>
       </c>
       <c r="J13" t="n">
-        <v>7703.003085</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5986.185579</v>
+        <v>4695.352964</v>
       </c>
     </row>
     <row r="14">
@@ -916,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>14305.724936</v>
       </c>
       <c r="C14" t="n">
-        <v>11120.027229</v>
+        <v>8735.041053249999</v>
       </c>
       <c r="D14" t="n">
-        <v>14305.720707</v>
+        <v>9585.149552999999</v>
       </c>
       <c r="E14" t="n">
-        <v>8735.03156025</v>
+        <v>6695.3773</v>
       </c>
       <c r="F14" t="n">
-        <v>9585.138666999999</v>
+        <v>6646.674439</v>
       </c>
       <c r="G14" t="n">
-        <v>6692.970496</v>
+        <v>9487.406014</v>
       </c>
       <c r="H14" t="n">
-        <v>6643.860699</v>
+        <v>9178.032263999999</v>
       </c>
       <c r="I14" t="n">
-        <v>9485.026313</v>
+        <v>6657.895089</v>
       </c>
       <c r="J14" t="n">
-        <v>9174.399729999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6649.385096</v>
+        <v>5838.202682</v>
       </c>
     </row>
     <row r="15">
@@ -952,33 +928,32 @@
           <t>半導體材料</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>35684.540649</v>
+      </c>
       <c r="C15" t="n">
-        <v>29527.568526</v>
+        <v>33341.832677</v>
       </c>
       <c r="D15" t="n">
-        <v>35684.540649</v>
+        <v>24770.886724</v>
       </c>
       <c r="E15" t="n">
-        <v>33341.832677</v>
+        <v>21506.286768</v>
       </c>
       <c r="F15" t="n">
-        <v>24770.886724</v>
+        <v>33362.212799</v>
       </c>
       <c r="G15" t="n">
-        <v>21506.286768</v>
+        <v>24153.683866</v>
       </c>
       <c r="H15" t="n">
-        <v>33362.212799</v>
+        <v>44202.585443</v>
       </c>
       <c r="I15" t="n">
-        <v>24153.683866</v>
+        <v>31307.142058</v>
       </c>
       <c r="J15" t="n">
-        <v>44202.585443</v>
-      </c>
-      <c r="K15" t="n">
-        <v>31307.142058</v>
+        <v>22968.081151</v>
       </c>
     </row>
     <row r="16">
@@ -987,33 +962,32 @@
           <t>半導體設備</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>18387.097511</v>
+      </c>
       <c r="C16" t="n">
-        <v>28437.085444</v>
+        <v>18772.393694</v>
       </c>
       <c r="D16" t="n">
-        <v>18387.097511</v>
+        <v>23991.340089</v>
       </c>
       <c r="E16" t="n">
-        <v>18772.393694</v>
+        <v>16183.796468</v>
       </c>
       <c r="F16" t="n">
-        <v>23991.340089</v>
+        <v>20919.253641</v>
       </c>
       <c r="G16" t="n">
-        <v>16183.796468</v>
+        <v>21320.266226</v>
       </c>
       <c r="H16" t="n">
-        <v>20919.253641</v>
+        <v>17242.611229</v>
       </c>
       <c r="I16" t="n">
-        <v>21320.266226</v>
+        <v>31532.197277</v>
       </c>
       <c r="J16" t="n">
-        <v>17242.611229</v>
-      </c>
-      <c r="K16" t="n">
-        <v>31532.197277</v>
+        <v>15866.876911</v>
       </c>
     </row>
     <row r="17">
@@ -1023,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>30953.730487</v>
       </c>
       <c r="C17" t="n">
-        <v>44987.968157</v>
+        <v>28733.570505</v>
       </c>
       <c r="D17" t="n">
-        <v>30953.651489</v>
+        <v>38078.11666</v>
       </c>
       <c r="E17" t="n">
-        <v>28733.507478</v>
+        <v>24953.722837</v>
       </c>
       <c r="F17" t="n">
-        <v>38078.083922</v>
+        <v>41336.354249</v>
       </c>
       <c r="G17" t="n">
-        <v>24953.469361</v>
+        <v>46582.502105</v>
       </c>
       <c r="H17" t="n">
-        <v>41336.094343</v>
+        <v>44569.088771</v>
       </c>
       <c r="I17" t="n">
-        <v>46582.338652</v>
+        <v>38390.21865</v>
       </c>
       <c r="J17" t="n">
-        <v>44567.919497</v>
-      </c>
-      <c r="K17" t="n">
-        <v>38389.504465</v>
+        <v>46809.599087</v>
       </c>
     </row>
     <row r="18">
@@ -1059,33 +1030,32 @@
           <t>導線架</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1374.791349</v>
+      </c>
       <c r="C18" t="n">
-        <v>1567.479099</v>
+        <v>931.905278</v>
       </c>
       <c r="D18" t="n">
-        <v>1374.791349</v>
+        <v>1551.429113</v>
       </c>
       <c r="E18" t="n">
-        <v>931.905278</v>
+        <v>916.4080719999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1551.429113</v>
+        <v>1259.522176</v>
       </c>
       <c r="G18" t="n">
-        <v>916.4080719999999</v>
+        <v>2058.870186</v>
       </c>
       <c r="H18" t="n">
-        <v>1259.522176</v>
+        <v>1142.857343</v>
       </c>
       <c r="I18" t="n">
-        <v>2058.870186</v>
+        <v>2181.757307</v>
       </c>
       <c r="J18" t="n">
-        <v>1142.857343</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2181.757307</v>
+        <v>851.002673</v>
       </c>
     </row>
     <row r="19">
@@ -1094,33 +1064,32 @@
           <t>居家生活</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>85.07476275</v>
+      </c>
       <c r="C19" t="n">
-        <v>110.671611</v>
+        <v>226.0066173333333</v>
       </c>
       <c r="D19" t="n">
-        <v>85.07476275</v>
+        <v>157.437316</v>
       </c>
       <c r="E19" t="n">
-        <v>226.0066173333333</v>
+        <v>90.02030033333332</v>
       </c>
       <c r="F19" t="n">
-        <v>157.437316</v>
+        <v>86.055667</v>
       </c>
       <c r="G19" t="n">
-        <v>90.02030033333332</v>
+        <v>94.680183</v>
       </c>
       <c r="H19" t="n">
-        <v>86.055667</v>
+        <v>102.442166</v>
       </c>
       <c r="I19" t="n">
-        <v>94.680183</v>
+        <v>136.288246</v>
       </c>
       <c r="J19" t="n">
-        <v>102.442166</v>
-      </c>
-      <c r="K19" t="n">
-        <v>136.288246</v>
+        <v>112.358103</v>
       </c>
     </row>
     <row r="20">
@@ -1129,33 +1098,32 @@
           <t>工業自動化</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>17169.781569</v>
+      </c>
       <c r="C20" t="n">
-        <v>18556.167825</v>
+        <v>26765.247924</v>
       </c>
       <c r="D20" t="n">
-        <v>17169.781569</v>
+        <v>21132.136662</v>
       </c>
       <c r="E20" t="n">
-        <v>26765.247924</v>
+        <v>11587.069143</v>
       </c>
       <c r="F20" t="n">
-        <v>21132.136662</v>
+        <v>11464.949012</v>
       </c>
       <c r="G20" t="n">
-        <v>11587.069143</v>
+        <v>35323.290674</v>
       </c>
       <c r="H20" t="n">
-        <v>11464.949012</v>
+        <v>30712.336311</v>
       </c>
       <c r="I20" t="n">
-        <v>35323.290674</v>
+        <v>21687.438595</v>
       </c>
       <c r="J20" t="n">
-        <v>30712.336311</v>
-      </c>
-      <c r="K20" t="n">
-        <v>21687.438595</v>
+        <v>10881.654325</v>
       </c>
     </row>
     <row r="21">
@@ -1164,33 +1132,32 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>3318.479694</v>
+      </c>
       <c r="C21" t="n">
-        <v>3139.560877</v>
+        <v>5802.953388</v>
       </c>
       <c r="D21" t="n">
-        <v>3318.479694</v>
+        <v>3962.280094</v>
       </c>
       <c r="E21" t="n">
-        <v>5802.953388</v>
+        <v>3170.634716</v>
       </c>
       <c r="F21" t="n">
-        <v>3962.280094</v>
+        <v>3466.111153</v>
       </c>
       <c r="G21" t="n">
-        <v>3170.634716</v>
+        <v>3968.727804</v>
       </c>
       <c r="H21" t="n">
-        <v>3466.111153</v>
+        <v>4713.418488</v>
       </c>
       <c r="I21" t="n">
-        <v>3968.727804</v>
+        <v>4481.736606</v>
       </c>
       <c r="J21" t="n">
-        <v>4713.418488</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4481.736606</v>
+        <v>3215.085467</v>
       </c>
     </row>
     <row r="22">
@@ -1199,33 +1166,32 @@
           <t>數位雲端</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>284.626499</v>
+      </c>
       <c r="C22" t="n">
-        <v>332.069325</v>
+        <v>234.591797</v>
       </c>
       <c r="D22" t="n">
-        <v>284.626499</v>
+        <v>213.95378</v>
       </c>
       <c r="E22" t="n">
-        <v>234.591797</v>
+        <v>146.3468013333333</v>
       </c>
       <c r="F22" t="n">
-        <v>213.95378</v>
+        <v>140.418245</v>
       </c>
       <c r="G22" t="n">
-        <v>146.3468013333333</v>
+        <v>213.065646</v>
       </c>
       <c r="H22" t="n">
-        <v>140.418245</v>
+        <v>136.491058</v>
       </c>
       <c r="I22" t="n">
-        <v>213.065646</v>
+        <v>198.7382336666667</v>
       </c>
       <c r="J22" t="n">
-        <v>136.491058</v>
-      </c>
-      <c r="K22" t="n">
-        <v>198.7382336666667</v>
+        <v>95.273578</v>
       </c>
     </row>
     <row r="23">
@@ -1235,34 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4.4233375</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6521165</v>
+        <v>2.78372875</v>
       </c>
       <c r="D23" t="n">
-        <v>4.4170895</v>
+        <v>1.707734</v>
       </c>
       <c r="E23" t="n">
-        <v>2.78047475</v>
+        <v>4.863267</v>
       </c>
       <c r="F23" t="n">
-        <v>1.703674</v>
+        <v>2.496508833333333</v>
       </c>
       <c r="G23" t="n">
-        <v>4.859908</v>
+        <v>1.159543</v>
       </c>
       <c r="H23" t="n">
-        <v>2.490104833333334</v>
+        <v>1.22882325</v>
       </c>
       <c r="I23" t="n">
-        <v>1.150598</v>
+        <v>0.568679</v>
       </c>
       <c r="J23" t="n">
-        <v>1.22426025</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.5626060000000001</v>
+        <v>0.993371</v>
       </c>
     </row>
     <row r="24">
@@ -1271,33 +1234,32 @@
           <t>機器人</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>579.415634</v>
+      </c>
       <c r="C24" t="n">
-        <v>798.4179339999999</v>
+        <v>881.8031559999999</v>
       </c>
       <c r="D24" t="n">
-        <v>579.415634</v>
+        <v>740.897229</v>
       </c>
       <c r="E24" t="n">
-        <v>881.8031559999999</v>
+        <v>612.1953099999999</v>
       </c>
       <c r="F24" t="n">
-        <v>740.897229</v>
+        <v>713.520144</v>
       </c>
       <c r="G24" t="n">
-        <v>612.1953099999999</v>
+        <v>2092.159241</v>
       </c>
       <c r="H24" t="n">
-        <v>713.520144</v>
+        <v>1392.909789</v>
       </c>
       <c r="I24" t="n">
-        <v>2092.159241</v>
+        <v>1417.841848</v>
       </c>
       <c r="J24" t="n">
-        <v>1392.909789</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1417.841848</v>
+        <v>1116.41372</v>
       </c>
     </row>
     <row r="25">
@@ -1306,33 +1268,32 @@
           <t>橡膠</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>285.874826</v>
+      </c>
       <c r="C25" t="n">
-        <v>527.454688</v>
+        <v>324.489912</v>
       </c>
       <c r="D25" t="n">
-        <v>285.874826</v>
+        <v>368.164356</v>
       </c>
       <c r="E25" t="n">
-        <v>324.489912</v>
+        <v>271.009081</v>
       </c>
       <c r="F25" t="n">
-        <v>368.164356</v>
+        <v>414.965774</v>
       </c>
       <c r="G25" t="n">
-        <v>271.009081</v>
+        <v>545.1641</v>
       </c>
       <c r="H25" t="n">
-        <v>414.965774</v>
+        <v>283.950176</v>
       </c>
       <c r="I25" t="n">
-        <v>545.1641</v>
+        <v>473.685355</v>
       </c>
       <c r="J25" t="n">
-        <v>283.950176</v>
-      </c>
-      <c r="K25" t="n">
-        <v>473.685355</v>
+        <v>559.696609</v>
       </c>
     </row>
     <row r="26">
@@ -1341,33 +1302,32 @@
           <t>水泥</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>1284.573526</v>
+      </c>
       <c r="C26" t="n">
-        <v>3770.951635</v>
+        <v>1171.957497</v>
       </c>
       <c r="D26" t="n">
-        <v>1284.573526</v>
+        <v>2992.647381</v>
       </c>
       <c r="E26" t="n">
-        <v>1171.957497</v>
+        <v>1857.383228</v>
       </c>
       <c r="F26" t="n">
-        <v>2992.647381</v>
+        <v>833.4631900000001</v>
       </c>
       <c r="G26" t="n">
-        <v>1857.383228</v>
+        <v>1101.311138</v>
       </c>
       <c r="H26" t="n">
-        <v>833.4631900000001</v>
+        <v>940.165023</v>
       </c>
       <c r="I26" t="n">
-        <v>1101.311138</v>
+        <v>856.65935</v>
       </c>
       <c r="J26" t="n">
-        <v>940.165023</v>
-      </c>
-      <c r="K26" t="n">
-        <v>856.65935</v>
+        <v>1255.344352</v>
       </c>
     </row>
     <row r="27">
@@ -1376,33 +1336,32 @@
           <t>汽車</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>1431.344338</v>
+      </c>
       <c r="C27" t="n">
-        <v>2137.2157825</v>
+        <v>2011.716407</v>
       </c>
       <c r="D27" t="n">
-        <v>1431.344338</v>
+        <v>3199.267601</v>
       </c>
       <c r="E27" t="n">
-        <v>2011.716407</v>
+        <v>1435.937866</v>
       </c>
       <c r="F27" t="n">
-        <v>3199.267601</v>
+        <v>2005.650755</v>
       </c>
       <c r="G27" t="n">
-        <v>1435.937866</v>
+        <v>2768.716692</v>
       </c>
       <c r="H27" t="n">
-        <v>2005.650755</v>
+        <v>3171.539994</v>
       </c>
       <c r="I27" t="n">
-        <v>2768.716692</v>
+        <v>3402.919164</v>
       </c>
       <c r="J27" t="n">
-        <v>3171.539994</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3402.919164</v>
+        <v>3001.265492</v>
       </c>
     </row>
     <row r="28">
@@ -1411,33 +1370,32 @@
           <t>油電燃氣</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>953.2518679999999</v>
+      </c>
       <c r="C28" t="n">
-        <v>1127.132142</v>
+        <v>3835.176519</v>
       </c>
       <c r="D28" t="n">
-        <v>953.2518679999999</v>
+        <v>3658.626385</v>
       </c>
       <c r="E28" t="n">
-        <v>3835.176519</v>
+        <v>2593.799925</v>
       </c>
       <c r="F28" t="n">
-        <v>3658.626385</v>
+        <v>3556.848112</v>
       </c>
       <c r="G28" t="n">
-        <v>2593.799925</v>
+        <v>2011.55405</v>
       </c>
       <c r="H28" t="n">
-        <v>3556.848112</v>
+        <v>2430.059817</v>
       </c>
       <c r="I28" t="n">
-        <v>2011.55405</v>
+        <v>3580.875052</v>
       </c>
       <c r="J28" t="n">
-        <v>2430.059817</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3580.875052</v>
+        <v>4567.160092</v>
       </c>
     </row>
     <row r="29">
@@ -1447,34 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1159.083804</v>
       </c>
       <c r="C29" t="n">
-        <v>2796.171064</v>
+        <v>1204.082537</v>
       </c>
       <c r="D29" t="n">
-        <v>1158.398251</v>
+        <v>1371.787172</v>
       </c>
       <c r="E29" t="n">
-        <v>1202.147611</v>
+        <v>1143.675889666667</v>
       </c>
       <c r="F29" t="n">
-        <v>1370.488331</v>
+        <v>1175.57370525</v>
       </c>
       <c r="G29" t="n">
-        <v>1143.403515666667</v>
+        <v>1745.240304</v>
       </c>
       <c r="H29" t="n">
-        <v>1174.58162225</v>
+        <v>1111.336422</v>
       </c>
       <c r="I29" t="n">
-        <v>1744.842309</v>
+        <v>1187.944573666667</v>
       </c>
       <c r="J29" t="n">
-        <v>1110.721052</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1187.202675666667</v>
+        <v>1047.138752666667</v>
       </c>
     </row>
     <row r="30">
@@ -1483,33 +1438,32 @@
           <t>玻璃</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>464.349189</v>
+      </c>
       <c r="C30" t="n">
-        <v>931.223287</v>
+        <v>460.082038</v>
       </c>
       <c r="D30" t="n">
-        <v>464.349189</v>
+        <v>1411.506215</v>
       </c>
       <c r="E30" t="n">
-        <v>460.082038</v>
+        <v>913.096038</v>
       </c>
       <c r="F30" t="n">
-        <v>1411.506215</v>
+        <v>716.628303</v>
       </c>
       <c r="G30" t="n">
-        <v>913.096038</v>
+        <v>1391.651459</v>
       </c>
       <c r="H30" t="n">
-        <v>716.628303</v>
+        <v>1434.343204</v>
       </c>
       <c r="I30" t="n">
-        <v>1391.651459</v>
+        <v>6893.350654</v>
       </c>
       <c r="J30" t="n">
-        <v>1434.343204</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6893.350654</v>
+        <v>10313.913704</v>
       </c>
     </row>
     <row r="31">
@@ -1518,33 +1472,32 @@
           <t>玻璃陶瓷</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>337.289111</v>
+      </c>
       <c r="C31" t="n">
-        <v>309.229901</v>
+        <v>1395.007583</v>
       </c>
       <c r="D31" t="n">
-        <v>337.289111</v>
+        <v>981.782769</v>
       </c>
       <c r="E31" t="n">
-        <v>1395.007583</v>
+        <v>300.275675</v>
       </c>
       <c r="F31" t="n">
-        <v>981.782769</v>
+        <v>573.402185</v>
       </c>
       <c r="G31" t="n">
-        <v>300.275675</v>
+        <v>257.059214</v>
       </c>
       <c r="H31" t="n">
-        <v>573.402185</v>
+        <v>150.92435</v>
       </c>
       <c r="I31" t="n">
-        <v>257.059214</v>
+        <v>244.369154</v>
       </c>
       <c r="J31" t="n">
-        <v>150.92435</v>
-      </c>
-      <c r="K31" t="n">
-        <v>244.369154</v>
+        <v>117.926959</v>
       </c>
     </row>
     <row r="32">
@@ -1553,33 +1506,32 @@
           <t>生技</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>1914.022671</v>
+      </c>
       <c r="C32" t="n">
-        <v>2995.886457</v>
+        <v>2767.071807</v>
       </c>
       <c r="D32" t="n">
-        <v>1914.022671</v>
+        <v>2175.603754</v>
       </c>
       <c r="E32" t="n">
-        <v>2767.071807</v>
+        <v>3293.053983</v>
       </c>
       <c r="F32" t="n">
-        <v>2175.603754</v>
+        <v>1634.098594</v>
       </c>
       <c r="G32" t="n">
-        <v>3293.053983</v>
+        <v>2034.884553</v>
       </c>
       <c r="H32" t="n">
-        <v>1634.098594</v>
+        <v>2066.430581</v>
       </c>
       <c r="I32" t="n">
-        <v>2034.884553</v>
+        <v>2022.323227</v>
       </c>
       <c r="J32" t="n">
-        <v>2066.430581</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2022.323227</v>
+        <v>2379.973052</v>
       </c>
     </row>
     <row r="33">
@@ -1589,34 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>3152.723616083334</v>
       </c>
       <c r="C33" t="n">
-        <v>4224.64068</v>
+        <v>2054.422690333333</v>
       </c>
       <c r="D33" t="n">
-        <v>3145.755844083334</v>
+        <v>3157.254720666666</v>
       </c>
       <c r="E33" t="n">
-        <v>2045.924671333333</v>
+        <v>4047.266548166667</v>
       </c>
       <c r="F33" t="n">
-        <v>3142.089271666667</v>
+        <v>2730.1196475</v>
       </c>
       <c r="G33" t="n">
-        <v>4037.758222166667</v>
+        <v>2356.587739416666</v>
       </c>
       <c r="H33" t="n">
-        <v>2720.3130545</v>
+        <v>1786.66304375</v>
       </c>
       <c r="I33" t="n">
-        <v>2335.765235416667</v>
+        <v>2015.060599</v>
       </c>
       <c r="J33" t="n">
-        <v>1768.65947375</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2005.192064</v>
+        <v>1769.755592083333</v>
       </c>
     </row>
     <row r="34">
@@ -1625,33 +1574,32 @@
           <t>石化</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>18522.008159</v>
+      </c>
       <c r="C34" t="n">
-        <v>16008.9466375</v>
+        <v>24138.976642</v>
       </c>
       <c r="D34" t="n">
-        <v>18522.008159</v>
+        <v>38592.8304785</v>
       </c>
       <c r="E34" t="n">
-        <v>24138.976642</v>
+        <v>17726.891727</v>
       </c>
       <c r="F34" t="n">
-        <v>38592.8304785</v>
+        <v>18001.843649</v>
       </c>
       <c r="G34" t="n">
-        <v>17726.891727</v>
+        <v>29683.7204415</v>
       </c>
       <c r="H34" t="n">
-        <v>18001.843649</v>
+        <v>37426.999642</v>
       </c>
       <c r="I34" t="n">
-        <v>29683.7204415</v>
+        <v>51575.626586</v>
       </c>
       <c r="J34" t="n">
-        <v>37426.999642</v>
-      </c>
-      <c r="K34" t="n">
-        <v>51575.626586</v>
+        <v>50158.028725</v>
       </c>
     </row>
     <row r="35">
@@ -1660,33 +1608,32 @@
           <t>紡織</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>907.837418</v>
+      </c>
       <c r="C35" t="n">
-        <v>864.776533</v>
+        <v>883.170031</v>
       </c>
       <c r="D35" t="n">
-        <v>907.837418</v>
+        <v>1354.065363</v>
       </c>
       <c r="E35" t="n">
-        <v>883.170031</v>
+        <v>1121.706863</v>
       </c>
       <c r="F35" t="n">
-        <v>1354.065363</v>
+        <v>932.818224</v>
       </c>
       <c r="G35" t="n">
-        <v>1121.706863</v>
+        <v>1830.670428</v>
       </c>
       <c r="H35" t="n">
-        <v>932.818224</v>
+        <v>1965.363705</v>
       </c>
       <c r="I35" t="n">
-        <v>1830.670428</v>
+        <v>3121.055908</v>
       </c>
       <c r="J35" t="n">
-        <v>1965.363705</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3018.006728</v>
+        <v>2532.299892</v>
       </c>
     </row>
     <row r="36">
@@ -1695,33 +1642,32 @@
           <t>綠能</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>1741.438457</v>
+      </c>
       <c r="C36" t="n">
-        <v>1649.814433333333</v>
+        <v>1913.072300666667</v>
       </c>
       <c r="D36" t="n">
-        <v>1741.438457</v>
+        <v>2251.441003</v>
       </c>
       <c r="E36" t="n">
-        <v>1913.072300666667</v>
+        <v>1989.455276</v>
       </c>
       <c r="F36" t="n">
-        <v>2251.441003</v>
+        <v>2036.013433</v>
       </c>
       <c r="G36" t="n">
-        <v>1989.455276</v>
+        <v>3601.325495</v>
       </c>
       <c r="H36" t="n">
-        <v>2036.013433</v>
+        <v>1921.06941</v>
       </c>
       <c r="I36" t="n">
-        <v>3601.325495</v>
+        <v>4151.709985</v>
       </c>
       <c r="J36" t="n">
-        <v>1921.06941</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4151.709985</v>
+        <v>2968.90518925</v>
       </c>
     </row>
     <row r="37">
@@ -1730,33 +1676,32 @@
           <t>網通</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>6766.767165</v>
+      </c>
       <c r="C37" t="n">
-        <v>9503.746923999999</v>
+        <v>9354.171284</v>
       </c>
       <c r="D37" t="n">
-        <v>6766.767165</v>
+        <v>14735.204401</v>
       </c>
       <c r="E37" t="n">
-        <v>9354.171284</v>
+        <v>12505.335512</v>
       </c>
       <c r="F37" t="n">
-        <v>14735.204401</v>
+        <v>12181.591653</v>
       </c>
       <c r="G37" t="n">
-        <v>12505.335512</v>
+        <v>17010.454022</v>
       </c>
       <c r="H37" t="n">
-        <v>12181.591653</v>
+        <v>14425.671246</v>
       </c>
       <c r="I37" t="n">
-        <v>17010.454022</v>
+        <v>15693.638504</v>
       </c>
       <c r="J37" t="n">
-        <v>14425.671246</v>
-      </c>
-      <c r="K37" t="n">
-        <v>15693.638504</v>
+        <v>11382.659629</v>
       </c>
     </row>
     <row r="38">
@@ -1765,33 +1710,32 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>1364.089271</v>
+      </c>
       <c r="C38" t="n">
-        <v>2327.684013</v>
+        <v>755.371776</v>
       </c>
       <c r="D38" t="n">
-        <v>1364.089271</v>
+        <v>1522.638212</v>
       </c>
       <c r="E38" t="n">
-        <v>755.371776</v>
+        <v>983.322091</v>
       </c>
       <c r="F38" t="n">
-        <v>1522.638212</v>
+        <v>514.825294</v>
       </c>
       <c r="G38" t="n">
-        <v>983.322091</v>
+        <v>678.614001</v>
       </c>
       <c r="H38" t="n">
-        <v>514.825294</v>
+        <v>812.177107</v>
       </c>
       <c r="I38" t="n">
-        <v>678.614001</v>
+        <v>487.561978</v>
       </c>
       <c r="J38" t="n">
-        <v>812.177107</v>
-      </c>
-      <c r="K38" t="n">
-        <v>487.561978</v>
+        <v>614.6217380000001</v>
       </c>
     </row>
     <row r="39">
@@ -1800,33 +1744,32 @@
           <t>航運</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>3869.600446</v>
+      </c>
       <c r="C39" t="n">
-        <v>5293.7077845</v>
+        <v>5798.788543</v>
       </c>
       <c r="D39" t="n">
-        <v>3869.600446</v>
+        <v>3937.918847</v>
       </c>
       <c r="E39" t="n">
-        <v>5798.788543</v>
+        <v>3621.251342</v>
       </c>
       <c r="F39" t="n">
-        <v>3937.918847</v>
+        <v>3802.02835</v>
       </c>
       <c r="G39" t="n">
-        <v>3621.251342</v>
+        <v>5064.0600025</v>
       </c>
       <c r="H39" t="n">
-        <v>3802.02835</v>
+        <v>4283.101274</v>
       </c>
       <c r="I39" t="n">
-        <v>5064.0600025</v>
+        <v>4286.426380333333</v>
       </c>
       <c r="J39" t="n">
-        <v>4283.101274</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4286.426380333333</v>
+        <v>3443.479777</v>
       </c>
     </row>
     <row r="40">
@@ -1835,33 +1778,32 @@
           <t>被動元件</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>38620.855354</v>
+      </c>
       <c r="C40" t="n">
-        <v>38221.871131</v>
+        <v>38787.989586</v>
       </c>
       <c r="D40" t="n">
-        <v>38620.855354</v>
+        <v>26515.935769</v>
       </c>
       <c r="E40" t="n">
-        <v>38787.989586</v>
+        <v>83369.59020000001</v>
       </c>
       <c r="F40" t="n">
-        <v>26515.935769</v>
+        <v>109528.620721</v>
       </c>
       <c r="G40" t="n">
-        <v>83369.59020000001</v>
+        <v>93985.398543</v>
       </c>
       <c r="H40" t="n">
-        <v>109528.620721</v>
+        <v>48833.372017</v>
       </c>
       <c r="I40" t="n">
-        <v>93985.398543</v>
+        <v>111204.781678</v>
       </c>
       <c r="J40" t="n">
-        <v>48833.372017</v>
-      </c>
-      <c r="K40" t="n">
-        <v>111204.781678</v>
+        <v>81211.36083799999</v>
       </c>
     </row>
     <row r="41">
@@ -1870,33 +1812,32 @@
           <t>觀光</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>193.129646</v>
+      </c>
       <c r="C41" t="n">
-        <v>128.294805</v>
+        <v>222.40962075</v>
       </c>
       <c r="D41" t="n">
-        <v>193.129646</v>
+        <v>156.903562</v>
       </c>
       <c r="E41" t="n">
-        <v>222.40962075</v>
+        <v>164.3006155</v>
       </c>
       <c r="F41" t="n">
-        <v>156.903562</v>
+        <v>143.66717925</v>
       </c>
       <c r="G41" t="n">
-        <v>164.2989565</v>
+        <v>155.329028</v>
       </c>
       <c r="H41" t="n">
-        <v>143.66557425</v>
+        <v>110.388879</v>
       </c>
       <c r="I41" t="n">
-        <v>155.325723</v>
+        <v>140.995561</v>
       </c>
       <c r="J41" t="n">
-        <v>110.384575</v>
-      </c>
-      <c r="K41" t="n">
-        <v>140.993987</v>
+        <v>224.812825</v>
       </c>
     </row>
     <row r="42">
@@ -1905,33 +1846,32 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>36425.530521</v>
+      </c>
       <c r="C42" t="n">
-        <v>55538.57203</v>
+        <v>29728.764487</v>
       </c>
       <c r="D42" t="n">
-        <v>36425.530521</v>
+        <v>45172.5952</v>
       </c>
       <c r="E42" t="n">
-        <v>29728.764487</v>
+        <v>32010.529296</v>
       </c>
       <c r="F42" t="n">
-        <v>45172.5952</v>
+        <v>44356.231581</v>
       </c>
       <c r="G42" t="n">
-        <v>32010.529296</v>
+        <v>51876.083843</v>
       </c>
       <c r="H42" t="n">
-        <v>44356.231581</v>
+        <v>37022.409219</v>
       </c>
       <c r="I42" t="n">
-        <v>51876.083843</v>
+        <v>40027.06992</v>
       </c>
       <c r="J42" t="n">
-        <v>37022.409219</v>
-      </c>
-      <c r="K42" t="n">
-        <v>40027.06992</v>
+        <v>58053.714944</v>
       </c>
     </row>
     <row r="43">
@@ -1940,33 +1880,32 @@
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>137.208998</v>
+      </c>
       <c r="C43" t="n">
-        <v>214.148055</v>
+        <v>140.3224923333333</v>
       </c>
       <c r="D43" t="n">
-        <v>137.208998</v>
+        <v>143.673452</v>
       </c>
       <c r="E43" t="n">
-        <v>140.3224923333333</v>
+        <v>126.829217</v>
       </c>
       <c r="F43" t="n">
-        <v>143.673452</v>
+        <v>153.965149</v>
       </c>
       <c r="G43" t="n">
-        <v>126.829217</v>
+        <v>216.040869</v>
       </c>
       <c r="H43" t="n">
-        <v>153.965149</v>
+        <v>144.108749</v>
       </c>
       <c r="I43" t="n">
-        <v>216.040869</v>
+        <v>151.587706</v>
       </c>
       <c r="J43" t="n">
-        <v>144.108749</v>
-      </c>
-      <c r="K43" t="n">
-        <v>151.587706</v>
+        <v>163.816396</v>
       </c>
     </row>
     <row r="44">
@@ -1975,33 +1914,32 @@
           <t>資訊服務</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>572.670523</v>
+      </c>
       <c r="C44" t="n">
-        <v>568.934852</v>
+        <v>273.551237</v>
       </c>
       <c r="D44" t="n">
-        <v>572.670523</v>
+        <v>406.0494</v>
       </c>
       <c r="E44" t="n">
-        <v>273.551237</v>
+        <v>192.38958</v>
       </c>
       <c r="F44" t="n">
-        <v>406.0494</v>
+        <v>159.333061</v>
       </c>
       <c r="G44" t="n">
-        <v>192.38958</v>
+        <v>305.280954</v>
       </c>
       <c r="H44" t="n">
-        <v>159.333061</v>
+        <v>466.65060525</v>
       </c>
       <c r="I44" t="n">
-        <v>305.280954</v>
+        <v>249.136108</v>
       </c>
       <c r="J44" t="n">
-        <v>466.65060525</v>
-      </c>
-      <c r="K44" t="n">
-        <v>249.136108</v>
+        <v>298.11259</v>
       </c>
     </row>
     <row r="45">
@@ -2010,33 +1948,32 @@
           <t>軍工</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>431.843473</v>
+      </c>
       <c r="C45" t="n">
-        <v>554.498075</v>
+        <v>558.7608739999999</v>
       </c>
       <c r="D45" t="n">
-        <v>431.843473</v>
+        <v>827.171639</v>
       </c>
       <c r="E45" t="n">
-        <v>558.7608739999999</v>
+        <v>608.8516980000001</v>
       </c>
       <c r="F45" t="n">
-        <v>827.171639</v>
+        <v>1163.125599</v>
       </c>
       <c r="G45" t="n">
-        <v>608.8516980000001</v>
+        <v>1017.672095</v>
       </c>
       <c r="H45" t="n">
-        <v>1163.125599</v>
+        <v>612.678449</v>
       </c>
       <c r="I45" t="n">
-        <v>1017.672095</v>
+        <v>779.085259</v>
       </c>
       <c r="J45" t="n">
-        <v>612.678449</v>
-      </c>
-      <c r="K45" t="n">
-        <v>779.085259</v>
+        <v>499.480815</v>
       </c>
     </row>
     <row r="46">
@@ -2045,33 +1982,32 @@
           <t>農業科技</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0.005351</v>
+      </c>
       <c r="C46" t="n">
-        <v>0.005706</v>
+        <v>0.003217</v>
       </c>
       <c r="D46" t="n">
-        <v>0.005351</v>
+        <v>0.003287</v>
       </c>
       <c r="E46" t="n">
-        <v>0.003217</v>
+        <v>0.00215</v>
       </c>
       <c r="F46" t="n">
-        <v>0.003287</v>
+        <v>0.002401</v>
       </c>
       <c r="G46" t="n">
-        <v>0.00215</v>
+        <v>0.008321</v>
       </c>
       <c r="H46" t="n">
-        <v>0.002401</v>
+        <v>0.004504</v>
       </c>
       <c r="I46" t="n">
-        <v>0.008321</v>
+        <v>0.023117</v>
       </c>
       <c r="J46" t="n">
-        <v>0.004504</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.023117</v>
+        <v>0.053269</v>
       </c>
     </row>
     <row r="47">
@@ -2080,33 +2016,32 @@
           <t>通信網路</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>2768.183649</v>
+      </c>
       <c r="C47" t="n">
-        <v>2285.728811</v>
+        <v>2160.042912</v>
       </c>
       <c r="D47" t="n">
-        <v>2768.183649</v>
+        <v>2537.16588</v>
       </c>
       <c r="E47" t="n">
-        <v>2160.042912</v>
+        <v>1944.562274</v>
       </c>
       <c r="F47" t="n">
-        <v>2537.16588</v>
+        <v>2607.919254</v>
       </c>
       <c r="G47" t="n">
-        <v>1944.562274</v>
+        <v>3108.633171</v>
       </c>
       <c r="H47" t="n">
-        <v>2607.919254</v>
+        <v>1946.205721</v>
       </c>
       <c r="I47" t="n">
-        <v>3108.633171</v>
+        <v>2257.682552</v>
       </c>
       <c r="J47" t="n">
-        <v>1946.205721</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2257.682552</v>
+        <v>2322.133139</v>
       </c>
     </row>
     <row r="48">
@@ -2115,33 +2050,32 @@
           <t>造紙</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>84.399334</v>
+      </c>
       <c r="C48" t="n">
-        <v>81.686544</v>
+        <v>158.144148</v>
       </c>
       <c r="D48" t="n">
-        <v>84.399334</v>
+        <v>104.815151</v>
       </c>
       <c r="E48" t="n">
-        <v>158.144148</v>
+        <v>152.916565</v>
       </c>
       <c r="F48" t="n">
-        <v>104.815151</v>
+        <v>102.306466</v>
       </c>
       <c r="G48" t="n">
-        <v>152.916565</v>
+        <v>118.380095</v>
       </c>
       <c r="H48" t="n">
-        <v>102.306466</v>
+        <v>103.558187</v>
       </c>
       <c r="I48" t="n">
-        <v>118.380095</v>
+        <v>646.385315</v>
       </c>
       <c r="J48" t="n">
-        <v>103.558187</v>
-      </c>
-      <c r="K48" t="n">
-        <v>646.385315</v>
+        <v>79.011393</v>
       </c>
     </row>
     <row r="49">
@@ -2150,33 +2084,32 @@
           <t>連接器</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>6628.107666</v>
+      </c>
       <c r="C49" t="n">
-        <v>12588.924363</v>
+        <v>7771.289255</v>
       </c>
       <c r="D49" t="n">
-        <v>6628.107666</v>
+        <v>10297.83788</v>
       </c>
       <c r="E49" t="n">
-        <v>7771.289255</v>
+        <v>9437.364121000001</v>
       </c>
       <c r="F49" t="n">
-        <v>10297.83788</v>
+        <v>8742.657853999999</v>
       </c>
       <c r="G49" t="n">
-        <v>9437.364121000001</v>
+        <v>7863.080042</v>
       </c>
       <c r="H49" t="n">
-        <v>8742.657853999999</v>
+        <v>9302.300510999999</v>
       </c>
       <c r="I49" t="n">
-        <v>7863.080042</v>
+        <v>10160.952478</v>
       </c>
       <c r="J49" t="n">
-        <v>9302.300510999999</v>
-      </c>
-      <c r="K49" t="n">
-        <v>10160.952478</v>
+        <v>8078.319146</v>
       </c>
     </row>
     <row r="50">
@@ -2185,33 +2118,32 @@
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>612.497166</v>
+      </c>
       <c r="C50" t="n">
-        <v>740.053436</v>
+        <v>752.428062</v>
       </c>
       <c r="D50" t="n">
-        <v>612.497166</v>
+        <v>692.888991</v>
       </c>
       <c r="E50" t="n">
-        <v>752.428062</v>
+        <v>646.441073</v>
       </c>
       <c r="F50" t="n">
-        <v>692.888991</v>
+        <v>664.655217</v>
       </c>
       <c r="G50" t="n">
-        <v>646.441073</v>
+        <v>1014.851735</v>
       </c>
       <c r="H50" t="n">
-        <v>664.655217</v>
+        <v>622.302297</v>
       </c>
       <c r="I50" t="n">
-        <v>1014.851735</v>
+        <v>977.906638</v>
       </c>
       <c r="J50" t="n">
-        <v>622.302297</v>
-      </c>
-      <c r="K50" t="n">
-        <v>977.906638</v>
+        <v>858.256694</v>
       </c>
     </row>
     <row r="51">
@@ -2220,33 +2152,32 @@
           <t>醫療通路</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0.018067</v>
+      </c>
       <c r="C51" t="n">
-        <v>0.014946</v>
+        <v>0.017467</v>
       </c>
       <c r="D51" t="n">
-        <v>0.018067</v>
+        <v>0.015909</v>
       </c>
       <c r="E51" t="n">
-        <v>0.017467</v>
+        <v>0.010093</v>
       </c>
       <c r="F51" t="n">
-        <v>0.015909</v>
+        <v>0.014062</v>
       </c>
       <c r="G51" t="n">
-        <v>0.010093</v>
+        <v>0.047371</v>
       </c>
       <c r="H51" t="n">
-        <v>0.014062</v>
+        <v>0.021222</v>
       </c>
       <c r="I51" t="n">
-        <v>0.047371</v>
+        <v>0.026907</v>
       </c>
       <c r="J51" t="n">
-        <v>0.021222</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.026907</v>
+        <v>0.07322099999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2255,33 +2186,32 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>5732.684626</v>
+      </c>
       <c r="C52" t="n">
-        <v>9224.021632</v>
+        <v>10246.93227</v>
       </c>
       <c r="D52" t="n">
-        <v>5732.684626</v>
+        <v>8616.418030999999</v>
       </c>
       <c r="E52" t="n">
-        <v>10246.93227</v>
+        <v>10196.150336</v>
       </c>
       <c r="F52" t="n">
-        <v>8616.418030999999</v>
+        <v>6597.266704</v>
       </c>
       <c r="G52" t="n">
-        <v>10196.150336</v>
+        <v>7939.043424</v>
       </c>
       <c r="H52" t="n">
-        <v>6597.266704</v>
+        <v>7452.984238</v>
       </c>
       <c r="I52" t="n">
-        <v>7939.043424</v>
+        <v>7304.302374</v>
       </c>
       <c r="J52" t="n">
-        <v>7452.984238</v>
-      </c>
-      <c r="K52" t="n">
-        <v>7304.302374</v>
+        <v>7877.259995</v>
       </c>
     </row>
     <row r="53">
@@ -2290,33 +2220,32 @@
           <t>鋼鐵</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>2553.3653815</v>
+      </c>
       <c r="C53" t="n">
-        <v>2840.801426</v>
+        <v>3519.341702</v>
       </c>
       <c r="D53" t="n">
-        <v>2553.3653815</v>
+        <v>6191.425248333333</v>
       </c>
       <c r="E53" t="n">
-        <v>3519.341702</v>
+        <v>7155.879135</v>
       </c>
       <c r="F53" t="n">
-        <v>6191.425248333333</v>
+        <v>3091.901302</v>
       </c>
       <c r="G53" t="n">
-        <v>7155.879135</v>
+        <v>3451.97244275</v>
       </c>
       <c r="H53" t="n">
-        <v>3091.901302</v>
+        <v>1879.15980825</v>
       </c>
       <c r="I53" t="n">
-        <v>3451.97244275</v>
+        <v>3532.391397</v>
       </c>
       <c r="J53" t="n">
-        <v>1879.15980825</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3532.391397</v>
+        <v>2544.125352</v>
       </c>
     </row>
     <row r="54">
@@ -2325,33 +2254,32 @@
           <t>零售</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>467.102515</v>
+      </c>
       <c r="C54" t="n">
-        <v>486.365714</v>
+        <v>316.776227</v>
       </c>
       <c r="D54" t="n">
-        <v>467.102515</v>
+        <v>353.129823</v>
       </c>
       <c r="E54" t="n">
-        <v>316.776227</v>
+        <v>467.278976</v>
       </c>
       <c r="F54" t="n">
-        <v>353.129823</v>
+        <v>627.997406</v>
       </c>
       <c r="G54" t="n">
-        <v>467.278976</v>
+        <v>242.656285</v>
       </c>
       <c r="H54" t="n">
-        <v>627.997406</v>
+        <v>329.846967</v>
       </c>
       <c r="I54" t="n">
-        <v>242.656285</v>
+        <v>407.87994</v>
       </c>
       <c r="J54" t="n">
-        <v>329.846967</v>
-      </c>
-      <c r="K54" t="n">
-        <v>407.87994</v>
+        <v>406.750587</v>
       </c>
     </row>
     <row r="55">
@@ -2360,33 +2288,32 @@
           <t>電信</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>918.019598</v>
+      </c>
       <c r="C55" t="n">
-        <v>1208.391141</v>
+        <v>1676.725028</v>
       </c>
       <c r="D55" t="n">
-        <v>918.019598</v>
+        <v>1524.028999</v>
       </c>
       <c r="E55" t="n">
-        <v>1676.725028</v>
+        <v>1248.190797</v>
       </c>
       <c r="F55" t="n">
-        <v>1524.028999</v>
+        <v>1458.3181</v>
       </c>
       <c r="G55" t="n">
-        <v>1248.190797</v>
+        <v>1239.700787</v>
       </c>
       <c r="H55" t="n">
-        <v>1458.3181</v>
+        <v>1019.972816</v>
       </c>
       <c r="I55" t="n">
-        <v>1239.700787</v>
+        <v>1027.931012</v>
       </c>
       <c r="J55" t="n">
-        <v>1019.972816</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1027.931012</v>
+        <v>1338.6324</v>
       </c>
     </row>
     <row r="56">
@@ -2395,33 +2322,32 @@
           <t>電動車</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>10685.838357</v>
+      </c>
       <c r="C56" t="n">
-        <v>8485.200322000001</v>
+        <v>11086.499208</v>
       </c>
       <c r="D56" t="n">
-        <v>10685.838357</v>
+        <v>15936.008962</v>
       </c>
       <c r="E56" t="n">
-        <v>11086.499208</v>
+        <v>7870.13773</v>
       </c>
       <c r="F56" t="n">
-        <v>15936.008962</v>
+        <v>7151.438405</v>
       </c>
       <c r="G56" t="n">
-        <v>7870.13773</v>
+        <v>13323.285339</v>
       </c>
       <c r="H56" t="n">
-        <v>7151.438405</v>
+        <v>13127.663375</v>
       </c>
       <c r="I56" t="n">
-        <v>13323.285339</v>
+        <v>8039.549699</v>
       </c>
       <c r="J56" t="n">
-        <v>13127.663375</v>
-      </c>
-      <c r="K56" t="n">
-        <v>8039.549699</v>
+        <v>8699.740658000001</v>
       </c>
     </row>
     <row r="57">
@@ -2430,33 +2356,32 @@
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>107.918206</v>
+      </c>
       <c r="C57" t="n">
-        <v>134.946384</v>
+        <v>240.957821</v>
       </c>
       <c r="D57" t="n">
-        <v>107.918206</v>
+        <v>280.614387</v>
       </c>
       <c r="E57" t="n">
-        <v>240.957821</v>
+        <v>241.632148</v>
       </c>
       <c r="F57" t="n">
-        <v>280.614387</v>
+        <v>160.750781</v>
       </c>
       <c r="G57" t="n">
-        <v>241.632148</v>
+        <v>199.358638</v>
       </c>
       <c r="H57" t="n">
-        <v>160.750781</v>
+        <v>156.92636</v>
       </c>
       <c r="I57" t="n">
-        <v>199.358638</v>
+        <v>294.384024</v>
       </c>
       <c r="J57" t="n">
-        <v>156.92636</v>
-      </c>
-      <c r="K57" t="n">
-        <v>294.384024</v>
+        <v>264.279907</v>
       </c>
     </row>
     <row r="58">
@@ -2465,33 +2390,32 @@
           <t>電子紙</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0.797876</v>
+      </c>
       <c r="C58" t="n">
-        <v>0.86441</v>
+        <v>1.227215</v>
       </c>
       <c r="D58" t="n">
-        <v>0.797876</v>
+        <v>0.803998</v>
       </c>
       <c r="E58" t="n">
-        <v>1.227215</v>
+        <v>0.610103</v>
       </c>
       <c r="F58" t="n">
-        <v>0.803998</v>
+        <v>0.848656</v>
       </c>
       <c r="G58" t="n">
-        <v>0.610103</v>
+        <v>1.13421</v>
       </c>
       <c r="H58" t="n">
-        <v>0.848656</v>
+        <v>1.650141</v>
       </c>
       <c r="I58" t="n">
-        <v>1.13421</v>
+        <v>0.983734</v>
       </c>
       <c r="J58" t="n">
-        <v>1.650141</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.983734</v>
+        <v>0.538445</v>
       </c>
     </row>
     <row r="59">
@@ -2500,33 +2424,32 @@
           <t>電子通路</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>3117.83436</v>
+      </c>
       <c r="C59" t="n">
-        <v>3231.589884</v>
+        <v>3284.358638</v>
       </c>
       <c r="D59" t="n">
-        <v>3117.83436</v>
+        <v>3269.037075</v>
       </c>
       <c r="E59" t="n">
-        <v>3284.358638</v>
+        <v>4556.196035</v>
       </c>
       <c r="F59" t="n">
-        <v>3269.037075</v>
+        <v>3278.903084</v>
       </c>
       <c r="G59" t="n">
-        <v>4556.196035</v>
+        <v>2987.686914</v>
       </c>
       <c r="H59" t="n">
-        <v>3278.903084</v>
+        <v>2359.443202</v>
       </c>
       <c r="I59" t="n">
-        <v>2987.686914</v>
+        <v>2828.691759</v>
       </c>
       <c r="J59" t="n">
-        <v>2359.443202</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2828.691759</v>
+        <v>4397.447876</v>
       </c>
     </row>
     <row r="60">
@@ -2535,33 +2458,32 @@
           <t>電子零組件</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>15702.55116</v>
+      </c>
       <c r="C60" t="n">
-        <v>14283.112728</v>
+        <v>16339.630617</v>
       </c>
       <c r="D60" t="n">
-        <v>15702.55116</v>
+        <v>13990.739466</v>
       </c>
       <c r="E60" t="n">
-        <v>16339.630617</v>
+        <v>17015.629412</v>
       </c>
       <c r="F60" t="n">
-        <v>13990.739466</v>
+        <v>22387.334106</v>
       </c>
       <c r="G60" t="n">
-        <v>17015.629412</v>
+        <v>21582.243303</v>
       </c>
       <c r="H60" t="n">
-        <v>22387.334106</v>
+        <v>19432.335148</v>
       </c>
       <c r="I60" t="n">
-        <v>21582.243303</v>
+        <v>12667.172518</v>
       </c>
       <c r="J60" t="n">
-        <v>19432.335148</v>
-      </c>
-      <c r="K60" t="n">
-        <v>12667.172518</v>
+        <v>29613.628193</v>
       </c>
     </row>
     <row r="61">
@@ -2571,34 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>2833.24706325</v>
       </c>
       <c r="C61" t="n">
-        <v>1915.343102333333</v>
+        <v>3220.483233</v>
       </c>
       <c r="D61" t="n">
-        <v>2833.24616725</v>
+        <v>3455.685055</v>
       </c>
       <c r="E61" t="n">
-        <v>3220.478314</v>
+        <v>2850.61244775</v>
       </c>
       <c r="F61" t="n">
-        <v>3455.682265</v>
+        <v>2993.695927</v>
       </c>
       <c r="G61" t="n">
-        <v>2850.60731175</v>
+        <v>2674.10022075</v>
       </c>
       <c r="H61" t="n">
-        <v>2993.69383</v>
+        <v>2069.6081</v>
       </c>
       <c r="I61" t="n">
-        <v>2674.09713375</v>
+        <v>1959.657431</v>
       </c>
       <c r="J61" t="n">
-        <v>2069.605911</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1959.642758</v>
+        <v>3331.120676</v>
       </c>
     </row>
     <row r="62">
@@ -2608,34 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>3864.484353</v>
       </c>
       <c r="C62" t="n">
-        <v>2208.565915</v>
+        <v>3658.219779</v>
       </c>
       <c r="D62" t="n">
-        <v>3855.509947</v>
+        <v>3713.579148</v>
       </c>
       <c r="E62" t="n">
-        <v>3600.229293</v>
+        <v>5625.03953</v>
       </c>
       <c r="F62" t="n">
-        <v>3649.210777</v>
+        <v>5045.504785</v>
       </c>
       <c r="G62" t="n">
-        <v>5574.354356</v>
+        <v>4618.943971</v>
       </c>
       <c r="H62" t="n">
-        <v>5000.174158</v>
+        <v>4452.85462</v>
       </c>
       <c r="I62" t="n">
-        <v>4563.137917</v>
+        <v>3549.041004</v>
       </c>
       <c r="J62" t="n">
-        <v>4398.736399</v>
-      </c>
-      <c r="K62" t="n">
-        <v>3519.123271</v>
+        <v>3017.801864</v>
       </c>
     </row>
     <row r="63">
@@ -2644,33 +2560,32 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>23766.421451</v>
+      </c>
       <c r="C63" t="n">
-        <v>44299.675634</v>
+        <v>24131.35528</v>
       </c>
       <c r="D63" t="n">
-        <v>23766.421451</v>
+        <v>42390.318478</v>
       </c>
       <c r="E63" t="n">
-        <v>24131.35528</v>
+        <v>61009.00298</v>
       </c>
       <c r="F63" t="n">
-        <v>42390.318478</v>
+        <v>39186.48104</v>
       </c>
       <c r="G63" t="n">
-        <v>61009.00298</v>
+        <v>58947.997898</v>
       </c>
       <c r="H63" t="n">
-        <v>39186.48104</v>
+        <v>25340.859125</v>
       </c>
       <c r="I63" t="n">
-        <v>58947.997898</v>
+        <v>18413.67049</v>
       </c>
       <c r="J63" t="n">
-        <v>25340.859125</v>
-      </c>
-      <c r="K63" t="n">
-        <v>18413.67049</v>
+        <v>14290.395492</v>
       </c>
     </row>
     <row r="64">
@@ -2679,33 +2594,32 @@
           <t>食品</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>672.670647</v>
+      </c>
       <c r="C64" t="n">
-        <v>894.284195</v>
+        <v>822.513379</v>
       </c>
       <c r="D64" t="n">
-        <v>672.670647</v>
+        <v>808.75627</v>
       </c>
       <c r="E64" t="n">
-        <v>822.513379</v>
+        <v>729.3189609999999</v>
       </c>
       <c r="F64" t="n">
-        <v>808.75627</v>
+        <v>1707.523625</v>
       </c>
       <c r="G64" t="n">
-        <v>729.3189609999999</v>
+        <v>1123.525856</v>
       </c>
       <c r="H64" t="n">
-        <v>1707.523625</v>
+        <v>1288.255756</v>
       </c>
       <c r="I64" t="n">
-        <v>1123.525856</v>
+        <v>1442.587978</v>
       </c>
       <c r="J64" t="n">
-        <v>1288.255756</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1442.587978</v>
+        <v>1056.262568</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -487,31 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85140.476152</v>
+        <v>82060.97606299999</v>
       </c>
       <c r="C2" t="n">
-        <v>97469.493455</v>
+        <v>95434.432019</v>
       </c>
       <c r="D2" t="n">
-        <v>93023.65412000001</v>
+        <v>109808.514004</v>
       </c>
       <c r="E2" t="n">
-        <v>80100.52979</v>
+        <v>90709.348566</v>
       </c>
       <c r="F2" t="n">
-        <v>79486.70570525</v>
+        <v>146377.709394</v>
       </c>
       <c r="G2" t="n">
-        <v>129848.67474</v>
+        <v>111836.151503</v>
       </c>
       <c r="H2" t="n">
-        <v>116164.155528</v>
+        <v>88197.360011</v>
       </c>
       <c r="I2" t="n">
-        <v>89863.707416</v>
+        <v>88784.65591</v>
       </c>
       <c r="J2" t="n">
-        <v>82060.97606299999</v>
+        <v>118029.640628</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86111.56320800001</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +529,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1051.289579</v>
+        <v>1351.696174</v>
       </c>
       <c r="C3" t="n">
-        <v>1205.972422</v>
+        <v>2096.961518</v>
       </c>
       <c r="D3" t="n">
-        <v>1376.309944</v>
+        <v>2895.581625</v>
       </c>
       <c r="E3" t="n">
-        <v>1788.730843</v>
+        <v>2419.14550725</v>
       </c>
       <c r="F3" t="n">
-        <v>1316.92416</v>
+        <v>3482.021308</v>
       </c>
       <c r="G3" t="n">
-        <v>1865.378455</v>
+        <v>2653.026445</v>
       </c>
       <c r="H3" t="n">
-        <v>1171.961645</v>
+        <v>2315.212176</v>
       </c>
       <c r="I3" t="n">
-        <v>1231.619958</v>
+        <v>1672.452944</v>
       </c>
       <c r="J3" t="n">
-        <v>1351.696174</v>
+        <v>1870.514358</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1820.151502</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +566,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138946.48812</v>
+        <v>170431.167476</v>
       </c>
       <c r="C4" t="n">
-        <v>189646.737822</v>
+        <v>159181.7152</v>
       </c>
       <c r="D4" t="n">
-        <v>182760.686487</v>
+        <v>221865.684942</v>
       </c>
       <c r="E4" t="n">
-        <v>128660.880246</v>
+        <v>165524.115202</v>
       </c>
       <c r="F4" t="n">
-        <v>123539.16242</v>
+        <v>303082.816948</v>
       </c>
       <c r="G4" t="n">
-        <v>205333.707724</v>
+        <v>193622.711519</v>
       </c>
       <c r="H4" t="n">
-        <v>205533.21934</v>
+        <v>147446.818662</v>
       </c>
       <c r="I4" t="n">
-        <v>162010.552511</v>
+        <v>124321.122321</v>
       </c>
       <c r="J4" t="n">
-        <v>170431.167476</v>
+        <v>150792.801026</v>
+      </c>
+      <c r="K4" t="n">
+        <v>147850.838611</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +603,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1327.895339</v>
+        <v>1992.966278</v>
       </c>
       <c r="C5" t="n">
-        <v>1707.386623</v>
+        <v>6388.321597</v>
       </c>
       <c r="D5" t="n">
-        <v>1902.962393</v>
+        <v>4515.853307</v>
       </c>
       <c r="E5" t="n">
-        <v>1122.586086</v>
+        <v>3162.179545</v>
       </c>
       <c r="F5" t="n">
-        <v>1601.886093</v>
+        <v>3258.561954</v>
       </c>
       <c r="G5" t="n">
-        <v>1716.223375</v>
+        <v>1346.914769</v>
       </c>
       <c r="H5" t="n">
-        <v>1784.390789</v>
+        <v>1923.767901</v>
       </c>
       <c r="I5" t="n">
-        <v>4443.690148</v>
+        <v>1581.217843</v>
       </c>
       <c r="J5" t="n">
-        <v>1992.966278</v>
+        <v>1589.279806</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1426.783736</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +640,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130648.847117</v>
+        <v>101210.657554</v>
       </c>
       <c r="C6" t="n">
-        <v>102906.419806</v>
+        <v>89951.08953700001</v>
       </c>
       <c r="D6" t="n">
-        <v>129641.407368</v>
+        <v>109727.515864</v>
       </c>
       <c r="E6" t="n">
-        <v>140476.595393</v>
+        <v>104235.103462</v>
       </c>
       <c r="F6" t="n">
-        <v>154082.840107</v>
+        <v>151269.855885</v>
       </c>
       <c r="G6" t="n">
-        <v>197491.603846</v>
+        <v>120306.325953</v>
       </c>
       <c r="H6" t="n">
-        <v>165285.893329</v>
+        <v>130064.351814</v>
       </c>
       <c r="I6" t="n">
-        <v>127508.207651</v>
+        <v>128906.794282</v>
       </c>
       <c r="J6" t="n">
-        <v>101210.657554</v>
+        <v>142583.75425</v>
+      </c>
+      <c r="K6" t="n">
+        <v>175994.789733</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +677,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10540.732272</v>
+        <v>17549.479583</v>
       </c>
       <c r="C7" t="n">
-        <v>13889.568317</v>
+        <v>51398.922299</v>
       </c>
       <c r="D7" t="n">
-        <v>13855.977711</v>
+        <v>56648.492805</v>
       </c>
       <c r="E7" t="n">
-        <v>20448.539832</v>
+        <v>43564.427475</v>
       </c>
       <c r="F7" t="n">
-        <v>15846.945404</v>
+        <v>40327.416367</v>
       </c>
       <c r="G7" t="n">
-        <v>24740.317784</v>
+        <v>53567.139487</v>
       </c>
       <c r="H7" t="n">
-        <v>25336.378851</v>
+        <v>25279.321246</v>
       </c>
       <c r="I7" t="n">
-        <v>22997.890573</v>
+        <v>30217.0626</v>
       </c>
       <c r="J7" t="n">
-        <v>17549.479583</v>
+        <v>30775.962933</v>
+      </c>
+      <c r="K7" t="n">
+        <v>27850.794304</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +714,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5236.54811</v>
+        <v>11700.144202</v>
       </c>
       <c r="C8" t="n">
-        <v>5028.359153</v>
+        <v>9923.101177</v>
       </c>
       <c r="D8" t="n">
-        <v>6200.80261</v>
+        <v>14089.832465</v>
       </c>
       <c r="E8" t="n">
-        <v>5956.565974</v>
+        <v>10043.258621</v>
       </c>
       <c r="F8" t="n">
-        <v>18678.998933</v>
+        <v>11367.800512</v>
       </c>
       <c r="G8" t="n">
-        <v>20069.059953</v>
+        <v>9290.113633999999</v>
       </c>
       <c r="H8" t="n">
-        <v>13943.679809</v>
+        <v>6401.606748</v>
       </c>
       <c r="I8" t="n">
-        <v>18547.719671</v>
+        <v>5530.783665</v>
       </c>
       <c r="J8" t="n">
-        <v>11700.144202</v>
+        <v>5227.592729</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6216.818898</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +751,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12877.494238</v>
+        <v>29647.371037</v>
       </c>
       <c r="C9" t="n">
-        <v>12170.44137225</v>
+        <v>34880.627577</v>
       </c>
       <c r="D9" t="n">
-        <v>28574.762822</v>
+        <v>43373.242818</v>
       </c>
       <c r="E9" t="n">
-        <v>20694.5899575</v>
+        <v>30713.706643</v>
       </c>
       <c r="F9" t="n">
-        <v>18024.656341</v>
+        <v>47858.980378</v>
       </c>
       <c r="G9" t="n">
-        <v>20594.013322</v>
+        <v>38701.195125</v>
       </c>
       <c r="H9" t="n">
-        <v>19539.969903</v>
+        <v>29034.133984</v>
       </c>
       <c r="I9" t="n">
-        <v>22697.275345</v>
+        <v>35222.48547</v>
       </c>
       <c r="J9" t="n">
-        <v>15356.4371</v>
+        <v>34042.91955</v>
+      </c>
+      <c r="K9" t="n">
+        <v>42756.617748</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +788,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1437.9102595</v>
+        <v>1570.4074355</v>
       </c>
       <c r="C10" t="n">
-        <v>1691.566047</v>
+        <v>1715.3806515</v>
       </c>
       <c r="D10" t="n">
-        <v>1739.207265</v>
+        <v>1700.879939</v>
       </c>
       <c r="E10" t="n">
-        <v>2361.4214135</v>
+        <v>1677.349480416667</v>
       </c>
       <c r="F10" t="n">
-        <v>2507.015691083333</v>
+        <v>2968.736749333333</v>
       </c>
       <c r="G10" t="n">
-        <v>2915.59794075</v>
+        <v>1863.8975865</v>
       </c>
       <c r="H10" t="n">
-        <v>2010.5327855</v>
+        <v>1660.79840675</v>
       </c>
       <c r="I10" t="n">
-        <v>1639.9031125</v>
+        <v>1890.91217525</v>
       </c>
       <c r="J10" t="n">
-        <v>1570.4074355</v>
+        <v>1789.04645175</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1726.716907666666</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +825,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5027.901959</v>
+        <v>3413.142047</v>
       </c>
       <c r="C11" t="n">
-        <v>4287.608381</v>
+        <v>4428.876894</v>
       </c>
       <c r="D11" t="n">
-        <v>5741.1415725</v>
+        <v>4573.556078</v>
       </c>
       <c r="E11" t="n">
-        <v>5931.790813</v>
+        <v>5066.849458</v>
       </c>
       <c r="F11" t="n">
-        <v>5709.634427</v>
+        <v>5176.826412</v>
       </c>
       <c r="G11" t="n">
-        <v>8910.522211</v>
+        <v>3792.995132</v>
       </c>
       <c r="H11" t="n">
-        <v>5980.956098</v>
+        <v>3971.737123</v>
       </c>
       <c r="I11" t="n">
-        <v>5153.703854</v>
+        <v>2607.64261</v>
       </c>
       <c r="J11" t="n">
-        <v>3413.142047</v>
+        <v>6270.54130125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3458.255305</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +862,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13061.21415</v>
+        <v>12900.263706</v>
       </c>
       <c r="C12" t="n">
-        <v>11174.18828</v>
+        <v>10926.729496</v>
       </c>
       <c r="D12" t="n">
-        <v>13638.882629</v>
+        <v>13504.697924</v>
       </c>
       <c r="E12" t="n">
-        <v>13065.508176</v>
+        <v>10933.252739</v>
       </c>
       <c r="F12" t="n">
-        <v>13474.480942</v>
+        <v>16680.755963</v>
       </c>
       <c r="G12" t="n">
-        <v>20011.949809</v>
+        <v>16906.893744</v>
       </c>
       <c r="H12" t="n">
-        <v>14586.43468</v>
+        <v>10640.922305</v>
       </c>
       <c r="I12" t="n">
-        <v>12412.488155</v>
+        <v>8829.759413</v>
       </c>
       <c r="J12" t="n">
-        <v>12900.263706</v>
+        <v>9388.852977</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10775.805214</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +899,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3371.427526</v>
+        <v>4695.352964</v>
       </c>
       <c r="C13" t="n">
-        <v>2394.061638</v>
+        <v>3307.298609</v>
       </c>
       <c r="D13" t="n">
-        <v>4286.652275</v>
+        <v>3235.156925</v>
       </c>
       <c r="E13" t="n">
-        <v>2976.017692</v>
+        <v>3959.015533</v>
       </c>
       <c r="F13" t="n">
-        <v>3786.824192</v>
+        <v>3231.178388</v>
       </c>
       <c r="G13" t="n">
-        <v>4021.459276</v>
+        <v>3960.347477</v>
       </c>
       <c r="H13" t="n">
-        <v>7703.003085</v>
+        <v>2417.560399</v>
       </c>
       <c r="I13" t="n">
-        <v>5986.185579</v>
+        <v>2771.525746</v>
       </c>
       <c r="J13" t="n">
-        <v>4695.352964</v>
+        <v>3454.18744</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2375.099497</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +936,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14305.724936</v>
+        <v>5838.202682</v>
       </c>
       <c r="C14" t="n">
-        <v>8735.041053249999</v>
+        <v>13174.327015</v>
       </c>
       <c r="D14" t="n">
-        <v>9585.149552999999</v>
+        <v>7189.191447</v>
       </c>
       <c r="E14" t="n">
-        <v>6695.3773</v>
+        <v>7385.884821</v>
       </c>
       <c r="F14" t="n">
-        <v>6646.674439</v>
+        <v>9671.434703000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9487.406014</v>
+        <v>6823.14329</v>
       </c>
       <c r="H14" t="n">
-        <v>9178.032263999999</v>
+        <v>5378.798716</v>
       </c>
       <c r="I14" t="n">
-        <v>6657.895089</v>
+        <v>5067.008517</v>
       </c>
       <c r="J14" t="n">
-        <v>5838.202682</v>
+        <v>6170.564575</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6495.070194</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35684.540649</v>
+        <v>22968.081151</v>
       </c>
       <c r="C15" t="n">
-        <v>33341.832677</v>
+        <v>19468.556038</v>
       </c>
       <c r="D15" t="n">
-        <v>24770.886724</v>
+        <v>40077.878692</v>
       </c>
       <c r="E15" t="n">
-        <v>21506.286768</v>
+        <v>23710.610413</v>
       </c>
       <c r="F15" t="n">
-        <v>33362.212799</v>
+        <v>45344.637937</v>
       </c>
       <c r="G15" t="n">
-        <v>24153.683866</v>
+        <v>28502.020962</v>
       </c>
       <c r="H15" t="n">
-        <v>44202.585443</v>
+        <v>29474.558918</v>
       </c>
       <c r="I15" t="n">
-        <v>31307.142058</v>
+        <v>20905.593194</v>
       </c>
       <c r="J15" t="n">
-        <v>22968.081151</v>
+        <v>22869.744188</v>
+      </c>
+      <c r="K15" t="n">
+        <v>35181.997593</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +1010,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18387.097511</v>
+        <v>15866.876911</v>
       </c>
       <c r="C16" t="n">
-        <v>18772.393694</v>
+        <v>18530.52396</v>
       </c>
       <c r="D16" t="n">
-        <v>23991.340089</v>
+        <v>17081.652832</v>
       </c>
       <c r="E16" t="n">
-        <v>16183.796468</v>
+        <v>13923.051787</v>
       </c>
       <c r="F16" t="n">
-        <v>20919.253641</v>
+        <v>20984.679592</v>
       </c>
       <c r="G16" t="n">
-        <v>21320.266226</v>
+        <v>18075.029301</v>
       </c>
       <c r="H16" t="n">
-        <v>17242.611229</v>
+        <v>10885.54886</v>
       </c>
       <c r="I16" t="n">
-        <v>31532.197277</v>
+        <v>10178.362449</v>
       </c>
       <c r="J16" t="n">
-        <v>15866.876911</v>
+        <v>14624.726406</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12350.877069</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +1047,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30953.730487</v>
+        <v>46809.599087</v>
       </c>
       <c r="C17" t="n">
-        <v>28733.570505</v>
+        <v>39256.618254</v>
       </c>
       <c r="D17" t="n">
-        <v>38078.11666</v>
+        <v>39564.844257</v>
       </c>
       <c r="E17" t="n">
-        <v>24953.722837</v>
+        <v>39324.200556</v>
       </c>
       <c r="F17" t="n">
-        <v>41336.354249</v>
+        <v>55652.472682</v>
       </c>
       <c r="G17" t="n">
-        <v>46582.502105</v>
+        <v>26977.665732</v>
       </c>
       <c r="H17" t="n">
-        <v>44569.088771</v>
+        <v>25679.187541</v>
       </c>
       <c r="I17" t="n">
-        <v>38390.21865</v>
+        <v>18361.073069</v>
       </c>
       <c r="J17" t="n">
-        <v>46809.599087</v>
+        <v>20715.519402</v>
+      </c>
+      <c r="K17" t="n">
+        <v>30246.361273</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1084,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1374.791349</v>
+        <v>851.002673</v>
       </c>
       <c r="C18" t="n">
-        <v>931.905278</v>
+        <v>846.211093</v>
       </c>
       <c r="D18" t="n">
-        <v>1551.429113</v>
+        <v>920.6671</v>
       </c>
       <c r="E18" t="n">
-        <v>916.4080719999999</v>
+        <v>656.8436369999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1259.522176</v>
+        <v>1135.755548</v>
       </c>
       <c r="G18" t="n">
-        <v>2058.870186</v>
+        <v>711.696551</v>
       </c>
       <c r="H18" t="n">
-        <v>1142.857343</v>
+        <v>578.367599</v>
       </c>
       <c r="I18" t="n">
-        <v>2181.757307</v>
+        <v>515.620049</v>
       </c>
       <c r="J18" t="n">
-        <v>851.002673</v>
+        <v>474.713156</v>
+      </c>
+      <c r="K18" t="n">
+        <v>483.392604</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1121,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.07476275</v>
+        <v>112.358103</v>
       </c>
       <c r="C19" t="n">
-        <v>226.0066173333333</v>
+        <v>219.5649815</v>
       </c>
       <c r="D19" t="n">
-        <v>157.437316</v>
+        <v>220.8968055</v>
       </c>
       <c r="E19" t="n">
-        <v>90.02030033333332</v>
+        <v>333.5251645</v>
       </c>
       <c r="F19" t="n">
-        <v>86.055667</v>
+        <v>371.724318</v>
       </c>
       <c r="G19" t="n">
-        <v>94.680183</v>
+        <v>340.844856</v>
       </c>
       <c r="H19" t="n">
-        <v>102.442166</v>
+        <v>478.877536</v>
       </c>
       <c r="I19" t="n">
-        <v>136.288246</v>
+        <v>327.893671</v>
       </c>
       <c r="J19" t="n">
-        <v>112.358103</v>
+        <v>283.604148</v>
+      </c>
+      <c r="K19" t="n">
+        <v>357.590444</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1158,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17169.781569</v>
+        <v>10881.654325</v>
       </c>
       <c r="C20" t="n">
-        <v>26765.247924</v>
+        <v>22683.159205</v>
       </c>
       <c r="D20" t="n">
-        <v>21132.136662</v>
+        <v>27348.945384</v>
       </c>
       <c r="E20" t="n">
-        <v>11587.069143</v>
+        <v>17437.834996</v>
       </c>
       <c r="F20" t="n">
-        <v>11464.949012</v>
+        <v>41879.135888</v>
       </c>
       <c r="G20" t="n">
-        <v>35323.290674</v>
+        <v>14191.568201</v>
       </c>
       <c r="H20" t="n">
-        <v>30712.336311</v>
+        <v>12678.851694</v>
       </c>
       <c r="I20" t="n">
-        <v>21687.438595</v>
+        <v>15494.785698</v>
       </c>
       <c r="J20" t="n">
-        <v>10881.654325</v>
+        <v>18710.0614</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16122.009331</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1195,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3318.479694</v>
+        <v>3215.085467</v>
       </c>
       <c r="C21" t="n">
-        <v>5802.953388</v>
+        <v>3650.649543</v>
       </c>
       <c r="D21" t="n">
-        <v>3962.280094</v>
+        <v>3211.059413</v>
       </c>
       <c r="E21" t="n">
-        <v>3170.634716</v>
+        <v>3044.335796</v>
       </c>
       <c r="F21" t="n">
-        <v>3466.111153</v>
+        <v>4266.437468</v>
       </c>
       <c r="G21" t="n">
-        <v>3968.727804</v>
+        <v>3621.255247</v>
       </c>
       <c r="H21" t="n">
-        <v>4713.418488</v>
+        <v>4151.474794</v>
       </c>
       <c r="I21" t="n">
-        <v>4481.736606</v>
+        <v>3373.680529</v>
       </c>
       <c r="J21" t="n">
-        <v>3215.085467</v>
+        <v>3096.345134</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2838.648272</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1232,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>284.626499</v>
+        <v>95.273578</v>
       </c>
       <c r="C22" t="n">
-        <v>234.591797</v>
+        <v>83.202314</v>
       </c>
       <c r="D22" t="n">
-        <v>213.95378</v>
+        <v>146.311388</v>
       </c>
       <c r="E22" t="n">
-        <v>146.3468013333333</v>
+        <v>149.448354</v>
       </c>
       <c r="F22" t="n">
-        <v>140.418245</v>
+        <v>228.552413</v>
       </c>
       <c r="G22" t="n">
-        <v>213.065646</v>
+        <v>228.59593</v>
       </c>
       <c r="H22" t="n">
-        <v>136.491058</v>
+        <v>148.972835</v>
       </c>
       <c r="I22" t="n">
-        <v>198.7382336666667</v>
+        <v>217.130414</v>
       </c>
       <c r="J22" t="n">
-        <v>95.273578</v>
+        <v>322.379927</v>
+      </c>
+      <c r="K22" t="n">
+        <v>422.57159</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1269,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.4233375</v>
+        <v>0.993371</v>
       </c>
       <c r="C23" t="n">
-        <v>2.78372875</v>
+        <v>1.78307375</v>
       </c>
       <c r="D23" t="n">
-        <v>1.707734</v>
+        <v>1.671217333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>4.863267</v>
+        <v>2.0712465</v>
       </c>
       <c r="F23" t="n">
-        <v>2.496508833333333</v>
+        <v>2.63044825</v>
       </c>
       <c r="G23" t="n">
-        <v>1.159543</v>
+        <v>2.833667</v>
       </c>
       <c r="H23" t="n">
-        <v>1.22882325</v>
+        <v>1.47260325</v>
       </c>
       <c r="I23" t="n">
-        <v>0.568679</v>
+        <v>1.32028125</v>
       </c>
       <c r="J23" t="n">
-        <v>0.993371</v>
+        <v>0.9817399999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.086043</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1306,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>579.415634</v>
+        <v>1116.41372</v>
       </c>
       <c r="C24" t="n">
-        <v>881.8031559999999</v>
+        <v>975.403637</v>
       </c>
       <c r="D24" t="n">
-        <v>740.897229</v>
+        <v>905.974587</v>
       </c>
       <c r="E24" t="n">
-        <v>612.1953099999999</v>
+        <v>526.089604</v>
       </c>
       <c r="F24" t="n">
-        <v>713.520144</v>
+        <v>1457.277657</v>
       </c>
       <c r="G24" t="n">
-        <v>2092.159241</v>
+        <v>653.56974</v>
       </c>
       <c r="H24" t="n">
-        <v>1392.909789</v>
+        <v>1082.038393</v>
       </c>
       <c r="I24" t="n">
-        <v>1417.841848</v>
+        <v>789.121836</v>
       </c>
       <c r="J24" t="n">
-        <v>1116.41372</v>
+        <v>678.47342</v>
+      </c>
+      <c r="K24" t="n">
+        <v>560.028791</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1343,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>285.874826</v>
+        <v>559.696609</v>
       </c>
       <c r="C25" t="n">
-        <v>324.489912</v>
+        <v>591.2121509999999</v>
       </c>
       <c r="D25" t="n">
-        <v>368.164356</v>
+        <v>411.916797</v>
       </c>
       <c r="E25" t="n">
-        <v>271.009081</v>
+        <v>693.882124</v>
       </c>
       <c r="F25" t="n">
-        <v>414.965774</v>
+        <v>834.998774</v>
       </c>
       <c r="G25" t="n">
-        <v>545.1641</v>
+        <v>661.627076</v>
       </c>
       <c r="H25" t="n">
-        <v>283.950176</v>
+        <v>474.962401</v>
       </c>
       <c r="I25" t="n">
-        <v>473.685355</v>
+        <v>356.818377</v>
       </c>
       <c r="J25" t="n">
-        <v>559.696609</v>
+        <v>327.770791</v>
+      </c>
+      <c r="K25" t="n">
+        <v>307.888329</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1380,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1284.573526</v>
+        <v>1255.344352</v>
       </c>
       <c r="C26" t="n">
-        <v>1171.957497</v>
+        <v>3679.082969</v>
       </c>
       <c r="D26" t="n">
-        <v>2992.647381</v>
+        <v>1782.611379</v>
       </c>
       <c r="E26" t="n">
-        <v>1857.383228</v>
+        <v>2476.659351</v>
       </c>
       <c r="F26" t="n">
-        <v>833.4631900000001</v>
+        <v>1668.468947</v>
       </c>
       <c r="G26" t="n">
-        <v>1101.311138</v>
+        <v>1906.351396</v>
       </c>
       <c r="H26" t="n">
-        <v>940.165023</v>
+        <v>1106.356106</v>
       </c>
       <c r="I26" t="n">
-        <v>856.65935</v>
+        <v>1202.872977</v>
       </c>
       <c r="J26" t="n">
-        <v>1255.344352</v>
+        <v>982.0145659999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3377.085099</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1417,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1431.344338</v>
+        <v>11701.00615</v>
       </c>
       <c r="C27" t="n">
-        <v>2011.716407</v>
+        <v>7792.562236</v>
       </c>
       <c r="D27" t="n">
-        <v>3199.267601</v>
+        <v>9551.441784000001</v>
       </c>
       <c r="E27" t="n">
-        <v>1435.937866</v>
+        <v>6319.221908</v>
       </c>
       <c r="F27" t="n">
-        <v>2005.650755</v>
+        <v>9002.351504</v>
       </c>
       <c r="G27" t="n">
-        <v>2768.716692</v>
+        <v>6343.406324</v>
       </c>
       <c r="H27" t="n">
-        <v>3171.539994</v>
+        <v>5278.593607</v>
       </c>
       <c r="I27" t="n">
-        <v>3402.919164</v>
+        <v>4951.307608</v>
       </c>
       <c r="J27" t="n">
-        <v>3001.265492</v>
+        <v>6806.019453</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5483.5149605</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1454,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>953.2518679999999</v>
+        <v>4567.157574</v>
       </c>
       <c r="C28" t="n">
-        <v>3835.176519</v>
+        <v>4464.077512</v>
       </c>
       <c r="D28" t="n">
-        <v>3658.626385</v>
+        <v>8026.554494</v>
       </c>
       <c r="E28" t="n">
-        <v>2593.799925</v>
+        <v>17251.803885</v>
       </c>
       <c r="F28" t="n">
-        <v>3556.848112</v>
+        <v>6638.344623</v>
       </c>
       <c r="G28" t="n">
-        <v>2011.55405</v>
+        <v>5969.8867385</v>
       </c>
       <c r="H28" t="n">
-        <v>2430.059817</v>
+        <v>8963.286382</v>
       </c>
       <c r="I28" t="n">
-        <v>3580.875052</v>
+        <v>5845.509506</v>
       </c>
       <c r="J28" t="n">
-        <v>4567.160092</v>
+        <v>4315.397605</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3943.029472</v>
       </c>
     </row>
     <row r="29">
@@ -1405,1221 +1491,1033 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1159.083804</v>
+        <v>1047.138793166667</v>
       </c>
       <c r="C29" t="n">
-        <v>1204.082537</v>
+        <v>1575.585877666667</v>
       </c>
       <c r="D29" t="n">
-        <v>1371.787172</v>
+        <v>1355.678808</v>
       </c>
       <c r="E29" t="n">
-        <v>1143.675889666667</v>
+        <v>948.559933</v>
       </c>
       <c r="F29" t="n">
-        <v>1175.57370525</v>
+        <v>1481.882935</v>
       </c>
       <c r="G29" t="n">
-        <v>1745.240304</v>
+        <v>921.225533</v>
       </c>
       <c r="H29" t="n">
-        <v>1111.336422</v>
+        <v>1287.748339</v>
       </c>
       <c r="I29" t="n">
-        <v>1187.944573666667</v>
+        <v>1097.726776</v>
       </c>
       <c r="J29" t="n">
-        <v>1047.138752666667</v>
+        <v>1008.621634</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1223.7303175</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>玻璃陶瓷</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>464.349189</v>
+        <v>10431.840663</v>
       </c>
       <c r="C30" t="n">
-        <v>460.082038</v>
+        <v>6506.24478</v>
       </c>
       <c r="D30" t="n">
-        <v>1411.506215</v>
+        <v>2927.730432</v>
       </c>
       <c r="E30" t="n">
-        <v>913.096038</v>
+        <v>12616.014929</v>
       </c>
       <c r="F30" t="n">
-        <v>716.628303</v>
+        <v>5295.728255</v>
       </c>
       <c r="G30" t="n">
-        <v>1391.651459</v>
+        <v>9593.106706</v>
       </c>
       <c r="H30" t="n">
-        <v>1434.343204</v>
+        <v>14525.081378</v>
       </c>
       <c r="I30" t="n">
-        <v>6893.350654</v>
+        <v>14764.888638</v>
       </c>
       <c r="J30" t="n">
-        <v>10313.913704</v>
+        <v>10582.289675</v>
+      </c>
+      <c r="K30" t="n">
+        <v>19618.558693</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷</t>
+          <t>生技醫療</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>337.289111</v>
+        <v>4149.801865083334</v>
       </c>
       <c r="C31" t="n">
-        <v>1395.007583</v>
+        <v>3720.87209275</v>
       </c>
       <c r="D31" t="n">
-        <v>981.782769</v>
+        <v>4189.765495</v>
       </c>
       <c r="E31" t="n">
-        <v>300.275675</v>
+        <v>3457.454643</v>
       </c>
       <c r="F31" t="n">
-        <v>573.402185</v>
+        <v>6989.188224</v>
       </c>
       <c r="G31" t="n">
-        <v>257.059214</v>
+        <v>6393.92870275</v>
       </c>
       <c r="H31" t="n">
-        <v>150.92435</v>
+        <v>5021.116329083334</v>
       </c>
       <c r="I31" t="n">
-        <v>244.369154</v>
+        <v>3148.95717875</v>
       </c>
       <c r="J31" t="n">
-        <v>117.926959</v>
+        <v>3987.6690155</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2998.78392925</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>生技</t>
+          <t>石化</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1914.022671</v>
+        <v>50158.028725</v>
       </c>
       <c r="C32" t="n">
-        <v>2767.071807</v>
+        <v>42232.718181</v>
       </c>
       <c r="D32" t="n">
-        <v>2175.603754</v>
+        <v>55929.601564</v>
       </c>
       <c r="E32" t="n">
-        <v>3293.053983</v>
+        <v>91141.357539</v>
       </c>
       <c r="F32" t="n">
-        <v>1634.098594</v>
+        <v>56762.360998</v>
       </c>
       <c r="G32" t="n">
-        <v>2034.884553</v>
+        <v>51513.200483</v>
       </c>
       <c r="H32" t="n">
-        <v>2066.430581</v>
+        <v>39124.732034</v>
       </c>
       <c r="I32" t="n">
-        <v>2022.323227</v>
+        <v>39590.881003</v>
       </c>
       <c r="J32" t="n">
-        <v>2379.973052</v>
+        <v>45804.859502</v>
+      </c>
+      <c r="K32" t="n">
+        <v>37423.45247233334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>生技醫療</t>
+          <t>紡織</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3152.723616083334</v>
+        <v>2532.299892</v>
       </c>
       <c r="C33" t="n">
-        <v>2054.422690333333</v>
+        <v>1842.722269</v>
       </c>
       <c r="D33" t="n">
-        <v>3157.254720666666</v>
+        <v>1312.871816</v>
       </c>
       <c r="E33" t="n">
-        <v>4047.266548166667</v>
+        <v>2704.808953</v>
       </c>
       <c r="F33" t="n">
-        <v>2730.1196475</v>
+        <v>2755.842148</v>
       </c>
       <c r="G33" t="n">
-        <v>2356.587739416666</v>
+        <v>1567.7892245</v>
       </c>
       <c r="H33" t="n">
-        <v>1786.66304375</v>
+        <v>1019.075243</v>
       </c>
       <c r="I33" t="n">
-        <v>2015.060599</v>
+        <v>1092.226384</v>
       </c>
       <c r="J33" t="n">
-        <v>1769.755592083333</v>
+        <v>829.024501</v>
+      </c>
+      <c r="K33" t="n">
+        <v>916.605739</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>石化</t>
+          <t>綠能</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18522.008159</v>
+        <v>2968.90518925</v>
       </c>
       <c r="C34" t="n">
-        <v>24138.976642</v>
+        <v>2355.699666</v>
       </c>
       <c r="D34" t="n">
-        <v>38592.8304785</v>
+        <v>2516.129288</v>
       </c>
       <c r="E34" t="n">
-        <v>17726.891727</v>
+        <v>1361.660627</v>
       </c>
       <c r="F34" t="n">
-        <v>18001.843649</v>
+        <v>2736.504571</v>
       </c>
       <c r="G34" t="n">
-        <v>29683.7204415</v>
+        <v>1751.39205925</v>
       </c>
       <c r="H34" t="n">
-        <v>37426.999642</v>
+        <v>2081.145656</v>
       </c>
       <c r="I34" t="n">
-        <v>51575.626586</v>
+        <v>1426.808585</v>
       </c>
       <c r="J34" t="n">
-        <v>50158.028725</v>
+        <v>1121.898895</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1528.765713</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>紡織</t>
+          <t>網通</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>907.837418</v>
+        <v>11382.659629</v>
       </c>
       <c r="C35" t="n">
-        <v>883.170031</v>
+        <v>13378.419226</v>
       </c>
       <c r="D35" t="n">
-        <v>1354.065363</v>
+        <v>16132.291819</v>
       </c>
       <c r="E35" t="n">
-        <v>1121.706863</v>
+        <v>12203.242913</v>
       </c>
       <c r="F35" t="n">
-        <v>932.818224</v>
+        <v>11703.76045</v>
       </c>
       <c r="G35" t="n">
-        <v>1830.670428</v>
+        <v>12703.616457</v>
       </c>
       <c r="H35" t="n">
-        <v>1965.363705</v>
+        <v>13402.771396</v>
       </c>
       <c r="I35" t="n">
-        <v>3121.055908</v>
+        <v>11425.688567</v>
       </c>
       <c r="J35" t="n">
-        <v>2532.299892</v>
+        <v>20110.469244</v>
+      </c>
+      <c r="K35" t="n">
+        <v>9588.452409</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>綠能</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1741.438457</v>
+        <v>614.6217380000001</v>
       </c>
       <c r="C36" t="n">
-        <v>1913.072300666667</v>
+        <v>1073.0414</v>
       </c>
       <c r="D36" t="n">
-        <v>2251.441003</v>
+        <v>1594.388937</v>
       </c>
       <c r="E36" t="n">
-        <v>1989.455276</v>
+        <v>1076.331173</v>
       </c>
       <c r="F36" t="n">
-        <v>2036.013433</v>
+        <v>1232.572688</v>
       </c>
       <c r="G36" t="n">
-        <v>3601.325495</v>
+        <v>1879.559285</v>
       </c>
       <c r="H36" t="n">
-        <v>1921.06941</v>
+        <v>1081.058934</v>
       </c>
       <c r="I36" t="n">
-        <v>4151.709985</v>
+        <v>863.168954</v>
       </c>
       <c r="J36" t="n">
-        <v>2968.90518925</v>
+        <v>1008.784159</v>
+      </c>
+      <c r="K36" t="n">
+        <v>810.950855</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>網通</t>
+          <t>航運</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6766.767165</v>
+        <v>4521.877945</v>
       </c>
       <c r="C37" t="n">
-        <v>9354.171284</v>
+        <v>25931.5456045</v>
       </c>
       <c r="D37" t="n">
-        <v>14735.204401</v>
+        <v>26286.154605</v>
       </c>
       <c r="E37" t="n">
-        <v>12505.335512</v>
+        <v>14965.124573</v>
       </c>
       <c r="F37" t="n">
-        <v>12181.591653</v>
+        <v>9830.857416000001</v>
       </c>
       <c r="G37" t="n">
-        <v>17010.454022</v>
+        <v>10698.718434</v>
       </c>
       <c r="H37" t="n">
-        <v>14425.671246</v>
+        <v>6433.64742575</v>
       </c>
       <c r="I37" t="n">
-        <v>15693.638504</v>
+        <v>5580.049872</v>
       </c>
       <c r="J37" t="n">
-        <v>11382.659629</v>
+        <v>5967.7019175</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5460.094539</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>被動元件</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1364.089271</v>
+        <v>81211.36083799999</v>
       </c>
       <c r="C38" t="n">
-        <v>755.371776</v>
+        <v>38791.176169</v>
       </c>
       <c r="D38" t="n">
-        <v>1522.638212</v>
+        <v>59016.945957</v>
       </c>
       <c r="E38" t="n">
-        <v>983.322091</v>
+        <v>60913.516455</v>
       </c>
       <c r="F38" t="n">
-        <v>514.825294</v>
+        <v>68946.483389</v>
       </c>
       <c r="G38" t="n">
-        <v>678.614001</v>
+        <v>44982.238539</v>
       </c>
       <c r="H38" t="n">
-        <v>812.177107</v>
+        <v>42998.291544</v>
       </c>
       <c r="I38" t="n">
-        <v>487.561978</v>
+        <v>52802.554316</v>
       </c>
       <c r="J38" t="n">
-        <v>614.6217380000001</v>
+        <v>48528.16413</v>
+      </c>
+      <c r="K38" t="n">
+        <v>63229.713007</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>航運</t>
+          <t>觀光</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3869.600446</v>
+        <v>224.812825</v>
       </c>
       <c r="C39" t="n">
-        <v>5798.788543</v>
+        <v>290.56792875</v>
       </c>
       <c r="D39" t="n">
-        <v>3937.918847</v>
+        <v>288.4396313333333</v>
       </c>
       <c r="E39" t="n">
-        <v>3621.251342</v>
+        <v>178.213842</v>
       </c>
       <c r="F39" t="n">
-        <v>3802.02835</v>
+        <v>510.696664</v>
       </c>
       <c r="G39" t="n">
-        <v>5064.0600025</v>
+        <v>272.6053706666667</v>
       </c>
       <c r="H39" t="n">
-        <v>4283.101274</v>
+        <v>192.2805496666666</v>
       </c>
       <c r="I39" t="n">
-        <v>4286.426380333333</v>
+        <v>208.14742075</v>
       </c>
       <c r="J39" t="n">
-        <v>3443.479777</v>
+        <v>180.24453425</v>
+      </c>
+      <c r="K39" t="n">
+        <v>197.9784773333333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>被動元件</t>
+          <t>記憶體</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>38620.855354</v>
+        <v>58053.714944</v>
       </c>
       <c r="C40" t="n">
-        <v>38787.989586</v>
+        <v>32763.385318</v>
       </c>
       <c r="D40" t="n">
-        <v>26515.935769</v>
+        <v>86759.32584075</v>
       </c>
       <c r="E40" t="n">
-        <v>83369.59020000001</v>
+        <v>46068.567366</v>
       </c>
       <c r="F40" t="n">
-        <v>109528.620721</v>
+        <v>61524.433382</v>
       </c>
       <c r="G40" t="n">
-        <v>93985.398543</v>
+        <v>37909.898727</v>
       </c>
       <c r="H40" t="n">
-        <v>48833.372017</v>
+        <v>36326.829469</v>
       </c>
       <c r="I40" t="n">
-        <v>111204.781678</v>
+        <v>29878.356119</v>
       </c>
       <c r="J40" t="n">
-        <v>81211.36083799999</v>
+        <v>28805.109067</v>
+      </c>
+      <c r="K40" t="n">
+        <v>27596.760349</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>觀光</t>
+          <t>貿易百貨</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>193.129646</v>
+        <v>570.5669830000001</v>
       </c>
       <c r="C41" t="n">
-        <v>222.40962075</v>
+        <v>652.434708</v>
       </c>
       <c r="D41" t="n">
-        <v>156.903562</v>
+        <v>579.070193</v>
       </c>
       <c r="E41" t="n">
-        <v>164.3006155</v>
+        <v>914.659041</v>
       </c>
       <c r="F41" t="n">
-        <v>143.66717925</v>
+        <v>1692.271876</v>
       </c>
       <c r="G41" t="n">
-        <v>155.329028</v>
+        <v>1432.72317875</v>
       </c>
       <c r="H41" t="n">
-        <v>110.388879</v>
+        <v>1434.016917</v>
       </c>
       <c r="I41" t="n">
-        <v>140.995561</v>
+        <v>540.506</v>
       </c>
       <c r="J41" t="n">
-        <v>224.812825</v>
+        <v>512.066064</v>
+      </c>
+      <c r="K41" t="n">
+        <v>559.753744</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>記憶體</t>
+          <t>資訊服務</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>36425.530521</v>
+        <v>298.11259</v>
       </c>
       <c r="C42" t="n">
-        <v>29728.764487</v>
+        <v>547.00186</v>
       </c>
       <c r="D42" t="n">
-        <v>45172.5952</v>
+        <v>988.503111</v>
       </c>
       <c r="E42" t="n">
-        <v>32010.529296</v>
+        <v>490.146396</v>
       </c>
       <c r="F42" t="n">
-        <v>44356.231581</v>
+        <v>897.756717</v>
       </c>
       <c r="G42" t="n">
-        <v>51876.083843</v>
+        <v>1129.16702625</v>
       </c>
       <c r="H42" t="n">
-        <v>37022.409219</v>
+        <v>1395.065596</v>
       </c>
       <c r="I42" t="n">
-        <v>40027.06992</v>
+        <v>467.8234276666667</v>
       </c>
       <c r="J42" t="n">
-        <v>58053.714944</v>
+        <v>471.164946</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1631.08507</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨</t>
+          <t>軍工</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>137.208998</v>
+        <v>499.480815</v>
       </c>
       <c r="C43" t="n">
-        <v>140.3224923333333</v>
+        <v>581.954833</v>
       </c>
       <c r="D43" t="n">
-        <v>143.673452</v>
+        <v>821.245906</v>
       </c>
       <c r="E43" t="n">
-        <v>126.829217</v>
+        <v>404.753469</v>
       </c>
       <c r="F43" t="n">
-        <v>153.965149</v>
+        <v>825.482802</v>
       </c>
       <c r="G43" t="n">
-        <v>216.040869</v>
+        <v>567.593296</v>
       </c>
       <c r="H43" t="n">
-        <v>144.108749</v>
+        <v>537.358792</v>
       </c>
       <c r="I43" t="n">
-        <v>151.587706</v>
+        <v>468.240531</v>
       </c>
       <c r="J43" t="n">
-        <v>163.816396</v>
+        <v>411.124527</v>
+      </c>
+      <c r="K43" t="n">
+        <v>399.027766</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>資訊服務</t>
+          <t>農業科技</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>572.670523</v>
+        <v>0.053269</v>
       </c>
       <c r="C44" t="n">
-        <v>273.551237</v>
+        <v>0.033151</v>
       </c>
       <c r="D44" t="n">
-        <v>406.0494</v>
+        <v>0.010244</v>
       </c>
       <c r="E44" t="n">
-        <v>192.38958</v>
+        <v>0.007863</v>
       </c>
       <c r="F44" t="n">
-        <v>159.333061</v>
+        <v>0.006552</v>
       </c>
       <c r="G44" t="n">
-        <v>305.280954</v>
+        <v>0.003161</v>
       </c>
       <c r="H44" t="n">
-        <v>466.65060525</v>
+        <v>0.002744</v>
       </c>
       <c r="I44" t="n">
-        <v>249.136108</v>
+        <v>0.002643</v>
       </c>
       <c r="J44" t="n">
-        <v>298.11259</v>
+        <v>0.002552</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.006565</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>軍工</t>
+          <t>通信網路</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>431.843473</v>
+        <v>3660.765539</v>
       </c>
       <c r="C45" t="n">
-        <v>558.7608739999999</v>
+        <v>2625.495679</v>
       </c>
       <c r="D45" t="n">
-        <v>827.171639</v>
+        <v>4139.05518</v>
       </c>
       <c r="E45" t="n">
-        <v>608.8516980000001</v>
+        <v>4408.433334</v>
       </c>
       <c r="F45" t="n">
-        <v>1163.125599</v>
+        <v>6875.836655</v>
       </c>
       <c r="G45" t="n">
-        <v>1017.672095</v>
+        <v>4134.497352</v>
       </c>
       <c r="H45" t="n">
-        <v>612.678449</v>
+        <v>5040.481585</v>
       </c>
       <c r="I45" t="n">
-        <v>779.085259</v>
+        <v>3031.189327</v>
       </c>
       <c r="J45" t="n">
-        <v>499.480815</v>
+        <v>3592.949261</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4734.635173</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>農業科技</t>
+          <t>造紙</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.005351</v>
+        <v>79.011393</v>
       </c>
       <c r="C46" t="n">
-        <v>0.003217</v>
+        <v>97.940826</v>
       </c>
       <c r="D46" t="n">
-        <v>0.003287</v>
+        <v>125.318998</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00215</v>
+        <v>656.125362</v>
       </c>
       <c r="F46" t="n">
-        <v>0.002401</v>
+        <v>214.773434</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008321</v>
+        <v>115.290054</v>
       </c>
       <c r="H46" t="n">
-        <v>0.004504</v>
+        <v>92.52786399999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.023117</v>
+        <v>122.622782</v>
       </c>
       <c r="J46" t="n">
-        <v>0.053269</v>
+        <v>102.029823</v>
+      </c>
+      <c r="K46" t="n">
+        <v>63.437995</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>通信網路</t>
+          <t>連接器</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2768.183649</v>
+        <v>8078.319146</v>
       </c>
       <c r="C47" t="n">
-        <v>2160.042912</v>
+        <v>9839.781273000001</v>
       </c>
       <c r="D47" t="n">
-        <v>2537.16588</v>
+        <v>14358.074213</v>
       </c>
       <c r="E47" t="n">
-        <v>1944.562274</v>
+        <v>17241.519264</v>
       </c>
       <c r="F47" t="n">
-        <v>2607.919254</v>
+        <v>9069.999048</v>
       </c>
       <c r="G47" t="n">
-        <v>3108.633171</v>
+        <v>6194.843082</v>
       </c>
       <c r="H47" t="n">
-        <v>1946.205721</v>
+        <v>5061.95717</v>
       </c>
       <c r="I47" t="n">
-        <v>2257.682552</v>
+        <v>4016.346834</v>
       </c>
       <c r="J47" t="n">
-        <v>2322.133139</v>
+        <v>4822.937477</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4710.065989</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>造紙</t>
+          <t>運動休閒</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>84.399334</v>
+        <v>858.256694</v>
       </c>
       <c r="C48" t="n">
-        <v>158.144148</v>
+        <v>1081.539801</v>
       </c>
       <c r="D48" t="n">
-        <v>104.815151</v>
+        <v>1120.54506475</v>
       </c>
       <c r="E48" t="n">
-        <v>152.916565</v>
+        <v>848.258089</v>
       </c>
       <c r="F48" t="n">
-        <v>102.306466</v>
+        <v>1534.009668</v>
       </c>
       <c r="G48" t="n">
-        <v>118.380095</v>
+        <v>1125.220267</v>
       </c>
       <c r="H48" t="n">
-        <v>103.558187</v>
+        <v>997.972957</v>
       </c>
       <c r="I48" t="n">
-        <v>646.385315</v>
+        <v>903.223312</v>
       </c>
       <c r="J48" t="n">
-        <v>79.011393</v>
+        <v>1174.488722</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1178.88235875</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>連接器</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6628.107666</v>
+        <v>7877.259995</v>
       </c>
       <c r="C49" t="n">
-        <v>7771.289255</v>
+        <v>8878.738735999999</v>
       </c>
       <c r="D49" t="n">
-        <v>10297.83788</v>
+        <v>10118.810306</v>
       </c>
       <c r="E49" t="n">
-        <v>9437.364121000001</v>
+        <v>12155.306408</v>
       </c>
       <c r="F49" t="n">
-        <v>8742.657853999999</v>
+        <v>15496.417758</v>
       </c>
       <c r="G49" t="n">
-        <v>7863.080042</v>
+        <v>14992.391934</v>
       </c>
       <c r="H49" t="n">
-        <v>9302.300510999999</v>
+        <v>10067.143468</v>
       </c>
       <c r="I49" t="n">
-        <v>10160.952478</v>
+        <v>9621.117287999999</v>
       </c>
       <c r="J49" t="n">
-        <v>8078.319146</v>
+        <v>10571.159237</v>
+      </c>
+      <c r="K49" t="n">
+        <v>8386.039221000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>運動休閒</t>
+          <t>鋼鐵</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>612.497166</v>
+        <v>2544.125352</v>
       </c>
       <c r="C50" t="n">
-        <v>752.428062</v>
+        <v>3866.41341325</v>
       </c>
       <c r="D50" t="n">
-        <v>692.888991</v>
+        <v>3397.314045</v>
       </c>
       <c r="E50" t="n">
-        <v>646.441073</v>
+        <v>6852.695963333333</v>
       </c>
       <c r="F50" t="n">
-        <v>664.655217</v>
+        <v>5087.392829</v>
       </c>
       <c r="G50" t="n">
-        <v>1014.851735</v>
+        <v>4387.80561</v>
       </c>
       <c r="H50" t="n">
-        <v>622.302297</v>
+        <v>3465.784863</v>
       </c>
       <c r="I50" t="n">
-        <v>977.906638</v>
+        <v>3343.74021</v>
       </c>
       <c r="J50" t="n">
-        <v>858.256694</v>
+        <v>2779.660097</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3620.29492225</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>醫療通路</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.018067</v>
+        <v>264.279907</v>
       </c>
       <c r="C51" t="n">
-        <v>0.017467</v>
+        <v>443.79431</v>
       </c>
       <c r="D51" t="n">
-        <v>0.015909</v>
+        <v>738.6906719999999</v>
       </c>
       <c r="E51" t="n">
-        <v>0.010093</v>
+        <v>431.019007</v>
       </c>
       <c r="F51" t="n">
-        <v>0.014062</v>
+        <v>409.881371</v>
       </c>
       <c r="G51" t="n">
-        <v>0.047371</v>
+        <v>249.532021</v>
       </c>
       <c r="H51" t="n">
-        <v>0.021222</v>
+        <v>207.790414</v>
       </c>
       <c r="I51" t="n">
-        <v>0.026907</v>
+        <v>174.997554</v>
       </c>
       <c r="J51" t="n">
-        <v>0.07322099999999999</v>
+        <v>125.795032</v>
+      </c>
+      <c r="K51" t="n">
+        <v>155.189499</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>電子通路</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5732.684626</v>
+        <v>4397.447876</v>
       </c>
       <c r="C52" t="n">
-        <v>10246.93227</v>
+        <v>5239.108744</v>
       </c>
       <c r="D52" t="n">
-        <v>8616.418030999999</v>
+        <v>6179.477361</v>
       </c>
       <c r="E52" t="n">
-        <v>10196.150336</v>
+        <v>4490.889025</v>
       </c>
       <c r="F52" t="n">
-        <v>6597.266704</v>
+        <v>5123.085956</v>
       </c>
       <c r="G52" t="n">
-        <v>7939.043424</v>
+        <v>3537.669758</v>
       </c>
       <c r="H52" t="n">
-        <v>7452.984238</v>
+        <v>3613.59471475</v>
       </c>
       <c r="I52" t="n">
-        <v>7304.302374</v>
+        <v>2919.11781</v>
       </c>
       <c r="J52" t="n">
-        <v>7877.259995</v>
+        <v>2875.676287</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3310.147664</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵</t>
+          <t>電子零組件</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2553.3653815</v>
+        <v>29613.628193</v>
       </c>
       <c r="C53" t="n">
-        <v>3519.341702</v>
+        <v>16199.311841</v>
       </c>
       <c r="D53" t="n">
-        <v>6191.425248333333</v>
+        <v>15853.533717</v>
       </c>
       <c r="E53" t="n">
-        <v>7155.879135</v>
+        <v>14779.86296466667</v>
       </c>
       <c r="F53" t="n">
-        <v>3091.901302</v>
+        <v>14465.035186</v>
       </c>
       <c r="G53" t="n">
-        <v>3451.97244275</v>
+        <v>12369.82966033333</v>
       </c>
       <c r="H53" t="n">
-        <v>1879.15980825</v>
+        <v>8840.385613</v>
       </c>
       <c r="I53" t="n">
-        <v>3532.391397</v>
+        <v>9901.63186</v>
       </c>
       <c r="J53" t="n">
-        <v>2544.125352</v>
+        <v>10721.13852266667</v>
+      </c>
+      <c r="K53" t="n">
+        <v>9752.979339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>467.102515</v>
+        <v>3331.120676</v>
       </c>
       <c r="C54" t="n">
-        <v>316.776227</v>
+        <v>2851.357159</v>
       </c>
       <c r="D54" t="n">
-        <v>353.129823</v>
+        <v>2526.839717</v>
       </c>
       <c r="E54" t="n">
-        <v>467.278976</v>
+        <v>3546.902833</v>
       </c>
       <c r="F54" t="n">
-        <v>627.997406</v>
+        <v>3274.420379</v>
       </c>
       <c r="G54" t="n">
-        <v>242.656285</v>
+        <v>2098.4072225</v>
       </c>
       <c r="H54" t="n">
-        <v>329.846967</v>
+        <v>2831.504</v>
       </c>
       <c r="I54" t="n">
-        <v>407.87994</v>
+        <v>3583.638983083334</v>
       </c>
       <c r="J54" t="n">
-        <v>406.750587</v>
+        <v>3623.130848</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4620.352306</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>電信</t>
+          <t>電腦週邊</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>918.019598</v>
+        <v>3017.801864</v>
       </c>
       <c r="C55" t="n">
-        <v>1676.725028</v>
+        <v>4370.473424</v>
       </c>
       <c r="D55" t="n">
-        <v>1524.028999</v>
+        <v>8852.417363</v>
       </c>
       <c r="E55" t="n">
-        <v>1248.190797</v>
+        <v>4470.291028</v>
       </c>
       <c r="F55" t="n">
-        <v>1458.3181</v>
+        <v>5018.532979</v>
       </c>
       <c r="G55" t="n">
-        <v>1239.700787</v>
+        <v>3194.964284</v>
       </c>
       <c r="H55" t="n">
-        <v>1019.972816</v>
+        <v>4976.850082</v>
       </c>
       <c r="I55" t="n">
-        <v>1027.931012</v>
+        <v>2330.66048375</v>
       </c>
       <c r="J55" t="n">
-        <v>1338.6324</v>
+        <v>2688.837942</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4316.675306</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>電動車</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10685.838357</v>
+        <v>1056.262568</v>
       </c>
       <c r="C56" t="n">
-        <v>11086.499208</v>
+        <v>1067.943964</v>
       </c>
       <c r="D56" t="n">
-        <v>15936.008962</v>
+        <v>1753.519909</v>
       </c>
       <c r="E56" t="n">
-        <v>7870.13773</v>
+        <v>1628.281254</v>
       </c>
       <c r="F56" t="n">
-        <v>7151.438405</v>
+        <v>3694.499608</v>
       </c>
       <c r="G56" t="n">
-        <v>13323.285339</v>
+        <v>1594.186972</v>
       </c>
       <c r="H56" t="n">
-        <v>13127.663375</v>
+        <v>1680.561113</v>
       </c>
       <c r="I56" t="n">
-        <v>8039.549699</v>
+        <v>1193.031047</v>
       </c>
       <c r="J56" t="n">
-        <v>8699.740658000001</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>107.918206</v>
-      </c>
-      <c r="C57" t="n">
-        <v>240.957821</v>
-      </c>
-      <c r="D57" t="n">
-        <v>280.614387</v>
-      </c>
-      <c r="E57" t="n">
-        <v>241.632148</v>
-      </c>
-      <c r="F57" t="n">
-        <v>160.750781</v>
-      </c>
-      <c r="G57" t="n">
-        <v>199.358638</v>
-      </c>
-      <c r="H57" t="n">
-        <v>156.92636</v>
-      </c>
-      <c r="I57" t="n">
-        <v>294.384024</v>
-      </c>
-      <c r="J57" t="n">
-        <v>264.279907</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>電子紙</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.797876</v>
-      </c>
-      <c r="C58" t="n">
-        <v>1.227215</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.803998</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.610103</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.848656</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.13421</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1.650141</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.983734</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.538445</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>電子通路</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3117.83436</v>
-      </c>
-      <c r="C59" t="n">
-        <v>3284.358638</v>
-      </c>
-      <c r="D59" t="n">
-        <v>3269.037075</v>
-      </c>
-      <c r="E59" t="n">
-        <v>4556.196035</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3278.903084</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2987.686914</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2359.443202</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2828.691759</v>
-      </c>
-      <c r="J59" t="n">
-        <v>4397.447876</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>電子零組件</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>15702.55116</v>
-      </c>
-      <c r="C60" t="n">
-        <v>16339.630617</v>
-      </c>
-      <c r="D60" t="n">
-        <v>13990.739466</v>
-      </c>
-      <c r="E60" t="n">
-        <v>17015.629412</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22387.334106</v>
-      </c>
-      <c r="G60" t="n">
-        <v>21582.243303</v>
-      </c>
-      <c r="H60" t="n">
-        <v>19432.335148</v>
-      </c>
-      <c r="I60" t="n">
-        <v>12667.172518</v>
-      </c>
-      <c r="J60" t="n">
-        <v>29613.628193</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2833.24706325</v>
-      </c>
-      <c r="C61" t="n">
-        <v>3220.483233</v>
-      </c>
-      <c r="D61" t="n">
-        <v>3455.685055</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2850.61244775</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2993.695927</v>
-      </c>
-      <c r="G61" t="n">
-        <v>2674.10022075</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2069.6081</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1959.657431</v>
-      </c>
-      <c r="J61" t="n">
-        <v>3331.120676</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>電腦週邊</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3864.484353</v>
-      </c>
-      <c r="C62" t="n">
-        <v>3658.219779</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3713.579148</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5625.03953</v>
-      </c>
-      <c r="F62" t="n">
-        <v>5045.504785</v>
-      </c>
-      <c r="G62" t="n">
-        <v>4618.943971</v>
-      </c>
-      <c r="H62" t="n">
-        <v>4452.85462</v>
-      </c>
-      <c r="I62" t="n">
-        <v>3549.041004</v>
-      </c>
-      <c r="J62" t="n">
-        <v>3017.801864</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>面板</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>23766.421451</v>
-      </c>
-      <c r="C63" t="n">
-        <v>24131.35528</v>
-      </c>
-      <c r="D63" t="n">
-        <v>42390.318478</v>
-      </c>
-      <c r="E63" t="n">
-        <v>61009.00298</v>
-      </c>
-      <c r="F63" t="n">
-        <v>39186.48104</v>
-      </c>
-      <c r="G63" t="n">
-        <v>58947.997898</v>
-      </c>
-      <c r="H63" t="n">
-        <v>25340.859125</v>
-      </c>
-      <c r="I63" t="n">
-        <v>18413.67049</v>
-      </c>
-      <c r="J63" t="n">
-        <v>14290.395492</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>672.670647</v>
-      </c>
-      <c r="C64" t="n">
-        <v>822.513379</v>
-      </c>
-      <c r="D64" t="n">
-        <v>808.75627</v>
-      </c>
-      <c r="E64" t="n">
-        <v>729.3189609999999</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1707.523625</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1123.525856</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1288.255756</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1442.587978</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1056.262568</v>
+        <v>1146.071359</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1019.882468</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82060.97606299999</v>
+        <v>146377.709394</v>
       </c>
       <c r="C2" t="n">
-        <v>95434.432019</v>
+        <v>111836.151503</v>
       </c>
       <c r="D2" t="n">
-        <v>109808.514004</v>
+        <v>88197.360011</v>
       </c>
       <c r="E2" t="n">
-        <v>90709.348566</v>
+        <v>88784.65591</v>
       </c>
       <c r="F2" t="n">
-        <v>146377.709394</v>
+        <v>118029.640628</v>
       </c>
       <c r="G2" t="n">
-        <v>111836.151503</v>
+        <v>86111.56320800001</v>
       </c>
       <c r="H2" t="n">
-        <v>88197.360011</v>
+        <v>116746.221458</v>
       </c>
       <c r="I2" t="n">
-        <v>88784.65591</v>
+        <v>82646.584332</v>
       </c>
       <c r="J2" t="n">
-        <v>118029.640628</v>
-      </c>
-      <c r="K2" t="n">
-        <v>86111.56320800001</v>
+        <v>88589.038311</v>
       </c>
     </row>
     <row r="3">
@@ -529,34 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1351.696174</v>
+        <v>3482.021308</v>
       </c>
       <c r="C3" t="n">
-        <v>2096.961518</v>
+        <v>2653.026445</v>
       </c>
       <c r="D3" t="n">
-        <v>2895.581625</v>
+        <v>2315.212176</v>
       </c>
       <c r="E3" t="n">
-        <v>2419.14550725</v>
+        <v>1672.452944</v>
       </c>
       <c r="F3" t="n">
-        <v>3482.021308</v>
+        <v>1870.514358</v>
       </c>
       <c r="G3" t="n">
-        <v>2653.026445</v>
+        <v>1820.151502</v>
       </c>
       <c r="H3" t="n">
-        <v>2315.212176</v>
+        <v>2917.500566</v>
       </c>
       <c r="I3" t="n">
-        <v>1672.452944</v>
+        <v>2070.829852</v>
       </c>
       <c r="J3" t="n">
-        <v>1870.514358</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1820.151502</v>
+        <v>2092.097911</v>
       </c>
     </row>
     <row r="4">
@@ -566,34 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170431.167476</v>
+        <v>303082.816948</v>
       </c>
       <c r="C4" t="n">
-        <v>159181.7152</v>
+        <v>193622.711519</v>
       </c>
       <c r="D4" t="n">
-        <v>221865.684942</v>
+        <v>147446.818662</v>
       </c>
       <c r="E4" t="n">
-        <v>165524.115202</v>
+        <v>124321.122321</v>
       </c>
       <c r="F4" t="n">
-        <v>303082.816948</v>
+        <v>150792.801026</v>
       </c>
       <c r="G4" t="n">
-        <v>193622.711519</v>
+        <v>147850.838611</v>
       </c>
       <c r="H4" t="n">
-        <v>147446.818662</v>
+        <v>210144.106473</v>
       </c>
       <c r="I4" t="n">
-        <v>124321.122321</v>
+        <v>139875.023277</v>
       </c>
       <c r="J4" t="n">
-        <v>150792.801026</v>
-      </c>
-      <c r="K4" t="n">
-        <v>147850.838611</v>
+        <v>166051.110256</v>
       </c>
     </row>
     <row r="5">
@@ -603,34 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1992.966278</v>
+        <v>3258.561954</v>
       </c>
       <c r="C5" t="n">
-        <v>6388.321597</v>
+        <v>1346.914769</v>
       </c>
       <c r="D5" t="n">
-        <v>4515.853307</v>
+        <v>1923.767901</v>
       </c>
       <c r="E5" t="n">
-        <v>3162.179545</v>
+        <v>1581.217843</v>
       </c>
       <c r="F5" t="n">
-        <v>3258.561954</v>
+        <v>1589.279806</v>
       </c>
       <c r="G5" t="n">
-        <v>1346.914769</v>
+        <v>1426.783736</v>
       </c>
       <c r="H5" t="n">
-        <v>1923.767901</v>
+        <v>2424.657227</v>
       </c>
       <c r="I5" t="n">
-        <v>1581.217843</v>
+        <v>1546.911157</v>
       </c>
       <c r="J5" t="n">
-        <v>1589.279806</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1426.783736</v>
+        <v>1666.438213</v>
       </c>
     </row>
     <row r="6">
@@ -640,34 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>101210.657554</v>
+        <v>151269.855885</v>
       </c>
       <c r="C6" t="n">
-        <v>89951.08953700001</v>
+        <v>120306.325953</v>
       </c>
       <c r="D6" t="n">
-        <v>109727.515864</v>
+        <v>130064.351814</v>
       </c>
       <c r="E6" t="n">
-        <v>104235.103462</v>
+        <v>128906.794282</v>
       </c>
       <c r="F6" t="n">
-        <v>151269.855885</v>
+        <v>142583.75425</v>
       </c>
       <c r="G6" t="n">
-        <v>120306.325953</v>
+        <v>175994.789733</v>
       </c>
       <c r="H6" t="n">
-        <v>130064.351814</v>
+        <v>164386.057594</v>
       </c>
       <c r="I6" t="n">
-        <v>128906.794282</v>
+        <v>117708.84499</v>
       </c>
       <c r="J6" t="n">
-        <v>142583.75425</v>
-      </c>
-      <c r="K6" t="n">
-        <v>175994.789733</v>
+        <v>107080.03780825</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17549.479583</v>
+        <v>40327.416367</v>
       </c>
       <c r="C7" t="n">
-        <v>51398.922299</v>
+        <v>53567.139487</v>
       </c>
       <c r="D7" t="n">
-        <v>56648.492805</v>
+        <v>25279.321246</v>
       </c>
       <c r="E7" t="n">
-        <v>43564.427475</v>
+        <v>30217.0626</v>
       </c>
       <c r="F7" t="n">
-        <v>40327.416367</v>
+        <v>30775.962933</v>
       </c>
       <c r="G7" t="n">
-        <v>53567.139487</v>
+        <v>27850.794304</v>
       </c>
       <c r="H7" t="n">
-        <v>25279.321246</v>
+        <v>31164.966686</v>
       </c>
       <c r="I7" t="n">
-        <v>30217.0626</v>
+        <v>23663.186839</v>
       </c>
       <c r="J7" t="n">
-        <v>30775.962933</v>
-      </c>
-      <c r="K7" t="n">
-        <v>27850.794304</v>
+        <v>24522.438173</v>
       </c>
     </row>
     <row r="8">
@@ -714,34 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11700.144202</v>
+        <v>11367.800512</v>
       </c>
       <c r="C8" t="n">
-        <v>9923.101177</v>
+        <v>9290.113633999999</v>
       </c>
       <c r="D8" t="n">
-        <v>14089.832465</v>
+        <v>6401.606748</v>
       </c>
       <c r="E8" t="n">
-        <v>10043.258621</v>
+        <v>5530.783665</v>
       </c>
       <c r="F8" t="n">
-        <v>11367.800512</v>
+        <v>5227.592729</v>
       </c>
       <c r="G8" t="n">
-        <v>9290.113633999999</v>
+        <v>6216.818898</v>
       </c>
       <c r="H8" t="n">
-        <v>6401.606748</v>
+        <v>5003.552339</v>
       </c>
       <c r="I8" t="n">
-        <v>5530.783665</v>
+        <v>5074.958122</v>
       </c>
       <c r="J8" t="n">
-        <v>5227.592729</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6216.818898</v>
+        <v>8072.278837</v>
       </c>
     </row>
     <row r="9">
@@ -751,34 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29647.371037</v>
+        <v>47858.980378</v>
       </c>
       <c r="C9" t="n">
-        <v>34880.627577</v>
+        <v>38701.195125</v>
       </c>
       <c r="D9" t="n">
-        <v>43373.242818</v>
+        <v>29034.133984</v>
       </c>
       <c r="E9" t="n">
-        <v>30713.706643</v>
+        <v>35222.48547</v>
       </c>
       <c r="F9" t="n">
-        <v>47858.980378</v>
+        <v>34042.91955</v>
       </c>
       <c r="G9" t="n">
-        <v>38701.195125</v>
+        <v>42756.617748</v>
       </c>
       <c r="H9" t="n">
-        <v>29034.133984</v>
+        <v>32599.44009275</v>
       </c>
       <c r="I9" t="n">
-        <v>35222.48547</v>
+        <v>27002.968423</v>
       </c>
       <c r="J9" t="n">
-        <v>34042.91955</v>
-      </c>
-      <c r="K9" t="n">
-        <v>42756.617748</v>
+        <v>40226.79954233333</v>
       </c>
     </row>
     <row r="10">
@@ -788,34 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1570.4074355</v>
+        <v>2968.736749333333</v>
       </c>
       <c r="C10" t="n">
-        <v>1715.3806515</v>
+        <v>1863.8975865</v>
       </c>
       <c r="D10" t="n">
-        <v>1700.879939</v>
+        <v>1660.79840675</v>
       </c>
       <c r="E10" t="n">
-        <v>1677.349480416667</v>
+        <v>1890.91217525</v>
       </c>
       <c r="F10" t="n">
-        <v>2968.736749333333</v>
+        <v>1789.04645175</v>
       </c>
       <c r="G10" t="n">
-        <v>1863.8975865</v>
+        <v>1726.716907666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1660.79840675</v>
+        <v>2906.054243333333</v>
       </c>
       <c r="I10" t="n">
-        <v>1890.91217525</v>
+        <v>1877.928038</v>
       </c>
       <c r="J10" t="n">
-        <v>1789.04645175</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1726.716907666666</v>
+        <v>1650.858536666667</v>
       </c>
     </row>
     <row r="11">
@@ -825,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3413.142047</v>
+        <v>5176.826412</v>
       </c>
       <c r="C11" t="n">
-        <v>4428.876894</v>
+        <v>3792.995132</v>
       </c>
       <c r="D11" t="n">
-        <v>4573.556078</v>
+        <v>3971.737123</v>
       </c>
       <c r="E11" t="n">
-        <v>5066.849458</v>
+        <v>2607.64261</v>
       </c>
       <c r="F11" t="n">
-        <v>5176.826412</v>
+        <v>6270.54130125</v>
       </c>
       <c r="G11" t="n">
-        <v>3792.995132</v>
+        <v>3458.255305</v>
       </c>
       <c r="H11" t="n">
-        <v>3971.737123</v>
+        <v>5757.848463</v>
       </c>
       <c r="I11" t="n">
-        <v>2607.64261</v>
+        <v>4933.058583</v>
       </c>
       <c r="J11" t="n">
-        <v>6270.54130125</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3458.255305</v>
+        <v>2206.789234</v>
       </c>
     </row>
     <row r="12">
@@ -862,34 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12900.263706</v>
+        <v>16680.755963</v>
       </c>
       <c r="C12" t="n">
-        <v>10926.729496</v>
+        <v>16906.893744</v>
       </c>
       <c r="D12" t="n">
-        <v>13504.697924</v>
+        <v>10640.922305</v>
       </c>
       <c r="E12" t="n">
-        <v>10933.252739</v>
+        <v>8829.759413</v>
       </c>
       <c r="F12" t="n">
-        <v>16680.755963</v>
+        <v>9388.852977</v>
       </c>
       <c r="G12" t="n">
-        <v>16906.893744</v>
+        <v>10775.805214</v>
       </c>
       <c r="H12" t="n">
-        <v>10640.922305</v>
+        <v>9931.147682000001</v>
       </c>
       <c r="I12" t="n">
-        <v>8829.759413</v>
+        <v>7817.170597</v>
       </c>
       <c r="J12" t="n">
-        <v>9388.852977</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10775.805214</v>
+        <v>13651.147226</v>
       </c>
     </row>
     <row r="13">
@@ -899,34 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4695.352964</v>
+        <v>3231.178388</v>
       </c>
       <c r="C13" t="n">
-        <v>3307.298609</v>
+        <v>3960.347477</v>
       </c>
       <c r="D13" t="n">
-        <v>3235.156925</v>
+        <v>2417.560399</v>
       </c>
       <c r="E13" t="n">
-        <v>3959.015533</v>
+        <v>2771.525746</v>
       </c>
       <c r="F13" t="n">
-        <v>3231.178388</v>
+        <v>3454.18744</v>
       </c>
       <c r="G13" t="n">
-        <v>3960.347477</v>
+        <v>2375.099497</v>
       </c>
       <c r="H13" t="n">
-        <v>2417.560399</v>
+        <v>2925.270128</v>
       </c>
       <c r="I13" t="n">
-        <v>2771.525746</v>
+        <v>1318.721641</v>
       </c>
       <c r="J13" t="n">
-        <v>3454.18744</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2375.099497</v>
+        <v>1292.076477</v>
       </c>
     </row>
     <row r="14">
@@ -936,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5838.202682</v>
+        <v>9671.434703000001</v>
       </c>
       <c r="C14" t="n">
-        <v>13174.327015</v>
+        <v>6823.14329</v>
       </c>
       <c r="D14" t="n">
-        <v>7189.191447</v>
+        <v>5378.798716</v>
       </c>
       <c r="E14" t="n">
-        <v>7385.884821</v>
+        <v>5067.008517</v>
       </c>
       <c r="F14" t="n">
-        <v>9671.434703000001</v>
+        <v>6170.564575</v>
       </c>
       <c r="G14" t="n">
-        <v>6823.14329</v>
+        <v>6495.070194</v>
       </c>
       <c r="H14" t="n">
-        <v>5378.798716</v>
+        <v>6903.437777</v>
       </c>
       <c r="I14" t="n">
-        <v>5067.008517</v>
+        <v>4959.918107</v>
       </c>
       <c r="J14" t="n">
-        <v>6170.564575</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6495.070194</v>
+        <v>5343.092632</v>
       </c>
     </row>
     <row r="15">
@@ -973,34 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22968.081151</v>
+        <v>45344.637937</v>
       </c>
       <c r="C15" t="n">
-        <v>19468.556038</v>
+        <v>28502.020962</v>
       </c>
       <c r="D15" t="n">
-        <v>40077.878692</v>
+        <v>29474.558918</v>
       </c>
       <c r="E15" t="n">
-        <v>23710.610413</v>
+        <v>20905.593194</v>
       </c>
       <c r="F15" t="n">
-        <v>45344.637937</v>
+        <v>22869.744188</v>
       </c>
       <c r="G15" t="n">
-        <v>28502.020962</v>
+        <v>35181.997593</v>
       </c>
       <c r="H15" t="n">
-        <v>29474.558918</v>
+        <v>33063.448277</v>
       </c>
       <c r="I15" t="n">
-        <v>20905.593194</v>
+        <v>26407.014911</v>
       </c>
       <c r="J15" t="n">
-        <v>22869.744188</v>
-      </c>
-      <c r="K15" t="n">
-        <v>35181.997593</v>
+        <v>27811.136893</v>
       </c>
     </row>
     <row r="16">
@@ -1010,34 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15866.876911</v>
+        <v>20984.679592</v>
       </c>
       <c r="C16" t="n">
-        <v>18530.52396</v>
+        <v>18075.029301</v>
       </c>
       <c r="D16" t="n">
-        <v>17081.652832</v>
+        <v>10885.54886</v>
       </c>
       <c r="E16" t="n">
-        <v>13923.051787</v>
+        <v>10178.362449</v>
       </c>
       <c r="F16" t="n">
-        <v>20984.679592</v>
+        <v>14624.726406</v>
       </c>
       <c r="G16" t="n">
-        <v>18075.029301</v>
+        <v>12350.877069</v>
       </c>
       <c r="H16" t="n">
-        <v>10885.54886</v>
+        <v>14349.347742</v>
       </c>
       <c r="I16" t="n">
-        <v>10178.362449</v>
+        <v>14115.947664</v>
       </c>
       <c r="J16" t="n">
-        <v>14624.726406</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12350.877069</v>
+        <v>11600.798043</v>
       </c>
     </row>
     <row r="17">
@@ -1047,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46809.599087</v>
+        <v>55652.472682</v>
       </c>
       <c r="C17" t="n">
-        <v>39256.618254</v>
+        <v>26977.665732</v>
       </c>
       <c r="D17" t="n">
-        <v>39564.844257</v>
+        <v>25679.187541</v>
       </c>
       <c r="E17" t="n">
-        <v>39324.200556</v>
+        <v>18361.073069</v>
       </c>
       <c r="F17" t="n">
-        <v>55652.472682</v>
+        <v>20715.519402</v>
       </c>
       <c r="G17" t="n">
-        <v>26977.665732</v>
+        <v>30246.361273</v>
       </c>
       <c r="H17" t="n">
-        <v>25679.187541</v>
+        <v>33791.051903</v>
       </c>
       <c r="I17" t="n">
-        <v>18361.073069</v>
+        <v>25023.535146</v>
       </c>
       <c r="J17" t="n">
-        <v>20715.519402</v>
-      </c>
-      <c r="K17" t="n">
-        <v>30246.361273</v>
+        <v>16460.690502</v>
       </c>
     </row>
     <row r="18">
@@ -1084,34 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>851.002673</v>
+        <v>1135.755548</v>
       </c>
       <c r="C18" t="n">
-        <v>846.211093</v>
+        <v>711.696551</v>
       </c>
       <c r="D18" t="n">
-        <v>920.6671</v>
+        <v>578.367599</v>
       </c>
       <c r="E18" t="n">
-        <v>656.8436369999999</v>
+        <v>515.620049</v>
       </c>
       <c r="F18" t="n">
-        <v>1135.755548</v>
+        <v>474.713156</v>
       </c>
       <c r="G18" t="n">
-        <v>711.696551</v>
+        <v>483.392604</v>
       </c>
       <c r="H18" t="n">
-        <v>578.367599</v>
+        <v>527.9513020000001</v>
       </c>
       <c r="I18" t="n">
-        <v>515.620049</v>
+        <v>264.580761</v>
       </c>
       <c r="J18" t="n">
-        <v>474.713156</v>
-      </c>
-      <c r="K18" t="n">
-        <v>483.392604</v>
+        <v>501.552545</v>
       </c>
     </row>
     <row r="19">
@@ -1121,34 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>112.358103</v>
+        <v>371.724318</v>
       </c>
       <c r="C19" t="n">
-        <v>219.5649815</v>
+        <v>340.844856</v>
       </c>
       <c r="D19" t="n">
-        <v>220.8968055</v>
+        <v>478.877536</v>
       </c>
       <c r="E19" t="n">
-        <v>333.5251645</v>
+        <v>327.893671</v>
       </c>
       <c r="F19" t="n">
-        <v>371.724318</v>
+        <v>283.604148</v>
       </c>
       <c r="G19" t="n">
-        <v>340.844856</v>
+        <v>357.590444</v>
       </c>
       <c r="H19" t="n">
-        <v>478.877536</v>
+        <v>346.415106</v>
       </c>
       <c r="I19" t="n">
-        <v>327.893671</v>
+        <v>175.401725</v>
       </c>
       <c r="J19" t="n">
-        <v>283.604148</v>
-      </c>
-      <c r="K19" t="n">
-        <v>357.590444</v>
+        <v>242.9557945</v>
       </c>
     </row>
     <row r="20">
@@ -1158,34 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10881.654325</v>
+        <v>41879.135888</v>
       </c>
       <c r="C20" t="n">
-        <v>22683.159205</v>
+        <v>14191.568201</v>
       </c>
       <c r="D20" t="n">
-        <v>27348.945384</v>
+        <v>12678.851694</v>
       </c>
       <c r="E20" t="n">
-        <v>17437.834996</v>
+        <v>15494.785698</v>
       </c>
       <c r="F20" t="n">
-        <v>41879.135888</v>
+        <v>18710.0614</v>
       </c>
       <c r="G20" t="n">
-        <v>14191.568201</v>
+        <v>16122.009331</v>
       </c>
       <c r="H20" t="n">
-        <v>12678.851694</v>
+        <v>29396.761097</v>
       </c>
       <c r="I20" t="n">
-        <v>15494.785698</v>
+        <v>11522.327561</v>
       </c>
       <c r="J20" t="n">
-        <v>18710.0614</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16122.009331</v>
+        <v>25762.800797</v>
       </c>
     </row>
     <row r="21">
@@ -1195,34 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3215.085467</v>
+        <v>4266.437468</v>
       </c>
       <c r="C21" t="n">
-        <v>3650.649543</v>
+        <v>3621.255247</v>
       </c>
       <c r="D21" t="n">
-        <v>3211.059413</v>
+        <v>4151.474794</v>
       </c>
       <c r="E21" t="n">
-        <v>3044.335796</v>
+        <v>3373.680529</v>
       </c>
       <c r="F21" t="n">
-        <v>4266.437468</v>
+        <v>3096.345134</v>
       </c>
       <c r="G21" t="n">
-        <v>3621.255247</v>
+        <v>2838.648272</v>
       </c>
       <c r="H21" t="n">
-        <v>4151.474794</v>
+        <v>3863.356957</v>
       </c>
       <c r="I21" t="n">
-        <v>3373.680529</v>
+        <v>3232.837444</v>
       </c>
       <c r="J21" t="n">
-        <v>3096.345134</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2838.648272</v>
+        <v>3861.262954</v>
       </c>
     </row>
     <row r="22">
@@ -1232,34 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>95.273578</v>
+        <v>228.552413</v>
       </c>
       <c r="C22" t="n">
-        <v>83.202314</v>
+        <v>228.59593</v>
       </c>
       <c r="D22" t="n">
-        <v>146.311388</v>
+        <v>148.972835</v>
       </c>
       <c r="E22" t="n">
-        <v>149.448354</v>
+        <v>217.130414</v>
       </c>
       <c r="F22" t="n">
-        <v>228.552413</v>
+        <v>322.379927</v>
       </c>
       <c r="G22" t="n">
-        <v>228.59593</v>
+        <v>422.57159</v>
       </c>
       <c r="H22" t="n">
-        <v>148.972835</v>
+        <v>323.7080105</v>
       </c>
       <c r="I22" t="n">
-        <v>217.130414</v>
+        <v>144.683167</v>
       </c>
       <c r="J22" t="n">
-        <v>322.379927</v>
-      </c>
-      <c r="K22" t="n">
-        <v>422.57159</v>
+        <v>127.241553</v>
       </c>
     </row>
     <row r="23">
@@ -1269,34 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.993371</v>
+        <v>2.63044825</v>
       </c>
       <c r="C23" t="n">
-        <v>1.78307375</v>
+        <v>2.833667</v>
       </c>
       <c r="D23" t="n">
-        <v>1.671217333333333</v>
+        <v>1.47260325</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0712465</v>
+        <v>1.32028125</v>
       </c>
       <c r="F23" t="n">
-        <v>2.63044825</v>
+        <v>0.9817399999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>2.833667</v>
+        <v>1.086043</v>
       </c>
       <c r="H23" t="n">
-        <v>1.47260325</v>
+        <v>0.87417925</v>
       </c>
       <c r="I23" t="n">
-        <v>1.32028125</v>
+        <v>1.143618</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9817399999999999</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.086043</v>
+        <v>1.338211333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1116.41372</v>
+        <v>1457.277657</v>
       </c>
       <c r="C24" t="n">
-        <v>975.403637</v>
+        <v>653.56974</v>
       </c>
       <c r="D24" t="n">
-        <v>905.974587</v>
+        <v>1082.038393</v>
       </c>
       <c r="E24" t="n">
-        <v>526.089604</v>
+        <v>789.121836</v>
       </c>
       <c r="F24" t="n">
-        <v>1457.277657</v>
+        <v>678.47342</v>
       </c>
       <c r="G24" t="n">
-        <v>653.56974</v>
+        <v>560.028791</v>
       </c>
       <c r="H24" t="n">
-        <v>1082.038393</v>
+        <v>2379.117345</v>
       </c>
       <c r="I24" t="n">
-        <v>789.121836</v>
+        <v>2879.210223</v>
       </c>
       <c r="J24" t="n">
-        <v>678.47342</v>
-      </c>
-      <c r="K24" t="n">
-        <v>560.028791</v>
+        <v>1068.16662</v>
       </c>
     </row>
     <row r="25">
@@ -1343,34 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>559.696609</v>
+        <v>834.998774</v>
       </c>
       <c r="C25" t="n">
-        <v>591.2121509999999</v>
+        <v>661.627076</v>
       </c>
       <c r="D25" t="n">
-        <v>411.916797</v>
+        <v>474.962401</v>
       </c>
       <c r="E25" t="n">
-        <v>693.882124</v>
+        <v>356.818377</v>
       </c>
       <c r="F25" t="n">
-        <v>834.998774</v>
+        <v>327.770791</v>
       </c>
       <c r="G25" t="n">
-        <v>661.627076</v>
+        <v>307.888329</v>
       </c>
       <c r="H25" t="n">
-        <v>474.962401</v>
+        <v>928.851329</v>
       </c>
       <c r="I25" t="n">
-        <v>356.818377</v>
+        <v>400.624759</v>
       </c>
       <c r="J25" t="n">
-        <v>327.770791</v>
-      </c>
-      <c r="K25" t="n">
-        <v>307.888329</v>
+        <v>273.361778</v>
       </c>
     </row>
     <row r="26">
@@ -1380,34 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1255.344352</v>
+        <v>1668.468947</v>
       </c>
       <c r="C26" t="n">
-        <v>3679.082969</v>
+        <v>1906.351396</v>
       </c>
       <c r="D26" t="n">
-        <v>1782.611379</v>
+        <v>1106.356106</v>
       </c>
       <c r="E26" t="n">
-        <v>2476.659351</v>
+        <v>1202.872977</v>
       </c>
       <c r="F26" t="n">
-        <v>1668.468947</v>
+        <v>982.0145659999999</v>
       </c>
       <c r="G26" t="n">
-        <v>1906.351396</v>
+        <v>3377.085099</v>
       </c>
       <c r="H26" t="n">
-        <v>1106.356106</v>
+        <v>1771.499985</v>
       </c>
       <c r="I26" t="n">
-        <v>1202.872977</v>
+        <v>1282.141432</v>
       </c>
       <c r="J26" t="n">
-        <v>982.0145659999999</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3377.085099</v>
+        <v>1123.66674</v>
       </c>
     </row>
     <row r="27">
@@ -1417,34 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11701.00615</v>
+        <v>9002.351504</v>
       </c>
       <c r="C27" t="n">
-        <v>7792.562236</v>
+        <v>6343.406324</v>
       </c>
       <c r="D27" t="n">
-        <v>9551.441784000001</v>
+        <v>5278.593607</v>
       </c>
       <c r="E27" t="n">
-        <v>6319.221908</v>
+        <v>4951.307608</v>
       </c>
       <c r="F27" t="n">
-        <v>9002.351504</v>
+        <v>6806.019453</v>
       </c>
       <c r="G27" t="n">
-        <v>6343.406324</v>
+        <v>5483.5149605</v>
       </c>
       <c r="H27" t="n">
-        <v>5278.593607</v>
+        <v>12019.31072</v>
       </c>
       <c r="I27" t="n">
-        <v>4951.307608</v>
+        <v>7835.189957</v>
       </c>
       <c r="J27" t="n">
-        <v>6806.019453</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5483.5149605</v>
+        <v>6304.168288</v>
       </c>
     </row>
     <row r="28">
@@ -1454,34 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4567.157574</v>
+        <v>6638.344623</v>
       </c>
       <c r="C28" t="n">
-        <v>4464.077512</v>
+        <v>5969.8867385</v>
       </c>
       <c r="D28" t="n">
-        <v>8026.554494</v>
+        <v>8963.286382</v>
       </c>
       <c r="E28" t="n">
-        <v>17251.803885</v>
+        <v>5845.509506</v>
       </c>
       <c r="F28" t="n">
-        <v>6638.344623</v>
+        <v>4315.397605</v>
       </c>
       <c r="G28" t="n">
-        <v>5969.8867385</v>
+        <v>3943.029472</v>
       </c>
       <c r="H28" t="n">
-        <v>8963.286382</v>
+        <v>1944.495665</v>
       </c>
       <c r="I28" t="n">
-        <v>5845.509506</v>
+        <v>2652.312861</v>
       </c>
       <c r="J28" t="n">
-        <v>4315.397605</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3943.029472</v>
+        <v>2240.920121</v>
       </c>
     </row>
     <row r="29">
@@ -1491,34 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1047.138793166667</v>
+        <v>1481.882935</v>
       </c>
       <c r="C29" t="n">
-        <v>1575.585877666667</v>
+        <v>921.225533</v>
       </c>
       <c r="D29" t="n">
-        <v>1355.678808</v>
+        <v>1287.748339</v>
       </c>
       <c r="E29" t="n">
-        <v>948.559933</v>
+        <v>1097.726776</v>
       </c>
       <c r="F29" t="n">
-        <v>1481.882935</v>
+        <v>1008.621634</v>
       </c>
       <c r="G29" t="n">
-        <v>921.225533</v>
+        <v>1223.7303175</v>
       </c>
       <c r="H29" t="n">
-        <v>1287.748339</v>
+        <v>3778.9339045</v>
       </c>
       <c r="I29" t="n">
-        <v>1097.726776</v>
+        <v>1650.0702305</v>
       </c>
       <c r="J29" t="n">
-        <v>1008.621634</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1223.7303175</v>
+        <v>1072.90880125</v>
       </c>
     </row>
     <row r="30">
@@ -1528,34 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10431.840663</v>
+        <v>5295.728255</v>
       </c>
       <c r="C30" t="n">
-        <v>6506.24478</v>
+        <v>9593.106706</v>
       </c>
       <c r="D30" t="n">
-        <v>2927.730432</v>
+        <v>14525.081378</v>
       </c>
       <c r="E30" t="n">
-        <v>12616.014929</v>
+        <v>14764.888638</v>
       </c>
       <c r="F30" t="n">
-        <v>5295.728255</v>
+        <v>10582.289675</v>
       </c>
       <c r="G30" t="n">
-        <v>9593.106706</v>
+        <v>19618.558693</v>
       </c>
       <c r="H30" t="n">
-        <v>14525.081378</v>
+        <v>8323.112531999999</v>
       </c>
       <c r="I30" t="n">
-        <v>14764.888638</v>
+        <v>8574.781219</v>
       </c>
       <c r="J30" t="n">
-        <v>10582.289675</v>
-      </c>
-      <c r="K30" t="n">
-        <v>19618.558693</v>
+        <v>4656.935608</v>
       </c>
     </row>
     <row r="31">
@@ -1565,34 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4149.801865083334</v>
+        <v>6989.188224</v>
       </c>
       <c r="C31" t="n">
-        <v>3720.87209275</v>
+        <v>6393.92870275</v>
       </c>
       <c r="D31" t="n">
-        <v>4189.765495</v>
+        <v>5021.116329083334</v>
       </c>
       <c r="E31" t="n">
-        <v>3457.454643</v>
+        <v>3148.95717875</v>
       </c>
       <c r="F31" t="n">
-        <v>6989.188224</v>
+        <v>3987.6690155</v>
       </c>
       <c r="G31" t="n">
-        <v>6393.92870275</v>
+        <v>2998.78392925</v>
       </c>
       <c r="H31" t="n">
-        <v>5021.116329083334</v>
+        <v>4680.430511666667</v>
       </c>
       <c r="I31" t="n">
-        <v>3148.95717875</v>
+        <v>2929.372245333333</v>
       </c>
       <c r="J31" t="n">
-        <v>3987.6690155</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2998.78392925</v>
+        <v>4411.32397675</v>
       </c>
     </row>
     <row r="32">
@@ -1602,34 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>50158.028725</v>
+        <v>56762.360998</v>
       </c>
       <c r="C32" t="n">
-        <v>42232.718181</v>
+        <v>51513.200483</v>
       </c>
       <c r="D32" t="n">
-        <v>55929.601564</v>
+        <v>39124.732034</v>
       </c>
       <c r="E32" t="n">
-        <v>91141.357539</v>
+        <v>39590.881003</v>
       </c>
       <c r="F32" t="n">
-        <v>56762.360998</v>
+        <v>45804.859502</v>
       </c>
       <c r="G32" t="n">
-        <v>51513.200483</v>
+        <v>37423.45247233334</v>
       </c>
       <c r="H32" t="n">
-        <v>39124.732034</v>
+        <v>40718.0378435</v>
       </c>
       <c r="I32" t="n">
-        <v>39590.881003</v>
+        <v>31654.4544115</v>
       </c>
       <c r="J32" t="n">
-        <v>45804.859502</v>
-      </c>
-      <c r="K32" t="n">
-        <v>37423.45247233334</v>
+        <v>25292.816004</v>
       </c>
     </row>
     <row r="33">
@@ -1639,34 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2532.299892</v>
+        <v>2755.842148</v>
       </c>
       <c r="C33" t="n">
-        <v>1842.722269</v>
+        <v>1567.7892245</v>
       </c>
       <c r="D33" t="n">
-        <v>1312.871816</v>
+        <v>1019.075243</v>
       </c>
       <c r="E33" t="n">
-        <v>2704.808953</v>
+        <v>1092.226384</v>
       </c>
       <c r="F33" t="n">
-        <v>2755.842148</v>
+        <v>829.024501</v>
       </c>
       <c r="G33" t="n">
-        <v>1567.7892245</v>
+        <v>916.605739</v>
       </c>
       <c r="H33" t="n">
-        <v>1019.075243</v>
+        <v>1642.835371</v>
       </c>
       <c r="I33" t="n">
-        <v>1092.226384</v>
+        <v>783.09935</v>
       </c>
       <c r="J33" t="n">
-        <v>829.024501</v>
-      </c>
-      <c r="K33" t="n">
-        <v>916.605739</v>
+        <v>701.288429</v>
       </c>
     </row>
     <row r="34">
@@ -1676,34 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2968.90518925</v>
+        <v>2736.504571</v>
       </c>
       <c r="C34" t="n">
-        <v>2355.699666</v>
+        <v>1751.39205925</v>
       </c>
       <c r="D34" t="n">
-        <v>2516.129288</v>
+        <v>2081.145656</v>
       </c>
       <c r="E34" t="n">
-        <v>1361.660627</v>
+        <v>1426.808585</v>
       </c>
       <c r="F34" t="n">
-        <v>2736.504571</v>
+        <v>1121.898895</v>
       </c>
       <c r="G34" t="n">
-        <v>1751.39205925</v>
+        <v>1528.765713</v>
       </c>
       <c r="H34" t="n">
-        <v>2081.145656</v>
+        <v>2085.870603</v>
       </c>
       <c r="I34" t="n">
-        <v>1426.808585</v>
+        <v>1248.380823</v>
       </c>
       <c r="J34" t="n">
-        <v>1121.898895</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1528.765713</v>
+        <v>1163.50581</v>
       </c>
     </row>
     <row r="35">
@@ -1713,34 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11382.659629</v>
+        <v>11703.76045</v>
       </c>
       <c r="C35" t="n">
-        <v>13378.419226</v>
+        <v>12703.616457</v>
       </c>
       <c r="D35" t="n">
-        <v>16132.291819</v>
+        <v>13402.771396</v>
       </c>
       <c r="E35" t="n">
-        <v>12203.242913</v>
+        <v>11425.688567</v>
       </c>
       <c r="F35" t="n">
-        <v>11703.76045</v>
+        <v>20110.469244</v>
       </c>
       <c r="G35" t="n">
-        <v>12703.616457</v>
+        <v>9588.452409</v>
       </c>
       <c r="H35" t="n">
-        <v>13402.771396</v>
+        <v>10422.690524</v>
       </c>
       <c r="I35" t="n">
-        <v>11425.688567</v>
+        <v>7350.793886</v>
       </c>
       <c r="J35" t="n">
-        <v>20110.469244</v>
-      </c>
-      <c r="K35" t="n">
-        <v>9588.452409</v>
+        <v>8254.514959</v>
       </c>
     </row>
     <row r="36">
@@ -1750,34 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>614.6217380000001</v>
+        <v>1232.572688</v>
       </c>
       <c r="C36" t="n">
-        <v>1073.0414</v>
+        <v>1879.559285</v>
       </c>
       <c r="D36" t="n">
-        <v>1594.388937</v>
+        <v>1081.058934</v>
       </c>
       <c r="E36" t="n">
-        <v>1076.331173</v>
+        <v>863.168954</v>
       </c>
       <c r="F36" t="n">
-        <v>1232.572688</v>
+        <v>1008.784159</v>
       </c>
       <c r="G36" t="n">
-        <v>1879.559285</v>
+        <v>810.950855</v>
       </c>
       <c r="H36" t="n">
-        <v>1081.058934</v>
+        <v>1069.52765</v>
       </c>
       <c r="I36" t="n">
-        <v>863.168954</v>
+        <v>625.322553</v>
       </c>
       <c r="J36" t="n">
-        <v>1008.784159</v>
-      </c>
-      <c r="K36" t="n">
-        <v>810.950855</v>
+        <v>504.335782</v>
       </c>
     </row>
     <row r="37">
@@ -1787,34 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4521.877945</v>
+        <v>9830.857416000001</v>
       </c>
       <c r="C37" t="n">
-        <v>25931.5456045</v>
+        <v>10698.718434</v>
       </c>
       <c r="D37" t="n">
-        <v>26286.154605</v>
+        <v>6433.64742575</v>
       </c>
       <c r="E37" t="n">
-        <v>14965.124573</v>
+        <v>5580.049872</v>
       </c>
       <c r="F37" t="n">
-        <v>9830.857416000001</v>
+        <v>5967.7019175</v>
       </c>
       <c r="G37" t="n">
-        <v>10698.718434</v>
+        <v>5460.094539</v>
       </c>
       <c r="H37" t="n">
-        <v>6433.64742575</v>
+        <v>7421.544591666667</v>
       </c>
       <c r="I37" t="n">
-        <v>5580.049872</v>
+        <v>4000.169336</v>
       </c>
       <c r="J37" t="n">
-        <v>5967.7019175</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5460.094539</v>
+        <v>3816.3079015</v>
       </c>
     </row>
     <row r="38">
@@ -1824,34 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>81211.36083799999</v>
+        <v>68946.483389</v>
       </c>
       <c r="C38" t="n">
-        <v>38791.176169</v>
+        <v>44982.238539</v>
       </c>
       <c r="D38" t="n">
-        <v>59016.945957</v>
+        <v>42998.291544</v>
       </c>
       <c r="E38" t="n">
-        <v>60913.516455</v>
+        <v>52802.554316</v>
       </c>
       <c r="F38" t="n">
-        <v>68946.483389</v>
+        <v>48528.16413</v>
       </c>
       <c r="G38" t="n">
-        <v>44982.238539</v>
+        <v>63229.713007</v>
       </c>
       <c r="H38" t="n">
-        <v>42998.291544</v>
+        <v>42515.79449</v>
       </c>
       <c r="I38" t="n">
-        <v>52802.554316</v>
+        <v>31069.095882</v>
       </c>
       <c r="J38" t="n">
-        <v>48528.16413</v>
-      </c>
-      <c r="K38" t="n">
-        <v>63229.713007</v>
+        <v>46536.087342</v>
       </c>
     </row>
     <row r="39">
@@ -1861,34 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>224.812825</v>
+        <v>510.696664</v>
       </c>
       <c r="C39" t="n">
-        <v>290.56792875</v>
+        <v>272.6053706666667</v>
       </c>
       <c r="D39" t="n">
-        <v>288.4396313333333</v>
+        <v>192.2805496666666</v>
       </c>
       <c r="E39" t="n">
-        <v>178.213842</v>
+        <v>208.14742075</v>
       </c>
       <c r="F39" t="n">
-        <v>510.696664</v>
+        <v>180.24453425</v>
       </c>
       <c r="G39" t="n">
-        <v>272.6053706666667</v>
+        <v>197.9784773333333</v>
       </c>
       <c r="H39" t="n">
-        <v>192.2805496666666</v>
+        <v>354.591014</v>
       </c>
       <c r="I39" t="n">
-        <v>208.14742075</v>
+        <v>195.01303075</v>
       </c>
       <c r="J39" t="n">
-        <v>180.24453425</v>
-      </c>
-      <c r="K39" t="n">
-        <v>197.9784773333333</v>
+        <v>135.9931465</v>
       </c>
     </row>
     <row r="40">
@@ -1898,34 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>58053.714944</v>
+        <v>61524.433382</v>
       </c>
       <c r="C40" t="n">
-        <v>32763.385318</v>
+        <v>37909.898727</v>
       </c>
       <c r="D40" t="n">
-        <v>86759.32584075</v>
+        <v>36326.829469</v>
       </c>
       <c r="E40" t="n">
-        <v>46068.567366</v>
+        <v>29878.356119</v>
       </c>
       <c r="F40" t="n">
-        <v>61524.433382</v>
+        <v>28805.109067</v>
       </c>
       <c r="G40" t="n">
-        <v>37909.898727</v>
+        <v>27596.760349</v>
       </c>
       <c r="H40" t="n">
-        <v>36326.829469</v>
+        <v>39636.541815</v>
       </c>
       <c r="I40" t="n">
-        <v>29878.356119</v>
+        <v>53887.722178</v>
       </c>
       <c r="J40" t="n">
-        <v>28805.109067</v>
-      </c>
-      <c r="K40" t="n">
-        <v>27596.760349</v>
+        <v>66055.94876</v>
       </c>
     </row>
     <row r="41">
@@ -1935,34 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>570.5669830000001</v>
+        <v>1692.271876</v>
       </c>
       <c r="C41" t="n">
-        <v>652.434708</v>
+        <v>1432.72317875</v>
       </c>
       <c r="D41" t="n">
-        <v>579.070193</v>
+        <v>1434.016917</v>
       </c>
       <c r="E41" t="n">
-        <v>914.659041</v>
+        <v>540.506</v>
       </c>
       <c r="F41" t="n">
-        <v>1692.271876</v>
+        <v>512.066064</v>
       </c>
       <c r="G41" t="n">
-        <v>1432.72317875</v>
+        <v>559.753744</v>
       </c>
       <c r="H41" t="n">
-        <v>1434.016917</v>
+        <v>674.713247</v>
       </c>
       <c r="I41" t="n">
-        <v>540.506</v>
+        <v>827.737049</v>
       </c>
       <c r="J41" t="n">
-        <v>512.066064</v>
-      </c>
-      <c r="K41" t="n">
-        <v>559.753744</v>
+        <v>531.438114</v>
       </c>
     </row>
     <row r="42">
@@ -1972,34 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>298.11259</v>
+        <v>897.756717</v>
       </c>
       <c r="C42" t="n">
-        <v>547.00186</v>
+        <v>1129.16702625</v>
       </c>
       <c r="D42" t="n">
-        <v>988.503111</v>
+        <v>1395.065596</v>
       </c>
       <c r="E42" t="n">
-        <v>490.146396</v>
+        <v>467.8234276666667</v>
       </c>
       <c r="F42" t="n">
-        <v>897.756717</v>
+        <v>471.164946</v>
       </c>
       <c r="G42" t="n">
-        <v>1129.16702625</v>
+        <v>1631.08507</v>
       </c>
       <c r="H42" t="n">
-        <v>1395.065596</v>
+        <v>2295.60777</v>
       </c>
       <c r="I42" t="n">
-        <v>467.8234276666667</v>
+        <v>1208.889418</v>
       </c>
       <c r="J42" t="n">
-        <v>471.164946</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1631.08507</v>
+        <v>593.346867</v>
       </c>
     </row>
     <row r="43">
@@ -2009,34 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>499.480815</v>
+        <v>825.482802</v>
       </c>
       <c r="C43" t="n">
-        <v>581.954833</v>
+        <v>567.593296</v>
       </c>
       <c r="D43" t="n">
-        <v>821.245906</v>
+        <v>537.358792</v>
       </c>
       <c r="E43" t="n">
-        <v>404.753469</v>
+        <v>468.240531</v>
       </c>
       <c r="F43" t="n">
-        <v>825.482802</v>
+        <v>411.124527</v>
       </c>
       <c r="G43" t="n">
-        <v>567.593296</v>
+        <v>399.027766</v>
       </c>
       <c r="H43" t="n">
-        <v>537.358792</v>
+        <v>383.342766</v>
       </c>
       <c r="I43" t="n">
-        <v>468.240531</v>
+        <v>463.576357</v>
       </c>
       <c r="J43" t="n">
-        <v>411.124527</v>
-      </c>
-      <c r="K43" t="n">
-        <v>399.027766</v>
+        <v>794.7014809999999</v>
       </c>
     </row>
     <row r="44">
@@ -2046,34 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.053269</v>
+        <v>0.006552</v>
       </c>
       <c r="C44" t="n">
-        <v>0.033151</v>
+        <v>0.003161</v>
       </c>
       <c r="D44" t="n">
-        <v>0.010244</v>
+        <v>0.002744</v>
       </c>
       <c r="E44" t="n">
-        <v>0.007863</v>
+        <v>0.002643</v>
       </c>
       <c r="F44" t="n">
-        <v>0.006552</v>
+        <v>0.002552</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003161</v>
+        <v>0.006565</v>
       </c>
       <c r="H44" t="n">
-        <v>0.002744</v>
+        <v>0.003519</v>
       </c>
       <c r="I44" t="n">
-        <v>0.002643</v>
+        <v>0.00265</v>
       </c>
       <c r="J44" t="n">
-        <v>0.002552</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.006565</v>
+        <v>0.002668</v>
       </c>
     </row>
     <row r="45">
@@ -2083,34 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3660.765539</v>
+        <v>6875.836655</v>
       </c>
       <c r="C45" t="n">
-        <v>2625.495679</v>
+        <v>4134.497352</v>
       </c>
       <c r="D45" t="n">
-        <v>4139.05518</v>
+        <v>5040.481585</v>
       </c>
       <c r="E45" t="n">
-        <v>4408.433334</v>
+        <v>3031.189327</v>
       </c>
       <c r="F45" t="n">
-        <v>6875.836655</v>
+        <v>3592.949261</v>
       </c>
       <c r="G45" t="n">
-        <v>4134.497352</v>
+        <v>4734.635173</v>
       </c>
       <c r="H45" t="n">
-        <v>5040.481585</v>
+        <v>4746.98077</v>
       </c>
       <c r="I45" t="n">
-        <v>3031.189327</v>
+        <v>3243.080218</v>
       </c>
       <c r="J45" t="n">
-        <v>3592.949261</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4734.635173</v>
+        <v>2669.762574</v>
       </c>
     </row>
     <row r="46">
@@ -2120,34 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>79.011393</v>
+        <v>214.773434</v>
       </c>
       <c r="C46" t="n">
-        <v>97.940826</v>
+        <v>115.290054</v>
       </c>
       <c r="D46" t="n">
-        <v>125.318998</v>
+        <v>92.52786399999999</v>
       </c>
       <c r="E46" t="n">
-        <v>656.125362</v>
+        <v>122.622782</v>
       </c>
       <c r="F46" t="n">
-        <v>214.773434</v>
+        <v>102.029823</v>
       </c>
       <c r="G46" t="n">
-        <v>115.290054</v>
+        <v>63.437995</v>
       </c>
       <c r="H46" t="n">
-        <v>92.52786399999999</v>
+        <v>114.494836</v>
       </c>
       <c r="I46" t="n">
-        <v>122.622782</v>
+        <v>84.344223</v>
       </c>
       <c r="J46" t="n">
-        <v>102.029823</v>
-      </c>
-      <c r="K46" t="n">
-        <v>63.437995</v>
+        <v>90.28041399999999</v>
       </c>
     </row>
     <row r="47">
@@ -2157,34 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8078.319146</v>
+        <v>9069.999048</v>
       </c>
       <c r="C47" t="n">
-        <v>9839.781273000001</v>
+        <v>6194.843082</v>
       </c>
       <c r="D47" t="n">
-        <v>14358.074213</v>
+        <v>5061.95717</v>
       </c>
       <c r="E47" t="n">
-        <v>17241.519264</v>
+        <v>4016.346834</v>
       </c>
       <c r="F47" t="n">
-        <v>9069.999048</v>
+        <v>4822.937477</v>
       </c>
       <c r="G47" t="n">
-        <v>6194.843082</v>
+        <v>4710.065989</v>
       </c>
       <c r="H47" t="n">
-        <v>5061.95717</v>
+        <v>8159.59898575</v>
       </c>
       <c r="I47" t="n">
-        <v>4016.346834</v>
+        <v>5479.199724</v>
       </c>
       <c r="J47" t="n">
-        <v>4822.937477</v>
-      </c>
-      <c r="K47" t="n">
-        <v>4710.065989</v>
+        <v>9045.950951250001</v>
       </c>
     </row>
     <row r="48">
@@ -2194,34 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>858.256694</v>
+        <v>1534.009668</v>
       </c>
       <c r="C48" t="n">
-        <v>1081.539801</v>
+        <v>1125.220267</v>
       </c>
       <c r="D48" t="n">
-        <v>1120.54506475</v>
+        <v>997.972957</v>
       </c>
       <c r="E48" t="n">
-        <v>848.258089</v>
+        <v>903.223312</v>
       </c>
       <c r="F48" t="n">
-        <v>1534.009668</v>
+        <v>1174.488722</v>
       </c>
       <c r="G48" t="n">
-        <v>1125.220267</v>
+        <v>1178.88235875</v>
       </c>
       <c r="H48" t="n">
-        <v>997.972957</v>
+        <v>1847.640544</v>
       </c>
       <c r="I48" t="n">
-        <v>903.223312</v>
+        <v>1356.932141</v>
       </c>
       <c r="J48" t="n">
-        <v>1174.488722</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1178.88235875</v>
+        <v>852.97355</v>
       </c>
     </row>
     <row r="49">
@@ -2231,34 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7877.259995</v>
+        <v>15496.417758</v>
       </c>
       <c r="C49" t="n">
-        <v>8878.738735999999</v>
+        <v>14992.391934</v>
       </c>
       <c r="D49" t="n">
-        <v>10118.810306</v>
+        <v>10067.143468</v>
       </c>
       <c r="E49" t="n">
-        <v>12155.306408</v>
+        <v>9621.117287999999</v>
       </c>
       <c r="F49" t="n">
-        <v>15496.417758</v>
+        <v>10571.159237</v>
       </c>
       <c r="G49" t="n">
-        <v>14992.391934</v>
+        <v>8386.039221000001</v>
       </c>
       <c r="H49" t="n">
-        <v>10067.143468</v>
+        <v>15328.529302</v>
       </c>
       <c r="I49" t="n">
-        <v>9621.117287999999</v>
+        <v>8032.445252</v>
       </c>
       <c r="J49" t="n">
-        <v>10571.159237</v>
-      </c>
-      <c r="K49" t="n">
-        <v>8386.039221000001</v>
+        <v>6821.958901</v>
       </c>
     </row>
     <row r="50">
@@ -2268,34 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2544.125352</v>
+        <v>5087.392829</v>
       </c>
       <c r="C50" t="n">
-        <v>3866.41341325</v>
+        <v>4387.80561</v>
       </c>
       <c r="D50" t="n">
-        <v>3397.314045</v>
+        <v>3465.784863</v>
       </c>
       <c r="E50" t="n">
-        <v>6852.695963333333</v>
+        <v>3343.74021</v>
       </c>
       <c r="F50" t="n">
-        <v>5087.392829</v>
+        <v>2779.660097</v>
       </c>
       <c r="G50" t="n">
-        <v>4387.80561</v>
+        <v>3620.29492225</v>
       </c>
       <c r="H50" t="n">
-        <v>3465.784863</v>
+        <v>3506.00050675</v>
       </c>
       <c r="I50" t="n">
-        <v>3343.74021</v>
+        <v>2266.613453</v>
       </c>
       <c r="J50" t="n">
-        <v>2779.660097</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3620.29492225</v>
+        <v>1834.357839</v>
       </c>
     </row>
     <row r="51">
@@ -2305,34 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>264.279907</v>
+        <v>409.881371</v>
       </c>
       <c r="C51" t="n">
-        <v>443.79431</v>
+        <v>249.532021</v>
       </c>
       <c r="D51" t="n">
-        <v>738.6906719999999</v>
+        <v>207.790414</v>
       </c>
       <c r="E51" t="n">
-        <v>431.019007</v>
+        <v>174.997554</v>
       </c>
       <c r="F51" t="n">
-        <v>409.881371</v>
+        <v>125.795032</v>
       </c>
       <c r="G51" t="n">
-        <v>249.532021</v>
+        <v>155.189499</v>
       </c>
       <c r="H51" t="n">
-        <v>207.790414</v>
+        <v>223.922859</v>
       </c>
       <c r="I51" t="n">
-        <v>174.997554</v>
+        <v>111.228816</v>
       </c>
       <c r="J51" t="n">
-        <v>125.795032</v>
-      </c>
-      <c r="K51" t="n">
-        <v>155.189499</v>
+        <v>111.982374</v>
       </c>
     </row>
     <row r="52">
@@ -2342,34 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4397.447876</v>
+        <v>5123.085956</v>
       </c>
       <c r="C52" t="n">
-        <v>5239.108744</v>
+        <v>3537.669758</v>
       </c>
       <c r="D52" t="n">
-        <v>6179.477361</v>
+        <v>3613.59471475</v>
       </c>
       <c r="E52" t="n">
-        <v>4490.889025</v>
+        <v>2919.11781</v>
       </c>
       <c r="F52" t="n">
-        <v>5123.085956</v>
+        <v>2875.676287</v>
       </c>
       <c r="G52" t="n">
-        <v>3537.669758</v>
+        <v>3310.147664</v>
       </c>
       <c r="H52" t="n">
-        <v>3613.59471475</v>
+        <v>4784.668911</v>
       </c>
       <c r="I52" t="n">
-        <v>2919.11781</v>
+        <v>2942.278787</v>
       </c>
       <c r="J52" t="n">
-        <v>2875.676287</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3310.147664</v>
+        <v>3837.356166</v>
       </c>
     </row>
     <row r="53">
@@ -2379,34 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29613.628193</v>
+        <v>14465.035186</v>
       </c>
       <c r="C53" t="n">
-        <v>16199.311841</v>
+        <v>12369.82966033333</v>
       </c>
       <c r="D53" t="n">
-        <v>15853.533717</v>
+        <v>8840.385613</v>
       </c>
       <c r="E53" t="n">
-        <v>14779.86296466667</v>
+        <v>9901.63186</v>
       </c>
       <c r="F53" t="n">
-        <v>14465.035186</v>
+        <v>10721.13852266667</v>
       </c>
       <c r="G53" t="n">
-        <v>12369.82966033333</v>
+        <v>9752.979339</v>
       </c>
       <c r="H53" t="n">
-        <v>8840.385613</v>
+        <v>11055.191895</v>
       </c>
       <c r="I53" t="n">
-        <v>9901.63186</v>
+        <v>5640.04917</v>
       </c>
       <c r="J53" t="n">
-        <v>10721.13852266667</v>
-      </c>
-      <c r="K53" t="n">
-        <v>9752.979339</v>
+        <v>8143.316922</v>
       </c>
     </row>
     <row r="54">
@@ -2416,34 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3331.120676</v>
+        <v>3274.420379</v>
       </c>
       <c r="C54" t="n">
-        <v>2851.357159</v>
+        <v>2098.4072225</v>
       </c>
       <c r="D54" t="n">
-        <v>2526.839717</v>
+        <v>2831.504</v>
       </c>
       <c r="E54" t="n">
-        <v>3546.902833</v>
+        <v>3583.638983083334</v>
       </c>
       <c r="F54" t="n">
-        <v>3274.420379</v>
+        <v>3623.130848</v>
       </c>
       <c r="G54" t="n">
-        <v>2098.4072225</v>
+        <v>4620.352306</v>
       </c>
       <c r="H54" t="n">
-        <v>2831.504</v>
+        <v>8125.080313</v>
       </c>
       <c r="I54" t="n">
-        <v>3583.638983083334</v>
+        <v>7617.140139</v>
       </c>
       <c r="J54" t="n">
-        <v>3623.130848</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4620.352306</v>
+        <v>8895.519708</v>
       </c>
     </row>
     <row r="55">
@@ -2453,34 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3017.801864</v>
+        <v>5018.532979</v>
       </c>
       <c r="C55" t="n">
-        <v>4370.473424</v>
+        <v>3194.964284</v>
       </c>
       <c r="D55" t="n">
-        <v>8852.417363</v>
+        <v>4976.850082</v>
       </c>
       <c r="E55" t="n">
-        <v>4470.291028</v>
+        <v>2330.66048375</v>
       </c>
       <c r="F55" t="n">
-        <v>5018.532979</v>
+        <v>2688.837942</v>
       </c>
       <c r="G55" t="n">
-        <v>3194.964284</v>
+        <v>4316.675306</v>
       </c>
       <c r="H55" t="n">
-        <v>4976.850082</v>
+        <v>4842.403042</v>
       </c>
       <c r="I55" t="n">
-        <v>2330.66048375</v>
+        <v>2993.76787</v>
       </c>
       <c r="J55" t="n">
-        <v>2688.837942</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4316.675306</v>
+        <v>2951.194948</v>
       </c>
     </row>
     <row r="56">
@@ -2490,34 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1056.262568</v>
+        <v>3694.499608</v>
       </c>
       <c r="C56" t="n">
-        <v>1067.943964</v>
+        <v>1594.186972</v>
       </c>
       <c r="D56" t="n">
-        <v>1753.519909</v>
+        <v>1680.561113</v>
       </c>
       <c r="E56" t="n">
-        <v>1628.281254</v>
+        <v>1193.031047</v>
       </c>
       <c r="F56" t="n">
-        <v>3694.499608</v>
+        <v>1146.071359</v>
       </c>
       <c r="G56" t="n">
-        <v>1594.186972</v>
+        <v>1019.882468</v>
       </c>
       <c r="H56" t="n">
-        <v>1680.561113</v>
+        <v>2317.043931</v>
       </c>
       <c r="I56" t="n">
-        <v>1193.031047</v>
+        <v>921.913347</v>
       </c>
       <c r="J56" t="n">
-        <v>1146.071359</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1019.882468</v>
+        <v>825.16806675</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_4.xlsx
+++ b/Result/analyze_4.xlsx
@@ -436,47 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>146377.709394</v>
+        <v>111836.151503</v>
       </c>
       <c r="C2" t="n">
-        <v>111836.151503</v>
+        <v>88197.360011</v>
       </c>
       <c r="D2" t="n">
-        <v>88197.360011</v>
+        <v>88784.65591</v>
       </c>
       <c r="E2" t="n">
-        <v>88784.65591</v>
+        <v>118029.640628</v>
       </c>
       <c r="F2" t="n">
-        <v>118029.640628</v>
+        <v>86111.56320800001</v>
       </c>
       <c r="G2" t="n">
-        <v>86111.56320800001</v>
+        <v>116746.221458</v>
       </c>
       <c r="H2" t="n">
-        <v>116746.221458</v>
+        <v>82646.584332</v>
       </c>
       <c r="I2" t="n">
-        <v>82646.584332</v>
+        <v>88894.89247200001</v>
       </c>
       <c r="J2" t="n">
-        <v>88589.038311</v>
+        <v>104489.814064</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3482.021308</v>
+        <v>2653.026445</v>
       </c>
       <c r="C3" t="n">
-        <v>2653.026445</v>
+        <v>2315.212176</v>
       </c>
       <c r="D3" t="n">
-        <v>2315.212176</v>
+        <v>1672.452944</v>
       </c>
       <c r="E3" t="n">
-        <v>1672.452944</v>
+        <v>1870.514358</v>
       </c>
       <c r="F3" t="n">
-        <v>1870.514358</v>
+        <v>1820.151502</v>
       </c>
       <c r="G3" t="n">
-        <v>1820.151502</v>
+        <v>2917.500566</v>
       </c>
       <c r="H3" t="n">
-        <v>2917.500566</v>
+        <v>2070.829852</v>
       </c>
       <c r="I3" t="n">
-        <v>2070.829852</v>
+        <v>2092.097911</v>
       </c>
       <c r="J3" t="n">
-        <v>2092.097911</v>
+        <v>2668.450556</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>303082.816948</v>
+        <v>193622.711519</v>
       </c>
       <c r="C4" t="n">
-        <v>193622.711519</v>
+        <v>147446.818662</v>
       </c>
       <c r="D4" t="n">
-        <v>147446.818662</v>
+        <v>124321.122321</v>
       </c>
       <c r="E4" t="n">
-        <v>124321.122321</v>
+        <v>150792.801026</v>
       </c>
       <c r="F4" t="n">
-        <v>150792.801026</v>
+        <v>147850.838611</v>
       </c>
       <c r="G4" t="n">
-        <v>147850.838611</v>
+        <v>210144.106473</v>
       </c>
       <c r="H4" t="n">
-        <v>210144.106473</v>
+        <v>139875.023277</v>
       </c>
       <c r="I4" t="n">
-        <v>139875.023277</v>
+        <v>166403.606773</v>
       </c>
       <c r="J4" t="n">
-        <v>166051.110256</v>
+        <v>209261.254144</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3258.561954</v>
+        <v>1346.914769</v>
       </c>
       <c r="C5" t="n">
-        <v>1346.914769</v>
+        <v>1923.767901</v>
       </c>
       <c r="D5" t="n">
-        <v>1923.767901</v>
+        <v>1581.217843</v>
       </c>
       <c r="E5" t="n">
-        <v>1581.217843</v>
+        <v>1589.279806</v>
       </c>
       <c r="F5" t="n">
-        <v>1589.279806</v>
+        <v>1426.783736</v>
       </c>
       <c r="G5" t="n">
-        <v>1426.783736</v>
+        <v>2424.657227</v>
       </c>
       <c r="H5" t="n">
-        <v>2424.657227</v>
+        <v>1546.911157</v>
       </c>
       <c r="I5" t="n">
-        <v>1546.911157</v>
+        <v>1666.438213</v>
       </c>
       <c r="J5" t="n">
-        <v>1666.438213</v>
+        <v>2495.512737</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151269.855885</v>
+        <v>120306.325953</v>
       </c>
       <c r="C6" t="n">
-        <v>120306.325953</v>
+        <v>130064.351814</v>
       </c>
       <c r="D6" t="n">
-        <v>130064.351814</v>
+        <v>128906.794282</v>
       </c>
       <c r="E6" t="n">
-        <v>128906.794282</v>
+        <v>142583.75425</v>
       </c>
       <c r="F6" t="n">
-        <v>142583.75425</v>
+        <v>175994.789733</v>
       </c>
       <c r="G6" t="n">
-        <v>175994.789733</v>
+        <v>164386.057594</v>
       </c>
       <c r="H6" t="n">
-        <v>164386.057594</v>
+        <v>117708.84499</v>
       </c>
       <c r="I6" t="n">
-        <v>117708.84499</v>
+        <v>107218.81280825</v>
       </c>
       <c r="J6" t="n">
-        <v>107080.03780825</v>
+        <v>101274.765621</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40327.416367</v>
+        <v>53567.139487</v>
       </c>
       <c r="C7" t="n">
-        <v>53567.139487</v>
+        <v>25279.321246</v>
       </c>
       <c r="D7" t="n">
-        <v>25279.321246</v>
+        <v>30217.0626</v>
       </c>
       <c r="E7" t="n">
-        <v>30217.0626</v>
+        <v>30775.962933</v>
       </c>
       <c r="F7" t="n">
-        <v>30775.962933</v>
+        <v>27850.794304</v>
       </c>
       <c r="G7" t="n">
-        <v>27850.794304</v>
+        <v>31164.966686</v>
       </c>
       <c r="H7" t="n">
-        <v>31164.966686</v>
+        <v>23663.186839</v>
       </c>
       <c r="I7" t="n">
-        <v>23663.186839</v>
+        <v>24522.438173</v>
       </c>
       <c r="J7" t="n">
-        <v>24522.438173</v>
+        <v>23324.740168</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11367.800512</v>
+        <v>9290.113633999999</v>
       </c>
       <c r="C8" t="n">
-        <v>9290.113633999999</v>
+        <v>6401.606748</v>
       </c>
       <c r="D8" t="n">
-        <v>6401.606748</v>
+        <v>5530.783665</v>
       </c>
       <c r="E8" t="n">
-        <v>5530.783665</v>
+        <v>5227.592729</v>
       </c>
       <c r="F8" t="n">
-        <v>5227.592729</v>
+        <v>6216.818898</v>
       </c>
       <c r="G8" t="n">
-        <v>6216.818898</v>
+        <v>5003.552339</v>
       </c>
       <c r="H8" t="n">
-        <v>5003.552339</v>
+        <v>5074.958122</v>
       </c>
       <c r="I8" t="n">
-        <v>5074.958122</v>
+        <v>8072.278837</v>
       </c>
       <c r="J8" t="n">
-        <v>8072.278837</v>
+        <v>5924.239259</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47858.980378</v>
+        <v>38701.195125</v>
       </c>
       <c r="C9" t="n">
-        <v>38701.195125</v>
+        <v>29034.133984</v>
       </c>
       <c r="D9" t="n">
-        <v>29034.133984</v>
+        <v>35222.48547</v>
       </c>
       <c r="E9" t="n">
-        <v>35222.48547</v>
+        <v>34042.91955</v>
       </c>
       <c r="F9" t="n">
-        <v>34042.91955</v>
+        <v>42756.617748</v>
       </c>
       <c r="G9" t="n">
-        <v>42756.617748</v>
+        <v>32599.44009275</v>
       </c>
       <c r="H9" t="n">
-        <v>32599.44009275</v>
+        <v>27002.968423</v>
       </c>
       <c r="I9" t="n">
-        <v>27002.968423</v>
+        <v>40226.79954233333</v>
       </c>
       <c r="J9" t="n">
-        <v>40226.79954233333</v>
+        <v>29051.444289</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2968.736749333333</v>
+        <v>1863.8975865</v>
       </c>
       <c r="C10" t="n">
-        <v>1863.8975865</v>
+        <v>1660.79840675</v>
       </c>
       <c r="D10" t="n">
-        <v>1660.79840675</v>
+        <v>1890.91217525</v>
       </c>
       <c r="E10" t="n">
-        <v>1890.91217525</v>
+        <v>1789.04645175</v>
       </c>
       <c r="F10" t="n">
-        <v>1789.04645175</v>
+        <v>1726.716907666666</v>
       </c>
       <c r="G10" t="n">
-        <v>1726.716907666666</v>
+        <v>2906.054243333333</v>
       </c>
       <c r="H10" t="n">
-        <v>2906.054243333333</v>
+        <v>1877.928038</v>
       </c>
       <c r="I10" t="n">
-        <v>1877.928038</v>
+        <v>1650.858536666667</v>
       </c>
       <c r="J10" t="n">
-        <v>1650.858536666667</v>
+        <v>2212.1589025</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5176.826412</v>
+        <v>3792.995132</v>
       </c>
       <c r="C11" t="n">
-        <v>3792.995132</v>
+        <v>3971.737123</v>
       </c>
       <c r="D11" t="n">
-        <v>3971.737123</v>
+        <v>2607.64261</v>
       </c>
       <c r="E11" t="n">
-        <v>2607.64261</v>
+        <v>6270.54130125</v>
       </c>
       <c r="F11" t="n">
-        <v>6270.54130125</v>
+        <v>3458.255305</v>
       </c>
       <c r="G11" t="n">
-        <v>3458.255305</v>
+        <v>5757.848463</v>
       </c>
       <c r="H11" t="n">
-        <v>5757.848463</v>
+        <v>4933.058583</v>
       </c>
       <c r="I11" t="n">
-        <v>4933.058583</v>
+        <v>2362.220734</v>
       </c>
       <c r="J11" t="n">
-        <v>2206.789234</v>
+        <v>2983.810816</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16680.755963</v>
+        <v>16906.893744</v>
       </c>
       <c r="C12" t="n">
-        <v>16906.893744</v>
+        <v>10640.922305</v>
       </c>
       <c r="D12" t="n">
-        <v>10640.922305</v>
+        <v>8829.759413</v>
       </c>
       <c r="E12" t="n">
-        <v>8829.759413</v>
+        <v>9388.852977</v>
       </c>
       <c r="F12" t="n">
-        <v>9388.852977</v>
+        <v>10775.805214</v>
       </c>
       <c r="G12" t="n">
-        <v>10775.805214</v>
+        <v>9931.147682000001</v>
       </c>
       <c r="H12" t="n">
-        <v>9931.147682000001</v>
+        <v>7817.170597</v>
       </c>
       <c r="I12" t="n">
-        <v>7817.170597</v>
+        <v>13684.747726</v>
       </c>
       <c r="J12" t="n">
-        <v>13651.147226</v>
+        <v>10182.161102</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3231.178388</v>
+        <v>3960.347477</v>
       </c>
       <c r="C13" t="n">
-        <v>3960.347477</v>
+        <v>2417.560399</v>
       </c>
       <c r="D13" t="n">
-        <v>2417.560399</v>
+        <v>2771.525746</v>
       </c>
       <c r="E13" t="n">
-        <v>2771.525746</v>
+        <v>3454.18744</v>
       </c>
       <c r="F13" t="n">
-        <v>3454.18744</v>
+        <v>2375.099497</v>
       </c>
       <c r="G13" t="n">
-        <v>2375.099497</v>
+        <v>2925.270128</v>
       </c>
       <c r="H13" t="n">
-        <v>2925.270128</v>
+        <v>1318.721641</v>
       </c>
       <c r="I13" t="n">
-        <v>1318.721641</v>
+        <v>1292.076477</v>
       </c>
       <c r="J13" t="n">
-        <v>1292.076477</v>
+        <v>1652.042024</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9671.434703000001</v>
+        <v>6823.14329</v>
       </c>
       <c r="C14" t="n">
-        <v>6823.14329</v>
+        <v>5378.798716</v>
       </c>
       <c r="D14" t="n">
-        <v>5378.798716</v>
+        <v>5067.008517</v>
       </c>
       <c r="E14" t="n">
-        <v>5067.008517</v>
+        <v>6170.564575</v>
       </c>
       <c r="F14" t="n">
-        <v>6170.564575</v>
+        <v>6495.070194</v>
       </c>
       <c r="G14" t="n">
-        <v>6495.070194</v>
+        <v>6903.437777</v>
       </c>
       <c r="H14" t="n">
-        <v>6903.437777</v>
+        <v>4959.918107</v>
       </c>
       <c r="I14" t="n">
-        <v>4959.918107</v>
+        <v>5343.092632</v>
       </c>
       <c r="J14" t="n">
-        <v>5343.092632</v>
+        <v>6094.141902</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45344.637937</v>
+        <v>28502.020962</v>
       </c>
       <c r="C15" t="n">
-        <v>28502.020962</v>
+        <v>29474.558918</v>
       </c>
       <c r="D15" t="n">
-        <v>29474.558918</v>
+        <v>20905.593194</v>
       </c>
       <c r="E15" t="n">
-        <v>20905.593194</v>
+        <v>22869.744188</v>
       </c>
       <c r="F15" t="n">
-        <v>22869.744188</v>
+        <v>35181.997593</v>
       </c>
       <c r="G15" t="n">
-        <v>35181.997593</v>
+        <v>33063.448277</v>
       </c>
       <c r="H15" t="n">
-        <v>33063.448277</v>
+        <v>26407.014911</v>
       </c>
       <c r="I15" t="n">
-        <v>26407.014911</v>
+        <v>28868.246893</v>
       </c>
       <c r="J15" t="n">
-        <v>27811.136893</v>
+        <v>28154.228619</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20984.679592</v>
+        <v>18075.029301</v>
       </c>
       <c r="C16" t="n">
-        <v>18075.029301</v>
+        <v>10885.54886</v>
       </c>
       <c r="D16" t="n">
-        <v>10885.54886</v>
+        <v>10178.362449</v>
       </c>
       <c r="E16" t="n">
-        <v>10178.362449</v>
+        <v>14624.726406</v>
       </c>
       <c r="F16" t="n">
-        <v>14624.726406</v>
+        <v>12350.877069</v>
       </c>
       <c r="G16" t="n">
-        <v>12350.877069</v>
+        <v>14349.347742</v>
       </c>
       <c r="H16" t="n">
-        <v>14349.347742</v>
+        <v>14115.947664</v>
       </c>
       <c r="I16" t="n">
-        <v>14115.947664</v>
+        <v>11676.882483</v>
       </c>
       <c r="J16" t="n">
-        <v>11600.798043</v>
+        <v>10206.976518</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55652.472682</v>
+        <v>26977.665732</v>
       </c>
       <c r="C17" t="n">
-        <v>26977.665732</v>
+        <v>25679.187541</v>
       </c>
       <c r="D17" t="n">
-        <v>25679.187541</v>
+        <v>18361.073069</v>
       </c>
       <c r="E17" t="n">
-        <v>18361.073069</v>
+        <v>20715.519402</v>
       </c>
       <c r="F17" t="n">
-        <v>20715.519402</v>
+        <v>30246.361273</v>
       </c>
       <c r="G17" t="n">
-        <v>30246.361273</v>
+        <v>33791.051903</v>
       </c>
       <c r="H17" t="n">
-        <v>33791.051903</v>
+        <v>25023.535146</v>
       </c>
       <c r="I17" t="n">
-        <v>25023.535146</v>
+        <v>16460.690502</v>
       </c>
       <c r="J17" t="n">
-        <v>16460.690502</v>
+        <v>33315.650325</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1135.755548</v>
+        <v>711.696551</v>
       </c>
       <c r="C18" t="n">
-        <v>711.696551</v>
+        <v>578.367599</v>
       </c>
       <c r="D18" t="n">
-        <v>578.367599</v>
+        <v>515.620049</v>
       </c>
       <c r="E18" t="n">
-        <v>515.620049</v>
+        <v>474.713156</v>
       </c>
       <c r="F18" t="n">
-        <v>474.713156</v>
+        <v>483.392604</v>
       </c>
       <c r="G18" t="n">
-        <v>483.392604</v>
+        <v>527.9513020000001</v>
       </c>
       <c r="H18" t="n">
-        <v>527.9513020000001</v>
+        <v>264.580761</v>
       </c>
       <c r="I18" t="n">
-        <v>264.580761</v>
+        <v>501.552545</v>
       </c>
       <c r="J18" t="n">
-        <v>501.552545</v>
+        <v>533.944302</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>371.724318</v>
+        <v>340.844856</v>
       </c>
       <c r="C19" t="n">
-        <v>340.844856</v>
+        <v>478.877536</v>
       </c>
       <c r="D19" t="n">
-        <v>478.877536</v>
+        <v>327.893671</v>
       </c>
       <c r="E19" t="n">
-        <v>327.893671</v>
+        <v>283.604148</v>
       </c>
       <c r="F19" t="n">
-        <v>283.604148</v>
+        <v>357.590444</v>
       </c>
       <c r="G19" t="n">
-        <v>357.590444</v>
+        <v>346.415106</v>
       </c>
       <c r="H19" t="n">
-        <v>346.415106</v>
+        <v>175.401725</v>
       </c>
       <c r="I19" t="n">
-        <v>175.401725</v>
+        <v>242.9557945</v>
       </c>
       <c r="J19" t="n">
-        <v>242.9557945</v>
+        <v>125.84979725</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>41879.135888</v>
+        <v>14191.568201</v>
       </c>
       <c r="C20" t="n">
-        <v>14191.568201</v>
+        <v>12678.851694</v>
       </c>
       <c r="D20" t="n">
-        <v>12678.851694</v>
+        <v>15494.785698</v>
       </c>
       <c r="E20" t="n">
-        <v>15494.785698</v>
+        <v>18710.0614</v>
       </c>
       <c r="F20" t="n">
-        <v>18710.0614</v>
+        <v>16122.009331</v>
       </c>
       <c r="G20" t="n">
-        <v>16122.009331</v>
+        <v>29396.761097</v>
       </c>
       <c r="H20" t="n">
-        <v>29396.761097</v>
+        <v>11522.327561</v>
       </c>
       <c r="I20" t="n">
-        <v>11522.327561</v>
+        <v>25922.080538</v>
       </c>
       <c r="J20" t="n">
-        <v>25762.800797</v>
+        <v>30951.283369</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4266.437468</v>
+        <v>3621.255247</v>
       </c>
       <c r="C21" t="n">
-        <v>3621.255247</v>
+        <v>4151.474794</v>
       </c>
       <c r="D21" t="n">
-        <v>4151.474794</v>
+        <v>3373.680529</v>
       </c>
       <c r="E21" t="n">
-        <v>3373.680529</v>
+        <v>3096.345134</v>
       </c>
       <c r="F21" t="n">
-        <v>3096.345134</v>
+        <v>2838.648272</v>
       </c>
       <c r="G21" t="n">
-        <v>2838.648272</v>
+        <v>3863.356957</v>
       </c>
       <c r="H21" t="n">
-        <v>3863.356957</v>
+        <v>3232.837444</v>
       </c>
       <c r="I21" t="n">
-        <v>3232.837444</v>
+        <v>3861.262954</v>
       </c>
       <c r="J21" t="n">
-        <v>3861.262954</v>
+        <v>3896.813257</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>228.552413</v>
+        <v>228.59593</v>
       </c>
       <c r="C22" t="n">
-        <v>228.59593</v>
+        <v>148.972835</v>
       </c>
       <c r="D22" t="n">
-        <v>148.972835</v>
+        <v>217.130414</v>
       </c>
       <c r="E22" t="n">
-        <v>217.130414</v>
+        <v>322.379927</v>
       </c>
       <c r="F22" t="n">
-        <v>322.379927</v>
+        <v>422.57159</v>
       </c>
       <c r="G22" t="n">
-        <v>422.57159</v>
+        <v>323.7080105</v>
       </c>
       <c r="H22" t="n">
-        <v>323.7080105</v>
+        <v>144.683167</v>
       </c>
       <c r="I22" t="n">
-        <v>144.683167</v>
+        <v>127.241553</v>
       </c>
       <c r="J22" t="n">
-        <v>127.241553</v>
+        <v>160.931578</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.63044825</v>
+        <v>2.833667</v>
       </c>
       <c r="C23" t="n">
-        <v>2.833667</v>
+        <v>1.47260325</v>
       </c>
       <c r="D23" t="n">
-        <v>1.47260325</v>
+        <v>1.32028125</v>
       </c>
       <c r="E23" t="n">
-        <v>1.32028125</v>
+        <v>0.9817399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9817399999999999</v>
+        <v>1.086043</v>
       </c>
       <c r="G23" t="n">
-        <v>1.086043</v>
+        <v>0.87417925</v>
       </c>
       <c r="H23" t="n">
-        <v>0.87417925</v>
+        <v>1.143618</v>
       </c>
       <c r="I23" t="n">
-        <v>1.143618</v>
+        <v>1.338211333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>1.338211333333333</v>
+        <v>1.736643</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1457.277657</v>
+        <v>653.56974</v>
       </c>
       <c r="C24" t="n">
-        <v>653.56974</v>
+        <v>1082.038393</v>
       </c>
       <c r="D24" t="n">
-        <v>1082.038393</v>
+        <v>789.121836</v>
       </c>
       <c r="E24" t="n">
-        <v>789.121836</v>
+        <v>678.47342</v>
       </c>
       <c r="F24" t="n">
-        <v>678.47342</v>
+        <v>560.028791</v>
       </c>
       <c r="G24" t="n">
-        <v>560.028791</v>
+        <v>2379.117345</v>
       </c>
       <c r="H24" t="n">
-        <v>2379.117345</v>
+        <v>2879.210223</v>
       </c>
       <c r="I24" t="n">
-        <v>2879.210223</v>
+        <v>1068.16662</v>
       </c>
       <c r="J24" t="n">
-        <v>1068.16662</v>
+        <v>1023.726546</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>834.998774</v>
+        <v>661.627076</v>
       </c>
       <c r="C25" t="n">
-        <v>661.627076</v>
+        <v>474.962401</v>
       </c>
       <c r="D25" t="n">
-        <v>474.962401</v>
+        <v>356.818377</v>
       </c>
       <c r="E25" t="n">
-        <v>356.818377</v>
+        <v>327.770791</v>
       </c>
       <c r="F25" t="n">
-        <v>327.770791</v>
+        <v>307.888329</v>
       </c>
       <c r="G25" t="n">
-        <v>307.888329</v>
+        <v>928.851329</v>
       </c>
       <c r="H25" t="n">
-        <v>928.851329</v>
+        <v>400.624759</v>
       </c>
       <c r="I25" t="n">
-        <v>400.624759</v>
+        <v>273.361778</v>
       </c>
       <c r="J25" t="n">
-        <v>273.361778</v>
+        <v>439.145581</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1668.468947</v>
+        <v>1906.351396</v>
       </c>
       <c r="C26" t="n">
-        <v>1906.351396</v>
+        <v>1106.356106</v>
       </c>
       <c r="D26" t="n">
-        <v>1106.356106</v>
+        <v>1202.872977</v>
       </c>
       <c r="E26" t="n">
-        <v>1202.872977</v>
+        <v>982.0145659999999</v>
       </c>
       <c r="F26" t="n">
-        <v>982.0145659999999</v>
+        <v>3377.085099</v>
       </c>
       <c r="G26" t="n">
-        <v>3377.085099</v>
+        <v>1771.499985</v>
       </c>
       <c r="H26" t="n">
-        <v>1771.499985</v>
+        <v>1282.141432</v>
       </c>
       <c r="I26" t="n">
-        <v>1282.141432</v>
+        <v>1123.66674</v>
       </c>
       <c r="J26" t="n">
-        <v>1123.66674</v>
+        <v>1390.829512</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9002.351504</v>
+        <v>6343.406324</v>
       </c>
       <c r="C27" t="n">
-        <v>6343.406324</v>
+        <v>5278.593607</v>
       </c>
       <c r="D27" t="n">
-        <v>5278.593607</v>
+        <v>4951.307608</v>
       </c>
       <c r="E27" t="n">
-        <v>4951.307608</v>
+        <v>6806.019453</v>
       </c>
       <c r="F27" t="n">
-        <v>6806.019453</v>
+        <v>5483.5149605</v>
       </c>
       <c r="G27" t="n">
-        <v>5483.5149605</v>
+        <v>12019.31072</v>
       </c>
       <c r="H27" t="n">
-        <v>12019.31072</v>
+        <v>7835.189957</v>
       </c>
       <c r="I27" t="n">
-        <v>7835.189957</v>
+        <v>6304.168288</v>
       </c>
       <c r="J27" t="n">
-        <v>6304.168288</v>
+        <v>6513.378774</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6638.344623</v>
+        <v>5969.8867385</v>
       </c>
       <c r="C28" t="n">
-        <v>5969.8867385</v>
+        <v>8963.286382</v>
       </c>
       <c r="D28" t="n">
-        <v>8963.286382</v>
+        <v>5845.509506</v>
       </c>
       <c r="E28" t="n">
-        <v>5845.509506</v>
+        <v>4315.397605</v>
       </c>
       <c r="F28" t="n">
-        <v>4315.397605</v>
+        <v>3943.029472</v>
       </c>
       <c r="G28" t="n">
-        <v>3943.029472</v>
+        <v>1944.495665</v>
       </c>
       <c r="H28" t="n">
-        <v>1944.495665</v>
+        <v>2652.312861</v>
       </c>
       <c r="I28" t="n">
-        <v>2652.312861</v>
+        <v>2240.920121</v>
       </c>
       <c r="J28" t="n">
-        <v>2240.920121</v>
+        <v>3425.149326</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1481.882935</v>
+        <v>921.225533</v>
       </c>
       <c r="C29" t="n">
-        <v>921.225533</v>
+        <v>1287.748339</v>
       </c>
       <c r="D29" t="n">
-        <v>1287.748339</v>
+        <v>1097.726776</v>
       </c>
       <c r="E29" t="n">
-        <v>1097.726776</v>
+        <v>1008.621634</v>
       </c>
       <c r="F29" t="n">
-        <v>1008.621634</v>
+        <v>1223.7303175</v>
       </c>
       <c r="G29" t="n">
-        <v>1223.7303175</v>
+        <v>3778.9339045</v>
       </c>
       <c r="H29" t="n">
-        <v>3778.9339045</v>
+        <v>1650.0702305</v>
       </c>
       <c r="I29" t="n">
-        <v>1650.0702305</v>
+        <v>1072.90880125</v>
       </c>
       <c r="J29" t="n">
-        <v>1072.90880125</v>
+        <v>1365.16376</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5295.728255</v>
+        <v>9593.106706</v>
       </c>
       <c r="C30" t="n">
-        <v>9593.106706</v>
+        <v>14525.081378</v>
       </c>
       <c r="D30" t="n">
-        <v>14525.081378</v>
+        <v>14764.888638</v>
       </c>
       <c r="E30" t="n">
-        <v>14764.888638</v>
+        <v>10582.289675</v>
       </c>
       <c r="F30" t="n">
-        <v>10582.289675</v>
+        <v>19618.558693</v>
       </c>
       <c r="G30" t="n">
-        <v>19618.558693</v>
+        <v>8323.112531999999</v>
       </c>
       <c r="H30" t="n">
-        <v>8323.112531999999</v>
+        <v>8574.781219</v>
       </c>
       <c r="I30" t="n">
-        <v>8574.781219</v>
+        <v>4656.935608</v>
       </c>
       <c r="J30" t="n">
-        <v>4656.935608</v>
+        <v>5520.727065</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6989.188224</v>
+        <v>6393.92870275</v>
       </c>
       <c r="C31" t="n">
-        <v>6393.92870275</v>
+        <v>5021.116329083334</v>
       </c>
       <c r="D31" t="n">
-        <v>5021.116329083334</v>
+        <v>3148.95717875</v>
       </c>
       <c r="E31" t="n">
-        <v>3148.95717875</v>
+        <v>3987.6690155</v>
       </c>
       <c r="F31" t="n">
-        <v>3987.6690155</v>
+        <v>2998.78392925</v>
       </c>
       <c r="G31" t="n">
-        <v>2998.78392925</v>
+        <v>4680.430511666667</v>
       </c>
       <c r="H31" t="n">
-        <v>4680.430511666667</v>
+        <v>2929.372245333333</v>
       </c>
       <c r="I31" t="n">
-        <v>2929.372245333333</v>
+        <v>4411.32397675</v>
       </c>
       <c r="J31" t="n">
-        <v>4411.32397675</v>
+        <v>5980.72514325</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>56762.360998</v>
+        <v>51513.200483</v>
       </c>
       <c r="C32" t="n">
-        <v>51513.200483</v>
+        <v>39124.732034</v>
       </c>
       <c r="D32" t="n">
-        <v>39124.732034</v>
+        <v>39590.881003</v>
       </c>
       <c r="E32" t="n">
-        <v>39590.881003</v>
+        <v>45804.859502</v>
       </c>
       <c r="F32" t="n">
-        <v>45804.859502</v>
+        <v>37423.45247233334</v>
       </c>
       <c r="G32" t="n">
-        <v>37423.45247233334</v>
+        <v>40718.0378435</v>
       </c>
       <c r="H32" t="n">
-        <v>40718.0378435</v>
+        <v>31654.4544115</v>
       </c>
       <c r="I32" t="n">
-        <v>31654.4544115</v>
+        <v>25292.816004</v>
       </c>
       <c r="J32" t="n">
-        <v>25292.816004</v>
+        <v>26123.934277</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2755.842148</v>
+        <v>1567.7892245</v>
       </c>
       <c r="C33" t="n">
-        <v>1567.7892245</v>
+        <v>1019.075243</v>
       </c>
       <c r="D33" t="n">
-        <v>1019.075243</v>
+        <v>1092.226384</v>
       </c>
       <c r="E33" t="n">
-        <v>1092.226384</v>
+        <v>829.024501</v>
       </c>
       <c r="F33" t="n">
-        <v>829.024501</v>
+        <v>916.605739</v>
       </c>
       <c r="G33" t="n">
-        <v>916.605739</v>
+        <v>1642.835371</v>
       </c>
       <c r="H33" t="n">
-        <v>1642.835371</v>
+        <v>783.09935</v>
       </c>
       <c r="I33" t="n">
-        <v>783.09935</v>
+        <v>701.288429</v>
       </c>
       <c r="J33" t="n">
-        <v>701.288429</v>
+        <v>967.56546125</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2736.504571</v>
+        <v>1751.39205925</v>
       </c>
       <c r="C34" t="n">
-        <v>1751.39205925</v>
+        <v>2081.145656</v>
       </c>
       <c r="D34" t="n">
-        <v>2081.145656</v>
+        <v>1426.808585</v>
       </c>
       <c r="E34" t="n">
-        <v>1426.808585</v>
+        <v>1121.898895</v>
       </c>
       <c r="F34" t="n">
-        <v>1121.898895</v>
+        <v>1528.765713</v>
       </c>
       <c r="G34" t="n">
-        <v>1528.765713</v>
+        <v>2085.870603</v>
       </c>
       <c r="H34" t="n">
-        <v>2085.870603</v>
+        <v>1248.380823</v>
       </c>
       <c r="I34" t="n">
-        <v>1248.380823</v>
+        <v>1163.50581</v>
       </c>
       <c r="J34" t="n">
-        <v>1163.50581</v>
+        <v>1638.666454</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11703.76045</v>
+        <v>12703.616457</v>
       </c>
       <c r="C35" t="n">
-        <v>12703.616457</v>
+        <v>13402.771396</v>
       </c>
       <c r="D35" t="n">
-        <v>13402.771396</v>
+        <v>11425.688567</v>
       </c>
       <c r="E35" t="n">
-        <v>11425.688567</v>
+        <v>20110.469244</v>
       </c>
       <c r="F35" t="n">
-        <v>20110.469244</v>
+        <v>9588.452409</v>
       </c>
       <c r="G35" t="n">
-        <v>9588.452409</v>
+        <v>10422.690524</v>
       </c>
       <c r="H35" t="n">
-        <v>10422.690524</v>
+        <v>7350.793886</v>
       </c>
       <c r="I35" t="n">
-        <v>7350.793886</v>
+        <v>8254.514959</v>
       </c>
       <c r="J35" t="n">
-        <v>8254.514959</v>
+        <v>10504.596854</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1232.572688</v>
+        <v>1879.559285</v>
       </c>
       <c r="C36" t="n">
-        <v>1879.559285</v>
+        <v>1081.058934</v>
       </c>
       <c r="D36" t="n">
-        <v>1081.058934</v>
+        <v>863.168954</v>
       </c>
       <c r="E36" t="n">
-        <v>863.168954</v>
+        <v>1008.784159</v>
       </c>
       <c r="F36" t="n">
-        <v>1008.784159</v>
+        <v>810.950855</v>
       </c>
       <c r="G36" t="n">
-        <v>810.950855</v>
+        <v>1069.52765</v>
       </c>
       <c r="H36" t="n">
-        <v>1069.52765</v>
+        <v>625.322553</v>
       </c>
       <c r="I36" t="n">
-        <v>625.322553</v>
+        <v>504.335782</v>
       </c>
       <c r="J36" t="n">
-        <v>504.335782</v>
+        <v>981.441862</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9830.857416000001</v>
+        <v>10698.718434</v>
       </c>
       <c r="C37" t="n">
-        <v>10698.718434</v>
+        <v>6433.64742575</v>
       </c>
       <c r="D37" t="n">
-        <v>6433.64742575</v>
+        <v>5580.049872</v>
       </c>
       <c r="E37" t="n">
-        <v>5580.049872</v>
+        <v>5967.7019175</v>
       </c>
       <c r="F37" t="n">
-        <v>5967.7019175</v>
+        <v>5460.094539</v>
       </c>
       <c r="G37" t="n">
-        <v>5460.094539</v>
+        <v>7421.544591666667</v>
       </c>
       <c r="H37" t="n">
-        <v>7421.544591666667</v>
+        <v>4000.169336</v>
       </c>
       <c r="I37" t="n">
-        <v>4000.169336</v>
+        <v>3816.3079015</v>
       </c>
       <c r="J37" t="n">
-        <v>3816.3079015</v>
+        <v>11371.0589855</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68946.483389</v>
+        <v>44982.238539</v>
       </c>
       <c r="C38" t="n">
-        <v>44982.238539</v>
+        <v>42998.291544</v>
       </c>
       <c r="D38" t="n">
-        <v>42998.291544</v>
+        <v>52802.554316</v>
       </c>
       <c r="E38" t="n">
-        <v>52802.554316</v>
+        <v>48528.16413</v>
       </c>
       <c r="F38" t="n">
-        <v>48528.16413</v>
+        <v>63229.713007</v>
       </c>
       <c r="G38" t="n">
-        <v>63229.713007</v>
+        <v>42515.79449</v>
       </c>
       <c r="H38" t="n">
-        <v>42515.79449</v>
+        <v>31069.095882</v>
       </c>
       <c r="I38" t="n">
-        <v>31069.095882</v>
+        <v>46536.087342</v>
       </c>
       <c r="J38" t="n">
-        <v>46536.087342</v>
+        <v>45672.382461</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>510.696664</v>
+        <v>272.6053706666667</v>
       </c>
       <c r="C39" t="n">
-        <v>272.6053706666667</v>
+        <v>192.2805496666666</v>
       </c>
       <c r="D39" t="n">
-        <v>192.2805496666666</v>
+        <v>208.14742075</v>
       </c>
       <c r="E39" t="n">
-        <v>208.14742075</v>
+        <v>180.24453425</v>
       </c>
       <c r="F39" t="n">
-        <v>180.24453425</v>
+        <v>197.9784773333333</v>
       </c>
       <c r="G39" t="n">
-        <v>197.9784773333333</v>
+        <v>354.591014</v>
       </c>
       <c r="H39" t="n">
-        <v>354.591014</v>
+        <v>195.01303075</v>
       </c>
       <c r="I39" t="n">
-        <v>195.01303075</v>
+        <v>135.9931465</v>
       </c>
       <c r="J39" t="n">
-        <v>135.9931465</v>
+        <v>202.787936</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>61524.433382</v>
+        <v>37909.898727</v>
       </c>
       <c r="C40" t="n">
-        <v>37909.898727</v>
+        <v>36326.829469</v>
       </c>
       <c r="D40" t="n">
-        <v>36326.829469</v>
+        <v>29878.356119</v>
       </c>
       <c r="E40" t="n">
-        <v>29878.356119</v>
+        <v>28805.109067</v>
       </c>
       <c r="F40" t="n">
-        <v>28805.109067</v>
+        <v>27596.760349</v>
       </c>
       <c r="G40" t="n">
-        <v>27596.760349</v>
+        <v>39636.541815</v>
       </c>
       <c r="H40" t="n">
-        <v>39636.541815</v>
+        <v>53887.722178</v>
       </c>
       <c r="I40" t="n">
-        <v>53887.722178</v>
+        <v>66086.18876</v>
       </c>
       <c r="J40" t="n">
-        <v>66055.94876</v>
+        <v>43696.826769</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1692.271876</v>
+        <v>1432.72317875</v>
       </c>
       <c r="C41" t="n">
-        <v>1432.72317875</v>
+        <v>1434.016917</v>
       </c>
       <c r="D41" t="n">
-        <v>1434.016917</v>
+        <v>540.506</v>
       </c>
       <c r="E41" t="n">
-        <v>540.506</v>
+        <v>512.066064</v>
       </c>
       <c r="F41" t="n">
-        <v>512.066064</v>
+        <v>559.753744</v>
       </c>
       <c r="G41" t="n">
-        <v>559.753744</v>
+        <v>674.713247</v>
       </c>
       <c r="H41" t="n">
-        <v>674.713247</v>
+        <v>827.737049</v>
       </c>
       <c r="I41" t="n">
-        <v>827.737049</v>
+        <v>550.180194</v>
       </c>
       <c r="J41" t="n">
-        <v>531.438114</v>
+        <v>898.481621</v>
       </c>
     </row>
     <row r="42">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>897.756717</v>
+        <v>1129.16702625</v>
       </c>
       <c r="C42" t="n">
-        <v>1129.16702625</v>
+        <v>1395.065596</v>
       </c>
       <c r="D42" t="n">
-        <v>1395.065596</v>
+        <v>467.8234276666667</v>
       </c>
       <c r="E42" t="n">
-        <v>467.8234276666667</v>
+        <v>471.164946</v>
       </c>
       <c r="F42" t="n">
-        <v>471.164946</v>
+        <v>1631.08507</v>
       </c>
       <c r="G42" t="n">
-        <v>1631.08507</v>
+        <v>2295.60777</v>
       </c>
       <c r="H42" t="n">
-        <v>2295.60777</v>
+        <v>1208.889418</v>
       </c>
       <c r="I42" t="n">
-        <v>1208.889418</v>
+        <v>593.346867</v>
       </c>
       <c r="J42" t="n">
-        <v>593.346867</v>
+        <v>1841.581173</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>825.482802</v>
+        <v>567.593296</v>
       </c>
       <c r="C43" t="n">
-        <v>567.593296</v>
+        <v>537.358792</v>
       </c>
       <c r="D43" t="n">
-        <v>537.358792</v>
+        <v>468.240531</v>
       </c>
       <c r="E43" t="n">
-        <v>468.240531</v>
+        <v>411.124527</v>
       </c>
       <c r="F43" t="n">
-        <v>411.124527</v>
+        <v>399.027766</v>
       </c>
       <c r="G43" t="n">
-        <v>399.027766</v>
+        <v>383.342766</v>
       </c>
       <c r="H43" t="n">
-        <v>383.342766</v>
+        <v>463.576357</v>
       </c>
       <c r="I43" t="n">
-        <v>463.576357</v>
+        <v>794.7014809999999</v>
       </c>
       <c r="J43" t="n">
-        <v>794.7014809999999</v>
+        <v>746.321226</v>
       </c>
     </row>
     <row r="44">
@@ -1915,31 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.006552</v>
+        <v>0.003161</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003161</v>
+        <v>0.002744</v>
       </c>
       <c r="D44" t="n">
-        <v>0.002744</v>
+        <v>0.002643</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002643</v>
+        <v>0.002552</v>
       </c>
       <c r="F44" t="n">
-        <v>0.002552</v>
+        <v>0.006565</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006565</v>
+        <v>0.003519</v>
       </c>
       <c r="H44" t="n">
-        <v>0.003519</v>
+        <v>0.00265</v>
       </c>
       <c r="I44" t="n">
-        <v>0.00265</v>
+        <v>0.002668</v>
       </c>
       <c r="J44" t="n">
-        <v>0.002668</v>
+        <v>0.003818</v>
       </c>
     </row>
     <row r="45">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6875.836655</v>
+        <v>4134.497352</v>
       </c>
       <c r="C45" t="n">
-        <v>4134.497352</v>
+        <v>5040.481585</v>
       </c>
       <c r="D45" t="n">
-        <v>5040.481585</v>
+        <v>3031.189327</v>
       </c>
       <c r="E45" t="n">
-        <v>3031.189327</v>
+        <v>3592.949261</v>
       </c>
       <c r="F45" t="n">
-        <v>3592.949261</v>
+        <v>4734.635173</v>
       </c>
       <c r="G45" t="n">
-        <v>4734.635173</v>
+        <v>4746.98077</v>
       </c>
       <c r="H45" t="n">
-        <v>4746.98077</v>
+        <v>3243.080218</v>
       </c>
       <c r="I45" t="n">
-        <v>3243.080218</v>
+        <v>2669.762574</v>
       </c>
       <c r="J45" t="n">
-        <v>2669.762574</v>
+        <v>4427.640853</v>
       </c>
     </row>
     <row r="46">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>214.773434</v>
+        <v>115.290054</v>
       </c>
       <c r="C46" t="n">
-        <v>115.290054</v>
+        <v>92.52786399999999</v>
       </c>
       <c r="D46" t="n">
-        <v>92.52786399999999</v>
+        <v>122.622782</v>
       </c>
       <c r="E46" t="n">
-        <v>122.622782</v>
+        <v>102.029823</v>
       </c>
       <c r="F46" t="n">
-        <v>102.029823</v>
+        <v>63.437995</v>
       </c>
       <c r="G46" t="n">
-        <v>63.437995</v>
+        <v>114.494836</v>
       </c>
       <c r="H46" t="n">
-        <v>114.494836</v>
+        <v>84.344223</v>
       </c>
       <c r="I46" t="n">
-        <v>84.344223</v>
+        <v>90.28041399999999</v>
       </c>
       <c r="J46" t="n">
-        <v>90.28041399999999</v>
+        <v>157.77093</v>
       </c>
     </row>
     <row r="47">
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9069.999048</v>
+        <v>6194.843082</v>
       </c>
       <c r="C47" t="n">
-        <v>6194.843082</v>
+        <v>5061.95717</v>
       </c>
       <c r="D47" t="n">
-        <v>5061.95717</v>
+        <v>4016.346834</v>
       </c>
       <c r="E47" t="n">
-        <v>4016.346834</v>
+        <v>4822.937477</v>
       </c>
       <c r="F47" t="n">
-        <v>4822.937477</v>
+        <v>4710.065989</v>
       </c>
       <c r="G47" t="n">
-        <v>4710.065989</v>
+        <v>8159.59898575</v>
       </c>
       <c r="H47" t="n">
-        <v>8159.59898575</v>
+        <v>5479.199724</v>
       </c>
       <c r="I47" t="n">
-        <v>5479.199724</v>
+        <v>9045.950951250001</v>
       </c>
       <c r="J47" t="n">
-        <v>9045.950951250001</v>
+        <v>8179.116299</v>
       </c>
     </row>
     <row r="48">
@@ -2051,31 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1534.009668</v>
+        <v>1125.220267</v>
       </c>
       <c r="C48" t="n">
-        <v>1125.220267</v>
+        <v>997.972957</v>
       </c>
       <c r="D48" t="n">
-        <v>997.972957</v>
+        <v>903.223312</v>
       </c>
       <c r="E48" t="n">
-        <v>903.223312</v>
+        <v>1174.488722</v>
       </c>
       <c r="F48" t="n">
-        <v>1174.488722</v>
+        <v>1178.88235875</v>
       </c>
       <c r="G48" t="n">
-        <v>1178.88235875</v>
+        <v>1847.640544</v>
       </c>
       <c r="H48" t="n">
-        <v>1847.640544</v>
+        <v>1356.932141</v>
       </c>
       <c r="I48" t="n">
-        <v>1356.932141</v>
+        <v>852.97355</v>
       </c>
       <c r="J48" t="n">
-        <v>852.97355</v>
+        <v>1244.727871</v>
       </c>
     </row>
     <row r="49">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15496.417758</v>
+        <v>14992.391934</v>
       </c>
       <c r="C49" t="n">
-        <v>14992.391934</v>
+        <v>10067.143468</v>
       </c>
       <c r="D49" t="n">
-        <v>10067.143468</v>
+        <v>9621.117287999999</v>
       </c>
       <c r="E49" t="n">
-        <v>9621.117287999999</v>
+        <v>10571.159237</v>
       </c>
       <c r="F49" t="n">
-        <v>10571.159237</v>
+        <v>8386.039221000001</v>
       </c>
       <c r="G49" t="n">
-        <v>8386.039221000001</v>
+        <v>15328.529302</v>
       </c>
       <c r="H49" t="n">
-        <v>15328.529302</v>
+        <v>8032.445252</v>
       </c>
       <c r="I49" t="n">
-        <v>8032.445252</v>
+        <v>6844.728901</v>
       </c>
       <c r="J49" t="n">
-        <v>6821.958901</v>
+        <v>9600.225437999999</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5087.392829</v>
+        <v>4387.80561</v>
       </c>
       <c r="C50" t="n">
-        <v>4387.80561</v>
+        <v>3465.784863</v>
       </c>
       <c r="D50" t="n">
-        <v>3465.784863</v>
+        <v>3343.74021</v>
       </c>
       <c r="E50" t="n">
-        <v>3343.74021</v>
+        <v>2779.660097</v>
       </c>
       <c r="F50" t="n">
-        <v>2779.660097</v>
+        <v>3620.29492225</v>
       </c>
       <c r="G50" t="n">
-        <v>3620.29492225</v>
+        <v>3506.00050675</v>
       </c>
       <c r="H50" t="n">
-        <v>3506.00050675</v>
+        <v>2266.613453</v>
       </c>
       <c r="I50" t="n">
-        <v>2266.613453</v>
+        <v>1834.357839</v>
       </c>
       <c r="J50" t="n">
-        <v>1834.357839</v>
+        <v>2876.671442</v>
       </c>
     </row>
     <row r="51">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>409.881371</v>
+        <v>249.532021</v>
       </c>
       <c r="C51" t="n">
-        <v>249.532021</v>
+        <v>207.790414</v>
       </c>
       <c r="D51" t="n">
-        <v>207.790414</v>
+        <v>174.997554</v>
       </c>
       <c r="E51" t="n">
-        <v>174.997554</v>
+        <v>125.795032</v>
       </c>
       <c r="F51" t="n">
-        <v>125.795032</v>
+        <v>155.189499</v>
       </c>
       <c r="G51" t="n">
-        <v>155.189499</v>
+        <v>223.922859</v>
       </c>
       <c r="H51" t="n">
-        <v>223.922859</v>
+        <v>111.228816</v>
       </c>
       <c r="I51" t="n">
-        <v>111.228816</v>
+        <v>111.982374</v>
       </c>
       <c r="J51" t="n">
-        <v>111.982374</v>
+        <v>351.721815</v>
       </c>
     </row>
     <row r="52">
@@ -2187,31 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5123.085956</v>
+        <v>3537.669758</v>
       </c>
       <c r="C52" t="n">
-        <v>3537.669758</v>
+        <v>3613.59471475</v>
       </c>
       <c r="D52" t="n">
-        <v>3613.59471475</v>
+        <v>2919.11781</v>
       </c>
       <c r="E52" t="n">
-        <v>2919.11781</v>
+        <v>2875.676287</v>
       </c>
       <c r="F52" t="n">
-        <v>2875.676287</v>
+        <v>3310.147664</v>
       </c>
       <c r="G52" t="n">
-        <v>3310.147664</v>
+        <v>4784.668911</v>
       </c>
       <c r="H52" t="n">
-        <v>4784.668911</v>
+        <v>2942.278787</v>
       </c>
       <c r="I52" t="n">
-        <v>2942.278787</v>
+        <v>3896.217632</v>
       </c>
       <c r="J52" t="n">
-        <v>3837.356166</v>
+        <v>3326.799352</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14465.035186</v>
+        <v>12369.82966033333</v>
       </c>
       <c r="C53" t="n">
-        <v>12369.82966033333</v>
+        <v>8840.385613</v>
       </c>
       <c r="D53" t="n">
-        <v>8840.385613</v>
+        <v>9901.63186</v>
       </c>
       <c r="E53" t="n">
-        <v>9901.63186</v>
+        <v>10721.13852266667</v>
       </c>
       <c r="F53" t="n">
-        <v>10721.13852266667</v>
+        <v>9752.979339</v>
       </c>
       <c r="G53" t="n">
-        <v>9752.979339</v>
+        <v>11055.191895</v>
       </c>
       <c r="H53" t="n">
-        <v>11055.191895</v>
+        <v>5640.04917</v>
       </c>
       <c r="I53" t="n">
-        <v>5640.04917</v>
+        <v>8143.316922</v>
       </c>
       <c r="J53" t="n">
-        <v>8143.316922</v>
+        <v>8152.420357</v>
       </c>
     </row>
     <row r="54">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3274.420379</v>
+        <v>2098.4072225</v>
       </c>
       <c r="C54" t="n">
-        <v>2098.4072225</v>
+        <v>2831.504</v>
       </c>
       <c r="D54" t="n">
-        <v>2831.504</v>
+        <v>3583.638983083334</v>
       </c>
       <c r="E54" t="n">
-        <v>3583.638983083334</v>
+        <v>3623.130848</v>
       </c>
       <c r="F54" t="n">
-        <v>3623.130848</v>
+        <v>4620.352306</v>
       </c>
       <c r="G54" t="n">
-        <v>4620.352306</v>
+        <v>8125.080313</v>
       </c>
       <c r="H54" t="n">
-        <v>8125.080313</v>
+        <v>7617.140139</v>
       </c>
       <c r="I54" t="n">
-        <v>7617.140139</v>
+        <v>8895.519708</v>
       </c>
       <c r="J54" t="n">
-        <v>8895.519708</v>
+        <v>3942.422084</v>
       </c>
     </row>
     <row r="55">
@@ -2289,31 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5018.532979</v>
+        <v>3194.964284</v>
       </c>
       <c r="C55" t="n">
-        <v>3194.964284</v>
+        <v>4976.850082</v>
       </c>
       <c r="D55" t="n">
-        <v>4976.850082</v>
+        <v>2330.66048375</v>
       </c>
       <c r="E55" t="n">
-        <v>2330.66048375</v>
+        <v>2688.837942</v>
       </c>
       <c r="F55" t="n">
-        <v>2688.837942</v>
+        <v>4316.675306</v>
       </c>
       <c r="G55" t="n">
-        <v>4316.675306</v>
+        <v>4842.403042</v>
       </c>
       <c r="H55" t="n">
-        <v>4842.403042</v>
+        <v>2993.76787</v>
       </c>
       <c r="I55" t="n">
-        <v>2993.76787</v>
+        <v>2951.194948</v>
       </c>
       <c r="J55" t="n">
-        <v>2951.194948</v>
+        <v>2961.18077</v>
       </c>
     </row>
     <row r="56">
@@ -2323,31 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3694.499608</v>
+        <v>1594.186972</v>
       </c>
       <c r="C56" t="n">
-        <v>1594.186972</v>
+        <v>1680.561113</v>
       </c>
       <c r="D56" t="n">
-        <v>1680.561113</v>
+        <v>1193.031047</v>
       </c>
       <c r="E56" t="n">
-        <v>1193.031047</v>
+        <v>1146.071359</v>
       </c>
       <c r="F56" t="n">
-        <v>1146.071359</v>
+        <v>1019.882468</v>
       </c>
       <c r="G56" t="n">
-        <v>1019.882468</v>
+        <v>2317.043931</v>
       </c>
       <c r="H56" t="n">
-        <v>2317.043931</v>
+        <v>921.913347</v>
       </c>
       <c r="I56" t="n">
-        <v>921.913347</v>
+        <v>825.16806675</v>
       </c>
       <c r="J56" t="n">
-        <v>825.16806675</v>
+        <v>1693.618555</v>
       </c>
     </row>
   </sheetData>
